--- a/data/processed/BR_processed_ind.xlsx
+++ b/data/processed/BR_processed_ind.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X67"/>
+  <dimension ref="A1:Y67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>dVdt_calc</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Xlag1_calc</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -615,20 +620,23 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>26.65402038712101</v>
+        <v>26.65401311124306</v>
       </c>
       <c r="U2" t="n">
-        <v>1.848680836312359</v>
+        <v>1.848679151181504</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2251989634134583</v>
+        <v>0.2252313546719042</v>
       </c>
       <c r="W2" t="n">
-        <v>5.969296685343798</v>
+        <v>5.970158382675687</v>
       </c>
       <c r="X2" t="n">
         <v>0.0023</v>
       </c>
+      <c r="Y2" t="n">
+        <v>23.31328380098466</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -695,20 +703,23 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>26.8145671512291</v>
+        <v>26.81456003824498</v>
       </c>
       <c r="U3" t="n">
-        <v>1.851714850230572</v>
+        <v>1.851713165069686</v>
       </c>
       <c r="V3" t="n">
-        <v>0.006094880997606118</v>
+        <v>0.006079853433416887</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1282670523799451</v>
+        <v>0.1278640288312575</v>
       </c>
       <c r="X3" t="n">
         <v>0.002428333333333334</v>
       </c>
+      <c r="Y3" t="n">
+        <v>26.65401311124306</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -775,20 +786,23 @@
         <v>0.1310102834270957</v>
       </c>
       <c r="T4" t="n">
-        <v>27.04657194999543</v>
+        <v>27.04656525594052</v>
       </c>
       <c r="U4" t="n">
-        <v>1.856117558563905</v>
+        <v>1.856115873403019</v>
       </c>
       <c r="V4" t="n">
-        <v>0.006462730079758033</v>
+        <v>0.006462808694442893</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1368600051072877</v>
+        <v>0.1368620630507388</v>
       </c>
       <c r="X4" t="n">
         <v>0.002603333333333333</v>
       </c>
+      <c r="Y4" t="n">
+        <v>26.81456003824498</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -855,20 +869,23 @@
         <v>0.3150449672599142</v>
       </c>
       <c r="T5" t="n">
-        <v>27.34710404954932</v>
+        <v>27.34710021604569</v>
       </c>
       <c r="U5" t="n">
-        <v>1.861851961341683</v>
+        <v>1.861850276180797</v>
       </c>
       <c r="V5" t="n">
-        <v>0.006890025903620562</v>
+        <v>0.006889873878741359</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1470751989734178</v>
+        <v>0.1470709834936617</v>
       </c>
       <c r="X5" t="n">
         <v>0.002815</v>
       </c>
+      <c r="Y5" t="n">
+        <v>27.04656525594052</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -935,20 +952,23 @@
         <v>0.462353720667521</v>
       </c>
       <c r="T6" t="n">
-        <v>27.65075512742524</v>
+        <v>27.65075345661634</v>
       </c>
       <c r="U6" t="n">
-        <v>1.867681961341683</v>
+        <v>1.867680276180797</v>
       </c>
       <c r="V6" t="n">
-        <v>0.007275897093367976</v>
+        <v>0.007276059687110452</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1565474199088301</v>
+        <v>0.1565518660143671</v>
       </c>
       <c r="X6" t="n">
         <v>0.003015</v>
       </c>
+      <c r="Y6" t="n">
+        <v>27.34710021604569</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1015,20 +1035,23 @@
         <v>0.6209461221159972</v>
       </c>
       <c r="T7" t="n">
-        <v>27.964866247524</v>
+        <v>27.96486690381572</v>
       </c>
       <c r="U7" t="n">
-        <v>1.873751336341683</v>
+        <v>1.873749651180797</v>
       </c>
       <c r="V7" t="n">
-        <v>0.007634538708099028</v>
+        <v>0.007634494500556047</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1655910984587926</v>
+        <v>0.1655898230009548</v>
       </c>
       <c r="X7" t="n">
         <v>0.003210000000000001</v>
       </c>
+      <c r="Y7" t="n">
+        <v>27.65075345661634</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,20 +1118,23 @@
         <v>0.9523209449429346</v>
       </c>
       <c r="T8" t="n">
-        <v>28.14125833024534</v>
+        <v>28.14125939280519</v>
       </c>
       <c r="U8" t="n">
-        <v>1.877176961341683</v>
+        <v>1.877175276180797</v>
       </c>
       <c r="V8" t="n">
-        <v>0.00782056716799282</v>
+        <v>0.007820573031697493</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1703845556327245</v>
+        <v>0.1703846824654642</v>
       </c>
       <c r="X8" t="n">
         <v>0.003315</v>
       </c>
+      <c r="Y8" t="n">
+        <v>27.96486690381572</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1175,20 +1201,23 @@
         <v>1.25504016023201</v>
       </c>
       <c r="T9" t="n">
-        <v>28.31681859237364</v>
+        <v>28.31682006754251</v>
       </c>
       <c r="U9" t="n">
-        <v>1.880598891897238</v>
+        <v>1.880597206736353</v>
       </c>
       <c r="V9" t="n">
-        <v>0.007995857028660904</v>
+        <v>0.007995870233119741</v>
       </c>
       <c r="W9" t="n">
-        <v>0.174971318264154</v>
+        <v>0.1749716551880656</v>
       </c>
       <c r="X9" t="n">
         <v>0.003416666666666667</v>
       </c>
+      <c r="Y9" t="n">
+        <v>28.14125939280519</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1255,20 +1284,23 @@
         <v>1.69587337268752</v>
       </c>
       <c r="T10" t="n">
-        <v>28.48804543680405</v>
+        <v>28.48804706694351</v>
       </c>
       <c r="U10" t="n">
-        <v>1.883948391897238</v>
+        <v>1.883946706736353</v>
       </c>
       <c r="V10" t="n">
-        <v>0.008158139631829394</v>
+        <v>0.008158145764426144</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1792827320209608</v>
+        <v>0.1792828694645364</v>
       </c>
       <c r="X10" t="n">
         <v>0.003513333333333334</v>
       </c>
+      <c r="Y10" t="n">
+        <v>28.31682006754251</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1335,20 +1367,23 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>27.23142901640801</v>
+        <v>27.23145296079409</v>
       </c>
       <c r="U11" t="n">
-        <v>1.908002341677709</v>
+        <v>1.90800233686873</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01870882700703183</v>
+        <v>0.01870831010401795</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3981447792948562</v>
+        <v>0.3981310530798082</v>
       </c>
       <c r="X11" t="n">
         <v>0.007799999999999998</v>
       </c>
+      <c r="Y11" t="n">
+        <v>26.32781437148795</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1415,20 +1450,23 @@
         <v>0.1961577414134905</v>
       </c>
       <c r="T12" t="n">
-        <v>27.96944792584428</v>
+        <v>27.96947227861317</v>
       </c>
       <c r="U12" t="n">
-        <v>1.922571091677708</v>
+        <v>1.92257108686873</v>
       </c>
       <c r="V12" t="n">
-        <v>0.02051080217046494</v>
+        <v>0.02051071490900611</v>
       </c>
       <c r="W12" t="n">
-        <v>0.4449265486506412</v>
+        <v>0.4449244950655394</v>
       </c>
       <c r="X12" t="n">
         <v>0.008849999999999998</v>
       </c>
+      <c r="Y12" t="n">
+        <v>27.23145296079409</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1495,20 +1533,23 @@
         <v>0.4648676866334254</v>
       </c>
       <c r="T13" t="n">
-        <v>28.96833593102093</v>
+        <v>28.96836793855088</v>
       </c>
       <c r="U13" t="n">
-        <v>1.942647675011042</v>
+        <v>1.942647670202063</v>
       </c>
       <c r="V13" t="n">
-        <v>0.02241098137984284</v>
+        <v>0.02241121869123013</v>
       </c>
       <c r="W13" t="n">
-        <v>0.49830161738856</v>
+        <v>0.498309042119181</v>
       </c>
       <c r="X13" t="n">
         <v>0.01012</v>
       </c>
+      <c r="Y13" t="n">
+        <v>27.96947227861317</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1575,20 +1616,23 @@
         <v>0.5273275582417261</v>
       </c>
       <c r="T14" t="n">
-        <v>30.01251949831358</v>
+        <v>30.012551032435</v>
       </c>
       <c r="U14" t="n">
-        <v>1.964087675011042</v>
+        <v>1.964087670202063</v>
       </c>
       <c r="V14" t="n">
-        <v>0.02393225965834785</v>
+        <v>0.02393237134192201</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5452905486507985</v>
+        <v>0.5452944730724245</v>
       </c>
       <c r="X14" t="n">
         <v>0.01132</v>
       </c>
+      <c r="Y14" t="n">
+        <v>28.96836793855088</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1655,20 +1699,23 @@
         <v>0.5669120469218694</v>
       </c>
       <c r="T15" t="n">
-        <v>31.10794101823598</v>
+        <v>31.10797224513737</v>
       </c>
       <c r="U15" t="n">
-        <v>1.987094341677708</v>
+        <v>1.98709433686873</v>
       </c>
       <c r="V15" t="n">
-        <v>0.02516136086860845</v>
+        <v>0.02516111466725047</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5873438611068159</v>
+        <v>0.5873367913989104</v>
       </c>
       <c r="X15" t="n">
         <v>0.01248</v>
       </c>
+      <c r="Y15" t="n">
+        <v>30.012551032435</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1735,20 +1782,23 @@
         <v>1.314363106233276</v>
       </c>
       <c r="T16" t="n">
-        <v>31.74610874627464</v>
+        <v>31.7461397651932</v>
       </c>
       <c r="U16" t="n">
-        <v>2.000747675011041</v>
+        <v>2.000747670202063</v>
       </c>
       <c r="V16" t="n">
-        <v>0.02574271870805249</v>
+        <v>0.02574269341415964</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6090544983942522</v>
+        <v>0.6090542900136535</v>
       </c>
       <c r="X16" t="n">
         <v>0.01312</v>
       </c>
+      <c r="Y16" t="n">
+        <v>31.10797224513737</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1815,20 +1865,23 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>19.99437755940318</v>
+        <v>19.99434722561607</v>
       </c>
       <c r="U17" t="n">
-        <v>1.878764940125168</v>
+        <v>1.878764027797204</v>
       </c>
       <c r="V17" t="n">
-        <v>0.006624104141946579</v>
+        <v>0.006624136125296541</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1111957162639446</v>
+        <v>0.1111961767348054</v>
       </c>
       <c r="X17" t="n">
         <v>0.001996666666666667</v>
       </c>
+      <c r="Y17" t="n">
+        <v>16.88071097278224</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1895,20 +1948,23 @@
         <v>0.09290978010103844</v>
       </c>
       <c r="T18" t="n">
-        <v>20.118231009696</v>
+        <v>20.11820097131467</v>
       </c>
       <c r="U18" t="n">
-        <v>1.880991523458501</v>
+        <v>1.880990611130537</v>
       </c>
       <c r="V18" t="n">
-        <v>0.006756697091481876</v>
+        <v>0.006756799854998181</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1139890981262553</v>
+        <v>0.1139909847038225</v>
       </c>
       <c r="X18" t="n">
         <v>0.002051666666666667</v>
       </c>
+      <c r="Y18" t="n">
+        <v>19.99434722561607</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1975,20 +2031,23 @@
         <v>0.1714635834683609</v>
       </c>
       <c r="T19" t="n">
-        <v>20.22571977901286</v>
+        <v>20.22568990616278</v>
       </c>
       <c r="U19" t="n">
-        <v>1.882928190125168</v>
+        <v>1.882927277797204</v>
       </c>
       <c r="V19" t="n">
-        <v>0.006866574313274501</v>
+        <v>0.006866587876487551</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1163418855636403</v>
+        <v>0.1163419771341342</v>
       </c>
       <c r="X19" t="n">
         <v>0.002098333333333333</v>
       </c>
+      <c r="Y19" t="n">
+        <v>20.11820097131467</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2055,20 +2114,23 @@
         <v>0.1940649581558863</v>
       </c>
       <c r="T20" t="n">
-        <v>20.34331500131972</v>
+        <v>20.34328539823888</v>
       </c>
       <c r="U20" t="n">
-        <v>1.885051523458501</v>
+        <v>1.885050611130537</v>
       </c>
       <c r="V20" t="n">
-        <v>0.006981696184601927</v>
+        <v>0.006981703852210943</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1188462149255302</v>
+        <v>0.1188461867469677</v>
       </c>
       <c r="X20" t="n">
         <v>0.002148333333333333</v>
       </c>
+      <c r="Y20" t="n">
+        <v>20.22568990616278</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2135,20 +2197,23 @@
         <v>0.2229784488956445</v>
       </c>
       <c r="T21" t="n">
-        <v>20.47352500365051</v>
+        <v>20.4734955867161</v>
       </c>
       <c r="U21" t="n">
-        <v>1.88740822484739</v>
+        <v>1.887407312519426</v>
       </c>
       <c r="V21" t="n">
-        <v>0.007103313807944911</v>
+        <v>0.007103353408241623</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1215384124780076</v>
+        <v>0.1215390370561618</v>
       </c>
       <c r="X21" t="n">
         <v>0.0022025</v>
       </c>
+      <c r="Y21" t="n">
+        <v>20.34328539823888</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2215,20 +2280,23 @@
         <v>0.2989185664601128</v>
       </c>
       <c r="T22" t="n">
-        <v>20.58184747469485</v>
+        <v>20.58181820907232</v>
       </c>
       <c r="U22" t="n">
-        <v>1.889373273458501</v>
+        <v>1.889372361130537</v>
       </c>
       <c r="V22" t="n">
-        <v>0.007200123015874504</v>
+        <v>0.007200136730610088</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1237178182753322</v>
+        <v>0.1237179128155578</v>
       </c>
       <c r="X22" t="n">
         <v>0.002246666666666667</v>
       </c>
+      <c r="Y22" t="n">
+        <v>20.4734955867161</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2295,20 +2363,23 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>15.01969587212995</v>
+        <v>15.01969250760888</v>
       </c>
       <c r="U23" t="n">
-        <v>1.792146596631902</v>
+        <v>1.792146527764305</v>
       </c>
       <c r="V23" t="n">
-        <v>0.009244307906717498</v>
+        <v>0.009244326228632355</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1221129472243336</v>
+        <v>0.1221131944166381</v>
       </c>
       <c r="X23" t="n">
         <v>0.001996666666666667</v>
       </c>
+      <c r="Y23" t="n">
+        <v>14.80438644777559</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2375,20 +2446,23 @@
         <v>0.05810793948216079</v>
       </c>
       <c r="T24" t="n">
-        <v>15.15570103214544</v>
+        <v>15.15569778641188</v>
       </c>
       <c r="U24" t="n">
-        <v>1.794373179965235</v>
+        <v>1.794373111097638</v>
       </c>
       <c r="V24" t="n">
-        <v>0.009401957732386484</v>
+        <v>0.009401995746227973</v>
       </c>
       <c r="W24" t="n">
-        <v>0.125164397725636</v>
+        <v>0.1251649463817385</v>
       </c>
       <c r="X24" t="n">
         <v>0.002051666666666667</v>
       </c>
+      <c r="Y24" t="n">
+        <v>15.01969250760888</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2455,20 +2529,23 @@
         <v>0.1219400842896329</v>
       </c>
       <c r="T25" t="n">
-        <v>15.27798261225939</v>
+        <v>15.27797946826978</v>
       </c>
       <c r="U25" t="n">
-        <v>1.796379818854124</v>
+        <v>1.796379749986527</v>
       </c>
       <c r="V25" t="n">
-        <v>0.00953582654555562</v>
+        <v>0.009535924639375432</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1278279583969302</v>
+        <v>0.12782943008243</v>
       </c>
       <c r="X25" t="n">
         <v>0.0021</v>
       </c>
+      <c r="Y25" t="n">
+        <v>15.15569778641188</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2535,20 +2612,23 @@
         <v>0.1703755277559266</v>
       </c>
       <c r="T26" t="n">
-        <v>15.40717948332247</v>
+        <v>15.40717642178005</v>
       </c>
       <c r="U26" t="n">
-        <v>1.798504818854124</v>
+        <v>1.798504749986527</v>
       </c>
       <c r="V26" t="n">
-        <v>0.009669652955602136</v>
+        <v>0.009669490718981348</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1305637593990719</v>
+        <v>0.1305612331413965</v>
       </c>
       <c r="X26" t="n">
         <v>0.00215</v>
       </c>
+      <c r="Y26" t="n">
+        <v>15.27797946826978</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2615,20 +2695,23 @@
         <v>0.2036432131066642</v>
       </c>
       <c r="T27" t="n">
-        <v>15.54576751668215</v>
+        <v>15.54576471769251</v>
       </c>
       <c r="U27" t="n">
-        <v>1.800789881354124</v>
+        <v>1.800789812486527</v>
       </c>
       <c r="V27" t="n">
-        <v>0.009804920718641658</v>
+        <v>0.009804969956134207</v>
       </c>
       <c r="W27" t="n">
-        <v>0.1334113877651218</v>
+        <v>0.1334121284519593</v>
       </c>
       <c r="X27" t="n">
         <v>0.0022025</v>
       </c>
+      <c r="Y27" t="n">
+        <v>15.40717642178005</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2695,20 +2778,23 @@
         <v>0.2220723133576301</v>
       </c>
       <c r="T28" t="n">
-        <v>15.66240312562252</v>
+        <v>15.66240050531441</v>
       </c>
       <c r="U28" t="n">
-        <v>1.802717492465235</v>
+        <v>1.802717423597638</v>
       </c>
       <c r="V28" t="n">
-        <v>0.009912773572118169</v>
+        <v>0.009912768036938789</v>
       </c>
       <c r="W28" t="n">
-        <v>0.1357455654918702</v>
+        <v>0.1357454553421338</v>
       </c>
       <c r="X28" t="n">
         <v>0.002245833333333333</v>
       </c>
+      <c r="Y28" t="n">
+        <v>15.54576471769251</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2775,20 +2861,23 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>23.93978428221004</v>
+        <v>23.93967898585161</v>
       </c>
       <c r="U29" t="n">
-        <v>2.09849416393484</v>
+        <v>2.098491694450313</v>
       </c>
       <c r="V29" t="n">
-        <v>0.01007979675570692</v>
+        <v>0.01007971427442612</v>
       </c>
       <c r="W29" t="n">
-        <v>0.1949533379260983</v>
+        <v>0.1949504513214563</v>
       </c>
       <c r="X29" t="n">
         <v>0.004063333333333333</v>
       </c>
+      <c r="Y29" t="n">
+        <v>23.76781114604884</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2855,20 +2944,23 @@
         <v>0.06375494686076261</v>
       </c>
       <c r="T30" t="n">
-        <v>24.22825041445948</v>
+        <v>24.22814583641843</v>
       </c>
       <c r="U30" t="n">
-        <v>2.104523719490396</v>
+        <v>2.104521250005869</v>
       </c>
       <c r="V30" t="n">
-        <v>0.01063206856027901</v>
+        <v>0.01063211796426457</v>
       </c>
       <c r="W30" t="n">
-        <v>0.2075172075993081</v>
+        <v>0.2075174500820442</v>
       </c>
       <c r="X30" t="n">
         <v>0.00435</v>
       </c>
+      <c r="Y30" t="n">
+        <v>23.93967898585161</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2935,20 +3027,23 @@
         <v>0.1716212668026328</v>
       </c>
       <c r="T31" t="n">
-        <v>24.54922625090641</v>
+        <v>24.54912557034737</v>
       </c>
       <c r="U31" t="n">
-        <v>2.111273719490396</v>
+        <v>2.111271250005868</v>
       </c>
       <c r="V31" t="n">
-        <v>0.01118066179690937</v>
+        <v>0.01118089966425217</v>
       </c>
       <c r="W31" t="n">
-        <v>0.2204078597538168</v>
+        <v>0.22041273201674</v>
       </c>
       <c r="X31" t="n">
         <v>0.00465</v>
       </c>
+      <c r="Y31" t="n">
+        <v>24.22814583641843</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3015,20 +3110,23 @@
         <v>0.2547670720457892</v>
       </c>
       <c r="T32" t="n">
-        <v>25.0069068659276</v>
+        <v>25.00680786787553</v>
       </c>
       <c r="U32" t="n">
-        <v>2.120973719490396</v>
+        <v>2.120971250005868</v>
       </c>
       <c r="V32" t="n">
-        <v>0.01186491756366023</v>
+        <v>0.0118658838353382</v>
       </c>
       <c r="W32" t="n">
-        <v>0.2371638962937377</v>
+        <v>0.2371870514484175</v>
       </c>
       <c r="X32" t="n">
         <v>0.005050000000000001</v>
       </c>
+      <c r="Y32" t="n">
+        <v>24.54912557034737</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3095,20 +3193,23 @@
         <v>0.3345630000595383</v>
       </c>
       <c r="T33" t="n">
-        <v>26.11055105190514</v>
+        <v>26.11045456428113</v>
       </c>
       <c r="U33" t="n">
-        <v>2.144734830601506</v>
+        <v>2.14473236111698</v>
       </c>
       <c r="V33" t="n">
-        <v>0.01316719187898204</v>
+        <v>0.01316721393135566</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2717716206251032</v>
+        <v>0.2717711091938156</v>
       </c>
       <c r="X33" t="n">
         <v>0.005916666666666667</v>
       </c>
+      <c r="Y33" t="n">
+        <v>25.00680786787553</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3175,20 +3276,23 @@
         <v>0.4114676331552647</v>
       </c>
       <c r="T34" t="n">
-        <v>26.57406864027899</v>
+        <v>26.57397314631664</v>
       </c>
       <c r="U34" t="n">
-        <v>2.154873719490395</v>
+        <v>2.154871250005869</v>
       </c>
       <c r="V34" t="n">
-        <v>0.01360386665824679</v>
+        <v>0.01360205894586814</v>
       </c>
       <c r="W34" t="n">
-        <v>0.2844346050813339</v>
+        <v>0.2843854565366162</v>
       </c>
       <c r="X34" t="n">
         <v>0.00625</v>
       </c>
+      <c r="Y34" t="n">
+        <v>26.11045456428113</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3255,20 +3359,23 @@
         <v>0.4067877264015557</v>
       </c>
       <c r="T35" t="n">
-        <v>27.30793717444327</v>
+        <v>27.30784322886136</v>
       </c>
       <c r="U35" t="n">
-        <v>2.171123719490395</v>
+        <v>2.171121250005869</v>
       </c>
       <c r="V35" t="n">
-        <v>0.0141875669288309</v>
+        <v>0.01418844280408847</v>
       </c>
       <c r="W35" t="n">
-        <v>0.302533107063322</v>
+        <v>0.302555887977083</v>
       </c>
       <c r="X35" t="n">
         <v>0.006750000000000001</v>
       </c>
+      <c r="Y35" t="n">
+        <v>26.57397314631664</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3335,20 +3442,23 @@
         <v>0.4021708299263646</v>
       </c>
       <c r="T36" t="n">
-        <v>27.82191919539128</v>
+        <v>27.82182632953165</v>
       </c>
       <c r="U36" t="n">
-        <v>2.182651497268173</v>
+        <v>2.182649027783647</v>
       </c>
       <c r="V36" t="n">
-        <v>0.01453694131186329</v>
+        <v>0.01453702929851717</v>
       </c>
       <c r="W36" t="n">
-        <v>0.3141554581083897</v>
+        <v>0.31415675529333</v>
       </c>
       <c r="X36" t="n">
         <v>0.007083333333333334</v>
       </c>
+      <c r="Y36" t="n">
+        <v>27.30784322886136</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3415,20 +3525,23 @@
         <v>0.3873938421634567</v>
       </c>
       <c r="T37" t="n">
-        <v>28.72218235691336</v>
+        <v>28.72212538886001</v>
       </c>
       <c r="U37" t="n">
-        <v>2.203141469490395</v>
+        <v>2.203139000005869</v>
       </c>
       <c r="V37" t="n">
-        <v>0.01504654261806108</v>
+        <v>0.01504659646470858</v>
       </c>
       <c r="W37" t="n">
-        <v>0.3325674607757125</v>
+        <v>0.3325682361029325</v>
       </c>
       <c r="X37" t="n">
         <v>0.007640000000000001</v>
       </c>
+      <c r="Y37" t="n">
+        <v>27.82182632953165</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3495,20 +3608,23 @@
         <v>0.3689307159607038</v>
       </c>
       <c r="T38" t="n">
-        <v>29.76550377987243</v>
+        <v>29.76547646662382</v>
       </c>
       <c r="U38" t="n">
-        <v>2.227373719490394</v>
+        <v>2.227371250005869</v>
       </c>
       <c r="V38" t="n">
-        <v>0.0155073882925051</v>
+        <v>0.01550780134710743</v>
       </c>
       <c r="W38" t="n">
-        <v>0.3513363680617561</v>
+        <v>0.3513482182048674</v>
       </c>
       <c r="X38" t="n">
         <v>0.00825</v>
       </c>
+      <c r="Y38" t="n">
+        <v>28.72212538886001</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3575,20 +3691,23 @@
         <v>0.3542503465167628</v>
       </c>
       <c r="T39" t="n">
-        <v>30.84543175400328</v>
+        <v>30.84541916586719</v>
       </c>
       <c r="U39" t="n">
-        <v>2.253023719490394</v>
+        <v>2.253021250005869</v>
       </c>
       <c r="V39" t="n">
-        <v>0.0158706878671298</v>
+        <v>0.01587052728317392</v>
       </c>
       <c r="W39" t="n">
-        <v>0.3683756819405863</v>
+        <v>0.3683704455222586</v>
       </c>
       <c r="X39" t="n">
         <v>0.00885</v>
       </c>
+      <c r="Y39" t="n">
+        <v>29.76547646662382</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3655,20 +3774,23 @@
         <v>0.363160750555521</v>
       </c>
       <c r="T40" t="n">
-        <v>31.81469629436059</v>
+        <v>31.81469618095175</v>
       </c>
       <c r="U40" t="n">
-        <v>2.276553580601505</v>
+        <v>2.27655111111698</v>
       </c>
       <c r="V40" t="n">
-        <v>0.01611699920377449</v>
+        <v>0.01611696629351479</v>
       </c>
       <c r="W40" t="n">
-        <v>0.3818588441723268</v>
+        <v>0.3818576537892139</v>
       </c>
       <c r="X40" t="n">
         <v>0.009366666666666667</v>
       </c>
+      <c r="Y40" t="n">
+        <v>30.84541916586719</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3735,20 +3857,23 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>28.24181435886335</v>
+        <v>28.24180486772746</v>
       </c>
       <c r="U41" t="n">
-        <v>2.19806993429644</v>
+        <v>2.198068889706438</v>
       </c>
       <c r="V41" t="n">
-        <v>0.00707998064950816</v>
+        <v>0.007062670572029382</v>
       </c>
       <c r="W41" t="n">
-        <v>0.109327025622538</v>
+        <v>0.1088380779834294</v>
       </c>
       <c r="X41" t="n">
         <v>0.007053333333333333</v>
       </c>
+      <c r="Y41" t="n">
+        <v>24.01327158029936</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3815,20 +3940,23 @@
         <v>0.05060060245371522</v>
       </c>
       <c r="T42" t="n">
-        <v>28.47192299696311</v>
+        <v>28.47191369338541</v>
       </c>
       <c r="U42" t="n">
-        <v>2.203330272890108</v>
+        <v>2.203329228300105</v>
       </c>
       <c r="V42" t="n">
-        <v>0.007575502399231828</v>
+        <v>0.007575500360812597</v>
       </c>
       <c r="W42" t="n">
-        <v>0.1171356409405757</v>
+        <v>0.1171354979034436</v>
       </c>
       <c r="X42" t="n">
         <v>0.007626666666666667</v>
       </c>
+      <c r="Y42" t="n">
+        <v>28.24180486772746</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3895,20 +4023,23 @@
         <v>0.1044036282464569</v>
       </c>
       <c r="T43" t="n">
-        <v>28.65988886456502</v>
+        <v>28.65987999470776</v>
       </c>
       <c r="U43" t="n">
-        <v>2.207645943872441</v>
+        <v>2.207644899282438</v>
       </c>
       <c r="V43" t="n">
-        <v>0.00794433763067366</v>
+        <v>0.007944459054254931</v>
       </c>
       <c r="W43" t="n">
-        <v>0.1229615293641455</v>
+        <v>0.1229649217430691</v>
       </c>
       <c r="X43" t="n">
         <v>0.008066666666666666</v>
       </c>
+      <c r="Y43" t="n">
+        <v>28.47191369338541</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3975,20 +4106,23 @@
         <v>0.1491197853115378</v>
       </c>
       <c r="T44" t="n">
-        <v>28.92564612515287</v>
+        <v>28.9256375489027</v>
       </c>
       <c r="U44" t="n">
-        <v>2.213776616669774</v>
+        <v>2.213775572079771</v>
       </c>
       <c r="V44" t="n">
-        <v>0.008420548538211437</v>
+        <v>0.008420554940521486</v>
       </c>
       <c r="W44" t="n">
-        <v>0.130503630636788</v>
+        <v>0.1305037237830004</v>
       </c>
       <c r="X44" t="n">
         <v>0.008653333333333332</v>
       </c>
+      <c r="Y44" t="n">
+        <v>28.65987999470776</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4055,20 +4189,23 @@
         <v>0.1918414613393818</v>
       </c>
       <c r="T45" t="n">
-        <v>29.46263383132069</v>
+        <v>29.46262799265684</v>
       </c>
       <c r="U45" t="n">
-        <v>2.226268768050802</v>
+        <v>2.226267723460799</v>
       </c>
       <c r="V45" t="n">
-        <v>0.009253023448474186</v>
+        <v>0.009253028607806763</v>
       </c>
       <c r="W45" t="n">
-        <v>0.1437184375107467</v>
+        <v>0.14371850055597</v>
       </c>
       <c r="X45" t="n">
         <v>0.009740000000000002</v>
       </c>
+      <c r="Y45" t="n">
+        <v>28.9256375489027</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4135,20 +4272,23 @@
         <v>0.2448076315621145</v>
       </c>
       <c r="T46" t="n">
-        <v>30.73245885393927</v>
+        <v>30.73245487163991</v>
       </c>
       <c r="U46" t="n">
-        <v>2.256377548159552</v>
+        <v>2.256376503569549</v>
       </c>
       <c r="V46" t="n">
-        <v>0.01074726375017955</v>
+        <v>0.01074722319542253</v>
       </c>
       <c r="W46" t="n">
-        <v>0.1673914784433465</v>
+        <v>0.1673901349917643</v>
       </c>
       <c r="X46" t="n">
         <v>0.01196</v>
       </c>
+      <c r="Y46" t="n">
+        <v>29.46262799265684</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4215,20 +4355,23 @@
         <v>0.2862295508009267</v>
       </c>
       <c r="T47" t="n">
-        <v>31.15248473083177</v>
+        <v>31.15248097080469</v>
       </c>
       <c r="U47" t="n">
-        <v>2.266516808298802</v>
+        <v>2.266515763708799</v>
       </c>
       <c r="V47" t="n">
-        <v>0.01113628526675103</v>
+        <v>0.01113714943474031</v>
       </c>
       <c r="W47" t="n">
-        <v>0.173465448776766</v>
+        <v>0.1734922688738111</v>
       </c>
       <c r="X47" t="n">
         <v>0.01262</v>
       </c>
+      <c r="Y47" t="n">
+        <v>30.73245487163991</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4295,20 +4438,23 @@
         <v>0.2889524121591054</v>
       </c>
       <c r="T48" t="n">
-        <v>31.55040316532968</v>
+        <v>31.55039960390232</v>
       </c>
       <c r="U48" t="n">
-        <v>2.276206817988802</v>
+        <v>2.276205773398799</v>
       </c>
       <c r="V48" t="n">
-        <v>0.0114707959356816</v>
+        <v>0.01147081403029764</v>
       </c>
       <c r="W48" t="n">
-        <v>0.1786663945102576</v>
+        <v>0.1786668611418356</v>
       </c>
       <c r="X48" t="n">
         <v>0.01322</v>
       </c>
+      <c r="Y48" t="n">
+        <v>31.15248097080469</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4375,20 +4521,23 @@
         <v>0.2916972101212668</v>
       </c>
       <c r="T49" t="n">
-        <v>31.95385657262386</v>
+        <v>31.95385449152545</v>
       </c>
       <c r="U49" t="n">
-        <v>2.286116605676357</v>
+        <v>2.286115561086354</v>
       </c>
       <c r="V49" t="n">
-        <v>0.01177718512329405</v>
+        <v>0.0117772325789504</v>
       </c>
       <c r="W49" t="n">
-        <v>0.1833458439376281</v>
+        <v>0.1833472602095393</v>
       </c>
       <c r="X49" t="n">
         <v>0.01380666666666667</v>
       </c>
+      <c r="Y49" t="n">
+        <v>31.55039960390232</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4455,20 +4604,23 @@
         <v>0.2947411967231239</v>
       </c>
       <c r="T50" t="n">
-        <v>32.83159112562513</v>
+        <v>32.83159453267135</v>
       </c>
       <c r="U50" t="n">
-        <v>2.307976849758802</v>
+        <v>2.307975805168799</v>
       </c>
       <c r="V50" t="n">
-        <v>0.01235138793668174</v>
+        <v>0.01235144894981185</v>
       </c>
       <c r="W50" t="n">
-        <v>0.1918521808461034</v>
+        <v>0.1918541072094664</v>
       </c>
       <c r="X50" t="n">
         <v>0.01502</v>
       </c>
+      <c r="Y50" t="n">
+        <v>31.95385449152545</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4535,20 +4687,23 @@
         <v>0.3061500936386944</v>
       </c>
       <c r="T51" t="n">
-        <v>33.75407862959444</v>
+        <v>33.75408934841732</v>
       </c>
       <c r="U51" t="n">
-        <v>2.331406873188802</v>
+        <v>2.331405828598798</v>
       </c>
       <c r="V51" t="n">
-        <v>0.01284377298643088</v>
+        <v>0.01284354032424172</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1986967725594131</v>
+        <v>0.1986888771392174</v>
       </c>
       <c r="X51" t="n">
         <v>0.01622</v>
       </c>
+      <c r="Y51" t="n">
+        <v>32.83159453267135</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4615,20 +4770,23 @@
         <v>0.3308651428571041</v>
       </c>
       <c r="T52" t="n">
-        <v>34.61645413183646</v>
+        <v>34.61647934287152</v>
       </c>
       <c r="U52" t="n">
-        <v>2.353744673304358</v>
+        <v>2.353743628714354</v>
       </c>
       <c r="V52" t="n">
-        <v>0.01322031698823076</v>
+        <v>0.01322023279290888</v>
       </c>
       <c r="W52" t="n">
-        <v>0.2034059950960809</v>
+        <v>0.2034031158610907</v>
       </c>
       <c r="X52" t="n">
         <v>0.01728666666666667</v>
       </c>
+      <c r="Y52" t="n">
+        <v>33.75408934841732</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4695,20 +4853,23 @@
         <v>0.3724108962071924</v>
       </c>
       <c r="T53" t="n">
-        <v>35.5274297311113</v>
+        <v>35.52745852248923</v>
       </c>
       <c r="U53" t="n">
-        <v>2.377810697370358</v>
+        <v>2.377809652780353</v>
       </c>
       <c r="V53" t="n">
-        <v>0.0135475534141766</v>
+        <v>0.01354761888355979</v>
       </c>
       <c r="W53" t="n">
-        <v>0.2068890589508223</v>
+        <v>0.2068914320190024</v>
       </c>
       <c r="X53" t="n">
         <v>0.01836666666666667</v>
       </c>
+      <c r="Y53" t="n">
+        <v>34.61647934287152</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4775,20 +4936,23 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>28.31816759563745</v>
+        <v>28.31815807173002</v>
       </c>
       <c r="U54" t="n">
-        <v>2.196893200352741</v>
+        <v>2.196892806246272</v>
       </c>
       <c r="V54" t="n">
-        <v>0.007044681899702128</v>
+        <v>0.0104122458017144</v>
       </c>
       <c r="W54" t="n">
-        <v>0.1088321301297718</v>
+        <v>0.2041952841576134</v>
       </c>
       <c r="X54" t="n">
         <v>0.007033333333333333</v>
       </c>
+      <c r="Y54" t="n">
+        <v>25.42114773996207</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4855,20 +5019,23 @@
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>28.49545451865742</v>
+        <v>28.49544506706755</v>
       </c>
       <c r="U55" t="n">
-        <v>2.20094484329327</v>
+        <v>2.2009444491868</v>
       </c>
       <c r="V55" t="n">
-        <v>0.007431766613129663</v>
+        <v>0.01098361402771199</v>
       </c>
       <c r="W55" t="n">
-        <v>0.1149286137067363</v>
+        <v>0.2161400311342437</v>
       </c>
       <c r="X55" t="n">
         <v>0.007480000000000001</v>
       </c>
+      <c r="Y55" t="n">
+        <v>28.31815807173002</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4935,20 +5102,23 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>28.74378505976747</v>
+        <v>28.74377626810038</v>
       </c>
       <c r="U56" t="n">
-        <v>2.206645293438159</v>
+        <v>2.206644899331689</v>
       </c>
       <c r="V56" t="n">
-        <v>0.00792480721407878</v>
+        <v>0.01171779493992934</v>
       </c>
       <c r="W56" t="n">
-        <v>0.1227124694134184</v>
+        <v>0.231737203693045</v>
       </c>
       <c r="X56" t="n">
         <v>0.008066666666666666</v>
       </c>
+      <c r="Y56" t="n">
+        <v>28.49544506706755</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5015,20 +5185,23 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>28.95677638719329</v>
+        <v>28.95676810524078</v>
       </c>
       <c r="U57" t="n">
-        <v>2.21155810390652</v>
+        <v>2.211557709800049</v>
       </c>
       <c r="V57" t="n">
-        <v>0.008309672514647912</v>
+        <v>0.01228114874974565</v>
       </c>
       <c r="W57" t="n">
-        <v>0.1288038414897075</v>
+        <v>0.2438049010993913</v>
       </c>
       <c r="X57" t="n">
         <v>0.008539999999999999</v>
       </c>
+      <c r="Y57" t="n">
+        <v>28.74377626810038</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5095,20 +5268,23 @@
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>29.23617425627321</v>
+        <v>29.23616617039069</v>
       </c>
       <c r="U58" t="n">
-        <v>2.218035888162076</v>
+        <v>2.218035494055605</v>
       </c>
       <c r="V58" t="n">
-        <v>0.008769849406943338</v>
+        <v>0.01296732616405267</v>
       </c>
       <c r="W58" t="n">
-        <v>0.136097251362464</v>
+        <v>0.2588153203139437</v>
       </c>
       <c r="X58" t="n">
         <v>0.009126666666666668</v>
       </c>
+      <c r="Y58" t="n">
+        <v>28.95676810524078</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5175,20 +5351,23 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>29.78688895628814</v>
+        <v>29.78688303409221</v>
       </c>
       <c r="U59" t="n">
-        <v>2.230915901042076</v>
+        <v>2.230915506935605</v>
       </c>
       <c r="V59" t="n">
-        <v>0.009558175360894783</v>
+        <v>0.01413302613406024</v>
       </c>
       <c r="W59" t="n">
-        <v>0.1486082928760876</v>
+        <v>0.2848787841656656</v>
       </c>
       <c r="X59" t="n">
         <v>0.01019333333333333</v>
       </c>
+      <c r="Y59" t="n">
+        <v>29.23616617039069</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5255,20 +5434,23 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>31.11036957820114</v>
+        <v>31.11037299829884</v>
       </c>
       <c r="U60" t="n">
-        <v>2.262489682615826</v>
+        <v>2.262489288509355</v>
       </c>
       <c r="V60" t="n">
-        <v>0.01100115506888931</v>
+        <v>0.01625169104512008</v>
       </c>
       <c r="W60" t="n">
-        <v>0.1713770914337036</v>
+        <v>0.3347232131708391</v>
       </c>
       <c r="X60" t="n">
         <v>0.01242666666666667</v>
       </c>
+      <c r="Y60" t="n">
+        <v>29.78688303409221</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5335,20 +5517,23 @@
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>31.52104214064321</v>
+        <v>31.52104556401108</v>
       </c>
       <c r="U61" t="n">
-        <v>2.272469359262159</v>
+        <v>2.272468965155688</v>
       </c>
       <c r="V61" t="n">
-        <v>0.01135506083682212</v>
+        <v>0.01678984232084768</v>
       </c>
       <c r="W61" t="n">
-        <v>0.1768627492080715</v>
+        <v>0.3481727318040841</v>
       </c>
       <c r="X61" t="n">
         <v>0.01305333333333333</v>
       </c>
+      <c r="Y61" t="n">
+        <v>31.11037299829884</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5415,20 +5600,23 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>31.94342679182958</v>
+        <v>31.94343200681957</v>
       </c>
       <c r="U62" t="n">
-        <v>2.282825952952076</v>
+        <v>2.282825558845605</v>
       </c>
       <c r="V62" t="n">
-        <v>0.01168416897368024</v>
+        <v>0.01726821272876278</v>
       </c>
       <c r="W62" t="n">
-        <v>0.1819023818855478</v>
+        <v>0.3602759005648064</v>
       </c>
       <c r="X62" t="n">
         <v>0.01367333333333333</v>
       </c>
+      <c r="Y62" t="n">
+        <v>31.52104556401108</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5495,20 +5683,23 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>32.3573948508518</v>
+        <v>32.35740187371602</v>
       </c>
       <c r="U63" t="n">
-        <v>2.293068185416521</v>
+        <v>2.293067791310049</v>
       </c>
       <c r="V63" t="n">
-        <v>0.01197580154919097</v>
+        <v>0.01769926545816089</v>
       </c>
       <c r="W63" t="n">
-        <v>0.1862834410193705</v>
+        <v>0.371479868678853</v>
       </c>
       <c r="X63" t="n">
         <v>0.01426</v>
       </c>
+      <c r="Y63" t="n">
+        <v>31.94343200681957</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5575,20 +5766,23 @@
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>33.25582517483905</v>
+        <v>33.2558324964522</v>
       </c>
       <c r="U64" t="n">
-        <v>2.315615985742077</v>
+        <v>2.315615591635606</v>
       </c>
       <c r="V64" t="n">
-        <v>0.01252037905729662</v>
+        <v>0.01851302896468444</v>
       </c>
       <c r="W64" t="n">
-        <v>0.1941545507687161</v>
+        <v>0.3934451172228779</v>
       </c>
       <c r="X64" t="n">
         <v>0.01547333333333333</v>
       </c>
+      <c r="Y64" t="n">
+        <v>32.35740187371602</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5655,20 +5849,23 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>34.1973460288418</v>
+        <v>34.19735342975477</v>
       </c>
       <c r="U65" t="n">
-        <v>2.339726009852077</v>
+        <v>2.339725615745605</v>
       </c>
       <c r="V65" t="n">
-        <v>0.01298466017321329</v>
+        <v>0.01919067788683726</v>
       </c>
       <c r="W65" t="n">
-        <v>0.2003441136011347</v>
+        <v>0.412573497054656</v>
       </c>
       <c r="X65" t="n">
         <v>0.01667333333333334</v>
       </c>
+      <c r="Y65" t="n">
+        <v>33.2558324964522</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5735,20 +5932,23 @@
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>34.69218483480882</v>
+        <v>34.69219227762835</v>
       </c>
       <c r="U66" t="n">
-        <v>2.352599994948271</v>
+        <v>2.3525996008418</v>
       </c>
       <c r="V66" t="n">
-        <v>0.01319326233753482</v>
+        <v>0.01948925539598507</v>
       </c>
       <c r="W66" t="n">
-        <v>0.2028867412425771</v>
+        <v>0.4213085438452883</v>
       </c>
       <c r="X66" t="n">
         <v>0.01728</v>
       </c>
+      <c r="Y66" t="n">
+        <v>34.19735342975477</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5815,19 +6015,22 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>35.04182832112816</v>
+        <v>35.0418357938299</v>
       </c>
       <c r="U67" t="n">
-        <v>2.361782254130521</v>
+        <v>2.36178186002405</v>
       </c>
       <c r="V67" t="n">
-        <v>0.01332665791637905</v>
+        <v>0.01970497486348605</v>
       </c>
       <c r="W67" t="n">
-        <v>0.2043750715436786</v>
+        <v>0.4278830064061876</v>
       </c>
       <c r="X67" t="n">
         <v>0.0177</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>34.69219227762835</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/BR_processed_ind.xlsx
+++ b/data/processed/BR_processed_ind.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y67"/>
+  <dimension ref="A1:AA67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,40 +516,50 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>qP_sqrt</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>rP_sqrt</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Xlag1</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Plag1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>X_calc</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>V_calc</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mu_calc</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dXdt_calc</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dVdt_calc</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Xlag1_calc</t>
         </is>
@@ -614,28 +624,34 @@
         <v>0.03252295278732637</v>
       </c>
       <c r="R2" t="n">
+        <v>0.03754548692326653</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1803412121156071</v>
+      </c>
+      <c r="T2" t="n">
         <v>19.55000000000009</v>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>26.65401311124306</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.848679151181504</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2252313546719042</v>
+        <v>26.65401336848298</v>
       </c>
       <c r="W2" t="n">
-        <v>5.970158382675687</v>
+        <v>1.848679229473595</v>
       </c>
       <c r="X2" t="n">
+        <v>0.2252279510788963</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>5.970067722284991</v>
+      </c>
+      <c r="Z2" t="n">
         <v>0.0023</v>
       </c>
-      <c r="Y2" t="n">
-        <v>23.31328380098466</v>
+      <c r="AA2" t="n">
+        <v>23.31328394075086</v>
       </c>
     </row>
     <row r="3">
@@ -697,28 +713,34 @@
         <v>0.1065167260919373</v>
       </c>
       <c r="R3" t="n">
+        <v>0.06664459174752829</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.3263690029582119</v>
+      </c>
+      <c r="T3" t="n">
         <v>23.07142857142841</v>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>26.81456003824498</v>
-      </c>
       <c r="U3" t="n">
-        <v>1.851713165069686</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.006079853433416887</v>
+        <v>26.81456869324099</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1278640288312575</v>
+        <v>1.851713413179842</v>
       </c>
       <c r="X3" t="n">
+        <v>0.006093564436306846</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.1282317294427486</v>
+      </c>
+      <c r="Z3" t="n">
         <v>0.002428333333333334</v>
       </c>
-      <c r="Y3" t="n">
-        <v>26.65401311124306</v>
+      <c r="AA3" t="n">
+        <v>26.65401336848298</v>
       </c>
     </row>
     <row r="4">
@@ -780,28 +802,34 @@
         <v>0.08474551698518029</v>
       </c>
       <c r="R4" t="n">
+        <v>0.0585577437900562</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.2911108328200452</v>
+      </c>
+      <c r="T4" t="n">
         <v>23.9821428571428</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.1310102834270957</v>
       </c>
-      <c r="T4" t="n">
-        <v>27.04656525594052</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.856115873403019</v>
-      </c>
       <c r="V4" t="n">
-        <v>0.006462808694442893</v>
+        <v>27.04657382863489</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1368620630507388</v>
+        <v>1.856116121454714</v>
       </c>
       <c r="X4" t="n">
+        <v>0.006462750056087044</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.1368605255335975</v>
+      </c>
+      <c r="Z4" t="n">
         <v>0.002603333333333333</v>
       </c>
-      <c r="Y4" t="n">
-        <v>26.81456003824498</v>
+      <c r="AA4" t="n">
+        <v>26.81456869324099</v>
       </c>
     </row>
     <row r="5">
@@ -863,28 +891,34 @@
         <v>0.06448817748780201</v>
       </c>
       <c r="R5" t="n">
+        <v>0.05054056312736721</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2539452253691769</v>
+      </c>
+      <c r="T5" t="n">
         <v>24.71428571428569</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.3150449672599142</v>
       </c>
-      <c r="T5" t="n">
-        <v>27.34710021604569</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.861850276180797</v>
-      </c>
       <c r="V5" t="n">
-        <v>0.006889873878741359</v>
+        <v>27.34710868323887</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1470709834936617</v>
+        <v>1.861850524232492</v>
       </c>
       <c r="X5" t="n">
+        <v>0.006890040482292315</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.1470755906637241</v>
+      </c>
+      <c r="Z5" t="n">
         <v>0.002815</v>
       </c>
-      <c r="Y5" t="n">
-        <v>27.04656525594052</v>
+      <c r="AA5" t="n">
+        <v>27.04657382863489</v>
       </c>
     </row>
     <row r="6">
@@ -946,28 +980,34 @@
         <v>0.112121445976553</v>
       </c>
       <c r="R6" t="n">
+        <v>0.06466559242177924</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3348454060854844</v>
+      </c>
+      <c r="T6" t="n">
         <v>25.24642857142839</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0.462353720667521</v>
       </c>
-      <c r="T6" t="n">
-        <v>27.65075345661634</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.867680276180797</v>
-      </c>
       <c r="V6" t="n">
-        <v>0.007276059687110452</v>
+        <v>27.65076181827065</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1565518660143671</v>
+        <v>1.867680524232492</v>
       </c>
       <c r="X6" t="n">
+        <v>0.007275870207412934</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.1565466800263603</v>
+      </c>
+      <c r="Z6" t="n">
         <v>0.003015</v>
       </c>
-      <c r="Y6" t="n">
-        <v>27.34710021604569</v>
+      <c r="AA6" t="n">
+        <v>27.34710868323887</v>
       </c>
     </row>
     <row r="7">
@@ -1029,28 +1069,34 @@
         <v>0.2218548813486614</v>
       </c>
       <c r="R7" t="n">
+        <v>0.0901238156173267</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.4710147358084048</v>
+      </c>
+      <c r="T7" t="n">
         <v>26.8128</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>0.6209461221159972</v>
       </c>
-      <c r="T7" t="n">
-        <v>27.96486690381572</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.873749651180797</v>
-      </c>
       <c r="V7" t="n">
-        <v>0.007634494500556047</v>
+        <v>27.96487515706328</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1655898230009548</v>
+        <v>1.873749899232492</v>
       </c>
       <c r="X7" t="n">
+        <v>0.007634523293687587</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.1655906834098245</v>
+      </c>
+      <c r="Z7" t="n">
         <v>0.003210000000000001</v>
       </c>
-      <c r="Y7" t="n">
-        <v>27.65075345661634</v>
+      <c r="AA7" t="n">
+        <v>27.65076181827065</v>
       </c>
     </row>
     <row r="8">
@@ -1112,28 +1158,34 @@
         <v>0.3242312467603854</v>
       </c>
       <c r="R8" t="n">
+        <v>0.1082808906095662</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5694130721720264</v>
+      </c>
+      <c r="T8" t="n">
         <v>27.31428571428567</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>0.9523209449429346</v>
       </c>
-      <c r="T8" t="n">
-        <v>28.14125939280519</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.877175276180797</v>
-      </c>
       <c r="V8" t="n">
-        <v>0.007820573031697493</v>
+        <v>28.14126758547796</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1703846824654642</v>
+        <v>1.877175524232492</v>
       </c>
       <c r="X8" t="n">
+        <v>0.007820569623933762</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.1703846427370974</v>
+      </c>
+      <c r="Z8" t="n">
         <v>0.003315</v>
       </c>
-      <c r="Y8" t="n">
-        <v>27.96486690381572</v>
+      <c r="AA8" t="n">
+        <v>27.96487515706328</v>
       </c>
     </row>
     <row r="9">
@@ -1195,28 +1247,34 @@
         <v>0.4847102107155994</v>
       </c>
       <c r="R9" t="n">
+        <v>0.1314793690318168</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.6962113261902592</v>
+      </c>
+      <c r="T9" t="n">
         <v>27.65357142857139</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>1.25504016023201</v>
       </c>
-      <c r="T9" t="n">
-        <v>28.31682006754251</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.880597206736353</v>
-      </c>
       <c r="V9" t="n">
-        <v>0.007995870233119741</v>
+        <v>28.31682820030403</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1749716551880656</v>
+        <v>1.880597454788048</v>
       </c>
       <c r="X9" t="n">
+        <v>0.007995866882157202</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.1749716173380987</v>
+      </c>
+      <c r="Z9" t="n">
         <v>0.003416666666666667</v>
       </c>
-      <c r="Y9" t="n">
-        <v>28.14125939280519</v>
+      <c r="AA9" t="n">
+        <v>28.14126758547796</v>
       </c>
     </row>
     <row r="10">
@@ -1278,28 +1336,34 @@
         <v>0.6709707039456413</v>
       </c>
       <c r="R10" t="n">
+        <v>0.153658332461822</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.8191280143821486</v>
+      </c>
+      <c r="T10" t="n">
         <v>28.03928571428575</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>1.69587337268752</v>
       </c>
-      <c r="T10" t="n">
-        <v>28.48804706694351</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.883946706736353</v>
-      </c>
       <c r="V10" t="n">
-        <v>0.008158145764426144</v>
+        <v>28.48805514192954</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1792828694645364</v>
+        <v>1.883946954788048</v>
       </c>
       <c r="X10" t="n">
+        <v>0.008158142377838717</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.1792828308002749</v>
+      </c>
+      <c r="Z10" t="n">
         <v>0.003513333333333334</v>
       </c>
-      <c r="Y10" t="n">
-        <v>28.31682006754251</v>
+      <c r="AA10" t="n">
+        <v>28.31682820030403</v>
       </c>
     </row>
     <row r="11">
@@ -1361,28 +1425,34 @@
         <v>0.1619956336149481</v>
       </c>
       <c r="R11" t="n">
+        <v>0.07756128526809224</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.4024868117279722</v>
+      </c>
+      <c r="T11" t="n">
         <v>26.35714285714281</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>27.23145296079409</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.90800233686873</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01870831010401795</v>
+        <v>27.23145296063369</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3981310530798082</v>
+        <v>1.908002336883929</v>
       </c>
       <c r="X11" t="n">
+        <v>0.01870851914241778</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.3981367454977016</v>
+      </c>
+      <c r="Z11" t="n">
         <v>0.007799999999999998</v>
       </c>
-      <c r="Y11" t="n">
-        <v>26.32781437148795</v>
+      <c r="AA11" t="n">
+        <v>26.32781445538231</v>
       </c>
     </row>
     <row r="12">
@@ -1444,28 +1514,34 @@
         <v>0.0921971490896749</v>
       </c>
       <c r="R12" t="n">
+        <v>0.06022672929531771</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3036398344909226</v>
+      </c>
+      <c r="T12" t="n">
         <v>26.92857142857148</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.1961577414134905</v>
       </c>
-      <c r="T12" t="n">
-        <v>27.96947227861317</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.92257108686873</v>
-      </c>
       <c r="V12" t="n">
-        <v>0.02051071490900611</v>
+        <v>27.9694722689493</v>
       </c>
       <c r="W12" t="n">
-        <v>0.4449244950655394</v>
+        <v>1.922571086883929</v>
       </c>
       <c r="X12" t="n">
+        <v>0.02051073157175735</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4449249609611882</v>
+      </c>
+      <c r="Z12" t="n">
         <v>0.008849999999999998</v>
       </c>
-      <c r="Y12" t="n">
-        <v>27.23145296079409</v>
+      <c r="AA12" t="n">
+        <v>27.23145296063369</v>
       </c>
     </row>
     <row r="13">
@@ -1521,34 +1597,40 @@
         <v>0.006274829559544594</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R13" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T13" t="n">
         <v>25.41785714285721</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.4648676866334254</v>
       </c>
-      <c r="T13" t="n">
-        <v>28.96836793855088</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.942647670202063</v>
-      </c>
       <c r="V13" t="n">
-        <v>0.02241121869123013</v>
+        <v>28.96836727463392</v>
       </c>
       <c r="W13" t="n">
-        <v>0.498309042119181</v>
+        <v>1.942647670217263</v>
       </c>
       <c r="X13" t="n">
+        <v>0.02241123524433885</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4983095102163055</v>
+      </c>
+      <c r="Z13" t="n">
         <v>0.01012</v>
       </c>
-      <c r="Y13" t="n">
-        <v>27.96947227861317</v>
+      <c r="AA13" t="n">
+        <v>27.9694722689493</v>
       </c>
     </row>
     <row r="14">
@@ -1610,28 +1692,34 @@
         <v>0.166038915540943</v>
       </c>
       <c r="R14" t="n">
+        <v>0.07737225717069976</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.4074787301699844</v>
+      </c>
+      <c r="T14" t="n">
         <v>27.31785714285721</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.5273275582417261</v>
       </c>
-      <c r="T14" t="n">
-        <v>30.012551032435</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.964087670202063</v>
-      </c>
       <c r="V14" t="n">
-        <v>0.02393237134192201</v>
+        <v>30.01254965667641</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5452944730724245</v>
+        <v>1.964087670217262</v>
       </c>
       <c r="X14" t="n">
+        <v>0.02393238700794108</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.5452949182549442</v>
+      </c>
+      <c r="Z14" t="n">
         <v>0.01132</v>
       </c>
-      <c r="Y14" t="n">
-        <v>28.96836793855088</v>
+      <c r="AA14" t="n">
+        <v>28.96836727463392</v>
       </c>
     </row>
     <row r="15">
@@ -1693,28 +1781,34 @@
         <v>0.6940734053890505</v>
       </c>
       <c r="R15" t="n">
+        <v>0.1504129176969866</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.8331106801554344</v>
+      </c>
+      <c r="T15" t="n">
         <v>27.73571428571431</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.5669120469218694</v>
       </c>
-      <c r="T15" t="n">
-        <v>31.10797224513737</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.98709433686873</v>
-      </c>
       <c r="V15" t="n">
-        <v>0.02516111466725047</v>
+        <v>31.10797015051896</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5873367913989104</v>
+        <v>1.987094336883929</v>
       </c>
       <c r="X15" t="n">
+        <v>0.02516114519472265</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.5873377015004719</v>
+      </c>
+      <c r="Z15" t="n">
         <v>0.01248</v>
       </c>
-      <c r="Y15" t="n">
-        <v>30.012551032435</v>
+      <c r="AA15" t="n">
+        <v>30.01254965667641</v>
       </c>
     </row>
     <row r="16">
@@ -1776,28 +1870,34 @@
         <v>1.033509465599738</v>
       </c>
       <c r="R16" t="n">
+        <v>0.1835437763974597</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.016616675841852</v>
+      </c>
+      <c r="T16" t="n">
         <v>30.67857142857135</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>1.314363106233276</v>
       </c>
-      <c r="T16" t="n">
-        <v>31.7461397651932</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.000747670202063</v>
-      </c>
       <c r="V16" t="n">
-        <v>0.02574269341415964</v>
+        <v>31.74613730418875</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6090542900136535</v>
+        <v>2.000747670217262</v>
       </c>
       <c r="X16" t="n">
+        <v>0.02574269542905198</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.6090543067655569</v>
+      </c>
+      <c r="Z16" t="n">
         <v>0.01312</v>
       </c>
-      <c r="Y16" t="n">
-        <v>31.10797224513737</v>
+      <c r="AA16" t="n">
+        <v>31.10797015051896</v>
       </c>
     </row>
     <row r="17">
@@ -1859,28 +1959,34 @@
         <v>0.0816312894067058</v>
       </c>
       <c r="R17" t="n">
+        <v>0.05155349562266365</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2857118993089119</v>
+      </c>
+      <c r="T17" t="n">
         <v>29.52857142857138</v>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>19.99434722561607</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.878764027797204</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.006624136125296541</v>
+        <v>19.9943493428161</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1111961767348054</v>
+        <v>1.878764110411336</v>
       </c>
       <c r="X17" t="n">
+        <v>0.006624133662702124</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.1111961402057659</v>
+      </c>
+      <c r="Z17" t="n">
         <v>0.001996666666666667</v>
       </c>
-      <c r="Y17" t="n">
-        <v>16.88071097278224</v>
+      <c r="AA17" t="n">
+        <v>16.88071214887976</v>
       </c>
     </row>
     <row r="18">
@@ -1942,28 +2048,34 @@
         <v>0.04078878183453907</v>
       </c>
       <c r="R18" t="n">
+        <v>0.0359356095867547</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2019623277607462</v>
+      </c>
+      <c r="T18" t="n">
         <v>30.71428571428574</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.09290978010103844</v>
       </c>
-      <c r="T18" t="n">
-        <v>20.11820097131467</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.880990611130537</v>
-      </c>
       <c r="V18" t="n">
-        <v>0.006756799854998181</v>
+        <v>20.1182030731978</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1139909847038225</v>
+        <v>1.88099069374467</v>
       </c>
       <c r="X18" t="n">
+        <v>0.006756696680435864</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.1139889218902052</v>
+      </c>
+      <c r="Z18" t="n">
         <v>0.002051666666666667</v>
       </c>
-      <c r="Y18" t="n">
-        <v>19.99434722561607</v>
+      <c r="AA18" t="n">
+        <v>19.9943493428161</v>
       </c>
     </row>
     <row r="19">
@@ -2025,28 +2137,34 @@
         <v>0.02413582546819065</v>
       </c>
       <c r="R19" t="n">
+        <v>0.02706031021828268</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1553570901767623</v>
+      </c>
+      <c r="T19" t="n">
         <v>31.58571428571431</v>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
         <v>0.1714635834683609</v>
       </c>
-      <c r="T19" t="n">
-        <v>20.22568990616278</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.882927277797204</v>
-      </c>
       <c r="V19" t="n">
-        <v>0.006866587876487551</v>
+        <v>20.22569199499107</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1163419771341342</v>
+        <v>1.882927360411336</v>
       </c>
       <c r="X19" t="n">
+        <v>0.006866586904202878</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.1163419704732665</v>
+      </c>
+      <c r="Z19" t="n">
         <v>0.002098333333333333</v>
       </c>
-      <c r="Y19" t="n">
-        <v>20.11820097131467</v>
+      <c r="AA19" t="n">
+        <v>20.1182030731978</v>
       </c>
     </row>
     <row r="20">
@@ -2108,28 +2226,34 @@
         <v>0.03974752399441857</v>
       </c>
       <c r="R20" t="n">
+        <v>0.03441311909386455</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.199367810828174</v>
+      </c>
+      <c r="T20" t="n">
         <v>32.96071428571437</v>
       </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
         <v>0.1940649581558863</v>
       </c>
-      <c r="T20" t="n">
-        <v>20.34328539823888</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.885050611130537</v>
-      </c>
       <c r="V20" t="n">
-        <v>0.006981703852210943</v>
+        <v>20.34328747236598</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1188461867469677</v>
+        <v>1.88505069374467</v>
       </c>
       <c r="X20" t="n">
+        <v>0.006981715983853094</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.1188464466776623</v>
+      </c>
+      <c r="Z20" t="n">
         <v>0.002148333333333333</v>
       </c>
-      <c r="Y20" t="n">
-        <v>20.22568990616278</v>
+      <c r="AA20" t="n">
+        <v>20.22569199499107</v>
       </c>
     </row>
     <row r="21">
@@ -2191,28 +2315,34 @@
         <v>0.07526448485171559</v>
       </c>
       <c r="R21" t="n">
+        <v>0.04747282035761839</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2743437348504894</v>
+      </c>
+      <c r="T21" t="n">
         <v>33.56309523809537</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>0.2229784488956445</v>
       </c>
-      <c r="T21" t="n">
-        <v>20.4734955867161</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.887407312519426</v>
-      </c>
       <c r="V21" t="n">
-        <v>0.007103353408241623</v>
+        <v>20.47349764508844</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1215390370561618</v>
+        <v>1.887407395133558</v>
       </c>
       <c r="X21" t="n">
+        <v>0.007103342896403787</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.1215388351071716</v>
+      </c>
+      <c r="Z21" t="n">
         <v>0.0022025</v>
       </c>
-      <c r="Y21" t="n">
-        <v>20.34328539823888</v>
+      <c r="AA21" t="n">
+        <v>20.34328747236598</v>
       </c>
     </row>
     <row r="22">
@@ -2274,28 +2404,34 @@
         <v>0.102602067198723</v>
       </c>
       <c r="R22" t="n">
+        <v>0.05491924762933701</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.3203155743930086</v>
+      </c>
+      <c r="T22" t="n">
         <v>33.39642857142849</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>0.2989185664601128</v>
       </c>
-      <c r="T22" t="n">
-        <v>20.58181820907232</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.889372361130537</v>
-      </c>
       <c r="V22" t="n">
-        <v>0.007200136730610088</v>
+        <v>20.58182025443793</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1237179128155578</v>
+        <v>1.889372443744669</v>
       </c>
       <c r="X22" t="n">
+        <v>0.007200135700517285</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.1237179049792681</v>
+      </c>
+      <c r="Z22" t="n">
         <v>0.002246666666666667</v>
       </c>
-      <c r="Y22" t="n">
-        <v>20.4734955867161</v>
+      <c r="AA22" t="n">
+        <v>20.47349764508844</v>
       </c>
     </row>
     <row r="23">
@@ -2357,28 +2493,34 @@
         <v>0.06320238611045444</v>
       </c>
       <c r="R23" t="n">
+        <v>0.0464330358326207</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.2514008474736202</v>
+      </c>
+      <c r="T23" t="n">
         <v>28.42857142857147</v>
       </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>15.01969250760888</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.792146527764305</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0.009244326228632355</v>
+        <v>15.01969296805368</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1221131944166381</v>
+        <v>1.792146539303604</v>
       </c>
       <c r="X23" t="n">
+        <v>0.00924435718584087</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.1221136632356617</v>
+      </c>
+      <c r="Z23" t="n">
         <v>0.001996666666666667</v>
       </c>
-      <c r="Y23" t="n">
-        <v>14.80438644777559</v>
+      <c r="AA23" t="n">
+        <v>14.80438687360635</v>
       </c>
     </row>
     <row r="24">
@@ -2440,28 +2582,34 @@
         <v>0.05093049240086417</v>
       </c>
       <c r="R24" t="n">
+        <v>0.04115887469949947</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.2256778509310654</v>
+      </c>
+      <c r="T24" t="n">
         <v>29.31428571428569</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.05810793948216079</v>
       </c>
-      <c r="T24" t="n">
-        <v>15.15569778641188</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.794373111097638</v>
-      </c>
       <c r="V24" t="n">
-        <v>0.009401995746227973</v>
+        <v>15.15569823705797</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1251649463817385</v>
+        <v>1.794373122636937</v>
       </c>
       <c r="X24" t="n">
+        <v>0.00940201309158991</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.1251652130959574</v>
+      </c>
+      <c r="Z24" t="n">
         <v>0.002051666666666667</v>
       </c>
-      <c r="Y24" t="n">
-        <v>15.01969250760888</v>
+      <c r="AA24" t="n">
+        <v>15.01969296805368</v>
       </c>
     </row>
     <row r="25">
@@ -2523,28 +2671,34 @@
         <v>0.03650228328522884</v>
       </c>
       <c r="R25" t="n">
+        <v>0.03434893131725996</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.1910557072825328</v>
+      </c>
+      <c r="T25" t="n">
         <v>30.06428571428577</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.1219400842896329</v>
       </c>
-      <c r="T25" t="n">
-        <v>15.27797946826978</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.796379749986527</v>
-      </c>
       <c r="V25" t="n">
-        <v>0.009535924639375432</v>
+        <v>15.27797991000348</v>
       </c>
       <c r="W25" t="n">
-        <v>0.12782943008243</v>
+        <v>1.796379761525826</v>
       </c>
       <c r="X25" t="n">
+        <v>0.009535909472786619</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.1278292021782632</v>
+      </c>
+      <c r="Z25" t="n">
         <v>0.0021</v>
       </c>
-      <c r="Y25" t="n">
-        <v>15.15569778641188</v>
+      <c r="AA25" t="n">
+        <v>15.15569823705797</v>
       </c>
     </row>
     <row r="26">
@@ -2606,28 +2760,34 @@
         <v>0.01662203559450923</v>
       </c>
       <c r="R26" t="n">
+        <v>0.02296789446903608</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.1289264735983624</v>
+      </c>
+      <c r="T26" t="n">
         <v>30.93809523809523</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.1703755277559266</v>
       </c>
-      <c r="T26" t="n">
-        <v>15.40717642178005</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.798504749986527</v>
-      </c>
       <c r="V26" t="n">
-        <v>0.009669490718981348</v>
+        <v>15.40717685453495</v>
       </c>
       <c r="W26" t="n">
-        <v>0.1305612331413965</v>
+        <v>1.798504761525826</v>
       </c>
       <c r="X26" t="n">
+        <v>0.009669568421304507</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.1305624341001924</v>
+      </c>
+      <c r="Z26" t="n">
         <v>0.00215</v>
       </c>
-      <c r="Y26" t="n">
-        <v>15.27797946826978</v>
+      <c r="AA26" t="n">
+        <v>15.27797991000348</v>
       </c>
     </row>
     <row r="27">
@@ -2683,34 +2843,40 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R27" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T27" t="n">
         <v>31.5095238095239</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>0.2036432131066642</v>
       </c>
-      <c r="T27" t="n">
-        <v>15.54576471769251</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.800789812486527</v>
-      </c>
       <c r="V27" t="n">
-        <v>0.009804969956134207</v>
+        <v>15.54576514061194</v>
       </c>
       <c r="W27" t="n">
-        <v>0.1334121284519593</v>
+        <v>1.800789824025826</v>
       </c>
       <c r="X27" t="n">
+        <v>0.009804949344494194</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.1334118117795324</v>
+      </c>
+      <c r="Z27" t="n">
         <v>0.0022025</v>
       </c>
-      <c r="Y27" t="n">
-        <v>15.40717642178005</v>
+      <c r="AA27" t="n">
+        <v>15.40717685453495</v>
       </c>
     </row>
     <row r="28">
@@ -2766,34 +2932,40 @@
         <v>0.07036365759109456</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R28" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T28" t="n">
         <v>31.73214285714281</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0.2220723133576301</v>
       </c>
-      <c r="T28" t="n">
-        <v>15.66240050531441</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.802717423597638</v>
-      </c>
       <c r="V28" t="n">
-        <v>0.009912768036938789</v>
+        <v>15.66240091965512</v>
       </c>
       <c r="W28" t="n">
-        <v>0.1357454553421338</v>
+        <v>1.802717435136937</v>
       </c>
       <c r="X28" t="n">
+        <v>0.009912767707050024</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.1357454538912589</v>
+      </c>
+      <c r="Z28" t="n">
         <v>0.002245833333333333</v>
       </c>
-      <c r="Y28" t="n">
-        <v>15.54576471769251</v>
+      <c r="AA28" t="n">
+        <v>15.54576514061194</v>
       </c>
     </row>
     <row r="29">
@@ -2855,28 +3027,34 @@
         <v>0.07399229663180125</v>
       </c>
       <c r="R29" t="n">
+        <v>0.05414454690340646</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.2720152507338536</v>
+      </c>
+      <c r="T29" t="n">
         <v>24.49345238095237</v>
       </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>23.93967898585161</v>
-      </c>
       <c r="U29" t="n">
-        <v>2.098491694450313</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0.01007971427442612</v>
+        <v>23.93968006453909</v>
       </c>
       <c r="W29" t="n">
-        <v>0.1949504513214563</v>
+        <v>2.098491720806879</v>
       </c>
       <c r="X29" t="n">
+        <v>0.01007997637280434</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.194956735239167</v>
+      </c>
+      <c r="Z29" t="n">
         <v>0.004063333333333333</v>
       </c>
-      <c r="Y29" t="n">
-        <v>23.76781114604884</v>
+      <c r="AA29" t="n">
+        <v>23.76781203213405</v>
       </c>
     </row>
     <row r="30">
@@ -2938,28 +3116,34 @@
         <v>0.06485638924285067</v>
       </c>
       <c r="R30" t="n">
+        <v>0.05116644028606399</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.2546691760752578</v>
+      </c>
+      <c r="T30" t="n">
         <v>25.23928571428564</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.06375494686076261</v>
       </c>
-      <c r="T30" t="n">
-        <v>24.22814583641843</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.104521250005869</v>
-      </c>
       <c r="V30" t="n">
-        <v>0.01063211796426457</v>
+        <v>24.22814684652792</v>
       </c>
       <c r="W30" t="n">
-        <v>0.2075174500820442</v>
+        <v>2.104521276362434</v>
       </c>
       <c r="X30" t="n">
+        <v>0.01063212456913026</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.207517619384608</v>
+      </c>
+      <c r="Z30" t="n">
         <v>0.00435</v>
       </c>
-      <c r="Y30" t="n">
-        <v>23.93967898585161</v>
+      <c r="AA30" t="n">
+        <v>23.93968006453909</v>
       </c>
     </row>
     <row r="31">
@@ -3021,28 +3205,34 @@
         <v>0.04872158819598323</v>
       </c>
       <c r="R31" t="n">
+        <v>0.0441207297966015</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.2207296722146418</v>
+      </c>
+      <c r="T31" t="n">
         <v>24.77321428571426</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>0.1716212668026328</v>
       </c>
-      <c r="T31" t="n">
-        <v>24.54912557034737</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.111271250005868</v>
-      </c>
       <c r="V31" t="n">
-        <v>0.01118089966425217</v>
+        <v>24.54912650345894</v>
       </c>
       <c r="W31" t="n">
-        <v>0.22041273201674</v>
+        <v>2.111271276362434</v>
       </c>
       <c r="X31" t="n">
+        <v>0.01118092410442565</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.2204133410545105</v>
+      </c>
+      <c r="Z31" t="n">
         <v>0.00465</v>
       </c>
-      <c r="Y31" t="n">
-        <v>24.22814583641843</v>
+      <c r="AA31" t="n">
+        <v>24.22814684652792</v>
       </c>
     </row>
     <row r="32">
@@ -3104,28 +3294,34 @@
         <v>0.03284030984725474</v>
       </c>
       <c r="R32" t="n">
+        <v>0.03536550708002241</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.1812189555406794</v>
+      </c>
+      <c r="T32" t="n">
         <v>25.0285714285714</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>0.2547670720457892</v>
       </c>
-      <c r="T32" t="n">
-        <v>25.00680786787553</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.120971250005868</v>
-      </c>
       <c r="V32" t="n">
-        <v>0.0118658838353382</v>
+        <v>25.00680869176568</v>
       </c>
       <c r="W32" t="n">
-        <v>0.2371870514484175</v>
+        <v>2.120971276362434</v>
       </c>
       <c r="X32" t="n">
+        <v>0.01186587573608902</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.2371868574664508</v>
+      </c>
+      <c r="Z32" t="n">
         <v>0.005050000000000001</v>
       </c>
-      <c r="Y32" t="n">
-        <v>24.54912557034737</v>
+      <c r="AA32" t="n">
+        <v>24.54912650345894</v>
       </c>
     </row>
     <row r="33">
@@ -3187,28 +3383,34 @@
         <v>0.002777158124534164</v>
       </c>
       <c r="R33" t="n">
+        <v>0.01006757845422143</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.05269874879476897</v>
+      </c>
+      <c r="T33" t="n">
         <v>26.25714285714279</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>0.3345630000595383</v>
       </c>
-      <c r="T33" t="n">
-        <v>26.11045456428113</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.14473236111698</v>
-      </c>
       <c r="V33" t="n">
-        <v>0.01316721393135566</v>
+        <v>26.11045512932166</v>
       </c>
       <c r="W33" t="n">
-        <v>0.2717711091938156</v>
+        <v>2.144732387473546</v>
       </c>
       <c r="X33" t="n">
+        <v>0.01316721250280378</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.271771078660095</v>
+      </c>
+      <c r="Z33" t="n">
         <v>0.005916666666666667</v>
       </c>
-      <c r="Y33" t="n">
-        <v>25.00680786787553</v>
+      <c r="AA33" t="n">
+        <v>25.00680869176568</v>
       </c>
     </row>
     <row r="34">
@@ -3264,34 +3466,40 @@
         <v>0.01145255846603085</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R34" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T34" t="n">
         <v>27.40000000000004</v>
       </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
         <v>0.4114676331552647</v>
       </c>
-      <c r="T34" t="n">
-        <v>26.57397314631664</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.154871250005869</v>
-      </c>
       <c r="V34" t="n">
-        <v>0.01360205894586814</v>
+        <v>26.57397360426178</v>
       </c>
       <c r="W34" t="n">
-        <v>0.2843854565366162</v>
+        <v>2.154871276362434</v>
       </c>
       <c r="X34" t="n">
+        <v>0.01360205481603644</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.2843853526340677</v>
+      </c>
+      <c r="Z34" t="n">
         <v>0.00625</v>
       </c>
-      <c r="Y34" t="n">
-        <v>26.11045456428113</v>
+      <c r="AA34" t="n">
+        <v>26.11045512932166</v>
       </c>
     </row>
     <row r="35">
@@ -3353,28 +3561,34 @@
         <v>0.001762949417501451</v>
       </c>
       <c r="R35" t="n">
+        <v>0.007839965084997607</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.04198749120275527</v>
+      </c>
+      <c r="T35" t="n">
         <v>28.4607142857143</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>0.4067877264015557</v>
       </c>
-      <c r="T35" t="n">
-        <v>27.30784322886136</v>
-      </c>
-      <c r="U35" t="n">
-        <v>2.171121250005869</v>
-      </c>
       <c r="V35" t="n">
-        <v>0.01418844280408847</v>
+        <v>27.30784352193885</v>
       </c>
       <c r="W35" t="n">
-        <v>0.302555887977083</v>
+        <v>2.171121276362435</v>
       </c>
       <c r="X35" t="n">
+        <v>0.01418840491525607</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.3025548575925655</v>
+      </c>
+      <c r="Z35" t="n">
         <v>0.006750000000000001</v>
       </c>
-      <c r="Y35" t="n">
-        <v>26.57397314631664</v>
+      <c r="AA35" t="n">
+        <v>26.57397360426178</v>
       </c>
     </row>
     <row r="36">
@@ -3436,28 +3650,34 @@
         <v>0.001647154283060745</v>
       </c>
       <c r="R36" t="n">
+        <v>0.007564472262002585</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.04058514855289733</v>
+      </c>
+      <c r="T36" t="n">
         <v>28.6821428571429</v>
       </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
         <v>0.4021708299263646</v>
       </c>
-      <c r="T36" t="n">
-        <v>27.82182632953165</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2.182649027783647</v>
-      </c>
       <c r="V36" t="n">
-        <v>0.01453702929851717</v>
+        <v>27.82182651078572</v>
       </c>
       <c r="W36" t="n">
-        <v>0.31415675529333</v>
+        <v>2.182649054140212</v>
       </c>
       <c r="X36" t="n">
+        <v>0.01453692586273916</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.3141538806580285</v>
+      </c>
+      <c r="Z36" t="n">
         <v>0.007083333333333334</v>
       </c>
-      <c r="Y36" t="n">
-        <v>27.30784322886136</v>
+      <c r="AA36" t="n">
+        <v>27.30784352193885</v>
       </c>
     </row>
     <row r="37">
@@ -3519,28 +3739,34 @@
         <v>0.0005503013934911842</v>
       </c>
       <c r="R37" t="n">
+        <v>0.004370963058975695</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.02345850364987469</v>
+      </c>
+      <c r="T37" t="n">
         <v>28.78571428571429</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>0.3873938421634567</v>
       </c>
-      <c r="T37" t="n">
-        <v>28.72212538886001</v>
-      </c>
-      <c r="U37" t="n">
-        <v>2.203139000005869</v>
-      </c>
       <c r="V37" t="n">
-        <v>0.01504659646470858</v>
+        <v>28.72212537780479</v>
       </c>
       <c r="W37" t="n">
-        <v>0.3325682361029325</v>
+        <v>2.203139026362434</v>
       </c>
       <c r="X37" t="n">
+        <v>0.01504659517082482</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.3325682000033916</v>
+      </c>
+      <c r="Z37" t="n">
         <v>0.007640000000000001</v>
       </c>
-      <c r="Y37" t="n">
-        <v>27.82182632953165</v>
+      <c r="AA37" t="n">
+        <v>27.82182651078572</v>
       </c>
     </row>
     <row r="38">
@@ -3602,28 +3828,34 @@
         <v>0.0004247662125730495</v>
       </c>
       <c r="R38" t="n">
+        <v>0.003775433716909023</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.02060985717012735</v>
+      </c>
+      <c r="T38" t="n">
         <v>28.80357142857139</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.3689307159607038</v>
       </c>
-      <c r="T38" t="n">
-        <v>29.76547646662382</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.227371250005869</v>
-      </c>
       <c r="V38" t="n">
-        <v>0.01550780134710743</v>
+        <v>29.76547634687633</v>
       </c>
       <c r="W38" t="n">
-        <v>0.3513482182048674</v>
+        <v>2.227371276362434</v>
       </c>
       <c r="X38" t="n">
+        <v>0.01550781476267443</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0.3513486174167029</v>
+      </c>
+      <c r="Z38" t="n">
         <v>0.00825</v>
       </c>
-      <c r="Y38" t="n">
-        <v>28.72212538886001</v>
+      <c r="AA38" t="n">
+        <v>28.72212537780479</v>
       </c>
     </row>
     <row r="39">
@@ -3685,28 +3917,34 @@
         <v>0.008954679612111731</v>
       </c>
       <c r="R39" t="n">
+        <v>0.01696173781741488</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.09462916892856943</v>
+      </c>
+      <c r="T39" t="n">
         <v>29.79999999999999</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.3542503465167628</v>
       </c>
-      <c r="T39" t="n">
-        <v>30.84541916586719</v>
-      </c>
-      <c r="U39" t="n">
-        <v>2.253021250005869</v>
-      </c>
       <c r="V39" t="n">
-        <v>0.01587052728317392</v>
+        <v>30.84541902494425</v>
       </c>
       <c r="W39" t="n">
-        <v>0.3683704455222586</v>
+        <v>2.253021276362434</v>
       </c>
       <c r="X39" t="n">
+        <v>0.01587053886464064</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.3683708024918843</v>
+      </c>
+      <c r="Z39" t="n">
         <v>0.00885</v>
       </c>
-      <c r="Y39" t="n">
-        <v>29.76547646662382</v>
+      <c r="AA39" t="n">
+        <v>29.76547634687633</v>
       </c>
     </row>
     <row r="40">
@@ -3768,28 +4006,34 @@
         <v>0.02192219084074996</v>
       </c>
       <c r="R40" t="n">
+        <v>0.02664331523520602</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.148061442788965</v>
+      </c>
+      <c r="T40" t="n">
         <v>31.12500000000002</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>0.363160750555521</v>
       </c>
-      <c r="T40" t="n">
-        <v>31.81469618095175</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2.27655111111698</v>
-      </c>
       <c r="V40" t="n">
-        <v>0.01611696629351479</v>
+        <v>31.8146960202547</v>
       </c>
       <c r="W40" t="n">
-        <v>0.3818576537892139</v>
+        <v>2.276551137473545</v>
       </c>
       <c r="X40" t="n">
+        <v>0.01611696618632926</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0.3818576499658321</v>
+      </c>
+      <c r="Z40" t="n">
         <v>0.009366666666666667</v>
       </c>
-      <c r="Y40" t="n">
-        <v>30.84541916586719</v>
+      <c r="AA40" t="n">
+        <v>30.84541902494425</v>
       </c>
     </row>
     <row r="41">
@@ -3851,28 +4095,34 @@
         <v>0.04292053230848831</v>
       </c>
       <c r="R41" t="n">
+        <v>0.03929002064237096</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.2071727113026431</v>
+      </c>
+      <c r="T41" t="n">
         <v>25.66428571428573</v>
       </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>28.24180486772746</v>
-      </c>
       <c r="U41" t="n">
-        <v>2.198068889706438</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0.007062670572029382</v>
+        <v>28.24180554491312</v>
       </c>
       <c r="W41" t="n">
-        <v>0.1088380779834294</v>
+        <v>2.198068908667902</v>
       </c>
       <c r="X41" t="n">
+        <v>0.007068164159168635</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0.1089932301946586</v>
+      </c>
+      <c r="Z41" t="n">
         <v>0.007053333333333333</v>
       </c>
-      <c r="Y41" t="n">
-        <v>24.01327158029936</v>
+      <c r="AA41" t="n">
+        <v>24.01327122841171</v>
       </c>
     </row>
     <row r="42">
@@ -3934,28 +4184,34 @@
         <v>0.03670292593065684</v>
       </c>
       <c r="R42" t="n">
+        <v>0.03606976413308337</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.1915800770713303</v>
+      </c>
+      <c r="T42" t="n">
         <v>27.80357142857142</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>0.05060060245371522</v>
       </c>
-      <c r="T42" t="n">
-        <v>28.47191369338541</v>
-      </c>
-      <c r="U42" t="n">
-        <v>2.203329228300105</v>
-      </c>
       <c r="V42" t="n">
-        <v>0.007575500360812597</v>
+        <v>28.47191433675219</v>
       </c>
       <c r="W42" t="n">
-        <v>0.1171354979034436</v>
+        <v>2.203329247622887</v>
       </c>
       <c r="X42" t="n">
+        <v>0.007575498547917375</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0.1171354497979989</v>
+      </c>
+      <c r="Z42" t="n">
         <v>0.007626666666666667</v>
       </c>
-      <c r="Y42" t="n">
-        <v>28.24180486772746</v>
+      <c r="AA42" t="n">
+        <v>28.24180554491312</v>
       </c>
     </row>
     <row r="43">
@@ -4017,28 +4273,34 @@
         <v>0.03226430616673658</v>
       </c>
       <c r="R43" t="n">
+        <v>0.03344169305227099</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.1796226772062386</v>
+      </c>
+      <c r="T43" t="n">
         <v>28.21071428571433</v>
       </c>
-      <c r="S43" t="n">
+      <c r="U43" t="n">
         <v>0.1044036282464569</v>
       </c>
-      <c r="T43" t="n">
-        <v>28.65987999470776</v>
-      </c>
-      <c r="U43" t="n">
-        <v>2.207644899282438</v>
-      </c>
       <c r="V43" t="n">
-        <v>0.007944459054254931</v>
+        <v>28.65988059431129</v>
       </c>
       <c r="W43" t="n">
-        <v>0.1229649217430691</v>
+        <v>2.20764491860522</v>
       </c>
       <c r="X43" t="n">
+        <v>0.007944458816790421</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0.1229649184265571</v>
+      </c>
+      <c r="Z43" t="n">
         <v>0.008066666666666666</v>
       </c>
-      <c r="Y43" t="n">
-        <v>28.47191369338541</v>
+      <c r="AA43" t="n">
+        <v>28.47191433675219</v>
       </c>
     </row>
     <row r="44">
@@ -4100,28 +4362,34 @@
         <v>0.02491516024776152</v>
       </c>
       <c r="R44" t="n">
+        <v>0.02890464370079389</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.1578453681542842</v>
+      </c>
+      <c r="T44" t="n">
         <v>28.84999999999995</v>
       </c>
-      <c r="S44" t="n">
+      <c r="U44" t="n">
         <v>0.1491197853115378</v>
       </c>
-      <c r="T44" t="n">
-        <v>28.9256375489027</v>
-      </c>
-      <c r="U44" t="n">
-        <v>2.213775572079771</v>
-      </c>
       <c r="V44" t="n">
-        <v>0.008420554940521486</v>
+        <v>28.92563808749308</v>
       </c>
       <c r="W44" t="n">
-        <v>0.1305037237830004</v>
+        <v>2.213775591402554</v>
       </c>
       <c r="X44" t="n">
+        <v>0.008420554709994834</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0.1305037205317169</v>
+      </c>
+      <c r="Z44" t="n">
         <v>0.008653333333333332</v>
       </c>
-      <c r="Y44" t="n">
-        <v>28.65987999470776</v>
+      <c r="AA44" t="n">
+        <v>28.65988059431129</v>
       </c>
     </row>
     <row r="45">
@@ -4183,28 +4451,34 @@
         <v>0.01583178431944987</v>
       </c>
       <c r="R45" t="n">
+        <v>0.02290151451210537</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.1258244186135977</v>
+      </c>
+      <c r="T45" t="n">
         <v>29.8214285714287</v>
       </c>
-      <c r="S45" t="n">
+      <c r="U45" t="n">
         <v>0.1918414613393818</v>
       </c>
-      <c r="T45" t="n">
-        <v>29.46262799265684</v>
-      </c>
-      <c r="U45" t="n">
-        <v>2.226267723460799</v>
-      </c>
       <c r="V45" t="n">
-        <v>0.009253028607806763</v>
+        <v>29.46262840771122</v>
       </c>
       <c r="W45" t="n">
-        <v>0.14371850055597</v>
+        <v>2.226267742783581</v>
       </c>
       <c r="X45" t="n">
+        <v>0.009253028396770656</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0.1437184974817057</v>
+      </c>
+      <c r="Z45" t="n">
         <v>0.009740000000000002</v>
       </c>
-      <c r="Y45" t="n">
-        <v>28.9256375489027</v>
+      <c r="AA45" t="n">
+        <v>28.92563808749308</v>
       </c>
     </row>
     <row r="46">
@@ -4266,28 +4540,34 @@
         <v>0.003813578138281135</v>
       </c>
       <c r="R46" t="n">
+        <v>0.01083418489561089</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.0617541750676109</v>
+      </c>
+      <c r="T46" t="n">
         <v>30.18571428571434</v>
       </c>
-      <c r="S46" t="n">
+      <c r="U46" t="n">
         <v>0.2448076315621145</v>
       </c>
-      <c r="T46" t="n">
-        <v>30.73245487163991</v>
-      </c>
-      <c r="U46" t="n">
-        <v>2.256376503569549</v>
-      </c>
       <c r="V46" t="n">
-        <v>0.01074722319542253</v>
+        <v>30.73245500743434</v>
       </c>
       <c r="W46" t="n">
-        <v>0.1673901349917643</v>
+        <v>2.256376522892332</v>
       </c>
       <c r="X46" t="n">
+        <v>0.01074724495172402</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.1673908057509535</v>
+      </c>
+      <c r="Z46" t="n">
         <v>0.01196</v>
       </c>
-      <c r="Y46" t="n">
-        <v>29.46262799265684</v>
+      <c r="AA46" t="n">
+        <v>29.46262840771122</v>
       </c>
     </row>
     <row r="47">
@@ -4349,28 +4629,34 @@
         <v>0.002635143243149769</v>
       </c>
       <c r="R47" t="n">
+        <v>0.008945242501938901</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.05133364630678176</v>
+      </c>
+      <c r="T47" t="n">
         <v>32.48928571428564</v>
       </c>
-      <c r="S47" t="n">
+      <c r="U47" t="n">
         <v>0.2862295508009267</v>
       </c>
-      <c r="T47" t="n">
-        <v>31.15248097080469</v>
-      </c>
-      <c r="U47" t="n">
-        <v>2.266515763708799</v>
-      </c>
       <c r="V47" t="n">
-        <v>0.01113714943474031</v>
+        <v>31.15248101756942</v>
       </c>
       <c r="W47" t="n">
-        <v>0.1734922688738111</v>
+        <v>2.266515783031581</v>
       </c>
       <c r="X47" t="n">
+        <v>0.0111372695428132</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0.1734960122774931</v>
+      </c>
+      <c r="Z47" t="n">
         <v>0.01262</v>
       </c>
-      <c r="Y47" t="n">
-        <v>30.73245487163991</v>
+      <c r="AA47" t="n">
+        <v>30.73245500743434</v>
       </c>
     </row>
     <row r="48">
@@ -4432,28 +4718,34 @@
         <v>0.003468413842637606</v>
       </c>
       <c r="R48" t="n">
+        <v>0.01023902645998351</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.05889324106073299</v>
+      </c>
+      <c r="T48" t="n">
         <v>32.9321428571429</v>
       </c>
-      <c r="S48" t="n">
+      <c r="U48" t="n">
         <v>0.2889524121591054</v>
       </c>
-      <c r="T48" t="n">
-        <v>31.55039960390232</v>
-      </c>
-      <c r="U48" t="n">
-        <v>2.276205773398799</v>
-      </c>
       <c r="V48" t="n">
-        <v>0.01147081403029764</v>
+        <v>31.55039956771036</v>
       </c>
       <c r="W48" t="n">
-        <v>0.1786668611418356</v>
+        <v>2.276205792721581</v>
       </c>
       <c r="X48" t="n">
+        <v>0.01147072886081365</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0.1786641753611795</v>
+      </c>
+      <c r="Z48" t="n">
         <v>0.01322</v>
       </c>
-      <c r="Y48" t="n">
-        <v>31.15248097080469</v>
+      <c r="AA48" t="n">
+        <v>31.15248101756942</v>
       </c>
     </row>
     <row r="49">
@@ -4515,28 +4807,34 @@
         <v>0.004427144891717553</v>
       </c>
       <c r="R49" t="n">
+        <v>0.01153270065092904</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.06653679351845529</v>
+      </c>
+      <c r="T49" t="n">
         <v>33.08366238246173</v>
       </c>
-      <c r="S49" t="n">
+      <c r="U49" t="n">
         <v>0.2916972101212668</v>
       </c>
-      <c r="T49" t="n">
-        <v>31.95385449152545</v>
-      </c>
-      <c r="U49" t="n">
-        <v>2.286115561086354</v>
-      </c>
       <c r="V49" t="n">
-        <v>0.0117772325789504</v>
+        <v>31.95385437249574</v>
       </c>
       <c r="W49" t="n">
-        <v>0.1833472602095393</v>
+        <v>2.286115580409136</v>
       </c>
       <c r="X49" t="n">
+        <v>0.01177719446570448</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.1833460432925698</v>
+      </c>
+      <c r="Z49" t="n">
         <v>0.01380666666666667</v>
       </c>
-      <c r="Y49" t="n">
-        <v>31.55039960390232</v>
+      <c r="AA49" t="n">
+        <v>31.55039956771036</v>
       </c>
     </row>
     <row r="50">
@@ -4598,28 +4896,34 @@
         <v>0.006989072490978496</v>
       </c>
       <c r="R50" t="n">
+        <v>0.01414625769441237</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.08360067279022637</v>
+      </c>
+      <c r="T50" t="n">
         <v>33.286006759061</v>
       </c>
-      <c r="S50" t="n">
+      <c r="U50" t="n">
         <v>0.2947411967231239</v>
       </c>
-      <c r="T50" t="n">
-        <v>32.83159453267135</v>
-      </c>
-      <c r="U50" t="n">
-        <v>2.307975805168799</v>
-      </c>
       <c r="V50" t="n">
-        <v>0.01235144894981185</v>
+        <v>32.83159423889894</v>
       </c>
       <c r="W50" t="n">
-        <v>0.1918541072094664</v>
+        <v>2.307975824491581</v>
       </c>
       <c r="X50" t="n">
+        <v>0.01235149451992449</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0.1918556034210608</v>
+      </c>
+      <c r="Z50" t="n">
         <v>0.01502</v>
       </c>
-      <c r="Y50" t="n">
-        <v>31.95385449152545</v>
+      <c r="AA50" t="n">
+        <v>31.95385437249574</v>
       </c>
     </row>
     <row r="51">
@@ -4681,28 +4985,34 @@
         <v>0.01216839656025612</v>
       </c>
       <c r="R51" t="n">
+        <v>0.01855989829652208</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.1103104553533169</v>
+      </c>
+      <c r="T51" t="n">
         <v>34.92500000000002</v>
       </c>
-      <c r="S51" t="n">
+      <c r="U51" t="n">
         <v>0.3061500936386944</v>
       </c>
-      <c r="T51" t="n">
-        <v>33.75408934841732</v>
-      </c>
-      <c r="U51" t="n">
-        <v>2.331405828598798</v>
-      </c>
       <c r="V51" t="n">
-        <v>0.01284354032424172</v>
+        <v>33.75408893078473</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1986888771392174</v>
+        <v>2.331405847921581</v>
       </c>
       <c r="X51" t="n">
+        <v>0.01284345245977919</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0.1986859108423037</v>
+      </c>
+      <c r="Z51" t="n">
         <v>0.01622</v>
       </c>
-      <c r="Y51" t="n">
-        <v>32.83159453267135</v>
+      <c r="AA51" t="n">
+        <v>32.83159423889894</v>
       </c>
     </row>
     <row r="52">
@@ -4764,28 +5074,34 @@
         <v>0.01961652719811411</v>
       </c>
       <c r="R52" t="n">
+        <v>0.02311497993131076</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.1400590132698146</v>
+      </c>
+      <c r="T52" t="n">
         <v>35.32500000000002</v>
       </c>
-      <c r="S52" t="n">
+      <c r="U52" t="n">
         <v>0.3308651428571041</v>
       </c>
-      <c r="T52" t="n">
-        <v>34.61647934287152</v>
-      </c>
-      <c r="U52" t="n">
-        <v>2.353743628714354</v>
-      </c>
       <c r="V52" t="n">
-        <v>0.01322023279290888</v>
+        <v>34.6164789037036</v>
       </c>
       <c r="W52" t="n">
-        <v>0.2034031158610907</v>
+        <v>2.353743648037137</v>
       </c>
       <c r="X52" t="n">
+        <v>0.01322031243075041</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0.2034058721493541</v>
+      </c>
+      <c r="Z52" t="n">
         <v>0.01728666666666667</v>
       </c>
-      <c r="Y52" t="n">
-        <v>33.75408934841732</v>
+      <c r="AA52" t="n">
+        <v>33.75408893078473</v>
       </c>
     </row>
     <row r="53">
@@ -4847,28 +5163,34 @@
         <v>0.02963924799363945</v>
       </c>
       <c r="R53" t="n">
+        <v>0.0284767157115998</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.1721605297204892</v>
+      </c>
+      <c r="T53" t="n">
         <v>36.71428571428564</v>
       </c>
-      <c r="S53" t="n">
+      <c r="U53" t="n">
         <v>0.3724108962071924</v>
       </c>
-      <c r="T53" t="n">
-        <v>35.52745852248923</v>
-      </c>
-      <c r="U53" t="n">
-        <v>2.377809652780353</v>
-      </c>
       <c r="V53" t="n">
-        <v>0.01354761888355979</v>
+        <v>35.52745806381636</v>
       </c>
       <c r="W53" t="n">
-        <v>0.2068914320190024</v>
+        <v>2.377809672103136</v>
       </c>
       <c r="X53" t="n">
+        <v>0.01354761894834775</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0.2068914338797341</v>
+      </c>
+      <c r="Z53" t="n">
         <v>0.01836666666666667</v>
       </c>
-      <c r="Y53" t="n">
-        <v>34.61647934287152</v>
+      <c r="AA53" t="n">
+        <v>34.6164789037036</v>
       </c>
     </row>
     <row r="54">
@@ -4924,34 +5246,40 @@
         <v>0.04417757490269928</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R54" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T54" t="n">
         <v>21.79285714285717</v>
       </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>28.31815807173002</v>
-      </c>
       <c r="U54" t="n">
-        <v>2.196892806246272</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>0.0104122458017144</v>
+        <v>28.31816032897402</v>
       </c>
       <c r="W54" t="n">
-        <v>0.2041952841576134</v>
+        <v>2.196892860793617</v>
       </c>
       <c r="X54" t="n">
+        <v>0.01041304424064643</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0.2042179130067702</v>
+      </c>
+      <c r="Z54" t="n">
         <v>0.007033333333333333</v>
       </c>
-      <c r="Y54" t="n">
-        <v>25.42114773996207</v>
+      <c r="AA54" t="n">
+        <v>25.42114792085842</v>
       </c>
     </row>
     <row r="55">
@@ -5007,34 +5335,40 @@
         <v>0.02615548495855645</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R55" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T55" t="n">
         <v>22.74159954433088</v>
       </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>28.49544506706755</v>
-      </c>
       <c r="U55" t="n">
-        <v>2.2009444491868</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>0.01098361402771199</v>
+        <v>28.49544748119097</v>
       </c>
       <c r="W55" t="n">
-        <v>0.2161400311342437</v>
+        <v>2.200944508712678</v>
       </c>
       <c r="X55" t="n">
+        <v>0.01098357822667265</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0.216139031898086</v>
+      </c>
+      <c r="Z55" t="n">
         <v>0.007480000000000001</v>
       </c>
-      <c r="Y55" t="n">
-        <v>28.31815807173002</v>
+      <c r="AA55" t="n">
+        <v>28.31816032897402</v>
       </c>
     </row>
     <row r="56">
@@ -5090,34 +5424,40 @@
         <v>0.02647932083128075</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R56" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T56" t="n">
         <v>22.97108767528296</v>
       </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>28.74377626810038</v>
-      </c>
       <c r="U56" t="n">
-        <v>2.206644899331689</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>0.01171779493992934</v>
+        <v>28.74377861466887</v>
       </c>
       <c r="W56" t="n">
-        <v>0.231737203693045</v>
+        <v>2.206644958857567</v>
       </c>
       <c r="X56" t="n">
+        <v>0.01171774454065133</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0.2317357767803047</v>
+      </c>
+      <c r="Z56" t="n">
         <v>0.008066666666666666</v>
       </c>
-      <c r="Y56" t="n">
-        <v>28.49544506706755</v>
+      <c r="AA56" t="n">
+        <v>28.49544748119097</v>
       </c>
     </row>
     <row r="57">
@@ -5173,34 +5513,40 @@
         <v>0.02163341820285943</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R57" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T57" t="n">
         <v>24.12500000000008</v>
       </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>28.95676810524078</v>
-      </c>
       <c r="U57" t="n">
-        <v>2.211557709800049</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>0.01228114874974565</v>
+        <v>28.95677039510294</v>
       </c>
       <c r="W57" t="n">
-        <v>0.2438049010993913</v>
+        <v>2.211557769325928</v>
       </c>
       <c r="X57" t="n">
+        <v>0.01228110398018093</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0.2438036270068062</v>
+      </c>
+      <c r="Z57" t="n">
         <v>0.008539999999999999</v>
       </c>
-      <c r="Y57" t="n">
-        <v>28.74377626810038</v>
+      <c r="AA57" t="n">
+        <v>28.74377861466887</v>
       </c>
     </row>
     <row r="58">
@@ -5256,34 +5602,40 @@
         <v>0.01944191146369945</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R58" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T58" t="n">
         <v>24.57500000000017</v>
       </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>29.23616617039069</v>
-      </c>
       <c r="U58" t="n">
-        <v>2.218035494055605</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>0.01296732616405267</v>
+        <v>29.2361683854742</v>
       </c>
       <c r="W58" t="n">
-        <v>0.2588153203139437</v>
+        <v>2.218035553581483</v>
       </c>
       <c r="X58" t="n">
+        <v>0.01296734667627982</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0.2588159428505661</v>
+      </c>
+      <c r="Z58" t="n">
         <v>0.009126666666666668</v>
       </c>
-      <c r="Y58" t="n">
-        <v>28.95676810524078</v>
+      <c r="AA58" t="n">
+        <v>28.95677039510294</v>
       </c>
     </row>
     <row r="59">
@@ -5339,34 +5691,40 @@
         <v>0.01658310436687791</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R59" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T59" t="n">
         <v>25.06785714285721</v>
       </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>29.78688303409221</v>
-      </c>
       <c r="U59" t="n">
-        <v>2.230915506935605</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>0.01413302613406024</v>
+        <v>29.78688518662393</v>
       </c>
       <c r="W59" t="n">
-        <v>0.2848787841656656</v>
+        <v>2.230915566461483</v>
       </c>
       <c r="X59" t="n">
+        <v>0.01413308769286362</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0.2848806420287301</v>
+      </c>
+      <c r="Z59" t="n">
         <v>0.01019333333333333</v>
       </c>
-      <c r="Y59" t="n">
-        <v>29.23616617039069</v>
+      <c r="AA59" t="n">
+        <v>29.2361683854742</v>
       </c>
     </row>
     <row r="60">
@@ -5422,34 +5780,40 @@
         <v>0.01821926693166444</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R60" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T60" t="n">
         <v>25.90000000000013</v>
       </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>31.11037299829884</v>
-      </c>
       <c r="U60" t="n">
-        <v>2.262489288509355</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>0.01625169104512008</v>
+        <v>31.11037508564176</v>
       </c>
       <c r="W60" t="n">
-        <v>0.3347232131708391</v>
+        <v>2.262489348035233</v>
       </c>
       <c r="X60" t="n">
+        <v>0.01625131044668814</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0.3347113995646889</v>
+      </c>
+      <c r="Z60" t="n">
         <v>0.01242666666666667</v>
       </c>
-      <c r="Y60" t="n">
-        <v>29.78688303409221</v>
+      <c r="AA60" t="n">
+        <v>29.78688518662393</v>
       </c>
     </row>
     <row r="61">
@@ -5505,34 +5869,40 @@
         <v>0.01480594697664882</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R61" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T61" t="n">
         <v>27.37499999999996</v>
       </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>31.52104556401108</v>
-      </c>
       <c r="U61" t="n">
-        <v>2.272468965155688</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>0.01678984232084768</v>
+        <v>31.5210476313021</v>
       </c>
       <c r="W61" t="n">
-        <v>0.3481727318040841</v>
+        <v>2.272469024681567</v>
       </c>
       <c r="X61" t="n">
+        <v>0.01679001717135276</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0.3481782708526754</v>
+      </c>
+      <c r="Z61" t="n">
         <v>0.01305333333333333</v>
       </c>
-      <c r="Y61" t="n">
-        <v>31.11037299829884</v>
+      <c r="AA61" t="n">
+        <v>31.11037508564176</v>
       </c>
     </row>
     <row r="62">
@@ -5588,34 +5958,40 @@
         <v>0.01899552184075797</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R62" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T62" t="n">
         <v>28.11428571428576</v>
       </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>31.94343200681957</v>
-      </c>
       <c r="U62" t="n">
-        <v>2.282825558845605</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>0.01726821272876278</v>
+        <v>31.94343405366691</v>
       </c>
       <c r="W62" t="n">
-        <v>0.3602759005648064</v>
+        <v>2.282825618371483</v>
       </c>
       <c r="X62" t="n">
+        <v>0.01726817068693205</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0.3602745856788814</v>
+      </c>
+      <c r="Z62" t="n">
         <v>0.01367333333333333</v>
       </c>
-      <c r="Y62" t="n">
-        <v>31.52104556401108</v>
+      <c r="AA62" t="n">
+        <v>31.5210476313021</v>
       </c>
     </row>
     <row r="63">
@@ -5671,34 +6047,40 @@
         <v>0.02233579751349438</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R63" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T63" t="n">
         <v>28.14285714285706</v>
       </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>32.35740187371602</v>
-      </c>
       <c r="U63" t="n">
-        <v>2.293067791310049</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>0.01769926545816089</v>
+        <v>32.35740390067283</v>
       </c>
       <c r="W63" t="n">
-        <v>0.371479868678853</v>
+        <v>2.293067850835928</v>
       </c>
       <c r="X63" t="n">
+        <v>0.01769926548522211</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0.3714798980485495</v>
+      </c>
+      <c r="Z63" t="n">
         <v>0.01426</v>
       </c>
-      <c r="Y63" t="n">
-        <v>31.94343200681957</v>
+      <c r="AA63" t="n">
+        <v>31.94343405366691</v>
       </c>
     </row>
     <row r="64">
@@ -5754,34 +6136,40 @@
         <v>0.01014663618242141</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R64" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T64" t="n">
         <v>29.46071428571427</v>
       </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>33.2558324964522</v>
-      </c>
       <c r="U64" t="n">
-        <v>2.315615591635606</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>0.01851302896468444</v>
+        <v>33.25583448054279</v>
       </c>
       <c r="W64" t="n">
-        <v>0.3934451172228779</v>
+        <v>2.315615651161483</v>
       </c>
       <c r="X64" t="n">
+        <v>0.01851307209935324</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0.3934465808882616</v>
+      </c>
+      <c r="Z64" t="n">
         <v>0.01547333333333333</v>
       </c>
-      <c r="Y64" t="n">
-        <v>32.35740187371602</v>
+      <c r="AA64" t="n">
+        <v>32.35740390067283</v>
       </c>
     </row>
     <row r="65">
@@ -5837,34 +6225,40 @@
         <v>0.00902987934884078</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R65" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T65" t="n">
         <v>30.54107142857147</v>
       </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>34.19735342975477</v>
-      </c>
       <c r="U65" t="n">
-        <v>2.339725615745605</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>0.01919067788683726</v>
+        <v>34.19735536914632</v>
       </c>
       <c r="W65" t="n">
-        <v>0.412573497054656</v>
+        <v>2.339725675271483</v>
       </c>
       <c r="X65" t="n">
+        <v>0.01919069898130528</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0.4125742480274263</v>
+      </c>
+      <c r="Z65" t="n">
         <v>0.01667333333333334</v>
       </c>
-      <c r="Y65" t="n">
-        <v>33.2558324964522</v>
+      <c r="AA65" t="n">
+        <v>33.25583448054279</v>
       </c>
     </row>
     <row r="66">
@@ -5920,34 +6314,40 @@
         <v>0.01371968923896166</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R66" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T66" t="n">
         <v>30.00357142857132</v>
       </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>34.69219227762835</v>
-      </c>
       <c r="U66" t="n">
-        <v>2.3525996008418</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>0.01948925539598507</v>
+        <v>34.69219417667006</v>
       </c>
       <c r="W66" t="n">
-        <v>0.4213085438452883</v>
+        <v>2.352599660367677</v>
       </c>
       <c r="X66" t="n">
+        <v>0.01948898852875239</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0.4212993151451641</v>
+      </c>
+      <c r="Z66" t="n">
         <v>0.01728</v>
       </c>
-      <c r="Y66" t="n">
-        <v>34.19735342975477</v>
+      <c r="AA66" t="n">
+        <v>34.19735536914632</v>
       </c>
     </row>
     <row r="67">
@@ -6003,34 +6403,40 @@
         <v>0.0224321685275548</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>1e-08</v>
       </c>
       <c r="R67" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T67" t="n">
         <v>30.12857142857151</v>
       </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>35.0418357938299</v>
-      </c>
       <c r="U67" t="n">
-        <v>2.36178186002405</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>0.01970497486348605</v>
+        <v>35.04183767661643</v>
       </c>
       <c r="W67" t="n">
-        <v>0.4278830064061876</v>
+        <v>2.361781919549927</v>
       </c>
       <c r="X67" t="n">
+        <v>0.01970497329658792</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0.4278829811081218</v>
+      </c>
+      <c r="Z67" t="n">
         <v>0.0177</v>
       </c>
-      <c r="Y67" t="n">
-        <v>34.69219227762835</v>
+      <c r="AA67" t="n">
+        <v>34.69219417667006</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/BR_processed_ind.xlsx
+++ b/data/processed/BR_processed_ind.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA67"/>
+  <dimension ref="A1:Y67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,50 +516,40 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>qP_sqrt</t>
+          <t>Xlag1</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>rP_sqrt</t>
+          <t>Plag1</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Xlag1</t>
+          <t>X_calc</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Plag1</t>
+          <t>V_calc</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>X_calc</t>
+          <t>mu_calc</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>V_calc</t>
+          <t>dXdt_calc</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mu_calc</t>
+          <t>dVdt_calc</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dXdt_calc</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dVdt_calc</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Xlag1_calc</t>
         </is>
@@ -624,33 +614,27 @@
         <v>0.03252295278732637</v>
       </c>
       <c r="R2" t="n">
-        <v>0.03754548692326653</v>
+        <v>19.55000000000009</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1803412121156071</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>19.55000000000009</v>
+        <v>26.65401336848298</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.848679229473595</v>
       </c>
       <c r="V2" t="n">
-        <v>26.65401336848298</v>
+        <v>0.2252279510788963</v>
       </c>
       <c r="W2" t="n">
-        <v>1.848679229473595</v>
+        <v>5.970067722284991</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2252279510788963</v>
+        <v>0.0023</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.970067722284991</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="AA2" t="n">
         <v>23.31328394075086</v>
       </c>
     </row>
@@ -713,33 +697,27 @@
         <v>0.1065167260919373</v>
       </c>
       <c r="R3" t="n">
-        <v>0.06664459174752829</v>
+        <v>23.07142857142841</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3263690029582119</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>23.07142857142841</v>
+        <v>26.81456869324099</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.851713413179842</v>
       </c>
       <c r="V3" t="n">
-        <v>26.81456869324099</v>
+        <v>0.006093564436306846</v>
       </c>
       <c r="W3" t="n">
-        <v>1.851713413179842</v>
+        <v>0.1282317294427486</v>
       </c>
       <c r="X3" t="n">
-        <v>0.006093564436306846</v>
+        <v>0.002428333333333334</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1282317294427486</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.002428333333333334</v>
-      </c>
-      <c r="AA3" t="n">
         <v>26.65401336848298</v>
       </c>
     </row>
@@ -802,33 +780,27 @@
         <v>0.08474551698518029</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0585577437900562</v>
+        <v>23.9821428571428</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2911108328200452</v>
+        <v>0.1310102834270957</v>
       </c>
       <c r="T4" t="n">
-        <v>23.9821428571428</v>
+        <v>27.04657382863489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1310102834270957</v>
+        <v>1.856116121454714</v>
       </c>
       <c r="V4" t="n">
-        <v>27.04657382863489</v>
+        <v>0.006462750056087044</v>
       </c>
       <c r="W4" t="n">
-        <v>1.856116121454714</v>
+        <v>0.1368605255335975</v>
       </c>
       <c r="X4" t="n">
-        <v>0.006462750056087044</v>
+        <v>0.002603333333333333</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1368605255335975</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.002603333333333333</v>
-      </c>
-      <c r="AA4" t="n">
         <v>26.81456869324099</v>
       </c>
     </row>
@@ -891,33 +863,27 @@
         <v>0.06448817748780201</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05054056312736721</v>
+        <v>24.71428571428569</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2539452253691769</v>
+        <v>0.3150449672599142</v>
       </c>
       <c r="T5" t="n">
-        <v>24.71428571428569</v>
+        <v>27.34710868323887</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3150449672599142</v>
+        <v>1.861850524232492</v>
       </c>
       <c r="V5" t="n">
-        <v>27.34710868323887</v>
+        <v>0.006890040482292315</v>
       </c>
       <c r="W5" t="n">
-        <v>1.861850524232492</v>
+        <v>0.1470755906637241</v>
       </c>
       <c r="X5" t="n">
-        <v>0.006890040482292315</v>
+        <v>0.002815</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1470755906637241</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.002815</v>
-      </c>
-      <c r="AA5" t="n">
         <v>27.04657382863489</v>
       </c>
     </row>
@@ -980,33 +946,27 @@
         <v>0.112121445976553</v>
       </c>
       <c r="R6" t="n">
-        <v>0.06466559242177924</v>
+        <v>25.24642857142839</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3348454060854844</v>
+        <v>0.462353720667521</v>
       </c>
       <c r="T6" t="n">
-        <v>25.24642857142839</v>
+        <v>27.65076181827065</v>
       </c>
       <c r="U6" t="n">
-        <v>0.462353720667521</v>
+        <v>1.867680524232492</v>
       </c>
       <c r="V6" t="n">
-        <v>27.65076181827065</v>
+        <v>0.007275870207412934</v>
       </c>
       <c r="W6" t="n">
-        <v>1.867680524232492</v>
+        <v>0.1565466800263603</v>
       </c>
       <c r="X6" t="n">
-        <v>0.007275870207412934</v>
+        <v>0.003015</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1565466800263603</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.003015</v>
-      </c>
-      <c r="AA6" t="n">
         <v>27.34710868323887</v>
       </c>
     </row>
@@ -1069,33 +1029,27 @@
         <v>0.2218548813486614</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0901238156173267</v>
+        <v>26.8128</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4710147358084048</v>
+        <v>0.6209461221159972</v>
       </c>
       <c r="T7" t="n">
-        <v>26.8128</v>
+        <v>27.96487515706328</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6209461221159972</v>
+        <v>1.873749899232492</v>
       </c>
       <c r="V7" t="n">
-        <v>27.96487515706328</v>
+        <v>0.007634523293687587</v>
       </c>
       <c r="W7" t="n">
-        <v>1.873749899232492</v>
+        <v>0.1655906834098245</v>
       </c>
       <c r="X7" t="n">
-        <v>0.007634523293687587</v>
+        <v>0.003210000000000001</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1655906834098245</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.003210000000000001</v>
-      </c>
-      <c r="AA7" t="n">
         <v>27.65076181827065</v>
       </c>
     </row>
@@ -1158,33 +1112,27 @@
         <v>0.3242312467603854</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1082808906095662</v>
+        <v>27.31428571428567</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5694130721720264</v>
+        <v>0.9523209449429346</v>
       </c>
       <c r="T8" t="n">
-        <v>27.31428571428567</v>
+        <v>28.14126758547796</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9523209449429346</v>
+        <v>1.877175524232492</v>
       </c>
       <c r="V8" t="n">
-        <v>28.14126758547796</v>
+        <v>0.007820569623933762</v>
       </c>
       <c r="W8" t="n">
-        <v>1.877175524232492</v>
+        <v>0.1703846427370974</v>
       </c>
       <c r="X8" t="n">
-        <v>0.007820569623933762</v>
+        <v>0.003315</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1703846427370974</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.003315</v>
-      </c>
-      <c r="AA8" t="n">
         <v>27.96487515706328</v>
       </c>
     </row>
@@ -1247,33 +1195,27 @@
         <v>0.4847102107155994</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1314793690318168</v>
+        <v>27.65357142857139</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6962113261902592</v>
+        <v>1.25504016023201</v>
       </c>
       <c r="T9" t="n">
-        <v>27.65357142857139</v>
+        <v>28.31682820030403</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25504016023201</v>
+        <v>1.880597454788048</v>
       </c>
       <c r="V9" t="n">
-        <v>28.31682820030403</v>
+        <v>0.007995866882157202</v>
       </c>
       <c r="W9" t="n">
-        <v>1.880597454788048</v>
+        <v>0.1749716173380987</v>
       </c>
       <c r="X9" t="n">
-        <v>0.007995866882157202</v>
+        <v>0.003416666666666667</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1749716173380987</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.003416666666666667</v>
-      </c>
-      <c r="AA9" t="n">
         <v>28.14126758547796</v>
       </c>
     </row>
@@ -1336,33 +1278,27 @@
         <v>0.6709707039456413</v>
       </c>
       <c r="R10" t="n">
-        <v>0.153658332461822</v>
+        <v>28.03928571428575</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8191280143821486</v>
+        <v>1.69587337268752</v>
       </c>
       <c r="T10" t="n">
-        <v>28.03928571428575</v>
+        <v>28.48805514192954</v>
       </c>
       <c r="U10" t="n">
-        <v>1.69587337268752</v>
+        <v>1.883946954788048</v>
       </c>
       <c r="V10" t="n">
-        <v>28.48805514192954</v>
+        <v>0.008158142377838717</v>
       </c>
       <c r="W10" t="n">
-        <v>1.883946954788048</v>
+        <v>0.1792828308002749</v>
       </c>
       <c r="X10" t="n">
-        <v>0.008158142377838717</v>
+        <v>0.003513333333333334</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1792828308002749</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.003513333333333334</v>
-      </c>
-      <c r="AA10" t="n">
         <v>28.31682820030403</v>
       </c>
     </row>
@@ -1425,33 +1361,27 @@
         <v>0.1619956336149481</v>
       </c>
       <c r="R11" t="n">
-        <v>0.07756128526809224</v>
+        <v>26.35714285714281</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4024868117279722</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>26.35714285714281</v>
+        <v>27.23145296063369</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.908002336883929</v>
       </c>
       <c r="V11" t="n">
-        <v>27.23145296063369</v>
+        <v>0.01870851914241778</v>
       </c>
       <c r="W11" t="n">
-        <v>1.908002336883929</v>
+        <v>0.3981367454977016</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01870851914241778</v>
+        <v>0.007799999999999998</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3981367454977016</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.007799999999999998</v>
-      </c>
-      <c r="AA11" t="n">
         <v>26.32781445538231</v>
       </c>
     </row>
@@ -1514,33 +1444,27 @@
         <v>0.0921971490896749</v>
       </c>
       <c r="R12" t="n">
-        <v>0.06022672929531771</v>
+        <v>26.92857142857148</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3036398344909226</v>
+        <v>0.1961577414134905</v>
       </c>
       <c r="T12" t="n">
-        <v>26.92857142857148</v>
+        <v>27.9694722689493</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1961577414134905</v>
+        <v>1.922571086883929</v>
       </c>
       <c r="V12" t="n">
-        <v>27.9694722689493</v>
+        <v>0.02051073157175735</v>
       </c>
       <c r="W12" t="n">
-        <v>1.922571086883929</v>
+        <v>0.4449249609611882</v>
       </c>
       <c r="X12" t="n">
-        <v>0.02051073157175735</v>
+        <v>0.008849999999999998</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4449249609611882</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0.008849999999999998</v>
-      </c>
-      <c r="AA12" t="n">
         <v>27.23145296063369</v>
       </c>
     </row>
@@ -1597,39 +1521,33 @@
         <v>0.006274829559544594</v>
       </c>
       <c r="P13" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0001</v>
+        <v>25.41785714285721</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0001</v>
+        <v>0.4648676866334254</v>
       </c>
       <c r="T13" t="n">
-        <v>25.41785714285721</v>
+        <v>28.96836727463392</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4648676866334254</v>
+        <v>1.942647670217263</v>
       </c>
       <c r="V13" t="n">
-        <v>28.96836727463392</v>
+        <v>0.02241123524433885</v>
       </c>
       <c r="W13" t="n">
-        <v>1.942647670217263</v>
+        <v>0.4983095102163055</v>
       </c>
       <c r="X13" t="n">
-        <v>0.02241123524433885</v>
+        <v>0.01012</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4983095102163055</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0.01012</v>
-      </c>
-      <c r="AA13" t="n">
         <v>27.9694722689493</v>
       </c>
     </row>
@@ -1692,33 +1610,27 @@
         <v>0.166038915540943</v>
       </c>
       <c r="R14" t="n">
-        <v>0.07737225717069976</v>
+        <v>27.31785714285721</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4074787301699844</v>
+        <v>0.5273275582417261</v>
       </c>
       <c r="T14" t="n">
-        <v>27.31785714285721</v>
+        <v>30.01254965667641</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5273275582417261</v>
+        <v>1.964087670217262</v>
       </c>
       <c r="V14" t="n">
-        <v>30.01254965667641</v>
+        <v>0.02393238700794108</v>
       </c>
       <c r="W14" t="n">
-        <v>1.964087670217262</v>
+        <v>0.5452949182549442</v>
       </c>
       <c r="X14" t="n">
-        <v>0.02393238700794108</v>
+        <v>0.01132</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.5452949182549442</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0.01132</v>
-      </c>
-      <c r="AA14" t="n">
         <v>28.96836727463392</v>
       </c>
     </row>
@@ -1781,33 +1693,27 @@
         <v>0.6940734053890505</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1504129176969866</v>
+        <v>27.73571428571431</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8331106801554344</v>
+        <v>0.5669120469218694</v>
       </c>
       <c r="T15" t="n">
-        <v>27.73571428571431</v>
+        <v>31.10797015051896</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5669120469218694</v>
+        <v>1.987094336883929</v>
       </c>
       <c r="V15" t="n">
-        <v>31.10797015051896</v>
+        <v>0.02516114519472265</v>
       </c>
       <c r="W15" t="n">
-        <v>1.987094336883929</v>
+        <v>0.5873377015004719</v>
       </c>
       <c r="X15" t="n">
-        <v>0.02516114519472265</v>
+        <v>0.01248</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.5873377015004719</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0.01248</v>
-      </c>
-      <c r="AA15" t="n">
         <v>30.01254965667641</v>
       </c>
     </row>
@@ -1870,33 +1776,27 @@
         <v>1.033509465599738</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1835437763974597</v>
+        <v>30.67857142857135</v>
       </c>
       <c r="S16" t="n">
-        <v>1.016616675841852</v>
+        <v>1.314363106233276</v>
       </c>
       <c r="T16" t="n">
-        <v>30.67857142857135</v>
+        <v>31.74613730418875</v>
       </c>
       <c r="U16" t="n">
-        <v>1.314363106233276</v>
+        <v>2.000747670217262</v>
       </c>
       <c r="V16" t="n">
-        <v>31.74613730418875</v>
+        <v>0.02574269542905198</v>
       </c>
       <c r="W16" t="n">
-        <v>2.000747670217262</v>
+        <v>0.6090543067655569</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02574269542905198</v>
+        <v>0.01312</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.6090543067655569</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0.01312</v>
-      </c>
-      <c r="AA16" t="n">
         <v>31.10797015051896</v>
       </c>
     </row>
@@ -1959,33 +1859,27 @@
         <v>0.0816312894067058</v>
       </c>
       <c r="R17" t="n">
-        <v>0.05155349562266365</v>
+        <v>29.52857142857138</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2857118993089119</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>29.52857142857138</v>
+        <v>19.99434821018733</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.878764049847864</v>
       </c>
       <c r="V17" t="n">
-        <v>19.9943493428161</v>
+        <v>0.006623948324800732</v>
       </c>
       <c r="W17" t="n">
-        <v>1.878764110411336</v>
+        <v>0.11119242751127</v>
       </c>
       <c r="X17" t="n">
-        <v>0.006624133662702124</v>
+        <v>0.001996666666666667</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1111961402057659</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0.001996666666666667</v>
-      </c>
-      <c r="AA17" t="n">
         <v>16.88071214887976</v>
       </c>
     </row>
@@ -2048,34 +1942,28 @@
         <v>0.04078878183453907</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0359356095867547</v>
+        <v>30.71428571428574</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2019623277607462</v>
+        <v>0.09290978010103844</v>
       </c>
       <c r="T18" t="n">
-        <v>30.71428571428574</v>
+        <v>20.11820220859315</v>
       </c>
       <c r="U18" t="n">
-        <v>0.09290978010103844</v>
+        <v>1.880990638206213</v>
       </c>
       <c r="V18" t="n">
-        <v>20.1182030731978</v>
+        <v>0.006756705910393339</v>
       </c>
       <c r="W18" t="n">
-        <v>1.88099069374467</v>
+        <v>0.1139891020336284</v>
       </c>
       <c r="X18" t="n">
-        <v>0.006756696680435864</v>
+        <v>0.002051666666666667</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1139889218902052</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0.002051666666666667</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>19.9943493428161</v>
+        <v>19.99434821018733</v>
       </c>
     </row>
     <row r="19">
@@ -2137,34 +2025,28 @@
         <v>0.02413582546819065</v>
       </c>
       <c r="R19" t="n">
-        <v>0.02706031021828268</v>
+        <v>31.58571428571431</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1553570901767623</v>
+        <v>0.1714635834683609</v>
       </c>
       <c r="T19" t="n">
-        <v>31.58571428571431</v>
+        <v>20.22569114062808</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1714635834683609</v>
+        <v>1.88292730487288</v>
       </c>
       <c r="V19" t="n">
-        <v>20.22569199499107</v>
+        <v>0.006866587396872273</v>
       </c>
       <c r="W19" t="n">
-        <v>1.882927360411336</v>
+        <v>0.1163419748585688</v>
       </c>
       <c r="X19" t="n">
-        <v>0.006866586904202878</v>
+        <v>0.002098333333333333</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1163419704732665</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0.002098333333333333</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>20.1182030731978</v>
+        <v>20.11820220859315</v>
       </c>
     </row>
     <row r="20">
@@ -2226,34 +2108,28 @@
         <v>0.03974752399441857</v>
       </c>
       <c r="R20" t="n">
-        <v>0.03441311909386455</v>
+        <v>32.96071428571437</v>
       </c>
       <c r="S20" t="n">
-        <v>0.199367810828174</v>
+        <v>0.1940649581558863</v>
       </c>
       <c r="T20" t="n">
-        <v>32.96071428571437</v>
+        <v>20.34328662960689</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1940649581558863</v>
+        <v>1.885050638206214</v>
       </c>
       <c r="V20" t="n">
-        <v>20.34328747236598</v>
+        <v>0.006981721188787508</v>
       </c>
       <c r="W20" t="n">
-        <v>1.88505069374467</v>
+        <v>0.1188465469566182</v>
       </c>
       <c r="X20" t="n">
-        <v>0.006981715983853094</v>
+        <v>0.002148333333333333</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.1188464466776623</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0.002148333333333333</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>20.22569199499107</v>
+        <v>20.22569114062808</v>
       </c>
     </row>
     <row r="21">
@@ -2315,34 +2191,28 @@
         <v>0.07526448485171559</v>
       </c>
       <c r="R21" t="n">
-        <v>0.04747282035761839</v>
+        <v>33.56309523809537</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2743437348504894</v>
+        <v>0.2229784488956445</v>
       </c>
       <c r="T21" t="n">
-        <v>33.56309523809537</v>
+        <v>20.47349681467529</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2229784488956445</v>
+        <v>1.887407339595103</v>
       </c>
       <c r="V21" t="n">
-        <v>20.47349764508844</v>
+        <v>0.007103361739172312</v>
       </c>
       <c r="W21" t="n">
-        <v>1.887407395133558</v>
+        <v>0.1215392152518453</v>
       </c>
       <c r="X21" t="n">
-        <v>0.007103342896403787</v>
+        <v>0.0022025</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1215388351071716</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0.0022025</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>20.34328747236598</v>
+        <v>20.34328662960689</v>
       </c>
     </row>
     <row r="22">
@@ -2404,34 +2274,28 @@
         <v>0.102602067198723</v>
       </c>
       <c r="R22" t="n">
-        <v>0.05491924762933701</v>
+        <v>33.39642857142849</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3203155743930086</v>
+        <v>0.2989185664601128</v>
       </c>
       <c r="T22" t="n">
-        <v>33.39642857142849</v>
+        <v>20.58181943419975</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2989185664601128</v>
+        <v>1.889372388206214</v>
       </c>
       <c r="V22" t="n">
-        <v>20.58182025443793</v>
+        <v>0.007200136199108651</v>
       </c>
       <c r="W22" t="n">
-        <v>1.889372443744669</v>
+        <v>0.1237179095912931</v>
       </c>
       <c r="X22" t="n">
-        <v>0.007200135700517285</v>
+        <v>0.002246666666666667</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.1237179049792681</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0.002246666666666667</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>20.47349764508844</v>
+        <v>20.47349681467529</v>
       </c>
     </row>
     <row r="23">
@@ -2493,33 +2357,27 @@
         <v>0.06320238611045444</v>
       </c>
       <c r="R23" t="n">
-        <v>0.0464330358326207</v>
+        <v>28.42857142857147</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2514008474736202</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>28.42857142857147</v>
+        <v>15.01969296805368</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.792146539303604</v>
       </c>
       <c r="V23" t="n">
-        <v>15.01969296805368</v>
+        <v>0.00924435718584087</v>
       </c>
       <c r="W23" t="n">
-        <v>1.792146539303604</v>
+        <v>0.1221136632356617</v>
       </c>
       <c r="X23" t="n">
-        <v>0.00924435718584087</v>
+        <v>0.001996666666666667</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.1221136632356617</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.001996666666666667</v>
-      </c>
-      <c r="AA23" t="n">
         <v>14.80438687360635</v>
       </c>
     </row>
@@ -2582,33 +2440,27 @@
         <v>0.05093049240086417</v>
       </c>
       <c r="R24" t="n">
-        <v>0.04115887469949947</v>
+        <v>29.31428571428569</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2256778509310654</v>
+        <v>0.05810793948216079</v>
       </c>
       <c r="T24" t="n">
-        <v>29.31428571428569</v>
+        <v>15.15569823705797</v>
       </c>
       <c r="U24" t="n">
-        <v>0.05810793948216079</v>
+        <v>1.794373122636937</v>
       </c>
       <c r="V24" t="n">
-        <v>15.15569823705797</v>
+        <v>0.00940201309158991</v>
       </c>
       <c r="W24" t="n">
-        <v>1.794373122636937</v>
+        <v>0.1251652130959574</v>
       </c>
       <c r="X24" t="n">
-        <v>0.00940201309158991</v>
+        <v>0.002051666666666667</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.1251652130959574</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0.002051666666666667</v>
-      </c>
-      <c r="AA24" t="n">
         <v>15.01969296805368</v>
       </c>
     </row>
@@ -2671,33 +2523,27 @@
         <v>0.03650228328522884</v>
       </c>
       <c r="R25" t="n">
-        <v>0.03434893131725996</v>
+        <v>30.06428571428577</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1910557072825328</v>
+        <v>0.1219400842896329</v>
       </c>
       <c r="T25" t="n">
-        <v>30.06428571428577</v>
+        <v>15.27797991000348</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1219400842896329</v>
+        <v>1.796379761525826</v>
       </c>
       <c r="V25" t="n">
-        <v>15.27797991000348</v>
+        <v>0.009535909472786619</v>
       </c>
       <c r="W25" t="n">
-        <v>1.796379761525826</v>
+        <v>0.1278292021782632</v>
       </c>
       <c r="X25" t="n">
-        <v>0.009535909472786619</v>
+        <v>0.0021</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.1278292021782632</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="AA25" t="n">
         <v>15.15569823705797</v>
       </c>
     </row>
@@ -2760,33 +2606,27 @@
         <v>0.01662203559450923</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02296789446903608</v>
+        <v>30.93809523809523</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1289264735983624</v>
+        <v>0.1703755277559266</v>
       </c>
       <c r="T26" t="n">
-        <v>30.93809523809523</v>
+        <v>15.40717685453495</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1703755277559266</v>
+        <v>1.798504761525826</v>
       </c>
       <c r="V26" t="n">
-        <v>15.40717685453495</v>
+        <v>0.009669568421304507</v>
       </c>
       <c r="W26" t="n">
-        <v>1.798504761525826</v>
+        <v>0.1305624341001924</v>
       </c>
       <c r="X26" t="n">
-        <v>0.009669568421304507</v>
+        <v>0.00215</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.1305624341001924</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0.00215</v>
-      </c>
-      <c r="AA26" t="n">
         <v>15.27797991000348</v>
       </c>
     </row>
@@ -2843,39 +2683,33 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.0001</v>
+        <v>31.5095238095239</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0001</v>
+        <v>0.2036432131066642</v>
       </c>
       <c r="T27" t="n">
-        <v>31.5095238095239</v>
+        <v>15.54576514061194</v>
       </c>
       <c r="U27" t="n">
-        <v>0.2036432131066642</v>
+        <v>1.800789824025826</v>
       </c>
       <c r="V27" t="n">
-        <v>15.54576514061194</v>
+        <v>0.009804949344494194</v>
       </c>
       <c r="W27" t="n">
-        <v>1.800789824025826</v>
+        <v>0.1334118117795324</v>
       </c>
       <c r="X27" t="n">
-        <v>0.009804949344494194</v>
+        <v>0.0022025</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.1334118117795324</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0.0022025</v>
-      </c>
-      <c r="AA27" t="n">
         <v>15.40717685453495</v>
       </c>
     </row>
@@ -2932,39 +2766,33 @@
         <v>0.07036365759109456</v>
       </c>
       <c r="P28" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.0001</v>
+        <v>31.73214285714281</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0001</v>
+        <v>0.2220723133576301</v>
       </c>
       <c r="T28" t="n">
-        <v>31.73214285714281</v>
+        <v>15.66240091965512</v>
       </c>
       <c r="U28" t="n">
-        <v>0.2220723133576301</v>
+        <v>1.802717435136937</v>
       </c>
       <c r="V28" t="n">
-        <v>15.66240091965512</v>
+        <v>0.009912767707050024</v>
       </c>
       <c r="W28" t="n">
-        <v>1.802717435136937</v>
+        <v>0.1357454538912589</v>
       </c>
       <c r="X28" t="n">
-        <v>0.009912767707050024</v>
+        <v>0.002245833333333333</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.1357454538912589</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0.002245833333333333</v>
-      </c>
-      <c r="AA28" t="n">
         <v>15.54576514061194</v>
       </c>
     </row>
@@ -3027,33 +2855,27 @@
         <v>0.07399229663180125</v>
       </c>
       <c r="R29" t="n">
-        <v>0.05414454690340646</v>
+        <v>24.49345238095237</v>
       </c>
       <c r="S29" t="n">
-        <v>0.2720152507338536</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>24.49345238095237</v>
+        <v>23.93968006453909</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.098491720806879</v>
       </c>
       <c r="V29" t="n">
-        <v>23.93968006453909</v>
+        <v>0.01007997637280434</v>
       </c>
       <c r="W29" t="n">
-        <v>2.098491720806879</v>
+        <v>0.194956735239167</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01007997637280434</v>
+        <v>0.004063333333333333</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.194956735239167</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0.004063333333333333</v>
-      </c>
-      <c r="AA29" t="n">
         <v>23.76781203213405</v>
       </c>
     </row>
@@ -3116,33 +2938,27 @@
         <v>0.06485638924285067</v>
       </c>
       <c r="R30" t="n">
-        <v>0.05116644028606399</v>
+        <v>25.23928571428564</v>
       </c>
       <c r="S30" t="n">
-        <v>0.2546691760752578</v>
+        <v>0.06375494686076261</v>
       </c>
       <c r="T30" t="n">
-        <v>25.23928571428564</v>
+        <v>24.22814684652792</v>
       </c>
       <c r="U30" t="n">
-        <v>0.06375494686076261</v>
+        <v>2.104521276362434</v>
       </c>
       <c r="V30" t="n">
-        <v>24.22814684652792</v>
+        <v>0.01063212456913026</v>
       </c>
       <c r="W30" t="n">
-        <v>2.104521276362434</v>
+        <v>0.207517619384608</v>
       </c>
       <c r="X30" t="n">
-        <v>0.01063212456913026</v>
+        <v>0.00435</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.207517619384608</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0.00435</v>
-      </c>
-      <c r="AA30" t="n">
         <v>23.93968006453909</v>
       </c>
     </row>
@@ -3205,33 +3021,27 @@
         <v>0.04872158819598323</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0441207297966015</v>
+        <v>24.77321428571426</v>
       </c>
       <c r="S31" t="n">
-        <v>0.2207296722146418</v>
+        <v>0.1716212668026328</v>
       </c>
       <c r="T31" t="n">
-        <v>24.77321428571426</v>
+        <v>24.54912650345894</v>
       </c>
       <c r="U31" t="n">
-        <v>0.1716212668026328</v>
+        <v>2.111271276362434</v>
       </c>
       <c r="V31" t="n">
-        <v>24.54912650345894</v>
+        <v>0.01118092410442565</v>
       </c>
       <c r="W31" t="n">
-        <v>2.111271276362434</v>
+        <v>0.2204133410545105</v>
       </c>
       <c r="X31" t="n">
-        <v>0.01118092410442565</v>
+        <v>0.00465</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.2204133410545105</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0.00465</v>
-      </c>
-      <c r="AA31" t="n">
         <v>24.22814684652792</v>
       </c>
     </row>
@@ -3294,33 +3104,27 @@
         <v>0.03284030984725474</v>
       </c>
       <c r="R32" t="n">
-        <v>0.03536550708002241</v>
+        <v>25.0285714285714</v>
       </c>
       <c r="S32" t="n">
-        <v>0.1812189555406794</v>
+        <v>0.2547670720457892</v>
       </c>
       <c r="T32" t="n">
-        <v>25.0285714285714</v>
+        <v>25.00680869176568</v>
       </c>
       <c r="U32" t="n">
-        <v>0.2547670720457892</v>
+        <v>2.120971276362434</v>
       </c>
       <c r="V32" t="n">
-        <v>25.00680869176568</v>
+        <v>0.01186587573608902</v>
       </c>
       <c r="W32" t="n">
-        <v>2.120971276362434</v>
+        <v>0.2371868574664508</v>
       </c>
       <c r="X32" t="n">
-        <v>0.01186587573608902</v>
+        <v>0.005050000000000001</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.2371868574664508</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0.005050000000000001</v>
-      </c>
-      <c r="AA32" t="n">
         <v>24.54912650345894</v>
       </c>
     </row>
@@ -3383,33 +3187,27 @@
         <v>0.002777158124534164</v>
       </c>
       <c r="R33" t="n">
-        <v>0.01006757845422143</v>
+        <v>26.25714285714279</v>
       </c>
       <c r="S33" t="n">
-        <v>0.05269874879476897</v>
+        <v>0.3345630000595383</v>
       </c>
       <c r="T33" t="n">
-        <v>26.25714285714279</v>
+        <v>26.11045512932166</v>
       </c>
       <c r="U33" t="n">
-        <v>0.3345630000595383</v>
+        <v>2.144732387473546</v>
       </c>
       <c r="V33" t="n">
-        <v>26.11045512932166</v>
+        <v>0.01316721250280378</v>
       </c>
       <c r="W33" t="n">
-        <v>2.144732387473546</v>
+        <v>0.271771078660095</v>
       </c>
       <c r="X33" t="n">
-        <v>0.01316721250280378</v>
+        <v>0.005916666666666667</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.271771078660095</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0.005916666666666667</v>
-      </c>
-      <c r="AA33" t="n">
         <v>25.00680869176568</v>
       </c>
     </row>
@@ -3466,39 +3264,33 @@
         <v>0.01145255846603085</v>
       </c>
       <c r="P34" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0.0001</v>
+        <v>27.40000000000004</v>
       </c>
       <c r="S34" t="n">
-        <v>0.0001</v>
+        <v>0.4114676331552647</v>
       </c>
       <c r="T34" t="n">
-        <v>27.40000000000004</v>
+        <v>26.57397360426178</v>
       </c>
       <c r="U34" t="n">
-        <v>0.4114676331552647</v>
+        <v>2.154871276362434</v>
       </c>
       <c r="V34" t="n">
-        <v>26.57397360426178</v>
+        <v>0.01360205481603644</v>
       </c>
       <c r="W34" t="n">
-        <v>2.154871276362434</v>
+        <v>0.2843853526340677</v>
       </c>
       <c r="X34" t="n">
-        <v>0.01360205481603644</v>
+        <v>0.00625</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.2843853526340677</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0.00625</v>
-      </c>
-      <c r="AA34" t="n">
         <v>26.11045512932166</v>
       </c>
     </row>
@@ -3561,33 +3353,27 @@
         <v>0.001762949417501451</v>
       </c>
       <c r="R35" t="n">
-        <v>0.007839965084997607</v>
+        <v>28.4607142857143</v>
       </c>
       <c r="S35" t="n">
-        <v>0.04198749120275527</v>
+        <v>0.4067877264015557</v>
       </c>
       <c r="T35" t="n">
-        <v>28.4607142857143</v>
+        <v>27.30784352193885</v>
       </c>
       <c r="U35" t="n">
-        <v>0.4067877264015557</v>
+        <v>2.171121276362435</v>
       </c>
       <c r="V35" t="n">
-        <v>27.30784352193885</v>
+        <v>0.01418840491525607</v>
       </c>
       <c r="W35" t="n">
-        <v>2.171121276362435</v>
+        <v>0.3025548575925655</v>
       </c>
       <c r="X35" t="n">
-        <v>0.01418840491525607</v>
+        <v>0.006750000000000001</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.3025548575925655</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0.006750000000000001</v>
-      </c>
-      <c r="AA35" t="n">
         <v>26.57397360426178</v>
       </c>
     </row>
@@ -3650,33 +3436,27 @@
         <v>0.001647154283060745</v>
       </c>
       <c r="R36" t="n">
-        <v>0.007564472262002585</v>
+        <v>28.6821428571429</v>
       </c>
       <c r="S36" t="n">
-        <v>0.04058514855289733</v>
+        <v>0.4021708299263646</v>
       </c>
       <c r="T36" t="n">
-        <v>28.6821428571429</v>
+        <v>27.82182651078572</v>
       </c>
       <c r="U36" t="n">
-        <v>0.4021708299263646</v>
+        <v>2.182649054140212</v>
       </c>
       <c r="V36" t="n">
-        <v>27.82182651078572</v>
+        <v>0.01453692586273916</v>
       </c>
       <c r="W36" t="n">
-        <v>2.182649054140212</v>
+        <v>0.3141538806580285</v>
       </c>
       <c r="X36" t="n">
-        <v>0.01453692586273916</v>
+        <v>0.007083333333333334</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.3141538806580285</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0.007083333333333334</v>
-      </c>
-      <c r="AA36" t="n">
         <v>27.30784352193885</v>
       </c>
     </row>
@@ -3739,33 +3519,27 @@
         <v>0.0005503013934911842</v>
       </c>
       <c r="R37" t="n">
-        <v>0.004370963058975695</v>
+        <v>28.78571428571429</v>
       </c>
       <c r="S37" t="n">
-        <v>0.02345850364987469</v>
+        <v>0.3873938421634567</v>
       </c>
       <c r="T37" t="n">
-        <v>28.78571428571429</v>
+        <v>28.72212537780479</v>
       </c>
       <c r="U37" t="n">
-        <v>0.3873938421634567</v>
+        <v>2.203139026362434</v>
       </c>
       <c r="V37" t="n">
-        <v>28.72212537780479</v>
+        <v>0.01504659517082482</v>
       </c>
       <c r="W37" t="n">
-        <v>2.203139026362434</v>
+        <v>0.3325682000033916</v>
       </c>
       <c r="X37" t="n">
-        <v>0.01504659517082482</v>
+        <v>0.007640000000000001</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.3325682000033916</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0.007640000000000001</v>
-      </c>
-      <c r="AA37" t="n">
         <v>27.82182651078572</v>
       </c>
     </row>
@@ -3828,33 +3602,27 @@
         <v>0.0004247662125730495</v>
       </c>
       <c r="R38" t="n">
-        <v>0.003775433716909023</v>
+        <v>28.80357142857139</v>
       </c>
       <c r="S38" t="n">
-        <v>0.02060985717012735</v>
+        <v>0.3689307159607038</v>
       </c>
       <c r="T38" t="n">
-        <v>28.80357142857139</v>
+        <v>29.76547634687633</v>
       </c>
       <c r="U38" t="n">
-        <v>0.3689307159607038</v>
+        <v>2.227371276362434</v>
       </c>
       <c r="V38" t="n">
-        <v>29.76547634687633</v>
+        <v>0.01550781476267443</v>
       </c>
       <c r="W38" t="n">
-        <v>2.227371276362434</v>
+        <v>0.3513486174167029</v>
       </c>
       <c r="X38" t="n">
-        <v>0.01550781476267443</v>
+        <v>0.00825</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.3513486174167029</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0.00825</v>
-      </c>
-      <c r="AA38" t="n">
         <v>28.72212537780479</v>
       </c>
     </row>
@@ -3917,33 +3685,27 @@
         <v>0.008954679612111731</v>
       </c>
       <c r="R39" t="n">
-        <v>0.01696173781741488</v>
+        <v>29.79999999999999</v>
       </c>
       <c r="S39" t="n">
-        <v>0.09462916892856943</v>
+        <v>0.3542503465167628</v>
       </c>
       <c r="T39" t="n">
-        <v>29.79999999999999</v>
+        <v>30.84541902494425</v>
       </c>
       <c r="U39" t="n">
-        <v>0.3542503465167628</v>
+        <v>2.253021276362434</v>
       </c>
       <c r="V39" t="n">
-        <v>30.84541902494425</v>
+        <v>0.01587053886464064</v>
       </c>
       <c r="W39" t="n">
-        <v>2.253021276362434</v>
+        <v>0.3683708024918843</v>
       </c>
       <c r="X39" t="n">
-        <v>0.01587053886464064</v>
+        <v>0.00885</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.3683708024918843</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0.00885</v>
-      </c>
-      <c r="AA39" t="n">
         <v>29.76547634687633</v>
       </c>
     </row>
@@ -4006,33 +3768,27 @@
         <v>0.02192219084074996</v>
       </c>
       <c r="R40" t="n">
-        <v>0.02664331523520602</v>
+        <v>31.12500000000002</v>
       </c>
       <c r="S40" t="n">
-        <v>0.148061442788965</v>
+        <v>0.363160750555521</v>
       </c>
       <c r="T40" t="n">
-        <v>31.12500000000002</v>
+        <v>31.8146960202547</v>
       </c>
       <c r="U40" t="n">
-        <v>0.363160750555521</v>
+        <v>2.276551137473545</v>
       </c>
       <c r="V40" t="n">
-        <v>31.8146960202547</v>
+        <v>0.01611696618632926</v>
       </c>
       <c r="W40" t="n">
-        <v>2.276551137473545</v>
+        <v>0.3818576499658321</v>
       </c>
       <c r="X40" t="n">
-        <v>0.01611696618632926</v>
+        <v>0.009366666666666667</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.3818576499658321</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0.009366666666666667</v>
-      </c>
-      <c r="AA40" t="n">
         <v>30.84541902494425</v>
       </c>
     </row>
@@ -4095,33 +3851,27 @@
         <v>0.04292053230848831</v>
       </c>
       <c r="R41" t="n">
-        <v>0.03929002064237096</v>
+        <v>25.66428571428573</v>
       </c>
       <c r="S41" t="n">
-        <v>0.2071727113026431</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>25.66428571428573</v>
+        <v>28.24180554491312</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.198068908667902</v>
       </c>
       <c r="V41" t="n">
-        <v>28.24180554491312</v>
+        <v>0.007068164159168635</v>
       </c>
       <c r="W41" t="n">
-        <v>2.198068908667902</v>
+        <v>0.1089932301946586</v>
       </c>
       <c r="X41" t="n">
-        <v>0.007068164159168635</v>
+        <v>0.007053333333333333</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.1089932301946586</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0.007053333333333333</v>
-      </c>
-      <c r="AA41" t="n">
         <v>24.01327122841171</v>
       </c>
     </row>
@@ -4184,33 +3934,27 @@
         <v>0.03670292593065684</v>
       </c>
       <c r="R42" t="n">
-        <v>0.03606976413308337</v>
+        <v>27.80357142857142</v>
       </c>
       <c r="S42" t="n">
-        <v>0.1915800770713303</v>
+        <v>0.05060060245371522</v>
       </c>
       <c r="T42" t="n">
-        <v>27.80357142857142</v>
+        <v>28.47191433675219</v>
       </c>
       <c r="U42" t="n">
-        <v>0.05060060245371522</v>
+        <v>2.203329247622887</v>
       </c>
       <c r="V42" t="n">
-        <v>28.47191433675219</v>
+        <v>0.007575498547917375</v>
       </c>
       <c r="W42" t="n">
-        <v>2.203329247622887</v>
+        <v>0.1171354497979989</v>
       </c>
       <c r="X42" t="n">
-        <v>0.007575498547917375</v>
+        <v>0.007626666666666667</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.1171354497979989</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0.007626666666666667</v>
-      </c>
-      <c r="AA42" t="n">
         <v>28.24180554491312</v>
       </c>
     </row>
@@ -4273,33 +4017,27 @@
         <v>0.03226430616673658</v>
       </c>
       <c r="R43" t="n">
-        <v>0.03344169305227099</v>
+        <v>28.21071428571433</v>
       </c>
       <c r="S43" t="n">
-        <v>0.1796226772062386</v>
+        <v>0.1044036282464569</v>
       </c>
       <c r="T43" t="n">
-        <v>28.21071428571433</v>
+        <v>28.65988059431129</v>
       </c>
       <c r="U43" t="n">
-        <v>0.1044036282464569</v>
+        <v>2.20764491860522</v>
       </c>
       <c r="V43" t="n">
-        <v>28.65988059431129</v>
+        <v>0.007944458816790421</v>
       </c>
       <c r="W43" t="n">
-        <v>2.20764491860522</v>
+        <v>0.1229649184265571</v>
       </c>
       <c r="X43" t="n">
-        <v>0.007944458816790421</v>
+        <v>0.008066666666666666</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.1229649184265571</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0.008066666666666666</v>
-      </c>
-      <c r="AA43" t="n">
         <v>28.47191433675219</v>
       </c>
     </row>
@@ -4362,33 +4100,27 @@
         <v>0.02491516024776152</v>
       </c>
       <c r="R44" t="n">
-        <v>0.02890464370079389</v>
+        <v>28.84999999999995</v>
       </c>
       <c r="S44" t="n">
-        <v>0.1578453681542842</v>
+        <v>0.1491197853115378</v>
       </c>
       <c r="T44" t="n">
-        <v>28.84999999999995</v>
+        <v>28.92563808749308</v>
       </c>
       <c r="U44" t="n">
-        <v>0.1491197853115378</v>
+        <v>2.213775591402554</v>
       </c>
       <c r="V44" t="n">
-        <v>28.92563808749308</v>
+        <v>0.008420554709994834</v>
       </c>
       <c r="W44" t="n">
-        <v>2.213775591402554</v>
+        <v>0.1305037205317169</v>
       </c>
       <c r="X44" t="n">
-        <v>0.008420554709994834</v>
+        <v>0.008653333333333332</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.1305037205317169</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0.008653333333333332</v>
-      </c>
-      <c r="AA44" t="n">
         <v>28.65988059431129</v>
       </c>
     </row>
@@ -4451,33 +4183,27 @@
         <v>0.01583178431944987</v>
       </c>
       <c r="R45" t="n">
-        <v>0.02290151451210537</v>
+        <v>29.8214285714287</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1258244186135977</v>
+        <v>0.1918414613393818</v>
       </c>
       <c r="T45" t="n">
-        <v>29.8214285714287</v>
+        <v>29.46262840771122</v>
       </c>
       <c r="U45" t="n">
-        <v>0.1918414613393818</v>
+        <v>2.226267742783581</v>
       </c>
       <c r="V45" t="n">
-        <v>29.46262840771122</v>
+        <v>0.009253028396770656</v>
       </c>
       <c r="W45" t="n">
-        <v>2.226267742783581</v>
+        <v>0.1437184974817057</v>
       </c>
       <c r="X45" t="n">
-        <v>0.009253028396770656</v>
+        <v>0.009740000000000002</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.1437184974817057</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0.009740000000000002</v>
-      </c>
-      <c r="AA45" t="n">
         <v>28.92563808749308</v>
       </c>
     </row>
@@ -4540,33 +4266,27 @@
         <v>0.003813578138281135</v>
       </c>
       <c r="R46" t="n">
-        <v>0.01083418489561089</v>
+        <v>30.18571428571434</v>
       </c>
       <c r="S46" t="n">
-        <v>0.0617541750676109</v>
+        <v>0.2448076315621145</v>
       </c>
       <c r="T46" t="n">
-        <v>30.18571428571434</v>
+        <v>30.73245500743434</v>
       </c>
       <c r="U46" t="n">
-        <v>0.2448076315621145</v>
+        <v>2.256376522892332</v>
       </c>
       <c r="V46" t="n">
-        <v>30.73245500743434</v>
+        <v>0.01074724495172402</v>
       </c>
       <c r="W46" t="n">
-        <v>2.256376522892332</v>
+        <v>0.1673908057509535</v>
       </c>
       <c r="X46" t="n">
-        <v>0.01074724495172402</v>
+        <v>0.01196</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.1673908057509535</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0.01196</v>
-      </c>
-      <c r="AA46" t="n">
         <v>29.46262840771122</v>
       </c>
     </row>
@@ -4629,33 +4349,27 @@
         <v>0.002635143243149769</v>
       </c>
       <c r="R47" t="n">
-        <v>0.008945242501938901</v>
+        <v>32.48928571428564</v>
       </c>
       <c r="S47" t="n">
-        <v>0.05133364630678176</v>
+        <v>0.2862295508009267</v>
       </c>
       <c r="T47" t="n">
-        <v>32.48928571428564</v>
+        <v>31.15248101756942</v>
       </c>
       <c r="U47" t="n">
-        <v>0.2862295508009267</v>
+        <v>2.266515783031581</v>
       </c>
       <c r="V47" t="n">
-        <v>31.15248101756942</v>
+        <v>0.0111372695428132</v>
       </c>
       <c r="W47" t="n">
-        <v>2.266515783031581</v>
+        <v>0.1734960122774931</v>
       </c>
       <c r="X47" t="n">
-        <v>0.0111372695428132</v>
+        <v>0.01262</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.1734960122774931</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0.01262</v>
-      </c>
-      <c r="AA47" t="n">
         <v>30.73245500743434</v>
       </c>
     </row>
@@ -4718,33 +4432,27 @@
         <v>0.003468413842637606</v>
       </c>
       <c r="R48" t="n">
-        <v>0.01023902645998351</v>
+        <v>32.9321428571429</v>
       </c>
       <c r="S48" t="n">
-        <v>0.05889324106073299</v>
+        <v>0.2889524121591054</v>
       </c>
       <c r="T48" t="n">
-        <v>32.9321428571429</v>
+        <v>31.55039956771036</v>
       </c>
       <c r="U48" t="n">
-        <v>0.2889524121591054</v>
+        <v>2.276205792721581</v>
       </c>
       <c r="V48" t="n">
-        <v>31.55039956771036</v>
+        <v>0.01147072886081365</v>
       </c>
       <c r="W48" t="n">
-        <v>2.276205792721581</v>
+        <v>0.1786641753611795</v>
       </c>
       <c r="X48" t="n">
-        <v>0.01147072886081365</v>
+        <v>0.01322</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.1786641753611795</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0.01322</v>
-      </c>
-      <c r="AA48" t="n">
         <v>31.15248101756942</v>
       </c>
     </row>
@@ -4807,33 +4515,27 @@
         <v>0.004427144891717553</v>
       </c>
       <c r="R49" t="n">
-        <v>0.01153270065092904</v>
+        <v>33.08366238246173</v>
       </c>
       <c r="S49" t="n">
-        <v>0.06653679351845529</v>
+        <v>0.2916972101212668</v>
       </c>
       <c r="T49" t="n">
-        <v>33.08366238246173</v>
+        <v>31.95385437249574</v>
       </c>
       <c r="U49" t="n">
-        <v>0.2916972101212668</v>
+        <v>2.286115580409136</v>
       </c>
       <c r="V49" t="n">
-        <v>31.95385437249574</v>
+        <v>0.01177719446570448</v>
       </c>
       <c r="W49" t="n">
-        <v>2.286115580409136</v>
+        <v>0.1833460432925698</v>
       </c>
       <c r="X49" t="n">
-        <v>0.01177719446570448</v>
+        <v>0.01380666666666667</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.1833460432925698</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0.01380666666666667</v>
-      </c>
-      <c r="AA49" t="n">
         <v>31.55039956771036</v>
       </c>
     </row>
@@ -4896,33 +4598,27 @@
         <v>0.006989072490978496</v>
       </c>
       <c r="R50" t="n">
-        <v>0.01414625769441237</v>
+        <v>33.286006759061</v>
       </c>
       <c r="S50" t="n">
-        <v>0.08360067279022637</v>
+        <v>0.2947411967231239</v>
       </c>
       <c r="T50" t="n">
-        <v>33.286006759061</v>
+        <v>32.83159423889894</v>
       </c>
       <c r="U50" t="n">
-        <v>0.2947411967231239</v>
+        <v>2.307975824491581</v>
       </c>
       <c r="V50" t="n">
-        <v>32.83159423889894</v>
+        <v>0.01235149451992449</v>
       </c>
       <c r="W50" t="n">
-        <v>2.307975824491581</v>
+        <v>0.1918556034210608</v>
       </c>
       <c r="X50" t="n">
-        <v>0.01235149451992449</v>
+        <v>0.01502</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.1918556034210608</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0.01502</v>
-      </c>
-      <c r="AA50" t="n">
         <v>31.95385437249574</v>
       </c>
     </row>
@@ -4985,33 +4681,27 @@
         <v>0.01216839656025612</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01855989829652208</v>
+        <v>34.92500000000002</v>
       </c>
       <c r="S51" t="n">
-        <v>0.1103104553533169</v>
+        <v>0.3061500936386944</v>
       </c>
       <c r="T51" t="n">
-        <v>34.92500000000002</v>
+        <v>33.75408893078473</v>
       </c>
       <c r="U51" t="n">
-        <v>0.3061500936386944</v>
+        <v>2.331405847921581</v>
       </c>
       <c r="V51" t="n">
-        <v>33.75408893078473</v>
+        <v>0.01284345245977919</v>
       </c>
       <c r="W51" t="n">
-        <v>2.331405847921581</v>
+        <v>0.1986859108423037</v>
       </c>
       <c r="X51" t="n">
-        <v>0.01284345245977919</v>
+        <v>0.01622</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.1986859108423037</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0.01622</v>
-      </c>
-      <c r="AA51" t="n">
         <v>32.83159423889894</v>
       </c>
     </row>
@@ -5074,33 +4764,27 @@
         <v>0.01961652719811411</v>
       </c>
       <c r="R52" t="n">
-        <v>0.02311497993131076</v>
+        <v>35.32500000000002</v>
       </c>
       <c r="S52" t="n">
-        <v>0.1400590132698146</v>
+        <v>0.3308651428571041</v>
       </c>
       <c r="T52" t="n">
-        <v>35.32500000000002</v>
+        <v>34.6164789037036</v>
       </c>
       <c r="U52" t="n">
-        <v>0.3308651428571041</v>
+        <v>2.353743648037137</v>
       </c>
       <c r="V52" t="n">
-        <v>34.6164789037036</v>
+        <v>0.01322031243075041</v>
       </c>
       <c r="W52" t="n">
-        <v>2.353743648037137</v>
+        <v>0.2034058721493541</v>
       </c>
       <c r="X52" t="n">
-        <v>0.01322031243075041</v>
+        <v>0.01728666666666667</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.2034058721493541</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0.01728666666666667</v>
-      </c>
-      <c r="AA52" t="n">
         <v>33.75408893078473</v>
       </c>
     </row>
@@ -5163,33 +4847,27 @@
         <v>0.02963924799363945</v>
       </c>
       <c r="R53" t="n">
-        <v>0.0284767157115998</v>
+        <v>36.71428571428564</v>
       </c>
       <c r="S53" t="n">
-        <v>0.1721605297204892</v>
+        <v>0.3724108962071924</v>
       </c>
       <c r="T53" t="n">
-        <v>36.71428571428564</v>
+        <v>35.52745806381636</v>
       </c>
       <c r="U53" t="n">
-        <v>0.3724108962071924</v>
+        <v>2.377809672103136</v>
       </c>
       <c r="V53" t="n">
-        <v>35.52745806381636</v>
+        <v>0.01354761894834775</v>
       </c>
       <c r="W53" t="n">
-        <v>2.377809672103136</v>
+        <v>0.2068914338797341</v>
       </c>
       <c r="X53" t="n">
-        <v>0.01354761894834775</v>
+        <v>0.01836666666666667</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.2068914338797341</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0.01836666666666667</v>
-      </c>
-      <c r="AA53" t="n">
         <v>34.6164789037036</v>
       </c>
     </row>
@@ -5246,39 +4924,33 @@
         <v>0.04417757490269928</v>
       </c>
       <c r="P54" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0.0001</v>
+        <v>21.79285714285717</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>21.79285714285717</v>
+        <v>28.31816032897402</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>2.196892860793617</v>
       </c>
       <c r="V54" t="n">
-        <v>28.31816032897402</v>
+        <v>0.01041304424064643</v>
       </c>
       <c r="W54" t="n">
-        <v>2.196892860793617</v>
+        <v>0.2042179130067702</v>
       </c>
       <c r="X54" t="n">
-        <v>0.01041304424064643</v>
+        <v>0.007033333333333333</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.2042179130067702</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0.007033333333333333</v>
-      </c>
-      <c r="AA54" t="n">
         <v>25.42114792085842</v>
       </c>
     </row>
@@ -5335,39 +5007,33 @@
         <v>0.02615548495855645</v>
       </c>
       <c r="P55" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.0001</v>
+        <v>22.74159954433088</v>
       </c>
       <c r="S55" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>22.74159954433088</v>
+        <v>28.49544748119097</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>2.200944508712678</v>
       </c>
       <c r="V55" t="n">
-        <v>28.49544748119097</v>
+        <v>0.01098357822667265</v>
       </c>
       <c r="W55" t="n">
-        <v>2.200944508712678</v>
+        <v>0.216139031898086</v>
       </c>
       <c r="X55" t="n">
-        <v>0.01098357822667265</v>
+        <v>0.007480000000000001</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.216139031898086</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0.007480000000000001</v>
-      </c>
-      <c r="AA55" t="n">
         <v>28.31816032897402</v>
       </c>
     </row>
@@ -5424,39 +5090,33 @@
         <v>0.02647932083128075</v>
       </c>
       <c r="P56" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0.0001</v>
+        <v>22.97108767528296</v>
       </c>
       <c r="S56" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>22.97108767528296</v>
+        <v>28.74377861466887</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>2.206644958857567</v>
       </c>
       <c r="V56" t="n">
-        <v>28.74377861466887</v>
+        <v>0.01171774454065133</v>
       </c>
       <c r="W56" t="n">
-        <v>2.206644958857567</v>
+        <v>0.2317357767803047</v>
       </c>
       <c r="X56" t="n">
-        <v>0.01171774454065133</v>
+        <v>0.008066666666666666</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.2317357767803047</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0.008066666666666666</v>
-      </c>
-      <c r="AA56" t="n">
         <v>28.49544748119097</v>
       </c>
     </row>
@@ -5513,39 +5173,33 @@
         <v>0.02163341820285943</v>
       </c>
       <c r="P57" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>0.0001</v>
+        <v>24.12500000000008</v>
       </c>
       <c r="S57" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>24.12500000000008</v>
+        <v>28.95677039510294</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>2.211557769325928</v>
       </c>
       <c r="V57" t="n">
-        <v>28.95677039510294</v>
+        <v>0.01228110398018093</v>
       </c>
       <c r="W57" t="n">
-        <v>2.211557769325928</v>
+        <v>0.2438036270068062</v>
       </c>
       <c r="X57" t="n">
-        <v>0.01228110398018093</v>
+        <v>0.008539999999999999</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.2438036270068062</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0.008539999999999999</v>
-      </c>
-      <c r="AA57" t="n">
         <v>28.74377861466887</v>
       </c>
     </row>
@@ -5602,39 +5256,33 @@
         <v>0.01944191146369945</v>
       </c>
       <c r="P58" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.0001</v>
+        <v>24.57500000000017</v>
       </c>
       <c r="S58" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>24.57500000000017</v>
+        <v>29.2361683854742</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>2.218035553581483</v>
       </c>
       <c r="V58" t="n">
-        <v>29.2361683854742</v>
+        <v>0.01296734667627982</v>
       </c>
       <c r="W58" t="n">
-        <v>2.218035553581483</v>
+        <v>0.2588159428505661</v>
       </c>
       <c r="X58" t="n">
-        <v>0.01296734667627982</v>
+        <v>0.009126666666666668</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.2588159428505661</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>0.009126666666666668</v>
-      </c>
-      <c r="AA58" t="n">
         <v>28.95677039510294</v>
       </c>
     </row>
@@ -5691,39 +5339,33 @@
         <v>0.01658310436687791</v>
       </c>
       <c r="P59" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0.0001</v>
+        <v>25.06785714285721</v>
       </c>
       <c r="S59" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>25.06785714285721</v>
+        <v>29.78688518662393</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>2.230915566461483</v>
       </c>
       <c r="V59" t="n">
-        <v>29.78688518662393</v>
+        <v>0.01413308769286362</v>
       </c>
       <c r="W59" t="n">
-        <v>2.230915566461483</v>
+        <v>0.2848806420287301</v>
       </c>
       <c r="X59" t="n">
-        <v>0.01413308769286362</v>
+        <v>0.01019333333333333</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.2848806420287301</v>
-      </c>
-      <c r="Z59" t="n">
-        <v>0.01019333333333333</v>
-      </c>
-      <c r="AA59" t="n">
         <v>29.2361683854742</v>
       </c>
     </row>
@@ -5780,39 +5422,33 @@
         <v>0.01821926693166444</v>
       </c>
       <c r="P60" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0.0001</v>
+        <v>25.90000000000013</v>
       </c>
       <c r="S60" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>25.90000000000013</v>
+        <v>31.11037508564176</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>2.262489348035233</v>
       </c>
       <c r="V60" t="n">
-        <v>31.11037508564176</v>
+        <v>0.01625131044668814</v>
       </c>
       <c r="W60" t="n">
-        <v>2.262489348035233</v>
+        <v>0.3347113995646889</v>
       </c>
       <c r="X60" t="n">
-        <v>0.01625131044668814</v>
+        <v>0.01242666666666667</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.3347113995646889</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>0.01242666666666667</v>
-      </c>
-      <c r="AA60" t="n">
         <v>29.78688518662393</v>
       </c>
     </row>
@@ -5869,39 +5505,33 @@
         <v>0.01480594697664882</v>
       </c>
       <c r="P61" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0.0001</v>
+        <v>27.37499999999996</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>27.37499999999996</v>
+        <v>31.5210476313021</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>2.272469024681567</v>
       </c>
       <c r="V61" t="n">
-        <v>31.5210476313021</v>
+        <v>0.01679001717135276</v>
       </c>
       <c r="W61" t="n">
-        <v>2.272469024681567</v>
+        <v>0.3481782708526754</v>
       </c>
       <c r="X61" t="n">
-        <v>0.01679001717135276</v>
+        <v>0.01305333333333333</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.3481782708526754</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0.01305333333333333</v>
-      </c>
-      <c r="AA61" t="n">
         <v>31.11037508564176</v>
       </c>
     </row>
@@ -5958,39 +5588,33 @@
         <v>0.01899552184075797</v>
       </c>
       <c r="P62" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.0001</v>
+        <v>28.11428571428576</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>28.11428571428576</v>
+        <v>31.94343405366691</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>2.282825618371483</v>
       </c>
       <c r="V62" t="n">
-        <v>31.94343405366691</v>
+        <v>0.01726817068693205</v>
       </c>
       <c r="W62" t="n">
-        <v>2.282825618371483</v>
+        <v>0.3602745856788814</v>
       </c>
       <c r="X62" t="n">
-        <v>0.01726817068693205</v>
+        <v>0.01367333333333333</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.3602745856788814</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>0.01367333333333333</v>
-      </c>
-      <c r="AA62" t="n">
         <v>31.5210476313021</v>
       </c>
     </row>
@@ -6047,39 +5671,33 @@
         <v>0.02233579751349438</v>
       </c>
       <c r="P63" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>0.0001</v>
+        <v>28.14285714285706</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>28.14285714285706</v>
+        <v>32.35740390067283</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>2.293067850835928</v>
       </c>
       <c r="V63" t="n">
-        <v>32.35740390067283</v>
+        <v>0.01769926548522211</v>
       </c>
       <c r="W63" t="n">
-        <v>2.293067850835928</v>
+        <v>0.3714798980485495</v>
       </c>
       <c r="X63" t="n">
-        <v>0.01769926548522211</v>
+        <v>0.01426</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.3714798980485495</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>0.01426</v>
-      </c>
-      <c r="AA63" t="n">
         <v>31.94343405366691</v>
       </c>
     </row>
@@ -6136,39 +5754,33 @@
         <v>0.01014663618242141</v>
       </c>
       <c r="P64" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.0001</v>
+        <v>29.46071428571427</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>29.46071428571427</v>
+        <v>33.25583448054279</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>2.315615651161483</v>
       </c>
       <c r="V64" t="n">
-        <v>33.25583448054279</v>
+        <v>0.01851307209935324</v>
       </c>
       <c r="W64" t="n">
-        <v>2.315615651161483</v>
+        <v>0.3934465808882616</v>
       </c>
       <c r="X64" t="n">
-        <v>0.01851307209935324</v>
+        <v>0.01547333333333333</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.3934465808882616</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>0.01547333333333333</v>
-      </c>
-      <c r="AA64" t="n">
         <v>32.35740390067283</v>
       </c>
     </row>
@@ -6225,39 +5837,33 @@
         <v>0.00902987934884078</v>
       </c>
       <c r="P65" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>0.0001</v>
+        <v>30.54107142857147</v>
       </c>
       <c r="S65" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>30.54107142857147</v>
+        <v>34.19735536914632</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>2.339725675271483</v>
       </c>
       <c r="V65" t="n">
-        <v>34.19735536914632</v>
+        <v>0.01919069898130528</v>
       </c>
       <c r="W65" t="n">
-        <v>2.339725675271483</v>
+        <v>0.4125742480274263</v>
       </c>
       <c r="X65" t="n">
-        <v>0.01919069898130528</v>
+        <v>0.01667333333333334</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.4125742480274263</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>0.01667333333333334</v>
-      </c>
-      <c r="AA65" t="n">
         <v>33.25583448054279</v>
       </c>
     </row>
@@ -6314,39 +5920,33 @@
         <v>0.01371968923896166</v>
       </c>
       <c r="P66" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0.0001</v>
+        <v>30.00357142857132</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>30.00357142857132</v>
+        <v>34.69219417667006</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>2.352599660367677</v>
       </c>
       <c r="V66" t="n">
-        <v>34.69219417667006</v>
+        <v>0.01948898852875239</v>
       </c>
       <c r="W66" t="n">
-        <v>2.352599660367677</v>
+        <v>0.4212993151451641</v>
       </c>
       <c r="X66" t="n">
-        <v>0.01948898852875239</v>
+        <v>0.01728</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.4212993151451641</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0.01728</v>
-      </c>
-      <c r="AA66" t="n">
         <v>34.19735536914632</v>
       </c>
     </row>
@@ -6403,39 +6003,33 @@
         <v>0.0224321685275548</v>
       </c>
       <c r="P67" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>1e-08</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>0.0001</v>
+        <v>30.12857142857151</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>30.12857142857151</v>
+        <v>35.04183767661643</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>2.361781919549927</v>
       </c>
       <c r="V67" t="n">
-        <v>35.04183767661643</v>
+        <v>0.01970497329658792</v>
       </c>
       <c r="W67" t="n">
-        <v>2.361781919549927</v>
+        <v>0.4278829811081218</v>
       </c>
       <c r="X67" t="n">
-        <v>0.01970497329658792</v>
+        <v>0.0177</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.4278829811081218</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>0.0177</v>
-      </c>
-      <c r="AA67" t="n">
         <v>34.69219417667006</v>
       </c>
     </row>

--- a/data/processed/BR_processed_ind.xlsx
+++ b/data/processed/BR_processed_ind.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y67"/>
+  <dimension ref="A1:AB69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,57 +501,72 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Xlag1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Plag1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>X_calc</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>V_calc</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mu_calc</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dXdt_calc</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dVdt_calc</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>FS_calc</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Xlag1_calc</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>mu</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>qP</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>rP</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Xlag1</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Plag1</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>X_calc</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>V_calc</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>mu_calc</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dXdt_calc</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dVdt_calc</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Xlag1_calc</t>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>qP_calc</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>rP_calc</t>
         </is>
       </c>
     </row>
@@ -605,37 +620,46 @@
         </is>
       </c>
       <c r="O2" t="n">
+        <v>19.55000000000009</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>26.65401311151907</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.848679151198421</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.225235414492541</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5.970266593250297</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="W2" t="n">
+        <v>23.31328393927748</v>
+      </c>
+      <c r="X2" t="n">
         <v>0.1678276210381796</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Y2" t="n">
         <v>0.001409663588305178</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Z2" t="n">
         <v>0.03252295278732637</v>
       </c>
-      <c r="R2" t="n">
-        <v>19.55000000000009</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>26.65401336848298</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.848679229473595</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.2252279510788963</v>
-      </c>
-      <c r="W2" t="n">
-        <v>5.970067722284991</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>23.31328394075086</v>
+      <c r="AA2" t="n">
+        <v>0.001220189719696315</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.03252295278732637</v>
       </c>
     </row>
     <row r="3">
@@ -688,37 +712,46 @@
         </is>
       </c>
       <c r="O3" t="n">
+        <v>23.07142857142841</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>26.81456003797826</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.851713165092423</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.006094311842885767</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.1282517247191745</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.002428333333333334</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.002428333333333334</v>
+      </c>
+      <c r="W3" t="n">
+        <v>26.65401311151907</v>
+      </c>
+      <c r="X3" t="n">
         <v>0.02650201917316335</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Y3" t="n">
         <v>0.004441501609194717</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Z3" t="n">
         <v>0.1065167260919373</v>
       </c>
-      <c r="R3" t="n">
-        <v>23.07142857142841</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>26.81456869324099</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.851713413179842</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.006093564436306846</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.1282317294427486</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.002428333333333334</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>26.65401336848298</v>
+      <c r="AA3" t="n">
+        <v>0.004012411300951165</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.1075910437264175</v>
       </c>
     </row>
     <row r="4">
@@ -771,37 +804,46 @@
         </is>
       </c>
       <c r="O4" t="n">
+        <v>23.9821428571428</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1310102834270957</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>27.04656525722977</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.856115873425756</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.006462731911821826</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1368599863515561</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.002603333333333333</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.002603333333333333</v>
+      </c>
+      <c r="W4" t="n">
+        <v>26.81456003797826</v>
+      </c>
+      <c r="X4" t="n">
         <v>5.19473822208176e-05</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Y4" t="n">
         <v>0.003429009357781865</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Z4" t="n">
         <v>0.08474551698518029</v>
       </c>
-      <c r="R4" t="n">
-        <v>23.9821428571428</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.1310102834270957</v>
-      </c>
-      <c r="T4" t="n">
-        <v>27.04657382863489</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.856116121454714</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.006462750056087044</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.1368605255335975</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.002603333333333333</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>26.81456869324099</v>
+      <c r="AA4" t="n">
+        <v>0.003294261940258428</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.08909847054160794</v>
       </c>
     </row>
     <row r="5">
@@ -854,37 +896,46 @@
         </is>
       </c>
       <c r="O5" t="n">
+        <v>24.71428571428569</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.3150449672599142</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>27.34710021724289</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.861850276203534</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.006890081998479314</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.1470766749719362</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.002815</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.002815</v>
+      </c>
+      <c r="W5" t="n">
+        <v>27.04656525722977</v>
+      </c>
+      <c r="X5" t="n">
         <v>0.009247963860255975</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Y5" t="n">
         <v>0.00255434852123139</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Z5" t="n">
         <v>0.06448817748780201</v>
       </c>
-      <c r="R5" t="n">
-        <v>24.71428571428569</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.3150449672599142</v>
-      </c>
-      <c r="T5" t="n">
-        <v>27.34710868323887</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.861850524232492</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.006890040482292315</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.1470755906637241</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.002815</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>27.04657382863489</v>
+      <c r="AA5" t="n">
+        <v>0.002529907594138891</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.06918563651728009</v>
       </c>
     </row>
     <row r="6">
@@ -937,37 +988,46 @@
         </is>
       </c>
       <c r="O6" t="n">
+        <v>25.24642857142839</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.462353720667521</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>27.65075345784634</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.867680276203534</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.007275831136120344</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1565455464147945</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.003015</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.003015</v>
+      </c>
+      <c r="W6" t="n">
+        <v>27.34710021724289</v>
+      </c>
+      <c r="X6" t="n">
         <v>0.00709381743588283</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Y6" t="n">
         <v>0.004181638843259673</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Z6" t="n">
         <v>0.112121445976553</v>
       </c>
-      <c r="R6" t="n">
-        <v>25.24642857142839</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.462353720667521</v>
-      </c>
-      <c r="T6" t="n">
-        <v>27.65076181827065</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.867680524232492</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.007275870207412934</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.1565466800263603</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.003015</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>27.34710868323887</v>
+      <c r="AA6" t="n">
+        <v>0.004332845827375171</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1198064517436091</v>
       </c>
     </row>
     <row r="7">
@@ -1020,37 +1080,46 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>26.8128</v>
       </c>
       <c r="P7" t="n">
+        <v>0.6209461221159972</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>27.96486690504897</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.873749651203534</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.007634549004260692</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1655913471976849</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.003210000000000001</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.003210000000000001</v>
+      </c>
+      <c r="W7" t="n">
+        <v>27.65075345784634</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0081223021414259</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Z7" t="n">
         <v>0.2218548813486614</v>
       </c>
-      <c r="R7" t="n">
-        <v>26.8128</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.6209461221159972</v>
-      </c>
-      <c r="T7" t="n">
-        <v>27.96487515706328</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.873749899232492</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.007634523293687587</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.1655906834098245</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.003210000000000001</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>27.65076181827065</v>
+      <c r="AA7" t="n">
+        <v>0.008700430054214071</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.2433063684827845</v>
       </c>
     </row>
     <row r="8">
@@ -1103,37 +1172,46 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>27.31428571428567</v>
       </c>
       <c r="P8" t="n">
+        <v>0.9523209449429346</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>28.1412593939992</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.877175276203534</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.007820572933980103</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.170384679723405</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.003315</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.003315</v>
+      </c>
+      <c r="W8" t="n">
+        <v>27.96486690504897</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>0.01172475127120083</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Z8" t="n">
         <v>0.3242312467603854</v>
       </c>
-      <c r="R8" t="n">
-        <v>27.31428571428567</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.9523209449429346</v>
-      </c>
-      <c r="T8" t="n">
-        <v>28.14126758547796</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.877175524232492</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.007820569623933762</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.1703846427370974</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.003315</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>27.96487515706328</v>
+      <c r="AA8" t="n">
+        <v>0.01278089828636537</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.3596705739649278</v>
       </c>
     </row>
     <row r="9">
@@ -1186,37 +1264,46 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>27.65357142857139</v>
       </c>
       <c r="P9" t="n">
+        <v>1.25504016023201</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>28.31682006871782</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.880597206759089</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.007995870233005839</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.1749716551927246</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.003416666666666667</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.003416666666666667</v>
+      </c>
+      <c r="W9" t="n">
+        <v>28.1412593939992</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
         <v>0.01728682448100467</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Z9" t="n">
         <v>0.4847102107155994</v>
       </c>
-      <c r="R9" t="n">
-        <v>27.65357142857139</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.25504016023201</v>
-      </c>
-      <c r="T9" t="n">
-        <v>28.31682820030403</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.880597454788048</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.007995866882157202</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.1749716173380987</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.003416666666666667</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>28.14126758547796</v>
+      <c r="AA9" t="n">
+        <v>0.01902416488705139</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.5387038540642539</v>
       </c>
     </row>
     <row r="10">
@@ -1269,37 +1356,46 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>28.03928571428575</v>
       </c>
       <c r="P10" t="n">
+        <v>1.69587337268752</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>28.48804706810432</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.88394670675909</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.00815814576399599</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1792828694602287</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.003513333333333334</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.003513333333333334</v>
+      </c>
+      <c r="W10" t="n">
+        <v>28.31682006871782</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
         <v>0.02361088313494781</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Z10" t="n">
         <v>0.6709707039456413</v>
       </c>
-      <c r="R10" t="n">
-        <v>28.03928571428575</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.69587337268752</v>
-      </c>
-      <c r="T10" t="n">
-        <v>28.48805514192954</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.883946954788048</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.008158142377838717</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.1792828308002749</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.003513333333333334</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>28.31682820030403</v>
+      <c r="AA10" t="n">
+        <v>0.02637900208746056</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.7514862530771985</v>
       </c>
     </row>
     <row r="11">
@@ -1352,37 +1448,46 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>26.35714285714281</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>27.23145296113909</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.908002336876444</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.0187088218943581</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.3981449898798762</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.007799999999999998</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.007799999999999998</v>
+      </c>
+      <c r="W11" t="n">
+        <v>26.3278144559028</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
         <v>0.006015752972438382</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Z11" t="n">
         <v>0.1619956336149481</v>
       </c>
-      <c r="R11" t="n">
-        <v>26.35714285714281</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>27.23145296063369</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.908002336883929</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.01870851914241778</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.3981367454977016</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.007799999999999998</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>26.32781445538231</v>
+      <c r="AA11" t="n">
+        <v>0.006010640046182783</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.1636784616839654</v>
       </c>
     </row>
     <row r="12">
@@ -1435,37 +1540,46 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>26.92857142857148</v>
       </c>
       <c r="P12" t="n">
+        <v>0.1961577414134905</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>27.96947227900406</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.922571086876444</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.02051067907382667</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.4449234927812163</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.008849999999999998</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.008849999999999998</v>
+      </c>
+      <c r="W12" t="n">
+        <v>27.23145296113909</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
         <v>0.00362725892161148</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Z12" t="n">
         <v>0.0921971490896749</v>
       </c>
-      <c r="R12" t="n">
-        <v>26.92857142857148</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.1961577414134905</v>
-      </c>
-      <c r="T12" t="n">
-        <v>27.9694722689493</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.922571086883929</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.02051073157175735</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.4449249609611882</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.008849999999999998</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>27.23145296063369</v>
+      <c r="AA12" t="n">
+        <v>0.003588200271870521</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.1003600680355974</v>
       </c>
     </row>
     <row r="13">
@@ -1518,37 +1632,46 @@
         </is>
       </c>
       <c r="O13" t="n">
+        <v>25.41785714285721</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.4648676866334254</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>28.9683679389311</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.942647670209778</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.02241122155096527</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.4983091249681805</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.01012</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.01012</v>
+      </c>
+      <c r="W13" t="n">
+        <v>27.96947227900406</v>
+      </c>
+      <c r="X13" t="n">
         <v>0.006274829559544594</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>25.41785714285721</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.4648676866334254</v>
-      </c>
-      <c r="T13" t="n">
-        <v>28.96836727463392</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.942647670217263</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.02241123524433885</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.4983095102163055</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.01012</v>
-      </c>
       <c r="Y13" t="n">
-        <v>27.9694722689493</v>
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.0001765021936132476</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.005112980486617013</v>
       </c>
     </row>
     <row r="14">
@@ -1601,37 +1724,46 @@
         </is>
       </c>
       <c r="O14" t="n">
+        <v>27.31785714285721</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.5273275582417261</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>30.01255103280837</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.964087670209778</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.02393237056821312</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.5452944498589103</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.01132</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.01132</v>
+      </c>
+      <c r="W14" t="n">
+        <v>28.9683679389311</v>
+      </c>
+      <c r="X14" t="n">
         <v>0.02643890324335607</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Y14" t="n">
         <v>0.0059864661796889</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Z14" t="n">
         <v>0.166038915540943</v>
       </c>
-      <c r="R14" t="n">
-        <v>27.31785714285721</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.5273275582417261</v>
-      </c>
-      <c r="T14" t="n">
-        <v>30.01254965667641</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.964087670217262</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.02393238700794108</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.5452949182549442</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.01132</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>28.96836727463392</v>
+      <c r="AA14" t="n">
+        <v>0.005834624532342146</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.1751119665341944</v>
       </c>
     </row>
     <row r="15">
@@ -1684,37 +1816,46 @@
         </is>
       </c>
       <c r="O15" t="n">
+        <v>27.73571428571431</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.5669120469218694</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>31.10797224550702</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.987094336876444</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.0251610435573475</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.5873345793217604</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.01248</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.01248</v>
+      </c>
+      <c r="W15" t="n">
+        <v>30.01255103280837</v>
+      </c>
+      <c r="X15" t="n">
         <v>0.00455350837092449</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Y15" t="n">
         <v>0.02262404581012045</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Z15" t="n">
         <v>0.6940734053890505</v>
       </c>
-      <c r="R15" t="n">
-        <v>27.73571428571431</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.5669120469218694</v>
-      </c>
-      <c r="T15" t="n">
-        <v>31.10797015051896</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.987094336883929</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.02516114519472265</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.5873377015004719</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.01248</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>30.01254965667641</v>
+      <c r="AA15" t="n">
+        <v>0.02327612397420667</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.7240730185726018</v>
       </c>
     </row>
     <row r="16">
@@ -1767,37 +1908,46 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>30.67857142857135</v>
       </c>
       <c r="P16" t="n">
+        <v>1.314363106233276</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>31.74613976555075</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.000747670209778</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.02574269343420042</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.6090542906575334</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.01312</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.01312</v>
+      </c>
+      <c r="W16" t="n">
+        <v>31.10797224550702</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
         <v>0.03368831785424067</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Z16" t="n">
         <v>1.033509465599738</v>
       </c>
-      <c r="R16" t="n">
-        <v>30.67857142857135</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.314363106233276</v>
-      </c>
-      <c r="T16" t="n">
-        <v>31.74613730418875</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.000747670217262</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.02574269542905198</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.6090543067655569</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.01312</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>31.10797015051896</v>
+      <c r="AA16" t="n">
+        <v>0.03569355102898607</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.133132459695009</v>
       </c>
     </row>
     <row r="17">
@@ -1850,37 +2000,46 @@
         </is>
       </c>
       <c r="O17" t="n">
+        <v>29.52857142857138</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>19.99434722408682</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.87876402776961</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.006624041782399131</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.1111942904013396</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.001996666666666667</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.001996666666666667</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16.88071110537751</v>
+      </c>
+      <c r="X17" t="n">
         <v>0.04062202704143002</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Y17" t="n">
         <v>0.002657762910916001</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Z17" t="n">
         <v>0.0816312894067058</v>
       </c>
-      <c r="R17" t="n">
-        <v>29.52857142857138</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>19.99434821018733</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.878764049847864</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.006623948324800732</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.11119242751127</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.001996666666666667</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>16.88071214887976</v>
+      <c r="AA17" t="n">
+        <v>0.004090749458226509</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.08179186507452586</v>
       </c>
     </row>
     <row r="18">
@@ -1933,37 +2092,46 @@
         </is>
       </c>
       <c r="O18" t="n">
+        <v>30.71428571428574</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.09290978010103844</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>20.11820096978532</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.880990611102943</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.006756702796297812</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.1139890320483953</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.002051666666666667</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.002051666666666667</v>
+      </c>
+      <c r="W18" t="n">
+        <v>19.99434722408682</v>
+      </c>
+      <c r="X18" t="n">
         <v>0.01789804707363351</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Y18" t="n">
         <v>0.001291368036371657</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Z18" t="n">
         <v>0.04078878183453907</v>
       </c>
-      <c r="R18" t="n">
-        <v>30.71428571428574</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.09290978010103844</v>
-      </c>
-      <c r="T18" t="n">
-        <v>20.11820220859315</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.880990638206213</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.006756705910393339</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.1139891020336284</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.002051666666666667</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>19.99434821018733</v>
+      <c r="AA18" t="n">
+        <v>0.002159985784733604</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.04345502810915009</v>
       </c>
     </row>
     <row r="19">
@@ -2016,37 +2184,46 @@
         </is>
       </c>
       <c r="O19" t="n">
+        <v>31.58571428571431</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.1714635834683609</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>20.22568990464505</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.88292727776961</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.006866587915325191</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.1163419779105917</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.002098333333333333</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.002098333333333333</v>
+      </c>
+      <c r="W19" t="n">
+        <v>20.11820096978532</v>
+      </c>
+      <c r="X19" t="n">
         <v>0.001401645203937436</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Y19" t="n">
         <v>0.000732260389109694</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Z19" t="n">
         <v>0.02413582546819065</v>
       </c>
-      <c r="R19" t="n">
-        <v>31.58571428571431</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.1714635834683609</v>
-      </c>
-      <c r="T19" t="n">
-        <v>20.22569114062808</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.88292730487288</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.006866587396872273</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0.1163419748585688</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.002098333333333333</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>20.11820220859315</v>
+      <c r="AA19" t="n">
+        <v>0.001421388845636275</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.02874857002576069</v>
       </c>
     </row>
     <row r="20">
@@ -2099,37 +2276,46 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>32.96071428571437</v>
       </c>
       <c r="P20" t="n">
+        <v>0.1940649581558863</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>20.34328539671193</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.885050611102943</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.006981708507962712</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.1188462814509948</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.002148333333333333</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.002148333333333333</v>
+      </c>
+      <c r="W20" t="n">
+        <v>20.22568990464505</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
         <v>0.001184262765768505</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Z20" t="n">
         <v>0.03974752399441857</v>
       </c>
-      <c r="R20" t="n">
-        <v>32.96071428571437</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.1940649581558863</v>
-      </c>
-      <c r="T20" t="n">
-        <v>20.34328662960689</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.885050638206214</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.006981721188787508</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.1188465469566182</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0.002148333333333333</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>20.22569114062808</v>
+      <c r="AA20" t="n">
+        <v>0.002253972861086382</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.0458532131895236</v>
       </c>
     </row>
     <row r="21">
@@ -2182,37 +2368,46 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>33.56309523809537</v>
       </c>
       <c r="P21" t="n">
+        <v>0.2229784488956445</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>20.47349558519533</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.887407312491832</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.007103330707160857</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.1215385722763077</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.0022025</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.0022025</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20.34328539671193</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
         <v>0.002253668672706708</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Z21" t="n">
         <v>0.07526448485171559</v>
       </c>
-      <c r="R21" t="n">
-        <v>33.56309523809537</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.2229784488956445</v>
-      </c>
-      <c r="T21" t="n">
-        <v>20.47349681467529</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.887407339595103</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0.007103361739172312</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0.1215392152518453</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0.0022025</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>20.34328662960689</v>
+      <c r="AA21" t="n">
+        <v>0.004133579428144476</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.08462882017317015</v>
       </c>
     </row>
     <row r="22">
@@ -2265,37 +2460,46 @@
         </is>
       </c>
       <c r="O22" t="n">
+        <v>33.39642857142849</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.2989185664601128</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>20.58181820755303</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.889372361102943</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.007200136731513198</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.1237179128246555</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.002246666666666667</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.002246666666666667</v>
+      </c>
+      <c r="W22" t="n">
+        <v>20.47349558519533</v>
+      </c>
+      <c r="X22" t="n">
         <v>0.00396735495458923</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Y22" t="n">
         <v>0.003016123760172439</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Z22" t="n">
         <v>0.102602067198723</v>
       </c>
-      <c r="R22" t="n">
-        <v>33.39642857142849</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.2989185664601128</v>
-      </c>
-      <c r="T22" t="n">
-        <v>20.58181943419975</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.889372388206214</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0.007200136199108651</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.1237179095912931</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.002246666666666667</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>20.47349681467529</v>
+      <c r="AA22" t="n">
+        <v>0.00553492897706259</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.1139189019976197</v>
       </c>
     </row>
     <row r="23">
@@ -2348,37 +2552,46 @@
         </is>
       </c>
       <c r="O23" t="n">
+        <v>28.42857142857147</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>15.01969250829702</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.792146527775721</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.009244457711781045</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.1221151692588028</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.001996666666666667</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.001996666666666667</v>
+      </c>
+      <c r="W23" t="n">
+        <v>14.80438644820013</v>
+      </c>
+      <c r="X23" t="n">
         <v>0.02124826378470669</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Y23" t="n">
         <v>0.002156026816633438</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Z23" t="n">
         <v>0.06320238611045444</v>
       </c>
-      <c r="R23" t="n">
-        <v>28.42857142857147</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>15.01969296805368</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.792146539303604</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0.00924435718584087</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0.1221136632356617</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.001996666666666667</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>14.80438687360635</v>
+      <c r="AA23" t="n">
+        <v>0.004235445898201378</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.06361509502651258</v>
       </c>
     </row>
     <row r="24">
@@ -2431,37 +2644,46 @@
         </is>
       </c>
       <c r="O24" t="n">
+        <v>29.31428571428569</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.05810793948216079</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>15.15569778710702</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.794373111109054</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.009402010871868823</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.1251651756272311</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.002051666666666667</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.002051666666666667</v>
+      </c>
+      <c r="W24" t="n">
+        <v>15.01969250829702</v>
+      </c>
+      <c r="X24" t="n">
         <v>0.00139773628339818</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Y24" t="n">
         <v>0.001694052966529097</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Z24" t="n">
         <v>0.05093049240086417</v>
       </c>
-      <c r="R24" t="n">
-        <v>29.31428571428569</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.05810793948216079</v>
-      </c>
-      <c r="T24" t="n">
-        <v>15.15569823705797</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.794373122636937</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0.00940201309158991</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.1251652130959574</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0.002051666666666667</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>15.01969296805368</v>
+      <c r="AA24" t="n">
+        <v>0.003538733655060629</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.0536319778251635</v>
       </c>
     </row>
     <row r="25">
@@ -2514,37 +2736,46 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>30.06428571428577</v>
       </c>
       <c r="P25" t="n">
+        <v>0.1219400842896329</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>15.27797946896859</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.796379749997943</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.009535870585130196</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.1278286042487415</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="W25" t="n">
+        <v>15.15569778710702</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
         <v>0.001179849082637842</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Z25" t="n">
         <v>0.03650228328522884</v>
       </c>
-      <c r="R25" t="n">
-        <v>30.06428571428577</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.1219400842896329</v>
-      </c>
-      <c r="T25" t="n">
-        <v>15.27797991000348</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.796379761525826</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0.009535909472786619</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0.1278292021782632</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>15.15569823705797</v>
+      <c r="AA25" t="n">
+        <v>0.00273972621461791</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.04185748085752747</v>
       </c>
     </row>
     <row r="26">
@@ -2597,37 +2828,46 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>30.93809523809523</v>
       </c>
       <c r="P26" t="n">
+        <v>0.1703755277559266</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>15.40717642247016</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.798504749997943</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.009669531240909355</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.1305618574758552</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.00215</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.00215</v>
+      </c>
+      <c r="W26" t="n">
+        <v>15.27797946896859</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
         <v>0.0005275241763407782</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Z26" t="n">
         <v>0.01662203559450923</v>
       </c>
-      <c r="R26" t="n">
-        <v>30.93809523809523</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.1703755277559266</v>
-      </c>
-      <c r="T26" t="n">
-        <v>15.40717685453495</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.798504761525826</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0.009669568421304507</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.1305624341001924</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0.00215</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>15.27797991000348</v>
+      <c r="AA26" t="n">
+        <v>0.001732058081469854</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.02668612443517123</v>
       </c>
     </row>
     <row r="27">
@@ -2680,37 +2920,46 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>31.5095238095239</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>0.2036432131066642</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>15.54576471838672</v>
       </c>
       <c r="R27" t="n">
-        <v>31.5095238095239</v>
+        <v>1.800789812497943</v>
       </c>
       <c r="S27" t="n">
-        <v>0.2036432131066642</v>
+        <v>0.009804928460793325</v>
       </c>
       <c r="T27" t="n">
-        <v>15.54576514061194</v>
+        <v>0.1334114833812312</v>
       </c>
       <c r="U27" t="n">
-        <v>1.800789824025826</v>
+        <v>0.0022025</v>
       </c>
       <c r="V27" t="n">
-        <v>0.009804949344494194</v>
+        <v>0.0022025</v>
       </c>
       <c r="W27" t="n">
-        <v>0.1334118117795324</v>
+        <v>15.40717642247016</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0022025</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>15.40717685453495</v>
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.0006703122036587194</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.01042051580594177</v>
       </c>
     </row>
     <row r="28">
@@ -2763,37 +3012,46 @@
         </is>
       </c>
       <c r="O28" t="n">
+        <v>31.73214285714281</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.2220723133576301</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>15.66240050600434</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.802717423609054</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.009912768032329064</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.1357454552760377</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.002245833333333333</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.002245833333333333</v>
+      </c>
+      <c r="W28" t="n">
+        <v>15.54576471838672</v>
+      </c>
+      <c r="X28" t="n">
         <v>0.07036365759109456</v>
       </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>31.73214285714281</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0.2220723133576301</v>
-      </c>
-      <c r="T28" t="n">
-        <v>15.66240091965512</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.802717435136937</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0.009912767707050024</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0.1357454538912589</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0.002245833333333333</v>
-      </c>
       <c r="Y28" t="n">
-        <v>15.54576514061194</v>
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.795387993961591e-05</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.0002812008582509814</v>
       </c>
     </row>
     <row r="29">
@@ -2846,37 +3104,46 @@
         </is>
       </c>
       <c r="O29" t="n">
+        <v>24.49345238095237</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>23.93967898481781</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.098491694429186</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.01007990385835065</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.1949549898908649</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.004063333333333333</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.004063333333333333</v>
+      </c>
+      <c r="W29" t="n">
+        <v>23.76781114532759</v>
+      </c>
+      <c r="X29" t="n">
         <v>0.01703599848924725</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Y29" t="n">
         <v>0.002931631959375182</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Z29" t="n">
         <v>0.07399229663180125</v>
       </c>
-      <c r="R29" t="n">
-        <v>24.49345238095237</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>23.93968006453909</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.098491720806879</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0.01007997637280434</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0.194956735239167</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0.004063333333333333</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>23.76781203213405</v>
+      <c r="AA29" t="n">
+        <v>0.003096509180803947</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.07412943576198766</v>
       </c>
     </row>
     <row r="30">
@@ -2929,37 +3196,46 @@
         </is>
       </c>
       <c r="O30" t="n">
+        <v>25.23928571428564</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.06375494686076261</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>24.2281458354068</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.104521249984742</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.01063211161318078</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.2075172961978925</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.00435</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.00435</v>
+      </c>
+      <c r="W30" t="n">
+        <v>23.93967898481781</v>
+      </c>
+      <c r="X30" t="n">
         <v>0.003897200232591663</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Y30" t="n">
         <v>0.002618004611547352</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Z30" t="n">
         <v>0.06485638924285067</v>
       </c>
-      <c r="R30" t="n">
-        <v>25.23928571428564</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0.06375494686076261</v>
-      </c>
-      <c r="T30" t="n">
-        <v>24.22814684652792</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.104521276362434</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0.01063212456913026</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0.207517619384608</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0.00435</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>23.93968006453909</v>
+      <c r="AA30" t="n">
+        <v>0.002715697513538642</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.06579631540286586</v>
       </c>
     </row>
     <row r="31">
@@ -3012,37 +3288,46 @@
         </is>
       </c>
       <c r="O31" t="n">
+        <v>24.77321428571426</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.1716212668026328</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>24.54912556934149</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.111271249984742</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.01118090176887276</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.220412783673763</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.00465</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.00465</v>
+      </c>
+      <c r="W31" t="n">
+        <v>24.2281458354068</v>
+      </c>
+      <c r="X31" t="n">
         <v>0.01411667984325947</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Y31" t="n">
         <v>0.00194663879778472</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Z31" t="n">
         <v>0.04872158819598323</v>
       </c>
-      <c r="R31" t="n">
-        <v>24.77321428571426</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0.1716212668026328</v>
-      </c>
-      <c r="T31" t="n">
-        <v>24.54912650345894</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.111271276362434</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0.01118092410442565</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0.2204133410545105</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.00465</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>24.22814684652792</v>
+      <c r="AA31" t="n">
+        <v>0.002019535772512294</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.0495778372711814</v>
       </c>
     </row>
     <row r="32">
@@ -3095,37 +3380,46 @@
         </is>
       </c>
       <c r="O32" t="n">
+        <v>25.0285714285714</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.2547670720457892</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>25.00680786687654</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.120971249984742</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.01186590941261322</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.2371876910443514</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.005050000000000001</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.005050000000000001</v>
+      </c>
+      <c r="W32" t="n">
+        <v>24.54912556934149</v>
+      </c>
+      <c r="X32" t="n">
         <v>0.01729347944990734</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Y32" t="n">
         <v>0.001250719091027115</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Z32" t="n">
         <v>0.03284030984725474</v>
       </c>
-      <c r="R32" t="n">
-        <v>25.0285714285714</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.2547670720457892</v>
-      </c>
-      <c r="T32" t="n">
-        <v>25.00680869176568</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.120971276362434</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0.01186587573608902</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.2371868574664508</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0.005050000000000001</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>24.54912650345894</v>
+      <c r="AA32" t="n">
+        <v>0.001332234624952042</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.03331493529977605</v>
       </c>
     </row>
     <row r="33">
@@ -3178,37 +3472,46 @@
         </is>
       </c>
       <c r="O33" t="n">
+        <v>26.25714285714279</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.3345630000595383</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>26.11045456330865</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.144732361095853</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.01316720048945217</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.2717707582087737</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.005916666666666667</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.005916666666666667</v>
+      </c>
+      <c r="W33" t="n">
+        <v>25.00680786687654</v>
+      </c>
+      <c r="X33" t="n">
         <v>0.01396089162246411</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Y33" t="n">
         <v>0.0001013561359319036</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Z33" t="n">
         <v>0.002777158124534164</v>
       </c>
-      <c r="R33" t="n">
-        <v>26.25714285714279</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0.3345630000595383</v>
-      </c>
-      <c r="T33" t="n">
-        <v>26.11045512932166</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.144732387473546</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0.01316721250280378</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0.271771078660095</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0.005916666666666667</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>25.00680869176568</v>
+      <c r="AA33" t="n">
+        <v>0.0001589641491270463</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.004150626192976762</v>
       </c>
     </row>
     <row r="34">
@@ -3261,37 +3564,46 @@
         </is>
       </c>
       <c r="O34" t="n">
+        <v>27.40000000000004</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.4114676331552647</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>26.57397314534753</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.154871249984741</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.01360207801067354</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.284385963153116</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="W34" t="n">
+        <v>26.11045456330865</v>
+      </c>
+      <c r="X34" t="n">
         <v>0.01145255846603085</v>
       </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>27.40000000000004</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0.4114676331552647</v>
-      </c>
-      <c r="T34" t="n">
-        <v>26.57397360426178</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.154871276362434</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0.01360205481603644</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.2843853526340677</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.00625</v>
-      </c>
       <c r="Y34" t="n">
-        <v>26.11045512932166</v>
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>4.439867806962225e-05</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.001179849278711072</v>
       </c>
     </row>
     <row r="35">
@@ -3344,37 +3656,46 @@
         </is>
       </c>
       <c r="O35" t="n">
+        <v>28.4607142857143</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.4067877264015557</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>27.30784322790872</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.171121249984742</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.0141884524772847</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.3025561521198283</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.006750000000000001</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.006750000000000001</v>
+      </c>
+      <c r="W35" t="n">
+        <v>26.57397314534753</v>
+      </c>
+      <c r="X35" t="n">
         <v>0.009152735978746178</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Y35" t="n">
         <v>6.146505253398153e-05</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Z35" t="n">
         <v>0.001762949417501451</v>
       </c>
-      <c r="R35" t="n">
-        <v>28.4607142857143</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0.4067877264015557</v>
-      </c>
-      <c r="T35" t="n">
-        <v>27.30784352193885</v>
-      </c>
-      <c r="U35" t="n">
-        <v>2.171121276362435</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0.01418840491525607</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0.3025548575925655</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0.006750000000000001</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>26.57397360426178</v>
+      <c r="AA35" t="n">
+        <v>4.578707085297216e-05</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.001250346152718113</v>
       </c>
     </row>
     <row r="36">
@@ -3427,37 +3748,46 @@
         </is>
       </c>
       <c r="O36" t="n">
+        <v>28.6821428571429</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.4021708299263646</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>27.82182632859926</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.182649027762519</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.01453689713190097</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.3141530781652856</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.007083333333333334</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.007083333333333334</v>
+      </c>
+      <c r="W36" t="n">
+        <v>27.30784322790872</v>
+      </c>
+      <c r="X36" t="n">
         <v>0.00813246080612828</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Y36" t="n">
         <v>5.72212406026065e-05</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Z36" t="n">
         <v>0.001647154283060745</v>
       </c>
-      <c r="R36" t="n">
-        <v>28.6821428571429</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0.4021708299263646</v>
-      </c>
-      <c r="T36" t="n">
-        <v>27.82182651078572</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2.182649054140212</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0.01453692586273916</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0.3141538806580285</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0.007083333333333334</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>27.30784352193885</v>
+      <c r="AA36" t="n">
+        <v>4.518776391829951e-05</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.001257206119912673</v>
       </c>
     </row>
     <row r="37">
@@ -3510,37 +3840,46 @@
         </is>
       </c>
       <c r="O37" t="n">
+        <v>28.78571428571429</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.3873938421634567</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>28.72212538793306</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.203138999984742</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.01504659661368045</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.332568240370033</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.007640000000000001</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.007640000000000001</v>
+      </c>
+      <c r="W37" t="n">
+        <v>27.82182632859926</v>
+      </c>
+      <c r="X37" t="n">
         <v>0.007018151213335786</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Y37" t="n">
         <v>1.910531806293016e-05</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="Z37" t="n">
         <v>0.0005503013934911842</v>
       </c>
-      <c r="R37" t="n">
-        <v>28.78571428571429</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.3873938421634567</v>
-      </c>
-      <c r="T37" t="n">
-        <v>28.72212537780479</v>
-      </c>
-      <c r="U37" t="n">
-        <v>2.203139026362434</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0.01504659517082482</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.3325682000033916</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.007640000000000001</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>27.82182651078572</v>
+      <c r="AA37" t="n">
+        <v>4.454302433905063e-05</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.001279370330223966</v>
       </c>
     </row>
     <row r="38">
@@ -3593,37 +3932,46 @@
         </is>
       </c>
       <c r="O38" t="n">
+        <v>28.80357142857139</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.3689307159607038</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>29.76547646571372</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.227371249984742</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.01550784152635049</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.3513494141473926</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.00825</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.00825</v>
+      </c>
+      <c r="W38" t="n">
+        <v>28.72212538793306</v>
+      </c>
+      <c r="X38" t="n">
         <v>0.01009923569250023</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Y38" t="n">
         <v>1.425389975077348e-05</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Z38" t="n">
         <v>0.0004247662125730495</v>
       </c>
-      <c r="R38" t="n">
-        <v>28.80357142857139</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0.3689307159607038</v>
-      </c>
-      <c r="T38" t="n">
-        <v>29.76547634687633</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2.227371276362434</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0.01550781476267443</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0.3513486174167029</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0.00825</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>28.72212537780479</v>
+      <c r="AA38" t="n">
+        <v>4.408174559026024e-05</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.001312114160934471</v>
       </c>
     </row>
     <row r="39">
@@ -3676,37 +4024,46 @@
         </is>
       </c>
       <c r="O39" t="n">
+        <v>29.79999999999999</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.3542503465167628</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>30.84541916498261</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.253021249984741</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.01587051772024678</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.3683701505380624</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.00885</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.00885</v>
+      </c>
+      <c r="W39" t="n">
+        <v>29.76547646571372</v>
+      </c>
+      <c r="X39" t="n">
         <v>0.007799312579268405</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Y39" t="n">
         <v>0.0002877005497867221</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="Z39" t="n">
         <v>0.008954679612111731</v>
       </c>
-      <c r="R39" t="n">
-        <v>29.79999999999999</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0.3542503465167628</v>
-      </c>
-      <c r="T39" t="n">
-        <v>30.84541902494425</v>
-      </c>
-      <c r="U39" t="n">
-        <v>2.253021276362434</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0.01587053886464064</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0.3683708024918843</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0.00885</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>29.76547634687633</v>
+      <c r="AA39" t="n">
+        <v>0.0003012099228746787</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.009290946327721547</v>
       </c>
     </row>
     <row r="40">
@@ -3759,55 +4116,64 @@
         </is>
       </c>
       <c r="O40" t="n">
+        <v>31.12500000000002</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.363160750555521</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>31.81469618008588</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.276551111095853</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.0161169662921108</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.381857653732939</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.009366666666666667</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.009366666666666667</v>
+      </c>
+      <c r="W40" t="n">
+        <v>30.84541916498261</v>
+      </c>
+      <c r="X40" t="n">
         <v>0.006429284455135683</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Y40" t="n">
         <v>0.0007098662467225611</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Z40" t="n">
         <v>0.02192219084074996</v>
       </c>
-      <c r="R40" t="n">
-        <v>31.12500000000002</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0.363160750555521</v>
-      </c>
-      <c r="T40" t="n">
-        <v>31.8146960202547</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2.276551137473545</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0.01611696618632926</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0.3818576499658321</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0.009366666666666667</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>30.84541902494425</v>
+      <c r="AA40" t="n">
+        <v>0.0006841428405296224</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.02176579661523088</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR07_T_32</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10.13333333333333</v>
+        <v>46.93333333333334</v>
       </c>
       <c r="D41" t="n">
-        <v>27.80357142857142</v>
+        <v>31.93571428571439</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
@@ -3816,63 +4182,72 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>2.111411826295212</v>
+        <v>2.515307377137465</v>
       </c>
       <c r="H41" t="n">
-        <v>0.05060060245371522</v>
+        <v>0.7360300997802449</v>
       </c>
       <c r="I41" t="n">
-        <v>29.01</v>
+        <v>32.01</v>
       </c>
       <c r="J41" t="n">
-        <v>1.292833793699242</v>
+        <v>0.3122489136229731</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.0006879481871742564</v>
+        <v>0.02633606438824609</v>
       </c>
       <c r="M41" t="n">
-        <v>0.04290404542881167</v>
+        <v>0.06894461020814052</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>0.04682466286201208</v>
+        <v>30.88214285714287</v>
       </c>
       <c r="P41" t="n">
-        <v>0.001543705722077936</v>
+        <v>0.3954213588988506</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.04292053230848831</v>
+        <v>34.84968576356186</v>
       </c>
       <c r="R41" t="n">
-        <v>25.66428571428573</v>
+        <v>2.35351377776252</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>0.01654179887468221</v>
       </c>
       <c r="T41" t="n">
-        <v>28.24180554491312</v>
+        <v>0.4152720349990039</v>
       </c>
       <c r="U41" t="n">
-        <v>2.198068908667902</v>
+        <v>0.01088666666666667</v>
       </c>
       <c r="V41" t="n">
-        <v>0.007068164159168635</v>
+        <v>0.01088666666666667</v>
       </c>
       <c r="W41" t="n">
-        <v>0.1089932301946586</v>
+        <v>31.81469618008588</v>
       </c>
       <c r="X41" t="n">
-        <v>0.007053333333333333</v>
+        <v>0.02024773721229721</v>
       </c>
       <c r="Y41" t="n">
-        <v>24.01327122841171</v>
+        <v>0.002400167963573594</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.07665107832241122</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0.002076037952137571</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0.07234927026522282</v>
       </c>
     </row>
     <row r="42">
@@ -3887,10 +4262,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>11.56666666666667</v>
+        <v>10.13333333333333</v>
       </c>
       <c r="D42" t="n">
-        <v>28.21071428571433</v>
+        <v>27.80357142857142</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -3899,25 +4274,25 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>2.092706775844421</v>
+        <v>2.111411826295212</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1044036282464569</v>
+        <v>0.05060060245371522</v>
       </c>
       <c r="I42" t="n">
-        <v>28.995</v>
+        <v>29.01</v>
       </c>
       <c r="J42" t="n">
-        <v>0.4995599667938492</v>
+        <v>1.292833793699242</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.01656280347506739</v>
+        <v>0.0006879481871742564</v>
       </c>
       <c r="M42" t="n">
-        <v>0.03752923222291429</v>
+        <v>0.04290404542881167</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -3925,37 +4300,46 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>0.009793628241382288</v>
+        <v>25.66428571428573</v>
       </c>
       <c r="P42" t="n">
-        <v>0.001301027884616268</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.03670292593065684</v>
+        <v>28.24180486689044</v>
       </c>
       <c r="R42" t="n">
-        <v>27.80357142857142</v>
+        <v>2.198068889704303</v>
       </c>
       <c r="S42" t="n">
-        <v>0.05060060245371522</v>
+        <v>0.007073425374068638</v>
       </c>
       <c r="T42" t="n">
-        <v>28.47191433675219</v>
+        <v>0.1091418130006905</v>
       </c>
       <c r="U42" t="n">
-        <v>2.203329247622887</v>
+        <v>0.007053333333333333</v>
       </c>
       <c r="V42" t="n">
-        <v>0.007575498547917375</v>
+        <v>0.003526666666666667</v>
       </c>
       <c r="W42" t="n">
-        <v>0.1171354497979989</v>
+        <v>24.01327123307239</v>
       </c>
       <c r="X42" t="n">
-        <v>0.007626666666666667</v>
+        <v>0.04682466286201208</v>
       </c>
       <c r="Y42" t="n">
-        <v>28.24180554491312</v>
+        <v>0.001543705722077936</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0.04292053230848831</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.001524917290366768</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.04306641655268557</v>
       </c>
     </row>
     <row r="43">
@@ -3970,10 +4354,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>12.66666666666667</v>
+        <v>11.56666666666667</v>
       </c>
       <c r="D43" t="n">
-        <v>28.84999999999995</v>
+        <v>28.21071428571433</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -3982,25 +4366,25 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>2.059106202419109</v>
+        <v>2.092706775844421</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1491197853115378</v>
+        <v>0.1044036282464569</v>
       </c>
       <c r="I43" t="n">
         <v>28.995</v>
       </c>
       <c r="J43" t="n">
-        <v>0.5552285401125786</v>
+        <v>0.4995599667938492</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.01268043122870065</v>
+        <v>-0.01656280347506739</v>
       </c>
       <c r="M43" t="n">
-        <v>0.03318261877259444</v>
+        <v>0.03752923222291429</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -4008,37 +4392,46 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>0.01308713559294417</v>
+        <v>27.80357142857142</v>
       </c>
       <c r="P43" t="n">
-        <v>0.00111834683420231</v>
+        <v>0.05060060245371522</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.03226430616673658</v>
+        <v>28.4719136932896</v>
       </c>
       <c r="R43" t="n">
-        <v>28.21071428571433</v>
+        <v>2.20332922829797</v>
       </c>
       <c r="S43" t="n">
-        <v>0.1044036282464569</v>
+        <v>0.007575517607850952</v>
       </c>
       <c r="T43" t="n">
-        <v>28.65988059431129</v>
+        <v>0.1171359889591415</v>
       </c>
       <c r="U43" t="n">
-        <v>2.20764491860522</v>
+        <v>0.007626666666666667</v>
       </c>
       <c r="V43" t="n">
-        <v>0.007944458816790421</v>
+        <v>0.003813333333333334</v>
       </c>
       <c r="W43" t="n">
-        <v>0.1229649184265571</v>
+        <v>28.24180486689044</v>
       </c>
       <c r="X43" t="n">
-        <v>0.008066666666666666</v>
+        <v>0.009793628241382288</v>
       </c>
       <c r="Y43" t="n">
-        <v>28.47191433675219</v>
+        <v>0.001301027884616268</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.03670292593065684</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.001330806855107746</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.03789061792106591</v>
       </c>
     </row>
     <row r="44">
@@ -4053,10 +4446,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>14.13333333333333</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="D44" t="n">
-        <v>29.8214285714287</v>
+        <v>28.84999999999995</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
@@ -4065,25 +4458,25 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>2.054382414798483</v>
+        <v>2.059106202419109</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1918414613393818</v>
+        <v>0.1491197853115378</v>
       </c>
       <c r="I44" t="n">
         <v>28.995</v>
       </c>
       <c r="J44" t="n">
-        <v>0.4551298135529764</v>
+        <v>0.5552285401125786</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.00225385966014273</v>
+        <v>-0.01268043122870065</v>
       </c>
       <c r="M44" t="n">
-        <v>0.02512562920803933</v>
+        <v>0.03318261877259444</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -4091,37 +4484,46 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>0.01416473965932023</v>
+        <v>28.21071428571433</v>
       </c>
       <c r="P44" t="n">
-        <v>0.0008354784274698437</v>
+        <v>0.1044036282464569</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.02491516024776152</v>
+        <v>28.65987999487133</v>
       </c>
       <c r="R44" t="n">
-        <v>28.84999999999995</v>
+        <v>2.207644899280303</v>
       </c>
       <c r="S44" t="n">
-        <v>0.1491197853115378</v>
+        <v>0.00794445905433588</v>
       </c>
       <c r="T44" t="n">
-        <v>28.92563808749308</v>
+        <v>0.1229649217459896</v>
       </c>
       <c r="U44" t="n">
-        <v>2.213775591402554</v>
+        <v>0.008066666666666666</v>
       </c>
       <c r="V44" t="n">
-        <v>0.008420554709994834</v>
+        <v>0.004033333333333333</v>
       </c>
       <c r="W44" t="n">
-        <v>0.1305037205317169</v>
+        <v>28.4719136932896</v>
       </c>
       <c r="X44" t="n">
-        <v>0.008653333333333332</v>
+        <v>0.01308713559294417</v>
       </c>
       <c r="Y44" t="n">
-        <v>28.65988059431129</v>
+        <v>0.00111834683420231</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.03226430616673658</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.001176819229347405</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0.03372749788875357</v>
       </c>
     </row>
     <row r="45">
@@ -4136,10 +4538,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16.85</v>
+        <v>14.13333333333333</v>
       </c>
       <c r="D45" t="n">
-        <v>30.18571428571434</v>
+        <v>29.8214285714287</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -4148,25 +4550,25 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>2.052763135178324</v>
+        <v>2.054382414798483</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2448076315621145</v>
+        <v>0.1918414613393818</v>
       </c>
       <c r="I45" t="n">
         <v>28.995</v>
       </c>
       <c r="J45" t="n">
-        <v>0.2858643792140457</v>
+        <v>0.4551298135529764</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.004342262917761283</v>
+        <v>-0.00225385966014273</v>
       </c>
       <c r="M45" t="n">
-        <v>0.01531393640884581</v>
+        <v>0.02512562920803933</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -4174,37 +4576,46 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>0.01158551351625574</v>
+        <v>28.84999999999995</v>
       </c>
       <c r="P45" t="n">
-        <v>0.0005244793669481729</v>
+        <v>0.1491197853115378</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.01583178431944987</v>
+        <v>28.92563754904613</v>
       </c>
       <c r="R45" t="n">
-        <v>29.8214285714287</v>
+        <v>2.213775572077636</v>
       </c>
       <c r="S45" t="n">
-        <v>0.1918414613393818</v>
+        <v>0.008420554940362099</v>
       </c>
       <c r="T45" t="n">
-        <v>29.46262840771122</v>
+        <v>0.1305037237789281</v>
       </c>
       <c r="U45" t="n">
-        <v>2.226267742783581</v>
+        <v>0.008653333333333332</v>
       </c>
       <c r="V45" t="n">
-        <v>0.009253028396770656</v>
+        <v>0.004326666666666666</v>
       </c>
       <c r="W45" t="n">
-        <v>0.1437184974817057</v>
+        <v>28.65987999487133</v>
       </c>
       <c r="X45" t="n">
-        <v>0.009740000000000002</v>
+        <v>0.01416473965932023</v>
       </c>
       <c r="Y45" t="n">
-        <v>28.92563808749308</v>
+        <v>0.0008354784274698437</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.02491516024776152</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.0008945528030802108</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0.02587551015038141</v>
       </c>
     </row>
     <row r="46">
@@ -4219,10 +4630,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>22.4</v>
+        <v>16.85</v>
       </c>
       <c r="D46" t="n">
-        <v>32.48928571428564</v>
+        <v>30.18571428571434</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
@@ -4231,25 +4642,25 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>2.136378998440389</v>
+        <v>2.052763135178324</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2862295508009267</v>
+        <v>0.2448076315621145</v>
       </c>
       <c r="I46" t="n">
         <v>28.995</v>
       </c>
       <c r="J46" t="n">
-        <v>0.2861652497401637</v>
+        <v>0.2858643792140457</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.002939955113684175</v>
+        <v>0.004342262917761283</v>
       </c>
       <c r="M46" t="n">
-        <v>0.003419686402695349</v>
+        <v>0.01531393640884581</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4257,37 +4668,46 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>0.01018412764647287</v>
+        <v>29.8214285714287</v>
       </c>
       <c r="P46" t="n">
-        <v>0.0001173795623522832</v>
+        <v>0.1918414613393818</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.003813578138281135</v>
+        <v>29.46262799242935</v>
       </c>
       <c r="R46" t="n">
-        <v>30.18571428571434</v>
+        <v>2.226267723458665</v>
       </c>
       <c r="S46" t="n">
-        <v>0.2448076315621145</v>
+        <v>0.009253028608468959</v>
       </c>
       <c r="T46" t="n">
-        <v>30.73245500743434</v>
+        <v>0.1437185005742468</v>
       </c>
       <c r="U46" t="n">
-        <v>2.256376522892332</v>
+        <v>0.009740000000000002</v>
       </c>
       <c r="V46" t="n">
-        <v>0.01074724495172402</v>
+        <v>0.004870000000000001</v>
       </c>
       <c r="W46" t="n">
-        <v>0.1673908057509535</v>
+        <v>28.92563754904613</v>
       </c>
       <c r="X46" t="n">
-        <v>0.01196</v>
+        <v>0.01158551351625574</v>
       </c>
       <c r="Y46" t="n">
-        <v>29.46262840771122</v>
+        <v>0.0005244793669481729</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.01583178431944987</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.0005561275272637982</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.0163849784521229</v>
       </c>
     </row>
     <row r="47">
@@ -4302,10 +4722,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>24.05</v>
+        <v>22.4</v>
       </c>
       <c r="D47" t="n">
-        <v>32.9321428571429</v>
+        <v>32.48928571428564</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -4314,25 +4734,25 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>2.119328558258994</v>
+        <v>2.136378998440389</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2889524121591054</v>
+        <v>0.2862295508009267</v>
       </c>
       <c r="I47" t="n">
-        <v>28.98962893733009</v>
+        <v>28.995</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2278965996953445</v>
+        <v>0.2861652497401637</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.003428148603602897</v>
+        <v>0.002939955113684175</v>
       </c>
       <c r="M47" t="n">
-        <v>0.002167744356653061</v>
+        <v>0.003419686402695349</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4340,37 +4760,46 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>0.0085377509283628</v>
+        <v>30.18571428571434</v>
       </c>
       <c r="P47" t="n">
-        <v>8.001736341849413e-05</v>
+        <v>0.2448076315621145</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.002635143243149769</v>
+        <v>30.73245487142585</v>
       </c>
       <c r="R47" t="n">
-        <v>32.48928571428564</v>
+        <v>2.256376503567415</v>
       </c>
       <c r="S47" t="n">
-        <v>0.2862295508009267</v>
+        <v>0.01074722783805307</v>
       </c>
       <c r="T47" t="n">
-        <v>31.15248101756942</v>
+        <v>0.1673902776698777</v>
       </c>
       <c r="U47" t="n">
-        <v>2.266515783031581</v>
+        <v>0.01196</v>
       </c>
       <c r="V47" t="n">
-        <v>0.0111372695428132</v>
+        <v>0.005979999999999999</v>
       </c>
       <c r="W47" t="n">
-        <v>0.1734960122774931</v>
+        <v>29.46262799242935</v>
       </c>
       <c r="X47" t="n">
-        <v>0.01262</v>
+        <v>0.01018412764647287</v>
       </c>
       <c r="Y47" t="n">
-        <v>30.73245500743434</v>
+        <v>0.0001173795623522832</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0.003813578138281135</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.000160639813569606</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0.004936855821082178</v>
       </c>
     </row>
     <row r="48">
@@ -4385,10 +4814,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>25.55</v>
+        <v>24.05</v>
       </c>
       <c r="D48" t="n">
-        <v>33.08366238246173</v>
+        <v>32.9321428571429</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -4397,25 +4826,25 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>2.122927932215827</v>
+        <v>2.119328558258994</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2916972101212668</v>
+        <v>0.2889524121591054</v>
       </c>
       <c r="I48" t="n">
-        <v>29.01</v>
+        <v>28.98962893733009</v>
       </c>
       <c r="J48" t="n">
-        <v>0.2049207718657497</v>
+        <v>0.2278965996953445</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.01007802025635504</v>
+        <v>0.003428148603602897</v>
       </c>
       <c r="M48" t="n">
-        <v>0.002083661045468459</v>
+        <v>0.002167744356653061</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -4423,37 +4852,46 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>0.01094124388489767</v>
+        <v>32.48928571428564</v>
       </c>
       <c r="P48" t="n">
-        <v>0.0001048376628482425</v>
+        <v>0.2862295508009267</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.003468413842637606</v>
+        <v>31.15248097069052</v>
       </c>
       <c r="R48" t="n">
-        <v>32.9321428571429</v>
+        <v>2.266515763706664</v>
       </c>
       <c r="S48" t="n">
-        <v>0.2889524121591054</v>
+        <v>0.01113732683946593</v>
       </c>
       <c r="T48" t="n">
-        <v>31.55039956771036</v>
+        <v>0.173497795470351</v>
       </c>
       <c r="U48" t="n">
-        <v>2.276205792721581</v>
+        <v>0.01262</v>
       </c>
       <c r="V48" t="n">
-        <v>0.01147072886081365</v>
+        <v>0.00631</v>
       </c>
       <c r="W48" t="n">
-        <v>0.1786641753611795</v>
+        <v>30.73245487142585</v>
       </c>
       <c r="X48" t="n">
-        <v>0.01322</v>
+        <v>0.0085377509283628</v>
       </c>
       <c r="Y48" t="n">
-        <v>31.15248101756942</v>
+        <v>8.001736341849413e-05</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.002635143243149769</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.000121230682064597</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.003776636516081191</v>
       </c>
     </row>
     <row r="49">
@@ -4468,10 +4906,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>27.01666666666667</v>
+        <v>25.55</v>
       </c>
       <c r="D49" t="n">
-        <v>33.286006759061</v>
+        <v>33.08366238246173</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
@@ -4480,25 +4918,25 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>2.149102129882635</v>
+        <v>2.122927932215827</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2947411967231239</v>
+        <v>0.2916972101212668</v>
       </c>
       <c r="I49" t="n">
         <v>29.01</v>
       </c>
       <c r="J49" t="n">
-        <v>0.2878082500112895</v>
+        <v>0.2049207718657497</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.01358415797906408</v>
+        <v>0.01007802025635504</v>
       </c>
       <c r="M49" t="n">
-        <v>0.002564129205513765</v>
+        <v>0.002083661045468459</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4506,37 +4944,46 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>0.01496737650102324</v>
+        <v>32.9321428571429</v>
       </c>
       <c r="P49" t="n">
-        <v>0.0001330031843039391</v>
+        <v>0.2889524121591054</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.004427144891717553</v>
+        <v>31.55039960381771</v>
       </c>
       <c r="R49" t="n">
-        <v>33.08366238246173</v>
+        <v>2.276205773396665</v>
       </c>
       <c r="S49" t="n">
-        <v>0.2916972101212668</v>
+        <v>0.01147068869907342</v>
       </c>
       <c r="T49" t="n">
-        <v>31.95385437249574</v>
+        <v>0.1786629068909775</v>
       </c>
       <c r="U49" t="n">
-        <v>2.286115580409136</v>
+        <v>0.01322</v>
       </c>
       <c r="V49" t="n">
-        <v>0.01177719446570448</v>
+        <v>0.00661</v>
       </c>
       <c r="W49" t="n">
-        <v>0.1833460432925698</v>
+        <v>31.15248097069052</v>
       </c>
       <c r="X49" t="n">
-        <v>0.01380666666666667</v>
+        <v>0.01094124388489767</v>
       </c>
       <c r="Y49" t="n">
-        <v>31.55039956771036</v>
+        <v>0.0001048376628482425</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.003468413842637606</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.0001197389718612531</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0.003777812410372821</v>
       </c>
     </row>
     <row r="50">
@@ -4551,10 +4998,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>30.05</v>
+        <v>27.01666666666667</v>
       </c>
       <c r="D50" t="n">
-        <v>34.92500000000002</v>
+        <v>33.286006759061</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -4563,25 +5010,25 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>2.204791765804646</v>
+        <v>2.149102129882635</v>
       </c>
       <c r="H50" t="n">
-        <v>0.3061500936386944</v>
+        <v>0.2947411967231239</v>
       </c>
       <c r="I50" t="n">
-        <v>28.995</v>
+        <v>29.01</v>
       </c>
       <c r="J50" t="n">
-        <v>0.3273118051359381</v>
+        <v>0.2878082500112895</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.01005866658037854</v>
+        <v>0.01358415797906408</v>
       </c>
       <c r="M50" t="n">
-        <v>0.005592359312335324</v>
+        <v>0.002564129205513765</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -4589,37 +5036,46 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>0.01393403278476044</v>
+        <v>33.08366238246173</v>
       </c>
       <c r="P50" t="n">
-        <v>0.0002001166067567213</v>
+        <v>0.2916972101212668</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.006989072490978496</v>
+        <v>31.95385449141564</v>
       </c>
       <c r="R50" t="n">
-        <v>33.286006759061</v>
+        <v>2.28611556108422</v>
       </c>
       <c r="S50" t="n">
-        <v>0.2947411967231239</v>
+        <v>0.01177718080478872</v>
       </c>
       <c r="T50" t="n">
-        <v>32.83159423889894</v>
+        <v>0.1833456058247001</v>
       </c>
       <c r="U50" t="n">
-        <v>2.307975824491581</v>
+        <v>0.01380666666666667</v>
       </c>
       <c r="V50" t="n">
-        <v>0.01235149451992449</v>
+        <v>0.006903333333333334</v>
       </c>
       <c r="W50" t="n">
-        <v>0.1918556034210608</v>
+        <v>31.55039960381771</v>
       </c>
       <c r="X50" t="n">
-        <v>0.01502</v>
+        <v>0.01496737650102324</v>
       </c>
       <c r="Y50" t="n">
-        <v>31.95385437249574</v>
+        <v>0.0001330031843039391</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.004427144891717553</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0.0001359515592164663</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0.004344176341084041</v>
       </c>
     </row>
     <row r="51">
@@ -4634,10 +5090,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>33.05</v>
+        <v>30.05</v>
       </c>
       <c r="D51" t="n">
-        <v>35.32500000000002</v>
+        <v>34.92500000000002</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -4646,25 +5102,25 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>2.222071473920533</v>
+        <v>2.204791765804646</v>
       </c>
       <c r="H51" t="n">
-        <v>0.3308651428571041</v>
+        <v>0.3061500936386944</v>
       </c>
       <c r="I51" t="n">
-        <v>29.01</v>
+        <v>28.995</v>
       </c>
       <c r="J51" t="n">
-        <v>0.3206543266788474</v>
+        <v>0.3273118051359381</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0.005559533698940396</v>
+        <v>0.01005866658037854</v>
       </c>
       <c r="M51" t="n">
-        <v>0.01134058524405515</v>
+        <v>0.005592359312335324</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -4672,37 +5128,46 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>0.01157922320647989</v>
+        <v>33.286006759061</v>
       </c>
       <c r="P51" t="n">
-        <v>0.0003444698247772432</v>
+        <v>0.2947411967231239</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.01216839656025612</v>
+        <v>32.83159453257404</v>
       </c>
       <c r="R51" t="n">
-        <v>34.92500000000002</v>
+        <v>2.307975805166664</v>
       </c>
       <c r="S51" t="n">
-        <v>0.3061500936386944</v>
+        <v>0.01235151587956077</v>
       </c>
       <c r="T51" t="n">
-        <v>33.75408893078473</v>
+        <v>0.1918563046190789</v>
       </c>
       <c r="U51" t="n">
-        <v>2.331405847921581</v>
+        <v>0.01502</v>
       </c>
       <c r="V51" t="n">
-        <v>0.01284345245977919</v>
+        <v>0.007509999999999999</v>
       </c>
       <c r="W51" t="n">
-        <v>0.1986859108423037</v>
+        <v>31.95385449141564</v>
       </c>
       <c r="X51" t="n">
-        <v>0.01622</v>
+        <v>0.01393403278476044</v>
       </c>
       <c r="Y51" t="n">
-        <v>32.83159423889894</v>
+        <v>0.0002001166067567213</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.006989072490978496</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.0002310196494435016</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0.007584743459586439</v>
       </c>
     </row>
     <row r="52">
@@ -4717,10 +5182,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>35.71666666666666</v>
+        <v>33.05</v>
       </c>
       <c r="D52" t="n">
-        <v>36.71428571428564</v>
+        <v>35.32500000000002</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
@@ -4729,25 +5194,25 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>2.225119195750334</v>
+        <v>2.222071473920533</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3724108962071924</v>
+        <v>0.3308651428571041</v>
       </c>
       <c r="I52" t="n">
-        <v>28.98</v>
+        <v>29.01</v>
       </c>
       <c r="J52" t="n">
-        <v>0.2482560989697474</v>
+        <v>0.3206543266788474</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0.005575616292307751</v>
+        <v>0.005559533698940396</v>
       </c>
       <c r="M52" t="n">
-        <v>0.01868335460030837</v>
+        <v>0.01134058524405515</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -4755,37 +5220,46 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>0.009267599997966548</v>
+        <v>34.92500000000002</v>
       </c>
       <c r="P52" t="n">
-        <v>0.0005343022972248991</v>
+        <v>0.3061500936386944</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.01961652719811411</v>
+        <v>33.75408934834007</v>
       </c>
       <c r="R52" t="n">
-        <v>35.32500000000002</v>
+        <v>2.331405828596664</v>
       </c>
       <c r="S52" t="n">
-        <v>0.3308651428571041</v>
+        <v>0.01284342625596111</v>
       </c>
       <c r="T52" t="n">
-        <v>34.6164789037036</v>
+        <v>0.1986850268676124</v>
       </c>
       <c r="U52" t="n">
-        <v>2.353743648037137</v>
+        <v>0.01622</v>
       </c>
       <c r="V52" t="n">
-        <v>0.01322031243075041</v>
+        <v>0.008110000000000001</v>
       </c>
       <c r="W52" t="n">
-        <v>0.2034058721493541</v>
+        <v>32.83159453257404</v>
       </c>
       <c r="X52" t="n">
-        <v>0.01728666666666667</v>
+        <v>0.01157922320647989</v>
       </c>
       <c r="Y52" t="n">
-        <v>33.75408893078473</v>
+        <v>0.0003444698247772432</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.01216839656025612</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0.000404172425993012</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.0136424721791035</v>
       </c>
     </row>
     <row r="53">
@@ -4800,10 +5274,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38.41666666666666</v>
+        <v>35.71666666666666</v>
       </c>
       <c r="D53" t="n">
-        <v>36.54999999999995</v>
+        <v>36.71428571428564</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -4812,25 +5286,25 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>2.238126974352284</v>
+        <v>2.225119195750334</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4370511859323505</v>
+        <v>0.3724108962071924</v>
       </c>
       <c r="I53" t="n">
         <v>28.98</v>
       </c>
       <c r="J53" t="n">
-        <v>0.09314611508350956</v>
+        <v>0.2482560989697474</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0.008164208448361089</v>
+        <v>0.005575616292307751</v>
       </c>
       <c r="M53" t="n">
-        <v>0.02804497875626173</v>
+        <v>0.01868335460030837</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -4838,82 +5312,91 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>0.006196243412663805</v>
+        <v>35.32500000000002</v>
       </c>
       <c r="P53" t="n">
-        <v>0.0008109233377192746</v>
+        <v>0.3308651428571041</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.02963924799363945</v>
+        <v>34.61647934279934</v>
       </c>
       <c r="R53" t="n">
-        <v>36.71428571428564</v>
+        <v>2.35374362871222</v>
       </c>
       <c r="S53" t="n">
-        <v>0.3724108962071924</v>
+        <v>0.0132203465779301</v>
       </c>
       <c r="T53" t="n">
-        <v>35.52745806381636</v>
+        <v>0.2034070546972727</v>
       </c>
       <c r="U53" t="n">
-        <v>2.377809672103136</v>
+        <v>0.01728666666666667</v>
       </c>
       <c r="V53" t="n">
-        <v>0.01354761894834775</v>
+        <v>0.008643333333333333</v>
       </c>
       <c r="W53" t="n">
-        <v>0.2068914338797341</v>
+        <v>33.75408934834007</v>
       </c>
       <c r="X53" t="n">
-        <v>0.01836666666666667</v>
+        <v>0.009267599997966548</v>
       </c>
       <c r="Y53" t="n">
-        <v>34.6164789037036</v>
+        <v>0.0005343022972248991</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.01961652719811411</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0.0006187360183830692</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0.02141846259900343</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BR09</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BR09_T_29</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>10.08333333333333</v>
+        <v>38.41666666666666</v>
       </c>
       <c r="D54" t="n">
-        <v>22.74159954433088</v>
+        <v>36.54999999999995</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>2.151754877317993</v>
+        <v>2.238126974352284</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.4370511859323505</v>
       </c>
       <c r="I54" t="n">
-        <v>28.995</v>
+        <v>28.98</v>
       </c>
       <c r="J54" t="n">
-        <v>0.8532992157616837</v>
+        <v>0.09314611508350956</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0.0143222143423807</v>
+        <v>0.008164208448361089</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>0.02804497875626173</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -4921,82 +5404,91 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>0.04417757490269928</v>
+        <v>36.71428571428564</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>0.3724108962071924</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>35.52745852239729</v>
       </c>
       <c r="R54" t="n">
-        <v>21.79285714285717</v>
+        <v>2.377809652778219</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>0.013547618883582</v>
       </c>
       <c r="T54" t="n">
-        <v>28.31816032897402</v>
+        <v>0.2068914320190097</v>
       </c>
       <c r="U54" t="n">
-        <v>2.196892860793617</v>
+        <v>0.01836666666666667</v>
       </c>
       <c r="V54" t="n">
-        <v>0.01041304424064643</v>
+        <v>0.009183333333333333</v>
       </c>
       <c r="W54" t="n">
-        <v>0.2042179130067702</v>
+        <v>34.61647934279934</v>
       </c>
       <c r="X54" t="n">
-        <v>0.007033333333333333</v>
+        <v>0.006196243412663805</v>
       </c>
       <c r="Y54" t="n">
-        <v>25.42114792085842</v>
+        <v>0.0008109233377192746</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.02963924799363945</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0.0008844102245227442</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0.03142084756851587</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BR09</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BR09_T_29</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>11.2</v>
+        <v>46.41666666666666</v>
       </c>
       <c r="D55" t="n">
-        <v>22.97108767528296</v>
+        <v>37.45357142857144</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>2.163697271557409</v>
+        <v>2.350696964539372</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>0.792026695150037</v>
       </c>
       <c r="I55" t="n">
-        <v>28.995</v>
+        <v>28.98</v>
       </c>
       <c r="J55" t="n">
-        <v>0.4955894525174036</v>
+        <v>0.2428851122484339</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0.00991189089150895</v>
+        <v>0.02098979306862803</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>0.05964752041359847</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -5004,37 +5496,46 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>0.02615548495855645</v>
+        <v>36.54999999999995</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>0.4370511859323505</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>38.42283179751898</v>
       </c>
       <c r="R55" t="n">
-        <v>22.74159954433088</v>
+        <v>2.457676399311553</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>0.01423124238248942</v>
       </c>
       <c r="T55" t="n">
-        <v>28.49544748119097</v>
+        <v>0.2096355868065863</v>
       </c>
       <c r="U55" t="n">
-        <v>2.200944508712678</v>
+        <v>0.02156666666666666</v>
       </c>
       <c r="V55" t="n">
-        <v>0.01098357822667265</v>
+        <v>0.01078333333333333</v>
       </c>
       <c r="W55" t="n">
-        <v>0.216139031898086</v>
+        <v>35.52745852239729</v>
       </c>
       <c r="X55" t="n">
-        <v>0.007480000000000001</v>
+        <v>0.01541414394739185</v>
       </c>
       <c r="Y55" t="n">
-        <v>28.31816032897402</v>
+        <v>0.001781396691915808</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0.06671966824328958</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0.001733285414237975</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0.06659773392835872</v>
       </c>
     </row>
     <row r="56">
@@ -5049,10 +5550,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>12.66666666666667</v>
+        <v>10.08333333333333</v>
       </c>
       <c r="D56" t="n">
-        <v>24.12500000000008</v>
+        <v>22.74159954433088</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -5061,22 +5562,22 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>2.18231465451585</v>
+        <v>2.151754877317993</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>28.98790163201834</v>
+        <v>28.995</v>
       </c>
       <c r="J56" t="n">
-        <v>0.527194572758186</v>
+        <v>0.8532992157616837</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0.01009690660006621</v>
+        <v>0.0143222143423807</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -5087,37 +5588,46 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>0.02647932083128075</v>
+        <v>21.79285714285717</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>28.31815807004039</v>
       </c>
       <c r="R56" t="n">
-        <v>22.97108767528296</v>
+        <v>2.196892806206484</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>0.01041196717294989</v>
       </c>
       <c r="T56" t="n">
-        <v>28.74377861466887</v>
+        <v>0.2041873938903916</v>
       </c>
       <c r="U56" t="n">
-        <v>2.206644958857567</v>
+        <v>0.007033333333333333</v>
       </c>
       <c r="V56" t="n">
-        <v>0.01171774454065133</v>
+        <v>0.003516666666666667</v>
       </c>
       <c r="W56" t="n">
-        <v>0.2317357767803047</v>
+        <v>25.42114791934122</v>
       </c>
       <c r="X56" t="n">
-        <v>0.008066666666666666</v>
+        <v>0.04417757490269928</v>
       </c>
       <c r="Y56" t="n">
-        <v>28.49544748119097</v>
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5132,10 +5642,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>13.85</v>
+        <v>11.2</v>
       </c>
       <c r="D57" t="n">
-        <v>24.57500000000017</v>
+        <v>22.97108767528296</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -5144,22 +5654,22 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>2.193791961026335</v>
+        <v>2.163697271557409</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>28.98710002854261</v>
+        <v>28.995</v>
       </c>
       <c r="J57" t="n">
-        <v>0.4106539365163594</v>
+        <v>0.4955894525174036</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0.01080044764312056</v>
+        <v>0.00991189089150895</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -5170,37 +5680,46 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>0.02163341820285943</v>
+        <v>22.74159954433088</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>28.49544506515976</v>
       </c>
       <c r="R57" t="n">
-        <v>24.12500000000008</v>
+        <v>2.200944449147011</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>0.01098357032200971</v>
       </c>
       <c r="T57" t="n">
-        <v>28.95677039510294</v>
+        <v>0.2161387857045839</v>
       </c>
       <c r="U57" t="n">
-        <v>2.211557769325928</v>
+        <v>0.007480000000000001</v>
       </c>
       <c r="V57" t="n">
-        <v>0.01228110398018093</v>
+        <v>0.00374</v>
       </c>
       <c r="W57" t="n">
-        <v>0.2438036270068062</v>
+        <v>28.31815807004039</v>
       </c>
       <c r="X57" t="n">
-        <v>0.008539999999999999</v>
+        <v>0.02615548495855645</v>
       </c>
       <c r="Y57" t="n">
-        <v>28.74377861466887</v>
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -5215,10 +5734,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>15.31666666666667</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="D58" t="n">
-        <v>25.06785714285721</v>
+        <v>24.12500000000008</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -5227,22 +5746,22 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>2.214828125862959</v>
+        <v>2.18231465451585</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>28.98</v>
+        <v>28.98790163201834</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3756303196153055</v>
+        <v>0.527194572758186</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0.009872310665280869</v>
+        <v>0.01009690660006621</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -5253,37 +5772,46 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>0.01944191146369945</v>
+        <v>22.97108767528296</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>28.74377626618266</v>
       </c>
       <c r="R58" t="n">
-        <v>24.57500000000017</v>
+        <v>2.2066448992919</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>0.01171780391374263</v>
       </c>
       <c r="T58" t="n">
-        <v>29.2361683854742</v>
+        <v>0.2317374616169707</v>
       </c>
       <c r="U58" t="n">
-        <v>2.218035553581483</v>
+        <v>0.008066666666666666</v>
       </c>
       <c r="V58" t="n">
-        <v>0.01296734667627982</v>
+        <v>0.004033333333333333</v>
       </c>
       <c r="W58" t="n">
-        <v>0.2588159428505661</v>
+        <v>28.49544506515976</v>
       </c>
       <c r="X58" t="n">
-        <v>0.009126666666666668</v>
+        <v>0.02647932083128075</v>
       </c>
       <c r="Y58" t="n">
-        <v>28.95677039510294</v>
+        <v>0</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5298,10 +5826,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>17.98333333333333</v>
+        <v>13.85</v>
       </c>
       <c r="D59" t="n">
-        <v>25.90000000000013</v>
+        <v>24.57500000000017</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -5310,22 +5838,22 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>2.214024096070052</v>
+        <v>2.193791961026335</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>28.98</v>
+        <v>28.98710002854261</v>
       </c>
       <c r="J59" t="n">
-        <v>0.3298559424945083</v>
+        <v>0.4106539365163594</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0.008518133778895404</v>
+        <v>0.01080044764312056</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -5336,37 +5864,46 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>0.01658310436687791</v>
+        <v>24.12500000000008</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>28.95676810363952</v>
       </c>
       <c r="R59" t="n">
-        <v>25.06785714285721</v>
+        <v>2.211557709760262</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>0.01228108243496568</v>
       </c>
       <c r="T59" t="n">
-        <v>29.78688518662393</v>
+        <v>0.2438029808221922</v>
       </c>
       <c r="U59" t="n">
-        <v>2.230915566461483</v>
+        <v>0.008539999999999999</v>
       </c>
       <c r="V59" t="n">
-        <v>0.01413308769286362</v>
+        <v>0.004269999999999999</v>
       </c>
       <c r="W59" t="n">
-        <v>0.2848806420287301</v>
+        <v>28.74377626618266</v>
       </c>
       <c r="X59" t="n">
-        <v>0.01019333333333333</v>
+        <v>0.02163341820285943</v>
       </c>
       <c r="Y59" t="n">
-        <v>29.2361683854742</v>
+        <v>0</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5381,10 +5918,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>23.56666666666667</v>
+        <v>15.31666666666667</v>
       </c>
       <c r="D60" t="n">
-        <v>27.37499999999996</v>
+        <v>25.06785714285721</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -5393,22 +5930,22 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>2.307573593937551</v>
+        <v>2.214828125862959</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>28.99338819905182</v>
+        <v>28.98</v>
       </c>
       <c r="J60" t="n">
-        <v>0.3454451519070621</v>
+        <v>0.3756303196153055</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0.0129230258223817</v>
+        <v>0.009872310665280869</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -5419,37 +5956,46 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>0.01821926693166444</v>
+        <v>24.57500000000017</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>29.2361661686984</v>
       </c>
       <c r="R60" t="n">
-        <v>25.90000000000013</v>
+        <v>2.218035494015818</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>0.01296737669517052</v>
       </c>
       <c r="T60" t="n">
-        <v>31.11037508564176</v>
+        <v>0.2588167976329628</v>
       </c>
       <c r="U60" t="n">
-        <v>2.262489348035233</v>
+        <v>0.009126666666666668</v>
       </c>
       <c r="V60" t="n">
-        <v>0.01625131044668814</v>
+        <v>0.004563333333333334</v>
       </c>
       <c r="W60" t="n">
-        <v>0.3347113995646889</v>
+        <v>28.95676810363952</v>
       </c>
       <c r="X60" t="n">
-        <v>0.01242666666666667</v>
+        <v>0.01944191146369945</v>
       </c>
       <c r="Y60" t="n">
-        <v>29.78688518662393</v>
+        <v>0</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5464,10 +6010,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>25.13333333333333</v>
+        <v>17.98333333333333</v>
       </c>
       <c r="D61" t="n">
-        <v>28.11428571428576</v>
+        <v>25.90000000000013</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -5476,22 +6022,22 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>2.324643491537374</v>
+        <v>2.214024096070052</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>28.98907356082457</v>
+        <v>28.98</v>
       </c>
       <c r="J61" t="n">
-        <v>0.2438328224960159</v>
+        <v>0.3298559424945083</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0.01425711185829255</v>
+        <v>0.008518133778895404</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -5502,37 +6048,46 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>0.01480594697664882</v>
+        <v>25.06785714285721</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>29.78688303253967</v>
       </c>
       <c r="R61" t="n">
-        <v>27.37499999999996</v>
+        <v>2.230915506895817</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>0.01413309295165512</v>
       </c>
       <c r="T61" t="n">
-        <v>31.5210476313021</v>
+        <v>0.2848807744362734</v>
       </c>
       <c r="U61" t="n">
-        <v>2.272469024681567</v>
+        <v>0.01019333333333333</v>
       </c>
       <c r="V61" t="n">
-        <v>0.01679001717135276</v>
+        <v>0.005096666666666667</v>
       </c>
       <c r="W61" t="n">
-        <v>0.3481782708526754</v>
+        <v>29.2361661686984</v>
       </c>
       <c r="X61" t="n">
-        <v>0.01305333333333333</v>
+        <v>0.01658310436687791</v>
       </c>
       <c r="Y61" t="n">
-        <v>31.11037508564176</v>
+        <v>0</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -5547,10 +6102,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>26.68333333333333</v>
+        <v>23.56666666666667</v>
       </c>
       <c r="D62" t="n">
-        <v>28.14285714285706</v>
+        <v>27.37499999999996</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -5559,22 +6114,22 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>2.352668497327067</v>
+        <v>2.307573593937551</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>28.995</v>
+        <v>28.99338819905182</v>
       </c>
       <c r="J62" t="n">
-        <v>0.3483746225501007</v>
+        <v>0.3454451519070621</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0.01556696786466986</v>
+        <v>0.0129230258223817</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -5585,37 +6140,46 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>0.01899552184075797</v>
+        <v>25.90000000000013</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>31.11037299665006</v>
       </c>
       <c r="R62" t="n">
-        <v>28.11428571428576</v>
+        <v>2.262489288469567</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>0.01625124162510059</v>
       </c>
       <c r="T62" t="n">
-        <v>31.94343405366691</v>
+        <v>0.3347092315256564</v>
       </c>
       <c r="U62" t="n">
-        <v>2.282825618371483</v>
+        <v>0.01242666666666667</v>
       </c>
       <c r="V62" t="n">
-        <v>0.01726817068693205</v>
+        <v>0.006213333333333333</v>
       </c>
       <c r="W62" t="n">
-        <v>0.3602745856788814</v>
+        <v>29.78688303253967</v>
       </c>
       <c r="X62" t="n">
-        <v>0.01367333333333333</v>
+        <v>0.01821926693166444</v>
       </c>
       <c r="Y62" t="n">
-        <v>31.5210476313021</v>
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -5630,10 +6194,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>28.15</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="D63" t="n">
-        <v>29.46071428571427</v>
+        <v>28.11428571428576</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -5642,22 +6206,22 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>2.375720882565579</v>
+        <v>2.324643491537374</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>28.995</v>
+        <v>28.98907356082457</v>
       </c>
       <c r="J63" t="n">
-        <v>0.4669603785258343</v>
+        <v>0.2438328224960159</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0.01540779486614794</v>
+        <v>0.01425711185829255</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -5668,37 +6232,46 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>0.02233579751349438</v>
+        <v>27.37499999999996</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>31.52104556228423</v>
       </c>
       <c r="R63" t="n">
-        <v>28.14285714285706</v>
+        <v>2.272468965115901</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>0.01679004299276455</v>
       </c>
       <c r="T63" t="n">
-        <v>32.35740390067283</v>
+        <v>0.3481790571704745</v>
       </c>
       <c r="U63" t="n">
-        <v>2.293067850835928</v>
+        <v>0.01305333333333333</v>
       </c>
       <c r="V63" t="n">
-        <v>0.01769926548522211</v>
+        <v>0.006526666666666667</v>
       </c>
       <c r="W63" t="n">
-        <v>0.3714798980485495</v>
+        <v>31.11037299665006</v>
       </c>
       <c r="X63" t="n">
-        <v>0.01426</v>
+        <v>0.01480594697664882</v>
       </c>
       <c r="Y63" t="n">
-        <v>31.94343405366691</v>
+        <v>0</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -5713,10 +6286,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>31.18333333333333</v>
+        <v>26.68333333333333</v>
       </c>
       <c r="D64" t="n">
-        <v>30.54107142857147</v>
+        <v>28.14285714285706</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -5725,22 +6298,22 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>2.429480867954015</v>
+        <v>2.352668497327067</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>28.98</v>
+        <v>28.995</v>
       </c>
       <c r="J64" t="n">
-        <v>0.1393496146836234</v>
+        <v>0.3483746225501007</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0.01356607661731992</v>
+        <v>0.01556696786466986</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -5751,37 +6324,46 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>0.01014663618242141</v>
+        <v>28.11428571428576</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>31.94343200509588</v>
       </c>
       <c r="R64" t="n">
-        <v>29.46071428571427</v>
+        <v>2.282825558805818</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>0.01726816390210312</v>
       </c>
       <c r="T64" t="n">
-        <v>33.25583448054279</v>
+        <v>0.360274340850948</v>
       </c>
       <c r="U64" t="n">
-        <v>2.315615651161483</v>
+        <v>0.01367333333333333</v>
       </c>
       <c r="V64" t="n">
-        <v>0.01851307209935324</v>
+        <v>0.006836666666666666</v>
       </c>
       <c r="W64" t="n">
-        <v>0.3934465808882616</v>
+        <v>31.52104556228423</v>
       </c>
       <c r="X64" t="n">
-        <v>0.01547333333333333</v>
+        <v>0.01899552184075797</v>
       </c>
       <c r="Y64" t="n">
-        <v>32.35740390067283</v>
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5796,10 +6378,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>34.18333333333334</v>
+        <v>28.15</v>
       </c>
       <c r="D65" t="n">
-        <v>30.00357142857132</v>
+        <v>29.46071428571427</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -5808,7 +6390,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>2.451704147576396</v>
+        <v>2.375720882565579</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -5817,13 +6399,13 @@
         <v>28.995</v>
       </c>
       <c r="J65" t="n">
-        <v>0.08855763882758942</v>
+        <v>0.4669603785258343</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0.01490221644458623</v>
+        <v>0.01540779486614794</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -5834,37 +6416,46 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>0.00902987934884078</v>
+        <v>28.14285714285706</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>32.3574018720367</v>
       </c>
       <c r="R65" t="n">
-        <v>30.54107142857147</v>
+        <v>2.293067791270262</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>0.01769926440963473</v>
       </c>
       <c r="T65" t="n">
-        <v>34.19735536914632</v>
+        <v>0.3714798347284995</v>
       </c>
       <c r="U65" t="n">
-        <v>2.339725675271483</v>
+        <v>0.01426</v>
       </c>
       <c r="V65" t="n">
-        <v>0.01919069898130528</v>
+        <v>0.007129999999999999</v>
       </c>
       <c r="W65" t="n">
-        <v>0.4125742480274263</v>
+        <v>31.94343200509588</v>
       </c>
       <c r="X65" t="n">
-        <v>0.01667333333333334</v>
+        <v>0.02233579751349438</v>
       </c>
       <c r="Y65" t="n">
-        <v>33.25583448054279</v>
+        <v>0</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -5879,10 +6470,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>35.7</v>
+        <v>31.18333333333333</v>
       </c>
       <c r="D66" t="n">
-        <v>30.12857142857151</v>
+        <v>30.54107142857147</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -5891,22 +6482,22 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>2.481063784627632</v>
+        <v>2.429480867954015</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>29.01</v>
+        <v>28.98</v>
       </c>
       <c r="J66" t="n">
-        <v>0.2239877292055531</v>
+        <v>0.1393496146836234</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0.01559421357166551</v>
+        <v>0.01356607661731992</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -5917,37 +6508,46 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>0.01371968923896166</v>
+        <v>29.46071428571427</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>33.25583249482232</v>
       </c>
       <c r="R66" t="n">
-        <v>30.00357142857132</v>
+        <v>2.315615591595817</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>0.01851308273432502</v>
       </c>
       <c r="T66" t="n">
-        <v>34.69219417667006</v>
+        <v>0.3934469053539372</v>
       </c>
       <c r="U66" t="n">
-        <v>2.352599660367677</v>
+        <v>0.01547333333333333</v>
       </c>
       <c r="V66" t="n">
-        <v>0.01948898852875239</v>
+        <v>0.007736666666666666</v>
       </c>
       <c r="W66" t="n">
-        <v>0.4212993151451641</v>
+        <v>32.3574018720367</v>
       </c>
       <c r="X66" t="n">
-        <v>0.01728</v>
+        <v>0.01014663618242141</v>
       </c>
       <c r="Y66" t="n">
-        <v>34.19735536914632</v>
+        <v>0</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5962,75 +6562,268 @@
         </is>
       </c>
       <c r="C67" t="n">
+        <v>34.18333333333334</v>
+      </c>
+      <c r="D67" t="n">
+        <v>30.00357142857132</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2.451704147576396</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>28.995</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.08855763882758942</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.01490221644458623</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>30.54107142857147</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>34.19735342816631</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2.339725615705817</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0.01919070522193477</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0.4125744318193387</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0.01667333333333334</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0.008336666666666668</v>
+      </c>
+      <c r="W67" t="n">
+        <v>33.25583249482232</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0.00902987934884078</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BR09</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>BR09_T_29</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="D68" t="n">
+        <v>30.12857142857151</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2.481063784627632</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.2239877292055531</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.01559421357166551</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>30.00357142857132</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>34.69219227608998</v>
+      </c>
+      <c r="R68" t="n">
+        <v>2.352599600802012</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0.01948896483444288</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.4212984636054069</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0.01728</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0.00864</v>
+      </c>
+      <c r="W68" t="n">
+        <v>34.19735342816631</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0.01371968923896166</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BR09</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BR09_T_29</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
         <v>36.75</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D69" t="n">
         <v>30.54107142857147</v>
       </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
         <v>2.497032422101453</v>
       </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
         <v>28.98</v>
       </c>
-      <c r="J67" t="n">
+      <c r="J69" t="n">
         <v>0.5198551448550432</v>
       </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
         <v>0.01351059041225433</v>
       </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="inlineStr">
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="O67" t="n">
+      <c r="O69" t="n">
+        <v>30.12857142857151</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>35.04183579224857</v>
+      </c>
+      <c r="R69" t="n">
+        <v>2.361781859984262</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0.01970497485318354</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0.4278830060214355</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0.00885</v>
+      </c>
+      <c r="W69" t="n">
+        <v>34.69219227608998</v>
+      </c>
+      <c r="X69" t="n">
         <v>0.0224321685275548</v>
       </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>30.12857142857151</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>35.04183767661643</v>
-      </c>
-      <c r="U67" t="n">
-        <v>2.361781919549927</v>
-      </c>
-      <c r="V67" t="n">
-        <v>0.01970497329658792</v>
-      </c>
-      <c r="W67" t="n">
-        <v>0.4278829811081218</v>
-      </c>
-      <c r="X67" t="n">
-        <v>0.0177</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>34.69219417667006</v>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/BR_processed_ind.xlsx
+++ b/data/processed/BR_processed_ind.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB69"/>
+  <dimension ref="A1:AB67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,7 +656,7 @@
         <v>0.03252295278732637</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001220189719696315</v>
+        <v>0.001220189719696316</v>
       </c>
       <c r="AB2" t="n">
         <v>0.03252295278732637</v>
@@ -1300,7 +1300,7 @@
         <v>0.4847102107155994</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01902416488705139</v>
+        <v>0.0190241648870514</v>
       </c>
       <c r="AB9" t="n">
         <v>0.5387038540642539</v>
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.006015752972438382</v>
+        <v>0.006015752972438381</v>
       </c>
       <c r="Z11" t="n">
         <v>0.1619956336149481</v>
@@ -1576,7 +1576,7 @@
         <v>0.0921971490896749</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.003588200271870521</v>
+        <v>0.003588200271870522</v>
       </c>
       <c r="AB12" t="n">
         <v>0.1003600680355974</v>
@@ -1754,13 +1754,13 @@
         <v>0.02643890324335607</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0059864661796889</v>
+        <v>0.005986466179688899</v>
       </c>
       <c r="Z14" t="n">
         <v>0.166038915540943</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.005834624532342146</v>
+        <v>0.005834624532342147</v>
       </c>
       <c r="AB14" t="n">
         <v>0.1751119665341944</v>
@@ -2030,13 +2030,13 @@
         <v>0.04062202704143002</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.002657762910916001</v>
+        <v>0.002657762910916</v>
       </c>
       <c r="Z17" t="n">
         <v>0.0816312894067058</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.004090749458226509</v>
+        <v>0.00409074945822651</v>
       </c>
       <c r="AB17" t="n">
         <v>0.08179186507452586</v>
@@ -2398,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.002253668672706708</v>
+        <v>0.002253668672706707</v>
       </c>
       <c r="Z21" t="n">
         <v>0.07526448485171559</v>
@@ -2588,7 +2588,7 @@
         <v>0.06320238611045444</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.004235445898201378</v>
+        <v>0.004235445898201379</v>
       </c>
       <c r="AB23" t="n">
         <v>0.06361509502651258</v>
@@ -2680,7 +2680,7 @@
         <v>0.05093049240086417</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.003538733655060629</v>
+        <v>0.003538733655060628</v>
       </c>
       <c r="AB24" t="n">
         <v>0.0536319778251635</v>
@@ -2956,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.0006703122036587194</v>
+        <v>0.0006703122036587193</v>
       </c>
       <c r="AB27" t="n">
         <v>0.01042051580594177</v>
@@ -3324,7 +3324,7 @@
         <v>0.04872158819598323</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.002019535772512294</v>
+        <v>0.002019535772512295</v>
       </c>
       <c r="AB31" t="n">
         <v>0.0495778372711814</v>
@@ -3778,7 +3778,7 @@
         <v>0.00813246080612828</v>
       </c>
       <c r="Y36" t="n">
-        <v>5.72212406026065e-05</v>
+        <v>5.722124060260651e-05</v>
       </c>
       <c r="Z36" t="n">
         <v>0.001647154283060745</v>
@@ -4161,19 +4161,19 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BR07_T_32</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>46.93333333333334</v>
+        <v>10.13333333333333</v>
       </c>
       <c r="D41" t="n">
-        <v>31.93571428571439</v>
+        <v>27.80357142857142</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
@@ -4182,72 +4182,72 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>2.515307377137465</v>
+        <v>2.111411826295212</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7360300997802449</v>
+        <v>0.05060060245371522</v>
       </c>
       <c r="I41" t="n">
-        <v>32.01</v>
+        <v>29.01</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3122489136229731</v>
+        <v>1.292833793699242</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.02633606438824609</v>
+        <v>0.0006879481871742564</v>
       </c>
       <c r="M41" t="n">
-        <v>0.06894461020814052</v>
+        <v>0.04290404542881167</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>30.88214285714287</v>
+        <v>25.66428571428573</v>
       </c>
       <c r="P41" t="n">
-        <v>0.3954213588988506</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>34.84968576356186</v>
+        <v>28.24180486689044</v>
       </c>
       <c r="R41" t="n">
-        <v>2.35351377776252</v>
+        <v>2.198068889704303</v>
       </c>
       <c r="S41" t="n">
-        <v>0.01654179887468221</v>
+        <v>0.007073425374068638</v>
       </c>
       <c r="T41" t="n">
-        <v>0.4152720349990039</v>
+        <v>0.1091418130006905</v>
       </c>
       <c r="U41" t="n">
-        <v>0.01088666666666667</v>
+        <v>0.007053333333333333</v>
       </c>
       <c r="V41" t="n">
-        <v>0.01088666666666667</v>
+        <v>0.003526666666666667</v>
       </c>
       <c r="W41" t="n">
-        <v>31.81469618008588</v>
+        <v>24.01327123307239</v>
       </c>
       <c r="X41" t="n">
-        <v>0.02024773721229721</v>
+        <v>0.04682466286201208</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.002400167963573594</v>
+        <v>0.001543705722077936</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.07665107832241122</v>
+        <v>0.04292053230848831</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.002076037952137571</v>
+        <v>0.001524917290366768</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.07234927026522282</v>
+        <v>0.04306641655268557</v>
       </c>
     </row>
     <row r="42">
@@ -4262,10 +4262,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>10.13333333333333</v>
+        <v>11.56666666666667</v>
       </c>
       <c r="D42" t="n">
-        <v>27.80357142857142</v>
+        <v>28.21071428571433</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -4274,72 +4274,72 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>2.111411826295212</v>
+        <v>2.092706775844421</v>
       </c>
       <c r="H42" t="n">
+        <v>0.1044036282464569</v>
+      </c>
+      <c r="I42" t="n">
+        <v>28.995</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.4995599667938492</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-0.01656280347506739</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.03752923222291429</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>27.80357142857142</v>
+      </c>
+      <c r="P42" t="n">
         <v>0.05060060245371522</v>
       </c>
-      <c r="I42" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="J42" t="n">
-        <v>1.292833793699242</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.0006879481871742564</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.04290404542881167</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O42" t="n">
-        <v>25.66428571428573</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
       <c r="Q42" t="n">
+        <v>28.4719136932896</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.20332922829797</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.007575517607850952</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.1171359889591415</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.007626666666666667</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.003813333333333334</v>
+      </c>
+      <c r="W42" t="n">
         <v>28.24180486689044</v>
       </c>
-      <c r="R42" t="n">
-        <v>2.198068889704303</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0.007073425374068638</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0.1091418130006905</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.007053333333333333</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0.003526666666666667</v>
-      </c>
-      <c r="W42" t="n">
-        <v>24.01327123307239</v>
-      </c>
       <c r="X42" t="n">
-        <v>0.04682466286201208</v>
+        <v>0.009793628241382288</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.001543705722077936</v>
+        <v>0.001301027884616268</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.04292053230848831</v>
+        <v>0.03670292593065684</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.001524917290366768</v>
+        <v>0.001330806855107746</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.04306641655268557</v>
+        <v>0.03789061792106591</v>
       </c>
     </row>
     <row r="43">
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>11.56666666666667</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="D43" t="n">
-        <v>28.21071428571433</v>
+        <v>28.84999999999995</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -4366,25 +4366,25 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>2.092706775844421</v>
+        <v>2.059106202419109</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1044036282464569</v>
+        <v>0.1491197853115378</v>
       </c>
       <c r="I43" t="n">
         <v>28.995</v>
       </c>
       <c r="J43" t="n">
-        <v>0.4995599667938492</v>
+        <v>0.5552285401125786</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.01656280347506739</v>
+        <v>-0.01268043122870065</v>
       </c>
       <c r="M43" t="n">
-        <v>0.03752923222291429</v>
+        <v>0.03318261877259444</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -4392,46 +4392,46 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>27.80357142857142</v>
+        <v>28.21071428571433</v>
       </c>
       <c r="P43" t="n">
-        <v>0.05060060245371522</v>
+        <v>0.1044036282464569</v>
       </c>
       <c r="Q43" t="n">
+        <v>28.65987999487133</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.207644899280303</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.00794445905433588</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0.1229649217459896</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.008066666666666666</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.004033333333333333</v>
+      </c>
+      <c r="W43" t="n">
         <v>28.4719136932896</v>
       </c>
-      <c r="R43" t="n">
-        <v>2.20332922829797</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0.007575517607850952</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0.1171359889591415</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0.007626666666666667</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0.003813333333333334</v>
-      </c>
-      <c r="W43" t="n">
-        <v>28.24180486689044</v>
-      </c>
       <c r="X43" t="n">
-        <v>0.009793628241382288</v>
+        <v>0.01308713559294417</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.001301027884616268</v>
+        <v>0.00111834683420231</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.03670292593065684</v>
+        <v>0.03226430616673658</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.001330806855107746</v>
+        <v>0.001176819229347405</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.03789061792106591</v>
+        <v>0.03372749788875357</v>
       </c>
     </row>
     <row r="44">
@@ -4446,10 +4446,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12.66666666666667</v>
+        <v>14.13333333333333</v>
       </c>
       <c r="D44" t="n">
-        <v>28.84999999999995</v>
+        <v>29.8214285714287</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
@@ -4458,25 +4458,25 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>2.059106202419109</v>
+        <v>2.054382414798483</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1491197853115378</v>
+        <v>0.1918414613393818</v>
       </c>
       <c r="I44" t="n">
         <v>28.995</v>
       </c>
       <c r="J44" t="n">
-        <v>0.5552285401125786</v>
+        <v>0.4551298135529764</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.01268043122870065</v>
+        <v>-0.00225385966014273</v>
       </c>
       <c r="M44" t="n">
-        <v>0.03318261877259444</v>
+        <v>0.02512562920803933</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -4484,46 +4484,46 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>28.21071428571433</v>
+        <v>28.84999999999995</v>
       </c>
       <c r="P44" t="n">
-        <v>0.1044036282464569</v>
+        <v>0.1491197853115378</v>
       </c>
       <c r="Q44" t="n">
+        <v>28.92563754904613</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2.213775572077636</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.008420554940362099</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0.1305037237789281</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0.008653333333333332</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.004326666666666666</v>
+      </c>
+      <c r="W44" t="n">
         <v>28.65987999487133</v>
       </c>
-      <c r="R44" t="n">
-        <v>2.207644899280303</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0.00794445905433588</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0.1229649217459896</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0.008066666666666666</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0.004033333333333333</v>
-      </c>
-      <c r="W44" t="n">
-        <v>28.4719136932896</v>
-      </c>
       <c r="X44" t="n">
-        <v>0.01308713559294417</v>
+        <v>0.01416473965932023</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.00111834683420231</v>
+        <v>0.0008354784274698437</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.03226430616673658</v>
+        <v>0.02491516024776152</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.001176819229347405</v>
+        <v>0.0008945528030802108</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.03372749788875357</v>
+        <v>0.02587551015038141</v>
       </c>
     </row>
     <row r="45">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>14.13333333333333</v>
+        <v>16.85</v>
       </c>
       <c r="D45" t="n">
-        <v>29.8214285714287</v>
+        <v>30.18571428571434</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -4550,25 +4550,25 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>2.054382414798483</v>
+        <v>2.052763135178324</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1918414613393818</v>
+        <v>0.2448076315621145</v>
       </c>
       <c r="I45" t="n">
         <v>28.995</v>
       </c>
       <c r="J45" t="n">
-        <v>0.4551298135529764</v>
+        <v>0.2858643792140457</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.00225385966014273</v>
+        <v>0.004342262917761283</v>
       </c>
       <c r="M45" t="n">
-        <v>0.02512562920803933</v>
+        <v>0.01531393640884581</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -4576,46 +4576,46 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>28.84999999999995</v>
+        <v>29.8214285714287</v>
       </c>
       <c r="P45" t="n">
-        <v>0.1491197853115378</v>
+        <v>0.1918414613393818</v>
       </c>
       <c r="Q45" t="n">
+        <v>29.46262799242935</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2.226267723458665</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.009253028608468959</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0.1437185005742468</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.009740000000000002</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.004870000000000001</v>
+      </c>
+      <c r="W45" t="n">
         <v>28.92563754904613</v>
       </c>
-      <c r="R45" t="n">
-        <v>2.213775572077636</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0.008420554940362099</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0.1305037237789281</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0.008653333333333332</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0.004326666666666666</v>
-      </c>
-      <c r="W45" t="n">
-        <v>28.65987999487133</v>
-      </c>
       <c r="X45" t="n">
-        <v>0.01416473965932023</v>
+        <v>0.01158551351625574</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.0008354784274698437</v>
+        <v>0.0005244793669481728</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.02491516024776152</v>
+        <v>0.01583178431944987</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.0008945528030802108</v>
+        <v>0.0005561275272637983</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.02587551015038141</v>
+        <v>0.0163849784521229</v>
       </c>
     </row>
     <row r="46">
@@ -4630,10 +4630,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.85</v>
+        <v>22.4</v>
       </c>
       <c r="D46" t="n">
-        <v>30.18571428571434</v>
+        <v>32.48928571428564</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
@@ -4642,25 +4642,25 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>2.052763135178324</v>
+        <v>2.136378998440389</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2448076315621145</v>
+        <v>0.2862295508009267</v>
       </c>
       <c r="I46" t="n">
         <v>28.995</v>
       </c>
       <c r="J46" t="n">
-        <v>0.2858643792140457</v>
+        <v>0.2861652497401637</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.004342262917761283</v>
+        <v>0.002939955113684175</v>
       </c>
       <c r="M46" t="n">
-        <v>0.01531393640884581</v>
+        <v>0.003419686402695349</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -4668,46 +4668,46 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>29.8214285714287</v>
+        <v>30.18571428571434</v>
       </c>
       <c r="P46" t="n">
-        <v>0.1918414613393818</v>
+        <v>0.2448076315621145</v>
       </c>
       <c r="Q46" t="n">
+        <v>30.73245487142585</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2.256376503567415</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.01074722783805307</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0.1673902776698777</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0.01196</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.005979999999999999</v>
+      </c>
+      <c r="W46" t="n">
         <v>29.46262799242935</v>
       </c>
-      <c r="R46" t="n">
-        <v>2.226267723458665</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0.009253028608468959</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0.1437185005742468</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0.009740000000000002</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0.004870000000000001</v>
-      </c>
-      <c r="W46" t="n">
-        <v>28.92563754904613</v>
-      </c>
       <c r="X46" t="n">
-        <v>0.01158551351625574</v>
+        <v>0.01018412764647287</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.0005244793669481729</v>
+        <v>0.0001173795623522832</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.01583178431944987</v>
+        <v>0.003813578138281135</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.0005561275272637982</v>
+        <v>0.000160639813569606</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.0163849784521229</v>
+        <v>0.004936855821082178</v>
       </c>
     </row>
     <row r="47">
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>22.4</v>
+        <v>24.05</v>
       </c>
       <c r="D47" t="n">
-        <v>32.48928571428564</v>
+        <v>32.9321428571429</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -4734,72 +4734,72 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>2.136378998440389</v>
+        <v>2.119328558258994</v>
       </c>
       <c r="H47" t="n">
+        <v>0.2889524121591054</v>
+      </c>
+      <c r="I47" t="n">
+        <v>28.98962893733009</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.2278965996953445</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.003428148603602897</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.002167744356653061</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>32.48928571428564</v>
+      </c>
+      <c r="P47" t="n">
         <v>0.2862295508009267</v>
       </c>
-      <c r="I47" t="n">
-        <v>28.995</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.2861652497401637</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0.002939955113684175</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.003419686402695349</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O47" t="n">
-        <v>30.18571428571434</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0.2448076315621145</v>
-      </c>
       <c r="Q47" t="n">
+        <v>31.15248097069052</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.266515763706664</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.01113732683946593</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0.173497795470351</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0.01262</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.00631</v>
+      </c>
+      <c r="W47" t="n">
         <v>30.73245487142585</v>
       </c>
-      <c r="R47" t="n">
-        <v>2.256376503567415</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0.01074722783805307</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0.1673902776698777</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0.01196</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0.005979999999999999</v>
-      </c>
-      <c r="W47" t="n">
-        <v>29.46262799242935</v>
-      </c>
       <c r="X47" t="n">
-        <v>0.01018412764647287</v>
+        <v>0.0085377509283628</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.0001173795623522832</v>
+        <v>8.001736341849413e-05</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.003813578138281135</v>
+        <v>0.002635143243149769</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.000160639813569606</v>
+        <v>0.000121230682064597</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.004936855821082178</v>
+        <v>0.003776636516081191</v>
       </c>
     </row>
     <row r="48">
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>24.05</v>
+        <v>25.55</v>
       </c>
       <c r="D48" t="n">
-        <v>32.9321428571429</v>
+        <v>33.08366238246173</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -4826,72 +4826,72 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>2.119328558258994</v>
+        <v>2.122927932215827</v>
       </c>
       <c r="H48" t="n">
+        <v>0.2916972101212668</v>
+      </c>
+      <c r="I48" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.2049207718657497</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.01007802025635504</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.002083661045468459</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>32.9321428571429</v>
+      </c>
+      <c r="P48" t="n">
         <v>0.2889524121591054</v>
       </c>
-      <c r="I48" t="n">
-        <v>28.98962893733009</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.2278965996953445</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.003428148603602897</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.002167744356653061</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O48" t="n">
-        <v>32.48928571428564</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0.2862295508009267</v>
-      </c>
       <c r="Q48" t="n">
+        <v>31.55039960381771</v>
+      </c>
+      <c r="R48" t="n">
+        <v>2.276205773396665</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.01147068869907342</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0.1786629068909775</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0.01322</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.00661</v>
+      </c>
+      <c r="W48" t="n">
         <v>31.15248097069052</v>
       </c>
-      <c r="R48" t="n">
-        <v>2.266515763706664</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0.01113732683946593</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0.173497795470351</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0.01262</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0.00631</v>
-      </c>
-      <c r="W48" t="n">
-        <v>30.73245487142585</v>
-      </c>
       <c r="X48" t="n">
-        <v>0.0085377509283628</v>
+        <v>0.01094124388489767</v>
       </c>
       <c r="Y48" t="n">
-        <v>8.001736341849413e-05</v>
+        <v>0.0001048376628482425</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.002635143243149769</v>
+        <v>0.003468413842637606</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.000121230682064597</v>
+        <v>0.0001197389718612531</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.003776636516081191</v>
+        <v>0.003777812410372821</v>
       </c>
     </row>
     <row r="49">
@@ -4906,10 +4906,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>25.55</v>
+        <v>27.01666666666667</v>
       </c>
       <c r="D49" t="n">
-        <v>33.08366238246173</v>
+        <v>33.286006759061</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
@@ -4918,25 +4918,25 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>2.122927932215827</v>
+        <v>2.149102129882635</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2916972101212668</v>
+        <v>0.2947411967231239</v>
       </c>
       <c r="I49" t="n">
         <v>29.01</v>
       </c>
       <c r="J49" t="n">
-        <v>0.2049207718657497</v>
+        <v>0.2878082500112895</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.01007802025635504</v>
+        <v>0.01358415797906408</v>
       </c>
       <c r="M49" t="n">
-        <v>0.002083661045468459</v>
+        <v>0.002564129205513765</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -4944,46 +4944,46 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>32.9321428571429</v>
+        <v>33.08366238246173</v>
       </c>
       <c r="P49" t="n">
-        <v>0.2889524121591054</v>
+        <v>0.2916972101212668</v>
       </c>
       <c r="Q49" t="n">
+        <v>31.95385449141564</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2.28611556108422</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.01177718080478872</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.1833456058247001</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.01380666666666667</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.006903333333333334</v>
+      </c>
+      <c r="W49" t="n">
         <v>31.55039960381771</v>
       </c>
-      <c r="R49" t="n">
-        <v>2.276205773396665</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0.01147068869907342</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0.1786629068909775</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0.01322</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0.00661</v>
-      </c>
-      <c r="W49" t="n">
-        <v>31.15248097069052</v>
-      </c>
       <c r="X49" t="n">
-        <v>0.01094124388489767</v>
+        <v>0.01496737650102324</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.0001048376628482425</v>
+        <v>0.0001330031843039391</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.003468413842637606</v>
+        <v>0.004427144891717553</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.0001197389718612531</v>
+        <v>0.0001359515592164663</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.003777812410372821</v>
+        <v>0.004344176341084041</v>
       </c>
     </row>
     <row r="50">
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>27.01666666666667</v>
+        <v>30.05</v>
       </c>
       <c r="D50" t="n">
-        <v>33.286006759061</v>
+        <v>34.92500000000002</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -5010,72 +5010,72 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>2.149102129882635</v>
+        <v>2.204791765804646</v>
       </c>
       <c r="H50" t="n">
+        <v>0.3061500936386944</v>
+      </c>
+      <c r="I50" t="n">
+        <v>28.995</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.3273118051359381</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.01005866658037854</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.005592359312335324</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>33.286006759061</v>
+      </c>
+      <c r="P50" t="n">
         <v>0.2947411967231239</v>
       </c>
-      <c r="I50" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.2878082500112895</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0.01358415797906408</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.002564129205513765</v>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O50" t="n">
-        <v>33.08366238246173</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0.2916972101212668</v>
-      </c>
       <c r="Q50" t="n">
+        <v>32.83159453257404</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2.307975805166664</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.01235151587956077</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.1918563046190789</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0.01502</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.007509999999999999</v>
+      </c>
+      <c r="W50" t="n">
         <v>31.95385449141564</v>
       </c>
-      <c r="R50" t="n">
-        <v>2.28611556108422</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0.01177718080478872</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0.1833456058247001</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0.01380666666666667</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0.006903333333333334</v>
-      </c>
-      <c r="W50" t="n">
-        <v>31.55039960381771</v>
-      </c>
       <c r="X50" t="n">
-        <v>0.01496737650102324</v>
+        <v>0.01393403278476044</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.0001330031843039391</v>
+        <v>0.0002001166067567213</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.004427144891717553</v>
+        <v>0.006989072490978496</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.0001359515592164663</v>
+        <v>0.0002310196494435016</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.004344176341084041</v>
+        <v>0.007584743459586439</v>
       </c>
     </row>
     <row r="51">
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>30.05</v>
+        <v>33.05</v>
       </c>
       <c r="D51" t="n">
-        <v>34.92500000000002</v>
+        <v>35.32500000000002</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -5102,72 +5102,72 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>2.204791765804646</v>
+        <v>2.222071473920533</v>
       </c>
       <c r="H51" t="n">
+        <v>0.3308651428571041</v>
+      </c>
+      <c r="I51" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.3206543266788474</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.005559533698940396</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.01134058524405515</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>34.92500000000002</v>
+      </c>
+      <c r="P51" t="n">
         <v>0.3061500936386944</v>
       </c>
-      <c r="I51" t="n">
-        <v>28.995</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.3273118051359381</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0.01005866658037854</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0.005592359312335324</v>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O51" t="n">
-        <v>33.286006759061</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0.2947411967231239</v>
-      </c>
       <c r="Q51" t="n">
+        <v>33.75408934834007</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2.331405828596664</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.01284342625596111</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.1986850268676124</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.008110000000000001</v>
+      </c>
+      <c r="W51" t="n">
         <v>32.83159453257404</v>
       </c>
-      <c r="R51" t="n">
-        <v>2.307975805166664</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0.01235151587956077</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0.1918563046190789</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0.01502</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0.007509999999999999</v>
-      </c>
-      <c r="W51" t="n">
-        <v>31.95385449141564</v>
-      </c>
       <c r="X51" t="n">
-        <v>0.01393403278476044</v>
+        <v>0.01157922320647989</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.0002001166067567213</v>
+        <v>0.0003444698247772432</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.006989072490978496</v>
+        <v>0.01216839656025612</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.0002310196494435016</v>
+        <v>0.0004041724259930121</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.007584743459586439</v>
+        <v>0.0136424721791035</v>
       </c>
     </row>
     <row r="52">
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>33.05</v>
+        <v>35.71666666666666</v>
       </c>
       <c r="D52" t="n">
-        <v>35.32500000000002</v>
+        <v>36.71428571428564</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
@@ -5194,72 +5194,72 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>2.222071473920533</v>
+        <v>2.225119195750334</v>
       </c>
       <c r="H52" t="n">
+        <v>0.3724108962071924</v>
+      </c>
+      <c r="I52" t="n">
+        <v>28.98</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.2482560989697474</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.005575616292307751</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.01868335460030837</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>35.32500000000002</v>
+      </c>
+      <c r="P52" t="n">
         <v>0.3308651428571041</v>
       </c>
-      <c r="I52" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0.3206543266788474</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0.005559533698940396</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0.01134058524405515</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O52" t="n">
-        <v>34.92500000000002</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0.3061500936386944</v>
-      </c>
       <c r="Q52" t="n">
+        <v>34.61647934279934</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2.35374362871222</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.0132203465779301</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0.2034070546972727</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0.01728666666666667</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.008643333333333333</v>
+      </c>
+      <c r="W52" t="n">
         <v>33.75408934834007</v>
       </c>
-      <c r="R52" t="n">
-        <v>2.331405828596664</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0.01284342625596111</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0.1986850268676124</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0.01622</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0.008110000000000001</v>
-      </c>
-      <c r="W52" t="n">
-        <v>32.83159453257404</v>
-      </c>
       <c r="X52" t="n">
-        <v>0.01157922320647989</v>
+        <v>0.009267599997966548</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.0003444698247772432</v>
+        <v>0.0005343022972248991</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.01216839656025612</v>
+        <v>0.01961652719811411</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.000404172425993012</v>
+        <v>0.0006187360183830693</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.0136424721791035</v>
+        <v>0.02141846259900343</v>
       </c>
     </row>
     <row r="53">
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>35.71666666666666</v>
+        <v>38.41666666666666</v>
       </c>
       <c r="D53" t="n">
-        <v>36.71428571428564</v>
+        <v>36.54999999999995</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -5286,25 +5286,25 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>2.225119195750334</v>
+        <v>2.238126974352284</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3724108962071924</v>
+        <v>0.4370511859323505</v>
       </c>
       <c r="I53" t="n">
         <v>28.98</v>
       </c>
       <c r="J53" t="n">
-        <v>0.2482560989697474</v>
+        <v>0.09314611508350956</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0.005575616292307751</v>
+        <v>0.008164208448361089</v>
       </c>
       <c r="M53" t="n">
-        <v>0.01868335460030837</v>
+        <v>0.02804497875626173</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -5312,91 +5312,91 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>35.32500000000002</v>
+        <v>36.71428571428564</v>
       </c>
       <c r="P53" t="n">
-        <v>0.3308651428571041</v>
+        <v>0.3724108962071924</v>
       </c>
       <c r="Q53" t="n">
+        <v>35.52745852239729</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2.377809652778219</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.013547618883582</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0.2068914320190097</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0.01836666666666667</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.009183333333333333</v>
+      </c>
+      <c r="W53" t="n">
         <v>34.61647934279934</v>
       </c>
-      <c r="R53" t="n">
-        <v>2.35374362871222</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0.0132203465779301</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0.2034070546972727</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0.01728666666666667</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0.008643333333333333</v>
-      </c>
-      <c r="W53" t="n">
-        <v>33.75408934834007</v>
-      </c>
       <c r="X53" t="n">
-        <v>0.009267599997966548</v>
+        <v>0.006196243412663805</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.0005343022972248991</v>
+        <v>0.0008109233377192746</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.01961652719811411</v>
+        <v>0.02963924799363945</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.0006187360183830692</v>
+        <v>0.0008844102245227442</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.02141846259900343</v>
+        <v>0.03142084756851587</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>38.41666666666666</v>
+        <v>10.08333333333333</v>
       </c>
       <c r="D54" t="n">
-        <v>36.54999999999995</v>
+        <v>22.74159954433088</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>2.238126974352284</v>
+        <v>2.151754877317993</v>
       </c>
       <c r="H54" t="n">
-        <v>0.4370511859323505</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>28.98</v>
+        <v>28.995</v>
       </c>
       <c r="J54" t="n">
-        <v>0.09314611508350956</v>
+        <v>0.8532992157616837</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0.008164208448361089</v>
+        <v>0.0143222143423807</v>
       </c>
       <c r="M54" t="n">
-        <v>0.02804497875626173</v>
+        <v>0</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -5404,91 +5404,91 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>36.71428571428564</v>
+        <v>21.79285714285717</v>
       </c>
       <c r="P54" t="n">
-        <v>0.3724108962071924</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>35.52745852239729</v>
+        <v>28.31815807004039</v>
       </c>
       <c r="R54" t="n">
-        <v>2.377809652778219</v>
+        <v>2.196892806206484</v>
       </c>
       <c r="S54" t="n">
-        <v>0.013547618883582</v>
+        <v>0.01041196717294989</v>
       </c>
       <c r="T54" t="n">
-        <v>0.2068914320190097</v>
+        <v>0.2041873938903916</v>
       </c>
       <c r="U54" t="n">
-        <v>0.01836666666666667</v>
+        <v>0.007033333333333333</v>
       </c>
       <c r="V54" t="n">
-        <v>0.009183333333333333</v>
+        <v>0.003516666666666667</v>
       </c>
       <c r="W54" t="n">
-        <v>34.61647934279934</v>
+        <v>25.42114791934122</v>
       </c>
       <c r="X54" t="n">
-        <v>0.006196243412663805</v>
+        <v>0.04417757490269928</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.0008109233377192746</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.02963924799363945</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.0008844102245227442</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.03142084756851587</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>46.41666666666666</v>
+        <v>11.2</v>
       </c>
       <c r="D55" t="n">
-        <v>37.45357142857144</v>
+        <v>22.97108767528296</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>2.350696964539372</v>
+        <v>2.163697271557409</v>
       </c>
       <c r="H55" t="n">
-        <v>0.792026695150037</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>28.98</v>
+        <v>28.995</v>
       </c>
       <c r="J55" t="n">
-        <v>0.2428851122484339</v>
+        <v>0.4955894525174036</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0.02098979306862803</v>
+        <v>0.00991189089150895</v>
       </c>
       <c r="M55" t="n">
-        <v>0.05964752041359847</v>
+        <v>0</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -5496,46 +5496,46 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>36.54999999999995</v>
+        <v>22.74159954433088</v>
       </c>
       <c r="P55" t="n">
-        <v>0.4370511859323505</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>38.42283179751898</v>
+        <v>28.49544506515976</v>
       </c>
       <c r="R55" t="n">
-        <v>2.457676399311553</v>
+        <v>2.200944449147011</v>
       </c>
       <c r="S55" t="n">
-        <v>0.01423124238248942</v>
+        <v>0.01098357032200971</v>
       </c>
       <c r="T55" t="n">
-        <v>0.2096355868065863</v>
+        <v>0.2161387857045839</v>
       </c>
       <c r="U55" t="n">
-        <v>0.02156666666666666</v>
+        <v>0.007480000000000001</v>
       </c>
       <c r="V55" t="n">
-        <v>0.01078333333333333</v>
+        <v>0.00374</v>
       </c>
       <c r="W55" t="n">
-        <v>35.52745852239729</v>
+        <v>28.31815807004039</v>
       </c>
       <c r="X55" t="n">
-        <v>0.01541414394739185</v>
+        <v>0.02615548495855645</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.001781396691915808</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.06671966824328958</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.001733285414237975</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.06659773392835872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10.08333333333333</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="D56" t="n">
-        <v>22.74159954433088</v>
+        <v>24.12500000000008</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -5562,22 +5562,22 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>2.151754877317993</v>
+        <v>2.18231465451585</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>28.995</v>
+        <v>28.98790163201834</v>
       </c>
       <c r="J56" t="n">
-        <v>0.8532992157616837</v>
+        <v>0.527194572758186</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0.0143222143423807</v>
+        <v>0.01009690660006621</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -5588,34 +5588,34 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>21.79285714285717</v>
+        <v>22.97108767528296</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>28.31815807004039</v>
+        <v>28.74377626618266</v>
       </c>
       <c r="R56" t="n">
-        <v>2.196892806206484</v>
+        <v>2.2066448992919</v>
       </c>
       <c r="S56" t="n">
-        <v>0.01041196717294989</v>
+        <v>0.01171780391374263</v>
       </c>
       <c r="T56" t="n">
-        <v>0.2041873938903916</v>
+        <v>0.2317374616169707</v>
       </c>
       <c r="U56" t="n">
-        <v>0.007033333333333333</v>
+        <v>0.008066666666666666</v>
       </c>
       <c r="V56" t="n">
-        <v>0.003516666666666667</v>
+        <v>0.004033333333333333</v>
       </c>
       <c r="W56" t="n">
-        <v>25.42114791934122</v>
+        <v>28.49544506515976</v>
       </c>
       <c r="X56" t="n">
-        <v>0.04417757490269928</v>
+        <v>0.02647932083128075</v>
       </c>
       <c r="Y56" t="n">
         <v>0</v>
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>11.2</v>
+        <v>13.85</v>
       </c>
       <c r="D57" t="n">
-        <v>22.97108767528296</v>
+        <v>24.57500000000017</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>2.163697271557409</v>
+        <v>2.193791961026335</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>28.995</v>
+        <v>28.98710002854261</v>
       </c>
       <c r="J57" t="n">
-        <v>0.4955894525174036</v>
+        <v>0.4106539365163594</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0.00991189089150895</v>
+        <v>0.01080044764312056</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -5680,34 +5680,34 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>22.74159954433088</v>
+        <v>24.12500000000008</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>28.49544506515976</v>
+        <v>28.95676810363952</v>
       </c>
       <c r="R57" t="n">
-        <v>2.200944449147011</v>
+        <v>2.211557709760262</v>
       </c>
       <c r="S57" t="n">
-        <v>0.01098357032200971</v>
+        <v>0.01228108243496568</v>
       </c>
       <c r="T57" t="n">
-        <v>0.2161387857045839</v>
+        <v>0.2438029808221922</v>
       </c>
       <c r="U57" t="n">
-        <v>0.007480000000000001</v>
+        <v>0.008539999999999999</v>
       </c>
       <c r="V57" t="n">
-        <v>0.00374</v>
+        <v>0.004269999999999999</v>
       </c>
       <c r="W57" t="n">
-        <v>28.31815807004039</v>
+        <v>28.74377626618266</v>
       </c>
       <c r="X57" t="n">
-        <v>0.02615548495855645</v>
+        <v>0.02163341820285943</v>
       </c>
       <c r="Y57" t="n">
         <v>0</v>
@@ -5734,10 +5734,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>12.66666666666667</v>
+        <v>15.31666666666667</v>
       </c>
       <c r="D58" t="n">
-        <v>24.12500000000008</v>
+        <v>25.06785714285721</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -5746,22 +5746,22 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>2.18231465451585</v>
+        <v>2.214828125862959</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>28.98790163201834</v>
+        <v>28.98</v>
       </c>
       <c r="J58" t="n">
-        <v>0.527194572758186</v>
+        <v>0.3756303196153055</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0.01009690660006621</v>
+        <v>0.009872310665280869</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -5772,34 +5772,34 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>22.97108767528296</v>
+        <v>24.57500000000017</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>28.74377626618266</v>
+        <v>29.2361661686984</v>
       </c>
       <c r="R58" t="n">
-        <v>2.2066448992919</v>
+        <v>2.218035494015818</v>
       </c>
       <c r="S58" t="n">
-        <v>0.01171780391374263</v>
+        <v>0.01296737669517052</v>
       </c>
       <c r="T58" t="n">
-        <v>0.2317374616169707</v>
+        <v>0.2588167976329628</v>
       </c>
       <c r="U58" t="n">
-        <v>0.008066666666666666</v>
+        <v>0.009126666666666668</v>
       </c>
       <c r="V58" t="n">
-        <v>0.004033333333333333</v>
+        <v>0.004563333333333334</v>
       </c>
       <c r="W58" t="n">
-        <v>28.49544506515976</v>
+        <v>28.95676810363952</v>
       </c>
       <c r="X58" t="n">
-        <v>0.02647932083128075</v>
+        <v>0.01944191146369945</v>
       </c>
       <c r="Y58" t="n">
         <v>0</v>
@@ -5826,10 +5826,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>13.85</v>
+        <v>17.98333333333333</v>
       </c>
       <c r="D59" t="n">
-        <v>24.57500000000017</v>
+        <v>25.90000000000013</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -5838,22 +5838,22 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>2.193791961026335</v>
+        <v>2.214024096070052</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>28.98710002854261</v>
+        <v>28.98</v>
       </c>
       <c r="J59" t="n">
-        <v>0.4106539365163594</v>
+        <v>0.3298559424945083</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0.01080044764312056</v>
+        <v>0.008518133778895404</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -5864,34 +5864,34 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>24.12500000000008</v>
+        <v>25.06785714285721</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>28.95676810363952</v>
+        <v>29.78688303253967</v>
       </c>
       <c r="R59" t="n">
-        <v>2.211557709760262</v>
+        <v>2.230915506895817</v>
       </c>
       <c r="S59" t="n">
-        <v>0.01228108243496568</v>
+        <v>0.01413309295165512</v>
       </c>
       <c r="T59" t="n">
-        <v>0.2438029808221922</v>
+        <v>0.2848807744362734</v>
       </c>
       <c r="U59" t="n">
-        <v>0.008539999999999999</v>
+        <v>0.01019333333333333</v>
       </c>
       <c r="V59" t="n">
-        <v>0.004269999999999999</v>
+        <v>0.005096666666666667</v>
       </c>
       <c r="W59" t="n">
-        <v>28.74377626618266</v>
+        <v>29.2361661686984</v>
       </c>
       <c r="X59" t="n">
-        <v>0.02163341820285943</v>
+        <v>0.01658310436687791</v>
       </c>
       <c r="Y59" t="n">
         <v>0</v>
@@ -5918,10 +5918,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>15.31666666666667</v>
+        <v>23.56666666666667</v>
       </c>
       <c r="D60" t="n">
-        <v>25.06785714285721</v>
+        <v>27.37499999999996</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>2.214828125862959</v>
+        <v>2.307573593937551</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>28.98</v>
+        <v>28.99338819905182</v>
       </c>
       <c r="J60" t="n">
-        <v>0.3756303196153055</v>
+        <v>0.3454451519070621</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0.009872310665280869</v>
+        <v>0.0129230258223817</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -5956,34 +5956,34 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>24.57500000000017</v>
+        <v>25.90000000000013</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>29.2361661686984</v>
+        <v>31.11037299665006</v>
       </c>
       <c r="R60" t="n">
-        <v>2.218035494015818</v>
+        <v>2.262489288469567</v>
       </c>
       <c r="S60" t="n">
-        <v>0.01296737669517052</v>
+        <v>0.01625124162510059</v>
       </c>
       <c r="T60" t="n">
-        <v>0.2588167976329628</v>
+        <v>0.3347092315256564</v>
       </c>
       <c r="U60" t="n">
-        <v>0.009126666666666668</v>
+        <v>0.01242666666666667</v>
       </c>
       <c r="V60" t="n">
-        <v>0.004563333333333334</v>
+        <v>0.006213333333333333</v>
       </c>
       <c r="W60" t="n">
-        <v>28.95676810363952</v>
+        <v>29.78688303253967</v>
       </c>
       <c r="X60" t="n">
-        <v>0.01944191146369945</v>
+        <v>0.01821926693166444</v>
       </c>
       <c r="Y60" t="n">
         <v>0</v>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>17.98333333333333</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="D61" t="n">
-        <v>25.90000000000013</v>
+        <v>28.11428571428576</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -6022,22 +6022,22 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>2.214024096070052</v>
+        <v>2.324643491537374</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>28.98</v>
+        <v>28.98907356082457</v>
       </c>
       <c r="J61" t="n">
-        <v>0.3298559424945083</v>
+        <v>0.2438328224960159</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0.008518133778895404</v>
+        <v>0.01425711185829255</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -6048,34 +6048,34 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>25.06785714285721</v>
+        <v>27.37499999999996</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>29.78688303253967</v>
+        <v>31.52104556228423</v>
       </c>
       <c r="R61" t="n">
-        <v>2.230915506895817</v>
+        <v>2.272468965115901</v>
       </c>
       <c r="S61" t="n">
-        <v>0.01413309295165512</v>
+        <v>0.01679004299276455</v>
       </c>
       <c r="T61" t="n">
-        <v>0.2848807744362734</v>
+        <v>0.3481790571704745</v>
       </c>
       <c r="U61" t="n">
-        <v>0.01019333333333333</v>
+        <v>0.01305333333333333</v>
       </c>
       <c r="V61" t="n">
-        <v>0.005096666666666667</v>
+        <v>0.006526666666666667</v>
       </c>
       <c r="W61" t="n">
-        <v>29.2361661686984</v>
+        <v>31.11037299665006</v>
       </c>
       <c r="X61" t="n">
-        <v>0.01658310436687791</v>
+        <v>0.01480594697664882</v>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
@@ -6102,10 +6102,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>23.56666666666667</v>
+        <v>26.68333333333333</v>
       </c>
       <c r="D62" t="n">
-        <v>27.37499999999996</v>
+        <v>28.14285714285706</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -6114,22 +6114,22 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>2.307573593937551</v>
+        <v>2.352668497327067</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>28.99338819905182</v>
+        <v>28.995</v>
       </c>
       <c r="J62" t="n">
-        <v>0.3454451519070621</v>
+        <v>0.3483746225501007</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0.0129230258223817</v>
+        <v>0.01556696786466986</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -6140,34 +6140,34 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>25.90000000000013</v>
+        <v>28.11428571428576</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>31.11037299665006</v>
+        <v>31.94343200509588</v>
       </c>
       <c r="R62" t="n">
-        <v>2.262489288469567</v>
+        <v>2.282825558805818</v>
       </c>
       <c r="S62" t="n">
-        <v>0.01625124162510059</v>
+        <v>0.01726816390210312</v>
       </c>
       <c r="T62" t="n">
-        <v>0.3347092315256564</v>
+        <v>0.360274340850948</v>
       </c>
       <c r="U62" t="n">
-        <v>0.01242666666666667</v>
+        <v>0.01367333333333333</v>
       </c>
       <c r="V62" t="n">
-        <v>0.006213333333333333</v>
+        <v>0.006836666666666666</v>
       </c>
       <c r="W62" t="n">
-        <v>29.78688303253967</v>
+        <v>31.52104556228423</v>
       </c>
       <c r="X62" t="n">
-        <v>0.01821926693166444</v>
+        <v>0.01899552184075797</v>
       </c>
       <c r="Y62" t="n">
         <v>0</v>
@@ -6194,10 +6194,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>25.13333333333333</v>
+        <v>28.15</v>
       </c>
       <c r="D63" t="n">
-        <v>28.11428571428576</v>
+        <v>29.46071428571427</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -6206,22 +6206,22 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>2.324643491537374</v>
+        <v>2.375720882565579</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>28.98907356082457</v>
+        <v>28.995</v>
       </c>
       <c r="J63" t="n">
-        <v>0.2438328224960159</v>
+        <v>0.4669603785258343</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0.01425711185829255</v>
+        <v>0.01540779486614794</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -6232,34 +6232,34 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>27.37499999999996</v>
+        <v>28.14285714285706</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>31.52104556228423</v>
+        <v>32.3574018720367</v>
       </c>
       <c r="R63" t="n">
-        <v>2.272468965115901</v>
+        <v>2.293067791270262</v>
       </c>
       <c r="S63" t="n">
-        <v>0.01679004299276455</v>
+        <v>0.01769926440963473</v>
       </c>
       <c r="T63" t="n">
-        <v>0.3481790571704745</v>
+        <v>0.3714798347284995</v>
       </c>
       <c r="U63" t="n">
-        <v>0.01305333333333333</v>
+        <v>0.01426</v>
       </c>
       <c r="V63" t="n">
-        <v>0.006526666666666667</v>
+        <v>0.007129999999999999</v>
       </c>
       <c r="W63" t="n">
-        <v>31.11037299665006</v>
+        <v>31.94343200509588</v>
       </c>
       <c r="X63" t="n">
-        <v>0.01480594697664882</v>
+        <v>0.02233579751349438</v>
       </c>
       <c r="Y63" t="n">
         <v>0</v>
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>26.68333333333333</v>
+        <v>31.18333333333333</v>
       </c>
       <c r="D64" t="n">
-        <v>28.14285714285706</v>
+        <v>30.54107142857147</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -6298,22 +6298,22 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>2.352668497327067</v>
+        <v>2.429480867954015</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>28.995</v>
+        <v>28.98</v>
       </c>
       <c r="J64" t="n">
-        <v>0.3483746225501007</v>
+        <v>0.1393496146836234</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0.01556696786466986</v>
+        <v>0.01356607661731992</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
@@ -6324,34 +6324,34 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>28.11428571428576</v>
+        <v>29.46071428571427</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>31.94343200509588</v>
+        <v>33.25583249482232</v>
       </c>
       <c r="R64" t="n">
-        <v>2.282825558805818</v>
+        <v>2.315615591595817</v>
       </c>
       <c r="S64" t="n">
-        <v>0.01726816390210312</v>
+        <v>0.01851308273432502</v>
       </c>
       <c r="T64" t="n">
-        <v>0.360274340850948</v>
+        <v>0.3934469053539372</v>
       </c>
       <c r="U64" t="n">
-        <v>0.01367333333333333</v>
+        <v>0.01547333333333333</v>
       </c>
       <c r="V64" t="n">
-        <v>0.006836666666666666</v>
+        <v>0.007736666666666666</v>
       </c>
       <c r="W64" t="n">
-        <v>31.52104556228423</v>
+        <v>32.3574018720367</v>
       </c>
       <c r="X64" t="n">
-        <v>0.01899552184075797</v>
+        <v>0.01014663618242141</v>
       </c>
       <c r="Y64" t="n">
         <v>0</v>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>28.15</v>
+        <v>34.18333333333334</v>
       </c>
       <c r="D65" t="n">
-        <v>29.46071428571427</v>
+        <v>30.00357142857132</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -6390,7 +6390,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>2.375720882565579</v>
+        <v>2.451704147576396</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -6399,13 +6399,13 @@
         <v>28.995</v>
       </c>
       <c r="J65" t="n">
-        <v>0.4669603785258343</v>
+        <v>0.08855763882758942</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0.01540779486614794</v>
+        <v>0.01490221644458623</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -6416,34 +6416,34 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>28.14285714285706</v>
+        <v>30.54107142857147</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>32.3574018720367</v>
+        <v>34.19735342816631</v>
       </c>
       <c r="R65" t="n">
-        <v>2.293067791270262</v>
+        <v>2.339725615705817</v>
       </c>
       <c r="S65" t="n">
-        <v>0.01769926440963473</v>
+        <v>0.01919070522193477</v>
       </c>
       <c r="T65" t="n">
-        <v>0.3714798347284995</v>
+        <v>0.4125744318193387</v>
       </c>
       <c r="U65" t="n">
-        <v>0.01426</v>
+        <v>0.01667333333333334</v>
       </c>
       <c r="V65" t="n">
-        <v>0.007129999999999999</v>
+        <v>0.008336666666666668</v>
       </c>
       <c r="W65" t="n">
-        <v>31.94343200509588</v>
+        <v>33.25583249482232</v>
       </c>
       <c r="X65" t="n">
-        <v>0.02233579751349438</v>
+        <v>0.00902987934884078</v>
       </c>
       <c r="Y65" t="n">
         <v>0</v>
@@ -6470,10 +6470,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>31.18333333333333</v>
+        <v>35.7</v>
       </c>
       <c r="D66" t="n">
-        <v>30.54107142857147</v>
+        <v>30.12857142857151</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -6482,22 +6482,22 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>2.429480867954015</v>
+        <v>2.481063784627632</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>28.98</v>
+        <v>29.01</v>
       </c>
       <c r="J66" t="n">
-        <v>0.1393496146836234</v>
+        <v>0.2239877292055531</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0.01356607661731992</v>
+        <v>0.01559421357166551</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -6508,34 +6508,34 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>29.46071428571427</v>
+        <v>30.00357142857132</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>33.25583249482232</v>
+        <v>34.69219227608998</v>
       </c>
       <c r="R66" t="n">
-        <v>2.315615591595817</v>
+        <v>2.352599600802012</v>
       </c>
       <c r="S66" t="n">
-        <v>0.01851308273432502</v>
+        <v>0.01948896483444288</v>
       </c>
       <c r="T66" t="n">
-        <v>0.3934469053539372</v>
+        <v>0.4212984636054069</v>
       </c>
       <c r="U66" t="n">
-        <v>0.01547333333333333</v>
+        <v>0.01728</v>
       </c>
       <c r="V66" t="n">
-        <v>0.007736666666666666</v>
+        <v>0.00864</v>
       </c>
       <c r="W66" t="n">
-        <v>32.3574018720367</v>
+        <v>34.19735342816631</v>
       </c>
       <c r="X66" t="n">
-        <v>0.01014663618242141</v>
+        <v>0.01371968923896166</v>
       </c>
       <c r="Y66" t="n">
         <v>0</v>
@@ -6562,10 +6562,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>34.18333333333334</v>
+        <v>36.75</v>
       </c>
       <c r="D67" t="n">
-        <v>30.00357142857132</v>
+        <v>30.54107142857147</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -6574,22 +6574,22 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>2.451704147576396</v>
+        <v>2.497032422101453</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>28.995</v>
+        <v>28.98</v>
       </c>
       <c r="J67" t="n">
-        <v>0.08855763882758942</v>
+        <v>0.5198551448550432</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0.01490221644458623</v>
+        <v>0.01351059041225433</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -6600,34 +6600,34 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>30.54107142857147</v>
+        <v>30.12857142857151</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>34.19735342816631</v>
+        <v>35.04183579224857</v>
       </c>
       <c r="R67" t="n">
-        <v>2.339725615705817</v>
+        <v>2.361781859984262</v>
       </c>
       <c r="S67" t="n">
-        <v>0.01919070522193477</v>
+        <v>0.01970497485318354</v>
       </c>
       <c r="T67" t="n">
-        <v>0.4125744318193387</v>
+        <v>0.4278830060214355</v>
       </c>
       <c r="U67" t="n">
-        <v>0.01667333333333334</v>
+        <v>0.0177</v>
       </c>
       <c r="V67" t="n">
-        <v>0.008336666666666668</v>
+        <v>0.00885</v>
       </c>
       <c r="W67" t="n">
-        <v>33.25583249482232</v>
+        <v>34.69219227608998</v>
       </c>
       <c r="X67" t="n">
-        <v>0.00902987934884078</v>
+        <v>0.0224321685275548</v>
       </c>
       <c r="Y67" t="n">
         <v>0</v>
@@ -6639,190 +6639,6 @@
         <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="D68" t="n">
-        <v>30.12857142857151</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
-        <v>2.481063784627632</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0.2239877292055531</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0.01559421357166551</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O68" t="n">
-        <v>30.00357142857132</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>34.69219227608998</v>
-      </c>
-      <c r="R68" t="n">
-        <v>2.352599600802012</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0.01948896483444288</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0.4212984636054069</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0.01728</v>
-      </c>
-      <c r="V68" t="n">
-        <v>0.00864</v>
-      </c>
-      <c r="W68" t="n">
-        <v>34.19735342816631</v>
-      </c>
-      <c r="X68" t="n">
-        <v>0.01371968923896166</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>36.75</v>
-      </c>
-      <c r="D69" t="n">
-        <v>30.54107142857147</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" t="n">
-        <v>2.497032422101453</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>28.98</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0.5198551448550432</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0.01351059041225433</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O69" t="n">
-        <v>30.12857142857151</v>
-      </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>35.04183579224857</v>
-      </c>
-      <c r="R69" t="n">
-        <v>2.361781859984262</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0.01970497485318354</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0.4278830060214355</v>
-      </c>
-      <c r="U69" t="n">
-        <v>0.0177</v>
-      </c>
-      <c r="V69" t="n">
-        <v>0.00885</v>
-      </c>
-      <c r="W69" t="n">
-        <v>34.69219227608998</v>
-      </c>
-      <c r="X69" t="n">
-        <v>0.0224321685275548</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB69" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/processed/BR_processed_ind.xlsx
+++ b/data/processed/BR_processed_ind.xlsx
@@ -718,16 +718,16 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>26.81456003797826</v>
+        <v>26.81456003794531</v>
       </c>
       <c r="R3" t="n">
         <v>1.851713165092423</v>
       </c>
       <c r="S3" t="n">
-        <v>0.006094311842885767</v>
+        <v>0.006094652876519476</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1282517247191745</v>
+        <v>0.1282608693858629</v>
       </c>
       <c r="U3" t="n">
         <v>0.002428333333333334</v>
@@ -748,7 +748,7 @@
         <v>0.1065167260919373</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004012411300951165</v>
+        <v>0.004012411300956096</v>
       </c>
       <c r="AB3" t="n">
         <v>0.1075910437264175</v>
@@ -810,16 +810,16 @@
         <v>0.1310102834270957</v>
       </c>
       <c r="Q4" t="n">
-        <v>27.04656525722977</v>
+        <v>27.04656525722954</v>
       </c>
       <c r="R4" t="n">
         <v>1.856115873425756</v>
       </c>
       <c r="S4" t="n">
-        <v>0.006462731911821826</v>
+        <v>0.006462734694132884</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1368599863515561</v>
+        <v>0.1368600616035126</v>
       </c>
       <c r="U4" t="n">
         <v>0.002603333333333333</v>
@@ -828,7 +828,7 @@
         <v>0.002603333333333333</v>
       </c>
       <c r="W4" t="n">
-        <v>26.81456003797826</v>
+        <v>26.81456003794531</v>
       </c>
       <c r="X4" t="n">
         <v>5.19473822208176e-05</v>
@@ -840,7 +840,7 @@
         <v>0.08474551698518029</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003294261940258428</v>
+        <v>0.003294261940258456</v>
       </c>
       <c r="AB4" t="n">
         <v>0.08909847054160794</v>
@@ -902,16 +902,16 @@
         <v>0.3150449672599142</v>
       </c>
       <c r="Q5" t="n">
-        <v>27.34710021724289</v>
+        <v>27.34710021724216</v>
       </c>
       <c r="R5" t="n">
         <v>1.861850276203534</v>
       </c>
       <c r="S5" t="n">
-        <v>0.006890081998479314</v>
+        <v>0.006890089633184113</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1470766749719362</v>
+        <v>0.1470768837589695</v>
       </c>
       <c r="U5" t="n">
         <v>0.002815</v>
@@ -920,7 +920,7 @@
         <v>0.002815</v>
       </c>
       <c r="W5" t="n">
-        <v>27.04656525722977</v>
+        <v>27.04656525722954</v>
       </c>
       <c r="X5" t="n">
         <v>0.009247963860255975</v>
@@ -932,10 +932,10 @@
         <v>0.06448817748780201</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002529907594138891</v>
+        <v>0.002529907594138958</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.06918563651728009</v>
+        <v>0.0691856365172801</v>
       </c>
     </row>
     <row r="6">
@@ -994,16 +994,16 @@
         <v>0.462353720667521</v>
       </c>
       <c r="Q6" t="n">
-        <v>27.65075345784634</v>
+        <v>27.65075345784807</v>
       </c>
       <c r="R6" t="n">
         <v>1.867680276203534</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007275831136120344</v>
+        <v>0.007275813451270728</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1565455464147945</v>
+        <v>0.1565450574153875</v>
       </c>
       <c r="U6" t="n">
         <v>0.003015</v>
@@ -1012,7 +1012,7 @@
         <v>0.003015</v>
       </c>
       <c r="W6" t="n">
-        <v>27.34710021724289</v>
+        <v>27.34710021724216</v>
       </c>
       <c r="X6" t="n">
         <v>0.00709381743588283</v>
@@ -1024,7 +1024,7 @@
         <v>0.112121445976553</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.004332845827375171</v>
+        <v>0.004332845827374901</v>
       </c>
       <c r="AB6" t="n">
         <v>0.1198064517436091</v>
@@ -1086,16 +1086,16 @@
         <v>0.6209461221159972</v>
       </c>
       <c r="Q7" t="n">
-        <v>27.96486690504897</v>
+        <v>27.96486690504821</v>
       </c>
       <c r="R7" t="n">
         <v>1.873749651203534</v>
       </c>
       <c r="S7" t="n">
-        <v>0.007634549004260692</v>
+        <v>0.007634557258848181</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1655913471976849</v>
+        <v>0.1655915780361208</v>
       </c>
       <c r="U7" t="n">
         <v>0.003210000000000001</v>
@@ -1104,7 +1104,7 @@
         <v>0.003210000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>27.65075345784634</v>
+        <v>27.65075345784807</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1116,7 +1116,7 @@
         <v>0.2218548813486614</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.008700430054214071</v>
+        <v>0.008700430054214307</v>
       </c>
       <c r="AB7" t="n">
         <v>0.2433063684827845</v>
@@ -1178,16 +1178,16 @@
         <v>0.9523209449429346</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.1412593939992</v>
+        <v>28.14125939399926</v>
       </c>
       <c r="R8" t="n">
         <v>1.877175276203534</v>
       </c>
       <c r="S8" t="n">
-        <v>0.007820572933980103</v>
+        <v>0.007820572933980101</v>
       </c>
       <c r="T8" t="n">
-        <v>0.170384679723405</v>
+        <v>0.1703846797234053</v>
       </c>
       <c r="U8" t="n">
         <v>0.003315</v>
@@ -1196,7 +1196,7 @@
         <v>0.003315</v>
       </c>
       <c r="W8" t="n">
-        <v>27.96486690504897</v>
+        <v>27.96486690504821</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1208,7 +1208,7 @@
         <v>0.3242312467603854</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01278089828636537</v>
+        <v>0.01278089828636535</v>
       </c>
       <c r="AB8" t="n">
         <v>0.3596705739649278</v>
@@ -1270,16 +1270,16 @@
         <v>1.25504016023201</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.31682006871782</v>
+        <v>28.31682006871788</v>
       </c>
       <c r="R9" t="n">
         <v>1.880597206759089</v>
       </c>
       <c r="S9" t="n">
-        <v>0.007995870233005839</v>
+        <v>0.007995870233005813</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1749716551927246</v>
+        <v>0.1749716551927243</v>
       </c>
       <c r="U9" t="n">
         <v>0.003416666666666667</v>
@@ -1288,7 +1288,7 @@
         <v>0.003416666666666667</v>
       </c>
       <c r="W9" t="n">
-        <v>28.1412593939992</v>
+        <v>28.14125939399926</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1300,7 +1300,7 @@
         <v>0.4847102107155994</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0190241648870514</v>
+        <v>0.01902416488705136</v>
       </c>
       <c r="AB9" t="n">
         <v>0.5387038540642539</v>
@@ -1362,16 +1362,16 @@
         <v>1.69587337268752</v>
       </c>
       <c r="Q10" t="n">
-        <v>28.48804706810432</v>
+        <v>28.48804706810439</v>
       </c>
       <c r="R10" t="n">
-        <v>1.88394670675909</v>
+        <v>1.883946706759089</v>
       </c>
       <c r="S10" t="n">
-        <v>0.00815814576399599</v>
+        <v>0.008158145763995973</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1792828694602287</v>
+        <v>0.1792828694602286</v>
       </c>
       <c r="U10" t="n">
         <v>0.003513333333333334</v>
@@ -1380,7 +1380,7 @@
         <v>0.003513333333333334</v>
       </c>
       <c r="W10" t="n">
-        <v>28.31682006871782</v>
+        <v>28.31682006871788</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1392,7 +1392,7 @@
         <v>0.6709707039456413</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.02637900208746056</v>
+        <v>0.0263790020874605</v>
       </c>
       <c r="AB10" t="n">
         <v>0.7514862530771985</v>
@@ -1460,10 +1460,10 @@
         <v>1.908002336876444</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0187088218943581</v>
+        <v>0.01870882202496487</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3981449898798762</v>
+        <v>0.3981449934364881</v>
       </c>
       <c r="U11" t="n">
         <v>0.007799999999999998</v>
@@ -1484,7 +1484,7 @@
         <v>0.1619956336149481</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.006010640046182783</v>
+        <v>0.006010640046182784</v>
       </c>
       <c r="AB11" t="n">
         <v>0.1636784616839654</v>
@@ -1546,16 +1546,16 @@
         <v>0.1961577414134905</v>
       </c>
       <c r="Q12" t="n">
-        <v>27.96947227900406</v>
+        <v>27.96947227900407</v>
       </c>
       <c r="R12" t="n">
         <v>1.922571086876444</v>
       </c>
       <c r="S12" t="n">
-        <v>0.02051067907382667</v>
+        <v>0.02051067912378411</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4449234927812163</v>
+        <v>0.4449234941784995</v>
       </c>
       <c r="U12" t="n">
         <v>0.008849999999999998</v>
@@ -1576,7 +1576,7 @@
         <v>0.0921971490896749</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.003588200271870522</v>
+        <v>0.003588200271870521</v>
       </c>
       <c r="AB12" t="n">
         <v>0.1003600680355974</v>
@@ -1638,16 +1638,16 @@
         <v>0.4648676866334254</v>
       </c>
       <c r="Q13" t="n">
-        <v>28.9683679389311</v>
+        <v>28.96836793893106</v>
       </c>
       <c r="R13" t="n">
-        <v>1.942647670209778</v>
+        <v>1.942647670209777</v>
       </c>
       <c r="S13" t="n">
-        <v>0.02241122155096527</v>
+        <v>0.022411221550434</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4983091249681805</v>
+        <v>0.4983091249527896</v>
       </c>
       <c r="U13" t="n">
         <v>0.01012</v>
@@ -1656,7 +1656,7 @@
         <v>0.01012</v>
       </c>
       <c r="W13" t="n">
-        <v>27.96947227900406</v>
+        <v>27.96947227900407</v>
       </c>
       <c r="X13" t="n">
         <v>0.006274829559544594</v>
@@ -1668,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0001765021936132476</v>
+        <v>0.000176502193613248</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.005112980486617013</v>
+        <v>0.005112980486617014</v>
       </c>
     </row>
     <row r="14">
@@ -1730,16 +1730,16 @@
         <v>0.5273275582417261</v>
       </c>
       <c r="Q14" t="n">
-        <v>30.01255103280837</v>
+        <v>30.0125510328083</v>
       </c>
       <c r="R14" t="n">
         <v>1.964087670209778</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02393237056821312</v>
+        <v>0.02393237056755607</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5452944498589103</v>
+        <v>0.545294449839189</v>
       </c>
       <c r="U14" t="n">
         <v>0.01132</v>
@@ -1748,7 +1748,7 @@
         <v>0.01132</v>
       </c>
       <c r="W14" t="n">
-        <v>28.9683679389311</v>
+        <v>28.96836793893106</v>
       </c>
       <c r="X14" t="n">
         <v>0.02643890324335607</v>
@@ -1760,7 +1760,7 @@
         <v>0.166038915540943</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.005834624532342147</v>
+        <v>0.00583462453234216</v>
       </c>
       <c r="AB14" t="n">
         <v>0.1751119665341944</v>
@@ -1822,16 +1822,16 @@
         <v>0.5669120469218694</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.10797224550702</v>
+        <v>31.10797224550694</v>
       </c>
       <c r="R15" t="n">
         <v>1.987094336876444</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0251610435573475</v>
+        <v>0.02516104333188622</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5873345793217604</v>
+        <v>0.5873345723081156</v>
       </c>
       <c r="U15" t="n">
         <v>0.01248</v>
@@ -1840,7 +1840,7 @@
         <v>0.01248</v>
       </c>
       <c r="W15" t="n">
-        <v>30.01255103280837</v>
+        <v>30.0125510328083</v>
       </c>
       <c r="X15" t="n">
         <v>0.00455350837092449</v>
@@ -1852,7 +1852,7 @@
         <v>0.6940734053890505</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.02327612397420667</v>
+        <v>0.02327612397420674</v>
       </c>
       <c r="AB15" t="n">
         <v>0.7240730185726018</v>
@@ -1914,16 +1914,16 @@
         <v>1.314363106233276</v>
       </c>
       <c r="Q16" t="n">
-        <v>31.74613976555075</v>
+        <v>31.74613976555108</v>
       </c>
       <c r="R16" t="n">
         <v>2.000747670209778</v>
       </c>
       <c r="S16" t="n">
-        <v>0.02574269343420042</v>
+        <v>0.02574269343420017</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6090542906575334</v>
+        <v>0.6090542906575316</v>
       </c>
       <c r="U16" t="n">
         <v>0.01312</v>
@@ -1932,7 +1932,7 @@
         <v>0.01312</v>
       </c>
       <c r="W16" t="n">
-        <v>31.10797224550702</v>
+        <v>31.10797224550694</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         <v>1.033509465599738</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.03569355102898607</v>
+        <v>0.0356935510289857</v>
       </c>
       <c r="AB16" t="n">
         <v>1.133132459695009</v>
@@ -2006,16 +2006,16 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>19.99434722408682</v>
+        <v>19.99434722414867</v>
       </c>
       <c r="R17" t="n">
-        <v>1.87876402776961</v>
+        <v>1.878764027770175</v>
       </c>
       <c r="S17" t="n">
-        <v>0.006624041782399131</v>
+        <v>0.00662367589221488</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1111942904013396</v>
+        <v>0.1111869746663001</v>
       </c>
       <c r="U17" t="n">
         <v>0.001996666666666667</v>
@@ -2036,10 +2036,10 @@
         <v>0.0816312894067058</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.00409074945822651</v>
+        <v>0.004090749458213853</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.08179186507452586</v>
+        <v>0.08179186507452584</v>
       </c>
     </row>
     <row r="18">
@@ -2098,16 +2098,16 @@
         <v>0.09290978010103844</v>
       </c>
       <c r="Q18" t="n">
-        <v>20.11820096978532</v>
+        <v>20.11820096981678</v>
       </c>
       <c r="R18" t="n">
-        <v>1.880990611102943</v>
+        <v>1.880990611103508</v>
       </c>
       <c r="S18" t="n">
-        <v>0.006756702796297812</v>
+        <v>0.006756701709062598</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1139890320483953</v>
+        <v>0.1139890101753636</v>
       </c>
       <c r="U18" t="n">
         <v>0.002051666666666667</v>
@@ -2116,7 +2116,7 @@
         <v>0.002051666666666667</v>
       </c>
       <c r="W18" t="n">
-        <v>19.99434722408682</v>
+        <v>19.99434722414867</v>
       </c>
       <c r="X18" t="n">
         <v>0.01789804707363351</v>
@@ -2128,10 +2128,10 @@
         <v>0.04078878183453907</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.002159985784733604</v>
+        <v>0.002159985784730224</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.04345502810915009</v>
+        <v>0.04345502810915004</v>
       </c>
     </row>
     <row r="19">
@@ -2190,16 +2190,16 @@
         <v>0.1714635834683609</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.22568990464505</v>
+        <v>20.22568990467636</v>
       </c>
       <c r="R19" t="n">
-        <v>1.88292727776961</v>
+        <v>1.882927277770174</v>
       </c>
       <c r="S19" t="n">
-        <v>0.006866587915325191</v>
+        <v>0.006866587915312488</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1163419779105917</v>
+        <v>0.1163419779105216</v>
       </c>
       <c r="U19" t="n">
         <v>0.002098333333333333</v>
@@ -2208,7 +2208,7 @@
         <v>0.002098333333333333</v>
       </c>
       <c r="W19" t="n">
-        <v>20.11820096978532</v>
+        <v>20.11820096981678</v>
       </c>
       <c r="X19" t="n">
         <v>0.001401645203937436</v>
@@ -2220,10 +2220,10 @@
         <v>0.02413582546819065</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.001421388845636275</v>
+        <v>0.001421388845634071</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.02874857002576069</v>
+        <v>0.02874857002576062</v>
       </c>
     </row>
     <row r="20">
@@ -2282,16 +2282,16 @@
         <v>0.1940649581558863</v>
       </c>
       <c r="Q20" t="n">
-        <v>20.34328539671193</v>
+        <v>20.34328539674237</v>
       </c>
       <c r="R20" t="n">
-        <v>1.885050611102943</v>
+        <v>1.885050611103508</v>
       </c>
       <c r="S20" t="n">
-        <v>0.006981708507962712</v>
+        <v>0.006981718078190372</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1188462814509948</v>
+        <v>0.1188464761410522</v>
       </c>
       <c r="U20" t="n">
         <v>0.002148333333333333</v>
@@ -2300,7 +2300,7 @@
         <v>0.002148333333333333</v>
       </c>
       <c r="W20" t="n">
-        <v>20.22568990464505</v>
+        <v>20.22568990467636</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2312,10 +2312,10 @@
         <v>0.03974752399441857</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.002253972861086382</v>
+        <v>0.002253972861083005</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.0458532131895236</v>
+        <v>0.04585321318952352</v>
       </c>
     </row>
     <row r="21">
@@ -2374,16 +2374,16 @@
         <v>0.2229784488956445</v>
       </c>
       <c r="Q21" t="n">
-        <v>20.47349558519533</v>
+        <v>20.47349558522638</v>
       </c>
       <c r="R21" t="n">
-        <v>1.887407312491832</v>
+        <v>1.887407312492397</v>
       </c>
       <c r="S21" t="n">
-        <v>0.007103330707160857</v>
+        <v>0.007103332026096677</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1215385722763077</v>
+        <v>0.1215385992797259</v>
       </c>
       <c r="U21" t="n">
         <v>0.0022025</v>
@@ -2392,7 +2392,7 @@
         <v>0.0022025</v>
       </c>
       <c r="W21" t="n">
-        <v>20.34328539671193</v>
+        <v>20.34328539674237</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2404,10 +2404,10 @@
         <v>0.07526448485171559</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.004133579428144476</v>
+        <v>0.0041335794281382</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.08462882017317015</v>
+        <v>0.08462882017317004</v>
       </c>
     </row>
     <row r="22">
@@ -2466,16 +2466,16 @@
         <v>0.2989185664601128</v>
       </c>
       <c r="Q22" t="n">
-        <v>20.58181820755303</v>
+        <v>20.58181820758407</v>
       </c>
       <c r="R22" t="n">
-        <v>1.889372361102943</v>
+        <v>1.889372361103508</v>
       </c>
       <c r="S22" t="n">
-        <v>0.007200136731513198</v>
+        <v>0.007200136731500186</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1237179128246555</v>
+        <v>0.1237179128245816</v>
       </c>
       <c r="U22" t="n">
         <v>0.002246666666666667</v>
@@ -2484,7 +2484,7 @@
         <v>0.002246666666666667</v>
       </c>
       <c r="W22" t="n">
-        <v>20.47349558519533</v>
+        <v>20.47349558522638</v>
       </c>
       <c r="X22" t="n">
         <v>0.00396735495458923</v>
@@ -2496,10 +2496,10 @@
         <v>0.102602067198723</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.00553492897706259</v>
+        <v>0.005534928977054236</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.1139189019976197</v>
+        <v>0.1139189019976196</v>
       </c>
     </row>
     <row r="23">
@@ -2558,16 +2558,16 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>15.01969250829702</v>
+        <v>15.01969250829701</v>
       </c>
       <c r="R23" t="n">
         <v>1.792146527775721</v>
       </c>
       <c r="S23" t="n">
-        <v>0.009244457711781045</v>
+        <v>0.009244457741737573</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1221151692588028</v>
+        <v>0.1221151697087406</v>
       </c>
       <c r="U23" t="n">
         <v>0.001996666666666667</v>
@@ -2588,7 +2588,7 @@
         <v>0.06320238611045444</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.004235445898201379</v>
+        <v>0.00423544589820138</v>
       </c>
       <c r="AB23" t="n">
         <v>0.06361509502651258</v>
@@ -2656,10 +2656,10 @@
         <v>1.794373111109054</v>
       </c>
       <c r="S24" t="n">
-        <v>0.009402010871868823</v>
+        <v>0.009402010873351092</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1251651756272311</v>
+        <v>0.1251651756496959</v>
       </c>
       <c r="U24" t="n">
         <v>0.002051666666666667</v>
@@ -2668,7 +2668,7 @@
         <v>0.002051666666666667</v>
       </c>
       <c r="W24" t="n">
-        <v>15.01969250829702</v>
+        <v>15.01969250829701</v>
       </c>
       <c r="X24" t="n">
         <v>0.00139773628339818</v>
@@ -2748,10 +2748,10 @@
         <v>1.796379749997943</v>
       </c>
       <c r="S25" t="n">
-        <v>0.009535870585130196</v>
+        <v>0.00953587058164054</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1278286042487415</v>
+        <v>0.1278286041954265</v>
       </c>
       <c r="U25" t="n">
         <v>0.0021</v>
@@ -2772,7 +2772,7 @@
         <v>0.03650228328522884</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.00273972621461791</v>
+        <v>0.002739726214617911</v>
       </c>
       <c r="AB25" t="n">
         <v>0.04185748085752747</v>
@@ -2834,16 +2834,16 @@
         <v>0.1703755277559266</v>
       </c>
       <c r="Q26" t="n">
-        <v>15.40717642247016</v>
+        <v>15.40717642247015</v>
       </c>
       <c r="R26" t="n">
         <v>1.798504749997943</v>
       </c>
       <c r="S26" t="n">
-        <v>0.009669531240909355</v>
+        <v>0.009669531246993858</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1305618574758552</v>
+        <v>0.1305618575696002</v>
       </c>
       <c r="U26" t="n">
         <v>0.00215</v>
@@ -2864,7 +2864,7 @@
         <v>0.01662203559450923</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.001732058081469854</v>
+        <v>0.001732058081469855</v>
       </c>
       <c r="AB26" t="n">
         <v>0.02668612443517123</v>
@@ -2926,16 +2926,16 @@
         <v>0.2036432131066642</v>
       </c>
       <c r="Q27" t="n">
-        <v>15.54576471838672</v>
+        <v>15.54576471838671</v>
       </c>
       <c r="R27" t="n">
-        <v>1.800789812497943</v>
+        <v>1.800789812497944</v>
       </c>
       <c r="S27" t="n">
-        <v>0.009804928460793325</v>
+        <v>0.009804928460010224</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1334114833812312</v>
+        <v>0.1334114833690572</v>
       </c>
       <c r="U27" t="n">
         <v>0.0022025</v>
@@ -2944,7 +2944,7 @@
         <v>0.0022025</v>
       </c>
       <c r="W27" t="n">
-        <v>15.40717642247016</v>
+        <v>15.40717642247015</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -2956,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.0006703122036587193</v>
+        <v>0.0006703122036587197</v>
       </c>
       <c r="AB27" t="n">
         <v>0.01042051580594177</v>
@@ -3021,13 +3021,13 @@
         <v>15.66240050600434</v>
       </c>
       <c r="R28" t="n">
-        <v>1.802717423609054</v>
+        <v>1.802717423609055</v>
       </c>
       <c r="S28" t="n">
-        <v>0.009912768032329064</v>
+        <v>0.009912768032329062</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1357454552760377</v>
+        <v>0.1357454552760376</v>
       </c>
       <c r="U28" t="n">
         <v>0.002245833333333333</v>
@@ -3036,7 +3036,7 @@
         <v>0.002245833333333333</v>
       </c>
       <c r="W28" t="n">
-        <v>15.54576471838672</v>
+        <v>15.54576471838671</v>
       </c>
       <c r="X28" t="n">
         <v>0.07036365759109456</v>
@@ -3113,13 +3113,13 @@
         <v>23.93967898481781</v>
       </c>
       <c r="R29" t="n">
-        <v>2.098491694429186</v>
+        <v>2.098491694429187</v>
       </c>
       <c r="S29" t="n">
-        <v>0.01007990385835065</v>
+        <v>0.01007990389195562</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1949549898908649</v>
+        <v>0.194954990695357</v>
       </c>
       <c r="U29" t="n">
         <v>0.004063333333333333</v>
@@ -3202,16 +3202,16 @@
         <v>0.06375494686076261</v>
       </c>
       <c r="Q30" t="n">
-        <v>24.2281458354068</v>
+        <v>24.22814583540682</v>
       </c>
       <c r="R30" t="n">
-        <v>2.104521249984742</v>
+        <v>2.104521249984743</v>
       </c>
       <c r="S30" t="n">
-        <v>0.01063211161318078</v>
+        <v>0.01063211162014986</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2075172961978925</v>
+        <v>0.2075172963667405</v>
       </c>
       <c r="U30" t="n">
         <v>0.00435</v>
@@ -3232,7 +3232,7 @@
         <v>0.06485638924285067</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.002715697513538642</v>
+        <v>0.00271569751353864</v>
       </c>
       <c r="AB30" t="n">
         <v>0.06579631540286586</v>
@@ -3294,16 +3294,16 @@
         <v>0.1716212668026328</v>
       </c>
       <c r="Q31" t="n">
-        <v>24.54912556934149</v>
+        <v>24.54912556934151</v>
       </c>
       <c r="R31" t="n">
-        <v>2.111271249984742</v>
+        <v>2.111271249984743</v>
       </c>
       <c r="S31" t="n">
-        <v>0.01118090176887276</v>
+        <v>0.01118090177937685</v>
       </c>
       <c r="T31" t="n">
-        <v>0.220412783673763</v>
+        <v>0.2204127839316294</v>
       </c>
       <c r="U31" t="n">
         <v>0.00465</v>
@@ -3312,7 +3312,7 @@
         <v>0.00465</v>
       </c>
       <c r="W31" t="n">
-        <v>24.2281458354068</v>
+        <v>24.22814583540682</v>
       </c>
       <c r="X31" t="n">
         <v>0.01411667984325947</v>
@@ -3324,7 +3324,7 @@
         <v>0.04872158819598323</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.002019535772512295</v>
+        <v>0.002019535772512294</v>
       </c>
       <c r="AB31" t="n">
         <v>0.0495778372711814</v>
@@ -3386,16 +3386,16 @@
         <v>0.2547670720457892</v>
       </c>
       <c r="Q32" t="n">
-        <v>25.00680786687654</v>
+        <v>25.00680786687655</v>
       </c>
       <c r="R32" t="n">
-        <v>2.120971249984742</v>
+        <v>2.120971249984743</v>
       </c>
       <c r="S32" t="n">
-        <v>0.01186590941261322</v>
+        <v>0.01186590939888761</v>
       </c>
       <c r="T32" t="n">
-        <v>0.2371876910443514</v>
+        <v>0.2371876907011177</v>
       </c>
       <c r="U32" t="n">
         <v>0.005050000000000001</v>
@@ -3404,7 +3404,7 @@
         <v>0.005050000000000001</v>
       </c>
       <c r="W32" t="n">
-        <v>24.54912556934149</v>
+        <v>24.54912556934151</v>
       </c>
       <c r="X32" t="n">
         <v>0.01729347944990734</v>
@@ -3478,16 +3478,16 @@
         <v>0.3345630000595383</v>
       </c>
       <c r="Q33" t="n">
-        <v>26.11045456330865</v>
+        <v>26.11045456330866</v>
       </c>
       <c r="R33" t="n">
-        <v>2.144732361095853</v>
+        <v>2.144732361095854</v>
       </c>
       <c r="S33" t="n">
-        <v>0.01316720048945217</v>
+        <v>0.01316720038405787</v>
       </c>
       <c r="T33" t="n">
-        <v>0.2717707582087737</v>
+        <v>0.2717707554568806</v>
       </c>
       <c r="U33" t="n">
         <v>0.005916666666666667</v>
@@ -3496,7 +3496,7 @@
         <v>0.005916666666666667</v>
       </c>
       <c r="W33" t="n">
-        <v>25.00680786687654</v>
+        <v>25.00680786687655</v>
       </c>
       <c r="X33" t="n">
         <v>0.01396089162246411</v>
@@ -3508,10 +3508,10 @@
         <v>0.002777158124534164</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.0001589641491270463</v>
+        <v>0.0001589641491270462</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.004150626192976762</v>
+        <v>0.004150626192976761</v>
       </c>
     </row>
     <row r="34">
@@ -3570,16 +3570,16 @@
         <v>0.4114676331552647</v>
       </c>
       <c r="Q34" t="n">
-        <v>26.57397314534753</v>
+        <v>26.57397314534754</v>
       </c>
       <c r="R34" t="n">
-        <v>2.154871249984741</v>
+        <v>2.154871249984743</v>
       </c>
       <c r="S34" t="n">
-        <v>0.01360207801067354</v>
+        <v>0.01360207800305404</v>
       </c>
       <c r="T34" t="n">
-        <v>0.284385963153116</v>
+        <v>0.2843859629506359</v>
       </c>
       <c r="U34" t="n">
         <v>0.00625</v>
@@ -3588,7 +3588,7 @@
         <v>0.00625</v>
       </c>
       <c r="W34" t="n">
-        <v>26.11045456330865</v>
+        <v>26.11045456330866</v>
       </c>
       <c r="X34" t="n">
         <v>0.01145255846603085</v>
@@ -3600,10 +3600,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>4.439867806962225e-05</v>
+        <v>4.43986780696222e-05</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.001179849278711072</v>
+        <v>0.001179849278711071</v>
       </c>
     </row>
     <row r="35">
@@ -3665,13 +3665,13 @@
         <v>27.30784322790872</v>
       </c>
       <c r="R35" t="n">
-        <v>2.171121249984742</v>
+        <v>2.171121249984743</v>
       </c>
       <c r="S35" t="n">
-        <v>0.0141884524772847</v>
+        <v>0.01418845246147928</v>
       </c>
       <c r="T35" t="n">
-        <v>0.3025561521198283</v>
+        <v>0.3025561516882164</v>
       </c>
       <c r="U35" t="n">
         <v>0.006750000000000001</v>
@@ -3680,7 +3680,7 @@
         <v>0.006750000000000001</v>
       </c>
       <c r="W35" t="n">
-        <v>26.57397314534753</v>
+        <v>26.57397314534754</v>
       </c>
       <c r="X35" t="n">
         <v>0.009152735978746178</v>
@@ -3692,10 +3692,10 @@
         <v>0.001762949417501451</v>
       </c>
       <c r="AA35" t="n">
-        <v>4.578707085297216e-05</v>
+        <v>4.578707085297215e-05</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.001250346152718113</v>
+        <v>0.001250346152718112</v>
       </c>
     </row>
     <row r="36">
@@ -3754,16 +3754,16 @@
         <v>0.4021708299263646</v>
       </c>
       <c r="Q36" t="n">
-        <v>27.82182632859926</v>
+        <v>27.82182632859923</v>
       </c>
       <c r="R36" t="n">
-        <v>2.182649027762519</v>
+        <v>2.182649027762521</v>
       </c>
       <c r="S36" t="n">
-        <v>0.01453689713190097</v>
+        <v>0.01453689738861425</v>
       </c>
       <c r="T36" t="n">
-        <v>0.3141530781652856</v>
+        <v>0.3141530853075174</v>
       </c>
       <c r="U36" t="n">
         <v>0.007083333333333334</v>
@@ -3784,7 +3784,7 @@
         <v>0.001647154283060745</v>
       </c>
       <c r="AA36" t="n">
-        <v>4.518776391829951e-05</v>
+        <v>4.518776391829954e-05</v>
       </c>
       <c r="AB36" t="n">
         <v>0.001257206119912673</v>
@@ -3846,16 +3846,16 @@
         <v>0.3873938421634567</v>
       </c>
       <c r="Q37" t="n">
-        <v>28.72212538793306</v>
+        <v>28.72212538793305</v>
       </c>
       <c r="R37" t="n">
-        <v>2.203138999984742</v>
+        <v>2.203138999984743</v>
       </c>
       <c r="S37" t="n">
-        <v>0.01504659661368045</v>
+        <v>0.01504659661323521</v>
       </c>
       <c r="T37" t="n">
-        <v>0.332568240370033</v>
+        <v>0.3325682403572446</v>
       </c>
       <c r="U37" t="n">
         <v>0.007640000000000001</v>
@@ -3864,7 +3864,7 @@
         <v>0.007640000000000001</v>
       </c>
       <c r="W37" t="n">
-        <v>27.82182632859926</v>
+        <v>27.82182632859923</v>
       </c>
       <c r="X37" t="n">
         <v>0.007018151213335786</v>
@@ -3876,10 +3876,10 @@
         <v>0.0005503013934911842</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.454302433905063e-05</v>
+        <v>4.454302433905062e-05</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.001279370330223966</v>
+        <v>0.001279370330223965</v>
       </c>
     </row>
     <row r="38">
@@ -3938,16 +3938,16 @@
         <v>0.3689307159607038</v>
       </c>
       <c r="Q38" t="n">
-        <v>29.76547646571372</v>
+        <v>29.76547646571371</v>
       </c>
       <c r="R38" t="n">
-        <v>2.227371249984742</v>
+        <v>2.227371249984743</v>
       </c>
       <c r="S38" t="n">
-        <v>0.01550784152635049</v>
+        <v>0.0155078415118352</v>
       </c>
       <c r="T38" t="n">
-        <v>0.3513494141473926</v>
+        <v>0.3513494137153382</v>
       </c>
       <c r="U38" t="n">
         <v>0.00825</v>
@@ -3956,7 +3956,7 @@
         <v>0.00825</v>
       </c>
       <c r="W38" t="n">
-        <v>28.72212538793306</v>
+        <v>28.72212538793305</v>
       </c>
       <c r="X38" t="n">
         <v>0.01009923569250023</v>
@@ -3968,10 +3968,10 @@
         <v>0.0004247662125730495</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.408174559026024e-05</v>
+        <v>4.408174559026023e-05</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.001312114160934471</v>
+        <v>0.00131211416093447</v>
       </c>
     </row>
     <row r="39">
@@ -4030,16 +4030,16 @@
         <v>0.3542503465167628</v>
       </c>
       <c r="Q39" t="n">
-        <v>30.84541916498261</v>
+        <v>30.84541916498249</v>
       </c>
       <c r="R39" t="n">
-        <v>2.253021249984741</v>
+        <v>2.253021249984743</v>
       </c>
       <c r="S39" t="n">
-        <v>0.01587051772024678</v>
+        <v>0.01587051773015364</v>
       </c>
       <c r="T39" t="n">
-        <v>0.3683701505380624</v>
+        <v>0.3683701508436424</v>
       </c>
       <c r="U39" t="n">
         <v>0.00885</v>
@@ -4048,7 +4048,7 @@
         <v>0.00885</v>
       </c>
       <c r="W39" t="n">
-        <v>29.76547646571372</v>
+        <v>29.76547646571371</v>
       </c>
       <c r="X39" t="n">
         <v>0.007799312579268405</v>
@@ -4060,10 +4060,10 @@
         <v>0.008954679612111731</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.0003012099228746787</v>
+        <v>0.0003012099228746798</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.009290946327721547</v>
+        <v>0.009290946327721546</v>
       </c>
     </row>
     <row r="40">
@@ -4125,13 +4125,13 @@
         <v>31.81469618008588</v>
       </c>
       <c r="R40" t="n">
-        <v>2.276551111095853</v>
+        <v>2.276551111095854</v>
       </c>
       <c r="S40" t="n">
-        <v>0.0161169662921108</v>
+        <v>0.01611696629211079</v>
       </c>
       <c r="T40" t="n">
-        <v>0.381857653732939</v>
+        <v>0.3818576537329387</v>
       </c>
       <c r="U40" t="n">
         <v>0.009366666666666667</v>
@@ -4140,7 +4140,7 @@
         <v>0.009366666666666667</v>
       </c>
       <c r="W40" t="n">
-        <v>30.84541916498261</v>
+        <v>30.84541916498249</v>
       </c>
       <c r="X40" t="n">
         <v>0.006429284455135683</v>
@@ -4214,16 +4214,16 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>28.24180486689044</v>
+        <v>28.24180486627348</v>
       </c>
       <c r="R41" t="n">
-        <v>2.198068889704303</v>
+        <v>2.198068889704301</v>
       </c>
       <c r="S41" t="n">
-        <v>0.007073425374068638</v>
+        <v>0.007080000683784983</v>
       </c>
       <c r="T41" t="n">
-        <v>0.1091418130006905</v>
+        <v>0.1093275116122504</v>
       </c>
       <c r="U41" t="n">
         <v>0.007053333333333333</v>
@@ -4244,7 +4244,7 @@
         <v>0.04292053230848831</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.001524917290366768</v>
+        <v>0.00152491729040008</v>
       </c>
       <c r="AB41" t="n">
         <v>0.04306641655268557</v>
@@ -4306,16 +4306,16 @@
         <v>0.05060060245371522</v>
       </c>
       <c r="Q42" t="n">
-        <v>28.4719136932896</v>
+        <v>28.47191369328903</v>
       </c>
       <c r="R42" t="n">
-        <v>2.20332922829797</v>
+        <v>2.203329228297967</v>
       </c>
       <c r="S42" t="n">
-        <v>0.007575517607850952</v>
+        <v>0.00757552039323006</v>
       </c>
       <c r="T42" t="n">
-        <v>0.1171359889591415</v>
+        <v>0.1171360682642126</v>
       </c>
       <c r="U42" t="n">
         <v>0.007626666666666667</v>
@@ -4324,7 +4324,7 @@
         <v>0.003813333333333334</v>
       </c>
       <c r="W42" t="n">
-        <v>28.24180486689044</v>
+        <v>28.24180486627348</v>
       </c>
       <c r="X42" t="n">
         <v>0.009793628241382288</v>
@@ -4336,7 +4336,7 @@
         <v>0.03670292593065684</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.001330806855107746</v>
+        <v>0.001330806855107773</v>
       </c>
       <c r="AB42" t="n">
         <v>0.03789061792106591</v>
@@ -4398,16 +4398,16 @@
         <v>0.1044036282464569</v>
       </c>
       <c r="Q43" t="n">
-        <v>28.65987999487133</v>
+        <v>28.65987999487103</v>
       </c>
       <c r="R43" t="n">
-        <v>2.207644899280303</v>
+        <v>2.2076448992803</v>
       </c>
       <c r="S43" t="n">
-        <v>0.00794445905433588</v>
+        <v>0.007944459054335953</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1229649217459896</v>
+        <v>0.1229649217459902</v>
       </c>
       <c r="U43" t="n">
         <v>0.008066666666666666</v>
@@ -4416,7 +4416,7 @@
         <v>0.004033333333333333</v>
       </c>
       <c r="W43" t="n">
-        <v>28.4719136932896</v>
+        <v>28.47191369328903</v>
       </c>
       <c r="X43" t="n">
         <v>0.01308713559294417</v>
@@ -4428,7 +4428,7 @@
         <v>0.03226430616673658</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.001176819229347405</v>
+        <v>0.001176819229347417</v>
       </c>
       <c r="AB43" t="n">
         <v>0.03372749788875357</v>
@@ -4490,16 +4490,16 @@
         <v>0.1491197853115378</v>
       </c>
       <c r="Q44" t="n">
-        <v>28.92563754904613</v>
+        <v>28.92563754904579</v>
       </c>
       <c r="R44" t="n">
-        <v>2.213775572077636</v>
+        <v>2.213775572077634</v>
       </c>
       <c r="S44" t="n">
-        <v>0.008420554940362099</v>
+        <v>0.008420554940362222</v>
       </c>
       <c r="T44" t="n">
-        <v>0.1305037237789281</v>
+        <v>0.13050372377893</v>
       </c>
       <c r="U44" t="n">
         <v>0.008653333333333332</v>
@@ -4508,7 +4508,7 @@
         <v>0.004326666666666666</v>
       </c>
       <c r="W44" t="n">
-        <v>28.65987999487133</v>
+        <v>28.65987999487103</v>
       </c>
       <c r="X44" t="n">
         <v>0.01416473965932023</v>
@@ -4520,7 +4520,7 @@
         <v>0.02491516024776152</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.0008945528030802108</v>
+        <v>0.0008945528030802212</v>
       </c>
       <c r="AB44" t="n">
         <v>0.02587551015038141</v>
@@ -4582,16 +4582,16 @@
         <v>0.1918414613393818</v>
       </c>
       <c r="Q45" t="n">
-        <v>29.46262799242935</v>
+        <v>29.46262799242903</v>
       </c>
       <c r="R45" t="n">
-        <v>2.226267723458665</v>
+        <v>2.226267723458661</v>
       </c>
       <c r="S45" t="n">
-        <v>0.009253028608468959</v>
+        <v>0.009253028608469023</v>
       </c>
       <c r="T45" t="n">
-        <v>0.1437185005742468</v>
+        <v>0.143718500574247</v>
       </c>
       <c r="U45" t="n">
         <v>0.009740000000000002</v>
@@ -4600,7 +4600,7 @@
         <v>0.004870000000000001</v>
       </c>
       <c r="W45" t="n">
-        <v>28.92563754904613</v>
+        <v>28.92563754904579</v>
       </c>
       <c r="X45" t="n">
         <v>0.01158551351625574</v>
@@ -4612,7 +4612,7 @@
         <v>0.01583178431944987</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.0005561275272637983</v>
+        <v>0.0005561275272638044</v>
       </c>
       <c r="AB45" t="n">
         <v>0.0163849784521229</v>
@@ -4674,16 +4674,16 @@
         <v>0.2448076315621145</v>
       </c>
       <c r="Q46" t="n">
-        <v>30.73245487142585</v>
+        <v>30.73245487142606</v>
       </c>
       <c r="R46" t="n">
-        <v>2.256376503567415</v>
+        <v>2.256376503567412</v>
       </c>
       <c r="S46" t="n">
-        <v>0.01074722783805307</v>
+        <v>0.01074722221765609</v>
       </c>
       <c r="T46" t="n">
-        <v>0.1673902776698777</v>
+        <v>0.1673901049412822</v>
       </c>
       <c r="U46" t="n">
         <v>0.01196</v>
@@ -4692,7 +4692,7 @@
         <v>0.005979999999999999</v>
       </c>
       <c r="W46" t="n">
-        <v>29.46262799242935</v>
+        <v>29.46262799242903</v>
       </c>
       <c r="X46" t="n">
         <v>0.01018412764647287</v>
@@ -4704,10 +4704,10 @@
         <v>0.003813578138281135</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.000160639813569606</v>
+        <v>0.000160639813569605</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.004936855821082178</v>
+        <v>0.00493685582108218</v>
       </c>
     </row>
     <row r="47">
@@ -4766,16 +4766,16 @@
         <v>0.2862295508009267</v>
       </c>
       <c r="Q47" t="n">
-        <v>31.15248097069052</v>
+        <v>31.15248097068831</v>
       </c>
       <c r="R47" t="n">
-        <v>2.266515763706664</v>
+        <v>2.266515763706662</v>
       </c>
       <c r="S47" t="n">
-        <v>0.01113732683946593</v>
+        <v>0.01113734544500751</v>
       </c>
       <c r="T47" t="n">
-        <v>0.173497795470351</v>
+        <v>0.1734983750791186</v>
       </c>
       <c r="U47" t="n">
         <v>0.01262</v>
@@ -4784,7 +4784,7 @@
         <v>0.00631</v>
       </c>
       <c r="W47" t="n">
-        <v>30.73245487142585</v>
+        <v>30.73245487142606</v>
       </c>
       <c r="X47" t="n">
         <v>0.0085377509283628</v>
@@ -4796,10 +4796,10 @@
         <v>0.002635143243149769</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.000121230682064597</v>
+        <v>0.0001212306820646056</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.003776636516081191</v>
+        <v>0.003776636516081192</v>
       </c>
     </row>
     <row r="48">
@@ -4858,16 +4858,16 @@
         <v>0.2889524121591054</v>
       </c>
       <c r="Q48" t="n">
-        <v>31.55039960381771</v>
+        <v>31.55039960381902</v>
       </c>
       <c r="R48" t="n">
-        <v>2.276205773396665</v>
+        <v>2.276205773396662</v>
       </c>
       <c r="S48" t="n">
-        <v>0.01147068869907342</v>
+        <v>0.0114706754208951</v>
       </c>
       <c r="T48" t="n">
-        <v>0.1786629068909775</v>
+        <v>0.1786624879591527</v>
       </c>
       <c r="U48" t="n">
         <v>0.01322</v>
@@ -4876,7 +4876,7 @@
         <v>0.00661</v>
       </c>
       <c r="W48" t="n">
-        <v>31.15248097069052</v>
+        <v>31.15248097068831</v>
       </c>
       <c r="X48" t="n">
         <v>0.01094124388489767</v>
@@ -4888,10 +4888,10 @@
         <v>0.003468413842637606</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.0001197389718612531</v>
+        <v>0.0001197389718612482</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.003777812410372821</v>
+        <v>0.003777812410372823</v>
       </c>
     </row>
     <row r="49">
@@ -4950,16 +4950,16 @@
         <v>0.2916972101212668</v>
       </c>
       <c r="Q49" t="n">
-        <v>31.95385449141564</v>
+        <v>31.95385449141525</v>
       </c>
       <c r="R49" t="n">
-        <v>2.28611556108422</v>
+        <v>2.286115561084217</v>
       </c>
       <c r="S49" t="n">
-        <v>0.01177718080478872</v>
+        <v>0.01177717876146381</v>
       </c>
       <c r="T49" t="n">
-        <v>0.1833456058247001</v>
+        <v>0.1833455405325909</v>
       </c>
       <c r="U49" t="n">
         <v>0.01380666666666667</v>
@@ -4968,7 +4968,7 @@
         <v>0.006903333333333334</v>
       </c>
       <c r="W49" t="n">
-        <v>31.55039960381771</v>
+        <v>31.55039960381902</v>
       </c>
       <c r="X49" t="n">
         <v>0.01496737650102324</v>
@@ -4980,10 +4980,10 @@
         <v>0.004427144891717553</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.0001359515592164663</v>
+        <v>0.000135951559216468</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.004344176341084041</v>
+        <v>0.004344176341084043</v>
       </c>
     </row>
     <row r="50">
@@ -5042,16 +5042,16 @@
         <v>0.2947411967231239</v>
       </c>
       <c r="Q50" t="n">
-        <v>32.83159453257404</v>
+        <v>32.83159453257299</v>
       </c>
       <c r="R50" t="n">
-        <v>2.307975805166664</v>
+        <v>2.307975805166662</v>
       </c>
       <c r="S50" t="n">
-        <v>0.01235151587956077</v>
+        <v>0.01235152298094111</v>
       </c>
       <c r="T50" t="n">
-        <v>0.1918563046190789</v>
+        <v>0.1918565377687123</v>
       </c>
       <c r="U50" t="n">
         <v>0.01502</v>
@@ -5060,7 +5060,7 @@
         <v>0.007509999999999999</v>
       </c>
       <c r="W50" t="n">
-        <v>31.95385449141564</v>
+        <v>31.95385449141525</v>
       </c>
       <c r="X50" t="n">
         <v>0.01393403278476044</v>
@@ -5072,10 +5072,10 @@
         <v>0.006989072490978496</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.0002310196494435016</v>
+        <v>0.0002310196494435091</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.007584743459586439</v>
+        <v>0.007584743459586441</v>
       </c>
     </row>
     <row r="51">
@@ -5134,16 +5134,16 @@
         <v>0.3061500936386944</v>
       </c>
       <c r="Q51" t="n">
-        <v>33.75408934834007</v>
+        <v>33.75408934834168</v>
       </c>
       <c r="R51" t="n">
-        <v>2.331405828596664</v>
+        <v>2.331405828596663</v>
       </c>
       <c r="S51" t="n">
-        <v>0.01284342625596111</v>
+        <v>0.01284341423264229</v>
       </c>
       <c r="T51" t="n">
-        <v>0.1986850268676124</v>
+        <v>0.1986846210314439</v>
       </c>
       <c r="U51" t="n">
         <v>0.01622</v>
@@ -5152,7 +5152,7 @@
         <v>0.008110000000000001</v>
       </c>
       <c r="W51" t="n">
-        <v>32.83159453257404</v>
+        <v>32.83159453257299</v>
       </c>
       <c r="X51" t="n">
         <v>0.01157922320647989</v>
@@ -5164,7 +5164,7 @@
         <v>0.01216839656025612</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.0004041724259930121</v>
+        <v>0.0004041724259929929</v>
       </c>
       <c r="AB51" t="n">
         <v>0.0136424721791035</v>
@@ -5226,16 +5226,16 @@
         <v>0.3308651428571041</v>
       </c>
       <c r="Q52" t="n">
-        <v>34.61647934279934</v>
+        <v>34.61647934279866</v>
       </c>
       <c r="R52" t="n">
-        <v>2.35374362871222</v>
+        <v>2.353743628712218</v>
       </c>
       <c r="S52" t="n">
-        <v>0.0132203465779301</v>
+        <v>0.01322035179421022</v>
       </c>
       <c r="T52" t="n">
-        <v>0.2034070546972727</v>
+        <v>0.2034072352665216</v>
       </c>
       <c r="U52" t="n">
         <v>0.01728666666666667</v>
@@ -5244,7 +5244,7 @@
         <v>0.008643333333333333</v>
       </c>
       <c r="W52" t="n">
-        <v>33.75408934834007</v>
+        <v>33.75408934834168</v>
       </c>
       <c r="X52" t="n">
         <v>0.009267599997966548</v>
@@ -5256,10 +5256,10 @@
         <v>0.01961652719811411</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.0006187360183830693</v>
+        <v>0.0006187360183830816</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.02141846259900343</v>
+        <v>0.02141846259900344</v>
       </c>
     </row>
     <row r="53">
@@ -5318,16 +5318,16 @@
         <v>0.3724108962071924</v>
       </c>
       <c r="Q53" t="n">
-        <v>35.52745852239729</v>
+        <v>35.52745852239767</v>
       </c>
       <c r="R53" t="n">
-        <v>2.377809652778219</v>
+        <v>2.377809652778218</v>
       </c>
       <c r="S53" t="n">
-        <v>0.013547618883582</v>
+        <v>0.01354761888358185</v>
       </c>
       <c r="T53" t="n">
-        <v>0.2068914320190097</v>
+        <v>0.2068914320190066</v>
       </c>
       <c r="U53" t="n">
         <v>0.01836666666666667</v>
@@ -5336,7 +5336,7 @@
         <v>0.009183333333333333</v>
       </c>
       <c r="W53" t="n">
-        <v>34.61647934279934</v>
+        <v>34.61647934279866</v>
       </c>
       <c r="X53" t="n">
         <v>0.006196243412663805</v>
@@ -5348,7 +5348,7 @@
         <v>0.02963924799363945</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.0008844102245227442</v>
+        <v>0.0008844102245227347</v>
       </c>
       <c r="AB53" t="n">
         <v>0.03142084756851587</v>

--- a/data/processed/BR_processed_ind.xlsx
+++ b/data/processed/BR_processed_ind.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD85"/>
+  <dimension ref="A1:AD69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -844,10 +844,10 @@
         <v>1.856115873425756</v>
       </c>
       <c r="U4" t="n">
-        <v>0.006462734694132884</v>
+        <v>0.006462734701134105</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1368600616035126</v>
+        <v>0.1368600617928715</v>
       </c>
       <c r="W4" t="n">
         <v>0.002603333333333333</v>
@@ -942,10 +942,10 @@
         <v>1.861850276203534</v>
       </c>
       <c r="U5" t="n">
-        <v>0.006890089633184113</v>
+        <v>0.006890089696224523</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1470768837589695</v>
+        <v>0.1470768854829419</v>
       </c>
       <c r="W5" t="n">
         <v>0.002815</v>
@@ -969,7 +969,7 @@
         <v>0.002529907594138958</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0691856365172801</v>
+        <v>0.06918563651728009</v>
       </c>
     </row>
     <row r="6">
@@ -1034,16 +1034,16 @@
         <v>0.462353720667521</v>
       </c>
       <c r="S6" t="n">
-        <v>27.65075345784807</v>
+        <v>27.65075345784806</v>
       </c>
       <c r="T6" t="n">
         <v>1.867680276203534</v>
       </c>
       <c r="U6" t="n">
-        <v>0.007275813451270728</v>
+        <v>0.007275813546525556</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1565450574153875</v>
+        <v>0.1565450600492553</v>
       </c>
       <c r="W6" t="n">
         <v>0.003015</v>
@@ -1064,7 +1064,7 @@
         <v>0.112121445976553</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.004332845827374901</v>
+        <v>0.004332845827374902</v>
       </c>
       <c r="AD6" t="n">
         <v>0.1198064517436091</v>
@@ -1132,16 +1132,16 @@
         <v>0.6209461221159972</v>
       </c>
       <c r="S7" t="n">
-        <v>27.96486690504821</v>
+        <v>27.96486690504819</v>
       </c>
       <c r="T7" t="n">
-        <v>1.873749651203534</v>
+        <v>1.873749651203535</v>
       </c>
       <c r="U7" t="n">
-        <v>0.007634557258848181</v>
+        <v>0.007634557396181491</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1655915780361208</v>
+        <v>0.1655915818766285</v>
       </c>
       <c r="W7" t="n">
         <v>0.003210000000000001</v>
@@ -1150,7 +1150,7 @@
         <v>0.003210000000000001</v>
       </c>
       <c r="Y7" t="n">
-        <v>27.65075345784807</v>
+        <v>27.65075345784806</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>0.2218548813486614</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.008700430054214307</v>
+        <v>0.008700430054214312</v>
       </c>
       <c r="AD7" t="n">
         <v>0.2433063684827845</v>
@@ -1230,13 +1230,13 @@
         <v>0.9523209449429346</v>
       </c>
       <c r="S8" t="n">
-        <v>28.14125939399926</v>
+        <v>28.14125939399925</v>
       </c>
       <c r="T8" t="n">
-        <v>1.877175276203534</v>
+        <v>1.877175276203535</v>
       </c>
       <c r="U8" t="n">
-        <v>0.007820572933980101</v>
+        <v>0.007820572933980099</v>
       </c>
       <c r="V8" t="n">
         <v>0.1703846797234053</v>
@@ -1248,7 +1248,7 @@
         <v>0.003315</v>
       </c>
       <c r="Y8" t="n">
-        <v>27.96486690504821</v>
+        <v>27.96486690504819</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
         <v>28.31682006871788</v>
       </c>
       <c r="T9" t="n">
-        <v>1.880597206759089</v>
+        <v>1.88059720675909</v>
       </c>
       <c r="U9" t="n">
         <v>0.007995870233005813</v>
@@ -1346,7 +1346,7 @@
         <v>0.003416666666666667</v>
       </c>
       <c r="Y9" t="n">
-        <v>28.14125939399926</v>
+        <v>28.14125939399925</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -1426,10 +1426,10 @@
         <v>1.69587337268752</v>
       </c>
       <c r="S10" t="n">
-        <v>28.48804706810439</v>
+        <v>28.48804706810438</v>
       </c>
       <c r="T10" t="n">
-        <v>1.883946706759089</v>
+        <v>1.88394670675909</v>
       </c>
       <c r="U10" t="n">
         <v>0.008158145763995973</v>
@@ -2112,16 +2112,16 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>19.99434722414867</v>
+        <v>19.99434722445</v>
       </c>
       <c r="T17" t="n">
-        <v>1.878764027770175</v>
+        <v>1.878764027775987</v>
       </c>
       <c r="U17" t="n">
-        <v>0.00662367589221488</v>
+        <v>0.006623944767816831</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1111869746663001</v>
+        <v>0.1111923506601871</v>
       </c>
       <c r="W17" t="n">
         <v>0.001996666666666667</v>
@@ -2142,10 +2142,10 @@
         <v>0.0816312894067058</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.004090749458213853</v>
+        <v>0.004090749458152188</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.08179186507452584</v>
+        <v>0.08179186507452553</v>
       </c>
     </row>
     <row r="18">
@@ -2210,16 +2210,16 @@
         <v>0.09290978010103844</v>
       </c>
       <c r="S18" t="n">
-        <v>20.11820096981678</v>
+        <v>20.11820097013989</v>
       </c>
       <c r="T18" t="n">
-        <v>1.880990611103508</v>
+        <v>1.88099061110932</v>
       </c>
       <c r="U18" t="n">
-        <v>0.006756701709062598</v>
+        <v>0.006756699312366905</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1139890101753636</v>
+        <v>0.1139889619600565</v>
       </c>
       <c r="W18" t="n">
         <v>0.002051666666666667</v>
@@ -2228,7 +2228,7 @@
         <v>0.002051666666666667</v>
       </c>
       <c r="Y18" t="n">
-        <v>19.99434722414867</v>
+        <v>19.99434722445</v>
       </c>
       <c r="Z18" t="n">
         <v>0.01789804707363351</v>
@@ -2240,10 +2240,10 @@
         <v>0.04078878183453907</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.002159985784730224</v>
+        <v>0.002159985784695504</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.04345502810915004</v>
+        <v>0.04345502810914946</v>
       </c>
     </row>
     <row r="19">
@@ -2308,16 +2308,16 @@
         <v>0.1714635834683609</v>
       </c>
       <c r="S19" t="n">
-        <v>20.22568990467636</v>
+        <v>20.22568990499862</v>
       </c>
       <c r="T19" t="n">
-        <v>1.882927277770174</v>
+        <v>1.882927277775987</v>
       </c>
       <c r="U19" t="n">
-        <v>0.006866587915312488</v>
+        <v>0.006866587915181886</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1163419779105216</v>
+        <v>0.1163419779098033</v>
       </c>
       <c r="W19" t="n">
         <v>0.002098333333333333</v>
@@ -2326,7 +2326,7 @@
         <v>0.002098333333333333</v>
       </c>
       <c r="Y19" t="n">
-        <v>20.11820096981678</v>
+        <v>20.11820097013989</v>
       </c>
       <c r="Z19" t="n">
         <v>0.001401645203937436</v>
@@ -2338,10 +2338,10 @@
         <v>0.02413582546819065</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.001421388845634071</v>
+        <v>0.001421388845611391</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.02874857002576062</v>
+        <v>0.02874857002575995</v>
       </c>
     </row>
     <row r="20">
@@ -2406,16 +2406,16 @@
         <v>0.1940649581558863</v>
       </c>
       <c r="S20" t="n">
-        <v>20.34328539674237</v>
+        <v>20.34328539706401</v>
       </c>
       <c r="T20" t="n">
-        <v>1.885050611103508</v>
+        <v>1.88505061110932</v>
       </c>
       <c r="U20" t="n">
-        <v>0.006981718078190372</v>
+        <v>0.006981716693788993</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1188464761410522</v>
+        <v>0.1188464479797303</v>
       </c>
       <c r="W20" t="n">
         <v>0.002148333333333333</v>
@@ -2424,7 +2424,7 @@
         <v>0.002148333333333333</v>
       </c>
       <c r="Y20" t="n">
-        <v>20.22568990467636</v>
+        <v>20.22568990499862</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -2436,10 +2436,10 @@
         <v>0.03974752399441857</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.002253972861083005</v>
+        <v>0.00225397286104733</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.04585321318952352</v>
+        <v>0.04585321318952273</v>
       </c>
     </row>
     <row r="21">
@@ -2504,16 +2504,16 @@
         <v>0.2229784488956445</v>
       </c>
       <c r="S21" t="n">
-        <v>20.47349558522638</v>
+        <v>20.47349558554726</v>
       </c>
       <c r="T21" t="n">
-        <v>1.887407312492397</v>
+        <v>1.887407312498209</v>
       </c>
       <c r="U21" t="n">
-        <v>0.007103332026096677</v>
+        <v>0.007103330146140919</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1215385992797259</v>
+        <v>0.1215385607924384</v>
       </c>
       <c r="W21" t="n">
         <v>0.0022025</v>
@@ -2522,7 +2522,7 @@
         <v>0.0022025</v>
       </c>
       <c r="Y21" t="n">
-        <v>20.34328539674237</v>
+        <v>20.34328539706401</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -2534,10 +2534,10 @@
         <v>0.07526448485171559</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.0041335794281382</v>
+        <v>0.004133579428073363</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.08462882017317004</v>
+        <v>0.08462882017316897</v>
       </c>
     </row>
     <row r="22">
@@ -2602,16 +2602,16 @@
         <v>0.2989185664601128</v>
       </c>
       <c r="S22" t="n">
-        <v>20.58181820758407</v>
+        <v>20.58181820790413</v>
       </c>
       <c r="T22" t="n">
-        <v>1.889372361103508</v>
+        <v>1.88937236110932</v>
       </c>
       <c r="U22" t="n">
-        <v>0.007200136731500186</v>
+        <v>0.007200136731366074</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1237179128245816</v>
+        <v>0.1237179128238205</v>
       </c>
       <c r="W22" t="n">
         <v>0.002246666666666667</v>
@@ -2620,7 +2620,7 @@
         <v>0.002246666666666667</v>
       </c>
       <c r="Y22" t="n">
-        <v>20.47349558522638</v>
+        <v>20.47349558554726</v>
       </c>
       <c r="Z22" t="n">
         <v>0.00396735495458923</v>
@@ -2632,10 +2632,10 @@
         <v>0.102602067198723</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.005534928977054236</v>
+        <v>0.005534928976968097</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.1139189019976196</v>
+        <v>0.1139189019976181</v>
       </c>
     </row>
     <row r="23">
@@ -3229,1323 +3229,1323 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BR06_T_29</t>
+          <t>BR07_T_32</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10.06666666666667</v>
+        <v>12.81666666666666</v>
       </c>
       <c r="D29" t="n">
-        <v>10.06666666666667</v>
+        <v>12.81666666666666</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>31.20357142857141</v>
+        <v>25.23928571428564</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.116285070733908</v>
+        <v>2.278816680963244</v>
       </c>
       <c r="I29" t="n">
-        <v>0.04619457646790387</v>
+        <v>0.06375494686076261</v>
       </c>
       <c r="J29" t="n">
-        <v>29.01</v>
+        <v>31.995</v>
       </c>
       <c r="K29" t="n">
-        <v>0.05099333988610194</v>
+        <v>0.4353959074716391</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.006036904047883653</v>
+        <v>-0.0004893160721017838</v>
       </c>
       <c r="N29" t="n">
-        <v>0.03959045447125712</v>
+        <v>0.07400598633331852</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.066666666666666</v>
+        <v>0.8166666666666629</v>
       </c>
       <c r="Q29" t="n">
-        <v>30.88928571428562</v>
+        <v>24.49345238095237</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>28.17336861939443</v>
+        <v>23.93967898481781</v>
       </c>
       <c r="T29" t="n">
-        <v>2.196855666671522</v>
+        <v>2.098491694429187</v>
       </c>
       <c r="U29" t="n">
-        <v>0.009101213044556741</v>
+        <v>0.01007990389195562</v>
       </c>
       <c r="V29" t="n">
-        <v>0.1984455156362072</v>
+        <v>0.194954990695357</v>
       </c>
       <c r="W29" t="n">
-        <v>0.00452</v>
+        <v>0.004063333333333333</v>
       </c>
       <c r="X29" t="n">
-        <v>0.00452</v>
+        <v>0.004063333333333333</v>
       </c>
       <c r="Y29" t="n">
-        <v>26.83706086689429</v>
+        <v>23.76781114532759</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>0.01703599848924725</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.00126455653152689</v>
+        <v>0.002931631959375182</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.03945868005696583</v>
+        <v>0.07399229663180125</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.001408617468021215</v>
+        <v>0.003096509180803947</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.03968549917027974</v>
+        <v>0.07412943576198766</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BR06_T_29</t>
+          <t>BR07_T_32</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11.11666666666667</v>
+        <v>14.25</v>
       </c>
       <c r="D30" t="n">
-        <v>11.11666666666667</v>
+        <v>14.25</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>31.77857142857137</v>
+        <v>24.77321428571426</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.081895592396174</v>
+        <v>2.248670452497834</v>
       </c>
       <c r="I30" t="n">
-        <v>0.08751468391291507</v>
+        <v>0.1716212668026328</v>
       </c>
       <c r="J30" t="n">
-        <v>28.995</v>
+        <v>32.01</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6127972060229903</v>
+        <v>0.1810170901112961</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.02714969469586716</v>
+        <v>-0.007667444579284276</v>
       </c>
       <c r="N30" t="n">
-        <v>0.04134005266540788</v>
+        <v>0.06544157794863636</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.116666666666667</v>
+        <v>2.249999999999996</v>
       </c>
       <c r="Q30" t="n">
-        <v>31.20357142857141</v>
+        <v>25.23928571428564</v>
       </c>
       <c r="R30" t="n">
-        <v>0.04619457646790387</v>
+        <v>0.06375494686076261</v>
       </c>
       <c r="S30" t="n">
-        <v>28.38851742900399</v>
+        <v>24.22814583540682</v>
       </c>
       <c r="T30" t="n">
-        <v>2.201767041671523</v>
+        <v>2.104521249984743</v>
       </c>
       <c r="U30" t="n">
-        <v>0.00964018476825455</v>
+        <v>0.01063211162014986</v>
       </c>
       <c r="V30" t="n">
-        <v>0.2113304059800998</v>
+        <v>0.2075172963667405</v>
       </c>
       <c r="W30" t="n">
-        <v>0.004835</v>
+        <v>0.00435</v>
       </c>
       <c r="X30" t="n">
-        <v>0.004835</v>
+        <v>0.00435</v>
       </c>
       <c r="Y30" t="n">
-        <v>28.17336861939443</v>
+        <v>23.93967898481781</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.006242493408637874</v>
+        <v>0.003897200232591663</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.001264965186188753</v>
+        <v>0.002618004611547352</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.04019878652395538</v>
+        <v>0.06485638924285067</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.001462994036885363</v>
+        <v>0.00271569751353864</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.04153223171464904</v>
+        <v>0.06579631540286586</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BR06_T_29</t>
+          <t>BR07_T_32</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>15.75</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>15.75</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>32.48571428571427</v>
+        <v>25.0285714285714</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.043322206012459</v>
+        <v>2.244283907325788</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1206964002097586</v>
+        <v>0.2547670720457892</v>
       </c>
       <c r="J31" t="n">
-        <v>29.01</v>
+        <v>32.01</v>
       </c>
       <c r="K31" t="n">
-        <v>0.662870013692769</v>
+        <v>0.3823145532014923</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.017692464037532</v>
+        <v>-0.002599879469374555</v>
       </c>
       <c r="N31" t="n">
-        <v>0.04546079677751647</v>
+        <v>0.04901672183657229</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.999999999999996</v>
+        <v>3.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>31.77857142857137</v>
+        <v>24.77321428571426</v>
       </c>
       <c r="R31" t="n">
-        <v>0.08751468391291507</v>
+        <v>0.1716212668026328</v>
       </c>
       <c r="S31" t="n">
-        <v>28.57992709273527</v>
+        <v>24.54912556934151</v>
       </c>
       <c r="T31" t="n">
-        <v>2.206155000004856</v>
+        <v>2.111271249984743</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01008037192673087</v>
+        <v>0.01118090177937685</v>
       </c>
       <c r="V31" t="n">
-        <v>0.2220276693774592</v>
+        <v>0.2204127839316294</v>
       </c>
       <c r="W31" t="n">
-        <v>0.005099999999999999</v>
+        <v>0.00465</v>
       </c>
       <c r="X31" t="n">
-        <v>0.005099999999999999</v>
+        <v>0.00465</v>
       </c>
       <c r="Y31" t="n">
-        <v>28.38851742900399</v>
+        <v>24.22814583540682</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.01174629408308222</v>
+        <v>0.01411667984325947</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.001367238701194155</v>
+        <v>0.00194663879778472</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.04441572580736439</v>
+        <v>0.04872158819598323</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.001600417391551022</v>
+        <v>0.002019535772512294</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.04573981236847377</v>
+        <v>0.0495778372711814</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BR06_T_29</t>
+          <t>BR07_T_32</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12.91666666666667</v>
+        <v>17.75</v>
       </c>
       <c r="D32" t="n">
-        <v>12.91666666666667</v>
+        <v>17.75</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>32.95357142857146</v>
+        <v>26.25714285714279</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.051229957265082</v>
+        <v>2.251576086548178</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1678144479310734</v>
+        <v>0.3345630000595383</v>
       </c>
       <c r="J32" t="n">
-        <v>28.98</v>
+        <v>31.98</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5916393844248193</v>
+        <v>0.428809017662136</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.005269961359712218</v>
+        <v>0.002166785495083</v>
       </c>
       <c r="N32" t="n">
-        <v>0.04979853414690221</v>
+        <v>0.0325183459304893</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.916666666666668</v>
+        <v>5.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>32.48571428571427</v>
+        <v>25.0285714285714</v>
       </c>
       <c r="R32" t="n">
-        <v>0.1206964002097586</v>
+        <v>0.2547670720457892</v>
       </c>
       <c r="S32" t="n">
-        <v>28.78848569274508</v>
+        <v>25.00680786687655</v>
       </c>
       <c r="T32" t="n">
-        <v>2.210956041671523</v>
+        <v>2.120971249984743</v>
       </c>
       <c r="U32" t="n">
-        <v>0.01052404225055447</v>
+        <v>0.01186590939888761</v>
       </c>
       <c r="V32" t="n">
-        <v>0.2329842713706737</v>
+        <v>0.2371876907011177</v>
       </c>
       <c r="W32" t="n">
-        <v>0.005375</v>
+        <v>0.005050000000000001</v>
       </c>
       <c r="X32" t="n">
-        <v>0.005375</v>
+        <v>0.005050000000000001</v>
       </c>
       <c r="Y32" t="n">
-        <v>28.57992709273527</v>
+        <v>24.54912556934151</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.01538455435646532</v>
+        <v>0.01729347944990734</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.001498089218409868</v>
+        <v>0.001250719091027115</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.04936739006524238</v>
+        <v>0.03284030984725474</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.00174397862377562</v>
+        <v>0.001332234624952042</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.0502065036590177</v>
+        <v>0.03331493529977605</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BR06_T_29</t>
+          <t>BR07_T_32</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>14.16666666666667</v>
+        <v>22.08333333333333</v>
       </c>
       <c r="D33" t="n">
-        <v>14.16666666666667</v>
+        <v>22.08333333333333</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>33.73214285714283</v>
+        <v>27.40000000000004</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.042865751547434</v>
+        <v>2.300076229570327</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2305584416204973</v>
+        <v>0.4114676331552647</v>
       </c>
       <c r="J33" t="n">
-        <v>29.01</v>
+        <v>31.995</v>
       </c>
       <c r="K33" t="n">
-        <v>0.5206489627095445</v>
+        <v>0.398400608225738</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.005256731176822081</v>
+        <v>-0.00133238024820435</v>
       </c>
       <c r="N33" t="n">
-        <v>0.05074941234338937</v>
+        <v>0.003015511680013446</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>5.166666666666668</v>
+        <v>10.08333333333333</v>
       </c>
       <c r="Q33" t="n">
-        <v>32.95357142857146</v>
+        <v>26.25714285714279</v>
       </c>
       <c r="R33" t="n">
-        <v>0.1678144479310734</v>
+        <v>0.3345630000595383</v>
       </c>
       <c r="S33" t="n">
-        <v>29.08893066557003</v>
+        <v>26.11045456330866</v>
       </c>
       <c r="T33" t="n">
-        <v>2.217909166671522</v>
+        <v>2.144732361095854</v>
       </c>
       <c r="U33" t="n">
-        <v>0.01110710364392404</v>
+        <v>0.01316720038405787</v>
       </c>
       <c r="V33" t="n">
-        <v>0.247679790593411</v>
+        <v>0.2717707554568806</v>
       </c>
       <c r="W33" t="n">
-        <v>0.00575</v>
+        <v>0.005916666666666667</v>
       </c>
       <c r="X33" t="n">
-        <v>0.00575</v>
+        <v>0.005916666666666667</v>
       </c>
       <c r="Y33" t="n">
-        <v>28.78848569274508</v>
+        <v>25.00680786687655</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.01286158828634814</v>
+        <v>0.01396089162246411</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.001486894452512595</v>
+        <v>0.0001013561359319036</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.05015613608564804</v>
+        <v>0.002777158124534164</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.001765178067932173</v>
+        <v>0.0001589641491270462</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.05134714243046385</v>
+        <v>0.004150626192976761</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BR06_T_29</t>
+          <t>BR07_T_32</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>15.75</v>
+        <v>23.75</v>
       </c>
       <c r="D34" t="n">
-        <v>15.75</v>
+        <v>23.75</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>34.17499999999994</v>
+        <v>28.4607142857143</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.043427422635005</v>
+        <v>2.268649013339584</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3101524146095156</v>
+        <v>0.4067877264015557</v>
       </c>
       <c r="J34" t="n">
-        <v>28.99609352861408</v>
+        <v>31.98</v>
       </c>
       <c r="K34" t="n">
-        <v>0.4487939891718003</v>
+        <v>0.3265950774100435</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.00141932920314981</v>
+        <v>-5.158002532211318e-05</v>
       </c>
       <c r="N34" t="n">
-        <v>0.05337380410075097</v>
+        <v>0</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>6.75</v>
+        <v>11.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>33.73214285714283</v>
+        <v>27.40000000000004</v>
       </c>
       <c r="R34" t="n">
-        <v>0.2305584416204973</v>
+        <v>0.4114676331552647</v>
       </c>
       <c r="S34" t="n">
-        <v>29.49554881223184</v>
+        <v>26.57397314534754</v>
       </c>
       <c r="T34" t="n">
-        <v>2.227389375004855</v>
+        <v>2.154871249984743</v>
       </c>
       <c r="U34" t="n">
-        <v>0.01180836764412159</v>
+        <v>0.01360207800305404</v>
       </c>
       <c r="V34" t="n">
-        <v>0.2658615522638877</v>
+        <v>0.2843859629506359</v>
       </c>
       <c r="W34" t="n">
-        <v>0.006225</v>
+        <v>0.00625</v>
       </c>
       <c r="X34" t="n">
-        <v>0.006225</v>
+        <v>0.00625</v>
       </c>
       <c r="Y34" t="n">
-        <v>29.08893066557003</v>
+        <v>26.11045456330866</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.0124376482115277</v>
+        <v>0.01145255846603085</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.001555475570429705</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.05315837761943506</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.001838941984103698</v>
+        <v>4.43986780696222e-05</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.0542406030549931</v>
+        <v>0.001179849278711071</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BR06_T_29</t>
+          <t>BR07_T_32</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>17.75</v>
+        <v>26.25</v>
       </c>
       <c r="D35" t="n">
-        <v>17.75</v>
+        <v>26.25</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>35.25357142857146</v>
+        <v>28.6821428571429</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.03289957117615</v>
+        <v>2.284143082979641</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4221965247171862</v>
+        <v>0.4021708299263646</v>
       </c>
       <c r="J35" t="n">
-        <v>29.01</v>
+        <v>31.98</v>
       </c>
       <c r="K35" t="n">
-        <v>0.4476368009367404</v>
+        <v>0.1367895124707587</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.003342623714389221</v>
+        <v>0.01001273194867519</v>
       </c>
       <c r="N35" t="n">
-        <v>0.05698882657592755</v>
+        <v>0</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>8.75</v>
+        <v>14.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>34.17499999999994</v>
+        <v>28.4607142857143</v>
       </c>
       <c r="R35" t="n">
-        <v>0.3101524146095156</v>
+        <v>0.4067877264015557</v>
       </c>
       <c r="S35" t="n">
-        <v>30.04965111830602</v>
+        <v>27.30784322790872</v>
       </c>
       <c r="T35" t="n">
-        <v>2.240439375004855</v>
+        <v>2.171121249984743</v>
       </c>
       <c r="U35" t="n">
-        <v>0.01263380301417569</v>
+        <v>0.01418845246147928</v>
       </c>
       <c r="V35" t="n">
-        <v>0.2881017975693222</v>
+        <v>0.3025561516882164</v>
       </c>
       <c r="W35" t="n">
-        <v>0.006824999999999999</v>
+        <v>0.006750000000000001</v>
       </c>
       <c r="X35" t="n">
-        <v>0.006824999999999999</v>
+        <v>0.006750000000000001</v>
       </c>
       <c r="Y35" t="n">
-        <v>29.49554881223184</v>
+        <v>26.57397314534754</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.01434189391717165</v>
+        <v>0.009152735978746178</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.001636232211738464</v>
+        <v>6.146505253398153e-05</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.05768302915025142</v>
+        <v>0.001762949417501451</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.001939288882568265</v>
+        <v>4.578707085297215e-05</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.05827495433878591</v>
+        <v>0.001250346152718112</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BR06_T_29</t>
+          <t>BR07_T_32</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>22.08333333333333</v>
+        <v>27.91666666666666</v>
       </c>
       <c r="D36" t="n">
-        <v>22.08333333333333</v>
+        <v>27.91666666666666</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>36.64642857142852</v>
+        <v>28.78571428571429</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2.099454389920735</v>
+        <v>2.31298452078502</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6867024494155662</v>
+        <v>0.3873938421634567</v>
       </c>
       <c r="J36" t="n">
-        <v>29.01</v>
+        <v>32.01</v>
       </c>
       <c r="K36" t="n">
-        <v>0.3657886287781853</v>
+        <v>0.1117051303339633</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.004849759608455484</v>
+        <v>0.009834545481641204</v>
       </c>
       <c r="N36" t="n">
-        <v>0.05650292924856072</v>
+        <v>0</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>13.08333333333333</v>
+        <v>15.91666666666666</v>
       </c>
       <c r="Q36" t="n">
-        <v>35.25357142857146</v>
+        <v>28.6821428571429</v>
       </c>
       <c r="R36" t="n">
-        <v>0.4221965247171862</v>
+        <v>0.4021708299263646</v>
       </c>
       <c r="S36" t="n">
-        <v>31.39750168284602</v>
+        <v>27.82182632859923</v>
       </c>
       <c r="T36" t="n">
-        <v>2.272831041671522</v>
+        <v>2.182649027762521</v>
       </c>
       <c r="U36" t="n">
-        <v>0.01418941592455493</v>
+        <v>0.01453689738861425</v>
       </c>
       <c r="V36" t="n">
-        <v>0.3332712665883056</v>
+        <v>0.3141530853075174</v>
       </c>
       <c r="W36" t="n">
-        <v>0.008124999999999999</v>
+        <v>0.007083333333333334</v>
       </c>
       <c r="X36" t="n">
-        <v>0.008124999999999999</v>
+        <v>0.007083333333333334</v>
       </c>
       <c r="Y36" t="n">
-        <v>30.04965111830602</v>
+        <v>27.30784322790872</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.0122915723272022</v>
+        <v>0.00813246080612828</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.001585126319326265</v>
+        <v>5.722124060260651e-05</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.05808921843788138</v>
+        <v>0.001647154283060745</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.001877785660032493</v>
+        <v>4.518776391829954e-05</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.05895777842089433</v>
+        <v>0.001257206119912673</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BR06_T_29</t>
+          <t>BR07_T_32</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>23.75</v>
+        <v>30.7</v>
       </c>
       <c r="D37" t="n">
-        <v>23.75</v>
+        <v>30.7</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>37.48928571428572</v>
+        <v>28.80357142857139</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2.083814358974711</v>
+        <v>2.339434992829764</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7743301252716717</v>
+        <v>0.3689307159607038</v>
       </c>
       <c r="J37" t="n">
-        <v>29.01</v>
+        <v>31.995</v>
       </c>
       <c r="K37" t="n">
-        <v>0.3195792660950653</v>
+        <v>0.1591840739798124</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.007434862434915586</v>
+        <v>0.003489528740332326</v>
       </c>
       <c r="N37" t="n">
-        <v>0.05577747296393511</v>
+        <v>0</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>14.75</v>
+        <v>18.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>36.64642857142852</v>
+        <v>28.78571428571429</v>
       </c>
       <c r="R37" t="n">
-        <v>0.6867024494155662</v>
+        <v>0.3873938421634567</v>
       </c>
       <c r="S37" t="n">
-        <v>31.96654988663085</v>
+        <v>28.72212538793305</v>
       </c>
       <c r="T37" t="n">
-        <v>2.286789375004856</v>
+        <v>2.203138999984743</v>
       </c>
       <c r="U37" t="n">
-        <v>0.0147041811639105</v>
+        <v>0.01504659661323521</v>
       </c>
       <c r="V37" t="n">
-        <v>0.3494748715399993</v>
+        <v>0.3325682403572446</v>
       </c>
       <c r="W37" t="n">
-        <v>0.008624999999999999</v>
+        <v>0.007640000000000001</v>
       </c>
       <c r="X37" t="n">
-        <v>0.008624999999999999</v>
+        <v>0.007640000000000001</v>
       </c>
       <c r="Y37" t="n">
-        <v>31.39750168284602</v>
+        <v>27.82182632859923</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.01209245951381016</v>
+        <v>0.007018151213335786</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.00156151850253121</v>
+        <v>1.910531806293016e-05</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.0585402132895361</v>
+        <v>0.0005503013934911842</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.001836231493122834</v>
+        <v>4.454302433905062e-05</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.05869798562831374</v>
+        <v>0.001279370330223965</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BR06_T_29</t>
+          <t>BR07_T_32</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>26.25</v>
+        <v>33.75</v>
       </c>
       <c r="D38" t="n">
-        <v>26.25</v>
+        <v>33.75</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>38.16071428571433</v>
+        <v>29.79999999999999</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2.134247935455769</v>
+        <v>2.329200727712629</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9154189117949879</v>
+        <v>0.3542503465167628</v>
       </c>
       <c r="J38" t="n">
-        <v>29</v>
+        <v>31.98</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1920743039133862</v>
+        <v>0.2652253372484213</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.01379940159901161</v>
+        <v>0.002792843482472269</v>
       </c>
       <c r="N38" t="n">
-        <v>0.05595354194166324</v>
+        <v>0</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>17.25</v>
+        <v>21.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>37.48928571428572</v>
+        <v>28.80357142857139</v>
       </c>
       <c r="R38" t="n">
-        <v>0.7743301252716717</v>
+        <v>0.3689307159607038</v>
       </c>
       <c r="S38" t="n">
-        <v>32.869340032439</v>
+        <v>29.76547646571371</v>
       </c>
       <c r="T38" t="n">
-        <v>2.309289375004856</v>
+        <v>2.227371249984743</v>
       </c>
       <c r="U38" t="n">
-        <v>0.01539236927068186</v>
+        <v>0.0155078415118352</v>
       </c>
       <c r="V38" t="n">
-        <v>0.3724976739484597</v>
+        <v>0.3513494137153382</v>
       </c>
       <c r="W38" t="n">
-        <v>0.009375</v>
+        <v>0.00825</v>
       </c>
       <c r="X38" t="n">
-        <v>0.009375</v>
+        <v>0.00825</v>
       </c>
       <c r="Y38" t="n">
-        <v>31.96654988663085</v>
+        <v>28.72212538793305</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.01149899702156292</v>
+        <v>0.01009923569250023</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.001621362830708351</v>
+        <v>1.425389975077348e-05</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.0618723637361384</v>
+        <v>0.0004247662125730495</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.001815365300551202</v>
+        <v>4.408174559026023e-05</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.05966985934690829</v>
+        <v>0.00131211416093447</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BR06_T_29</t>
+          <t>BR07_T_32</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>27.91666666666667</v>
+        <v>36.75</v>
       </c>
       <c r="D39" t="n">
-        <v>27.91666666666667</v>
+        <v>36.75</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>38.47500000000004</v>
+        <v>31.12500000000002</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2.159950079576069</v>
+        <v>2.349291749610435</v>
       </c>
       <c r="I39" t="n">
-        <v>1.010468610609401</v>
+        <v>0.363160750555521</v>
       </c>
       <c r="J39" t="n">
-        <v>28.99452240138233</v>
+        <v>32.01</v>
       </c>
       <c r="K39" t="n">
-        <v>0.08736852647961749</v>
+        <v>0.1493127970909461</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.009554658005047491</v>
+        <v>0.007052842307412845</v>
       </c>
       <c r="N39" t="n">
-        <v>0.05382789068097926</v>
+        <v>0.007864429537239377</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>18.91666666666667</v>
+        <v>24.75</v>
       </c>
       <c r="Q39" t="n">
-        <v>38.16071428571433</v>
+        <v>29.79999999999999</v>
       </c>
       <c r="R39" t="n">
-        <v>0.9154189117949879</v>
+        <v>0.3542503465167628</v>
       </c>
       <c r="S39" t="n">
-        <v>33.50232757221166</v>
+        <v>30.84541916498249</v>
       </c>
       <c r="T39" t="n">
-        <v>2.325331041671522</v>
+        <v>2.253021249984743</v>
       </c>
       <c r="U39" t="n">
-        <v>0.01579721905142694</v>
+        <v>0.01587051773015364</v>
       </c>
       <c r="V39" t="n">
-        <v>0.3869690327833194</v>
+        <v>0.3683701508436424</v>
       </c>
       <c r="W39" t="n">
-        <v>0.009874999999999998</v>
+        <v>0.00885</v>
       </c>
       <c r="X39" t="n">
-        <v>0.009874999999999998</v>
+        <v>0.00885</v>
       </c>
       <c r="Y39" t="n">
-        <v>32.869340032439</v>
+        <v>29.76547646571371</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.006694341927304691</v>
+        <v>0.007799312579268405</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.001515211284475293</v>
+        <v>0.0002877005497867221</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.05829775417018696</v>
+        <v>0.008954679612111731</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.001734776631452701</v>
+        <v>0.0003012099228746798</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.05811905497154628</v>
+        <v>0.009290946327721546</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BR06_T_29</t>
+          <t>BR07_T_32</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>30.78333333333333</v>
+        <v>39.33333333333334</v>
       </c>
       <c r="D40" t="n">
-        <v>30.78333333333333</v>
+        <v>39.33333333333334</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>37.925</v>
+        <v>30.88214285714287</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2.169398797524823</v>
+        <v>2.372062773813742</v>
       </c>
       <c r="I40" t="n">
-        <v>1.158051029644832</v>
+        <v>0.3954213588988506</v>
       </c>
       <c r="J40" t="n">
-        <v>29.01</v>
+        <v>32.01</v>
       </c>
       <c r="K40" t="n">
-        <v>0.03769831430539022</v>
+        <v>0.05927397226391524</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.005556079532218562</v>
+        <v>0.0106978221806986</v>
       </c>
       <c r="N40" t="n">
-        <v>0.04595636421154174</v>
+        <v>0.02013887067289918</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>21.78333333333333</v>
+        <v>27.33333333333334</v>
       </c>
       <c r="Q40" t="n">
-        <v>38.47500000000004</v>
+        <v>31.12500000000002</v>
       </c>
       <c r="R40" t="n">
-        <v>1.010468610609401</v>
+        <v>0.363160750555521</v>
       </c>
       <c r="S40" t="n">
-        <v>34.64542149429275</v>
+        <v>31.81469618008588</v>
       </c>
       <c r="T40" t="n">
-        <v>2.354872041671522</v>
+        <v>2.276551111095854</v>
       </c>
       <c r="U40" t="n">
-        <v>0.01639805372128809</v>
+        <v>0.01611696629211079</v>
       </c>
       <c r="V40" t="n">
-        <v>0.4101816828846233</v>
+        <v>0.3818576537329387</v>
       </c>
       <c r="W40" t="n">
-        <v>0.010735</v>
+        <v>0.009366666666666667</v>
       </c>
       <c r="X40" t="n">
-        <v>0.010735</v>
+        <v>0.009366666666666667</v>
       </c>
       <c r="Y40" t="n">
-        <v>33.50232757221166</v>
+        <v>30.84541916498249</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.003555137665813143</v>
+        <v>0.006429284455135683</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.001289974052226223</v>
+        <v>0.0007098662467225611</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.04892226593067951</v>
+        <v>0.02192219084074996</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.001478853277568896</v>
+        <v>0.0006841428405296224</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.05123549512959072</v>
+        <v>0.02176579661523088</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BR06_T_29</t>
+          <t>BR07_T_32</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>33.71666666666666</v>
+        <v>46.93333333333334</v>
       </c>
       <c r="D41" t="n">
-        <v>33.71666666666666</v>
+        <v>46.93333333333334</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>38.52142857142859</v>
+        <v>31.93571428571439</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2.190559164456776</v>
+        <v>2.515307377137465</v>
       </c>
       <c r="I41" t="n">
-        <v>1.271484763312922</v>
+        <v>0.7360300997802449</v>
       </c>
       <c r="J41" t="n">
-        <v>29.01</v>
+        <v>32.01</v>
       </c>
       <c r="K41" t="n">
-        <v>0.06799444389452616</v>
+        <v>0.3122489136229731</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.005386997700613615</v>
+        <v>0.02633606438824609</v>
       </c>
       <c r="N41" t="n">
-        <v>0.03689448171041039</v>
+        <v>0.06894461020814052</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>24.71666666666666</v>
+        <v>34.93333333333334</v>
       </c>
       <c r="Q41" t="n">
-        <v>37.925</v>
+        <v>30.88214285714287</v>
       </c>
       <c r="R41" t="n">
-        <v>1.158051029644832</v>
+        <v>0.3954213588988506</v>
       </c>
       <c r="S41" t="n">
-        <v>35.88074137169464</v>
+        <v>34.84968576356192</v>
       </c>
       <c r="T41" t="n">
-        <v>2.387652041671522</v>
+        <v>2.353513777762521</v>
       </c>
       <c r="U41" t="n">
-        <v>0.01689624439822985</v>
+        <v>0.01654179887468306</v>
       </c>
       <c r="V41" t="n">
-        <v>0.4317039019876593</v>
+        <v>0.4152720349990343</v>
       </c>
       <c r="W41" t="n">
-        <v>0.011615</v>
+        <v>0.01088666666666667</v>
       </c>
       <c r="X41" t="n">
-        <v>0.011615</v>
+        <v>0.01088666666666667</v>
       </c>
       <c r="Y41" t="n">
-        <v>34.64542149429275</v>
+        <v>31.81469618008588</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.004224295423804049</v>
+        <v>0.02024773721229721</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.001038936087870312</v>
+        <v>0.002400167963573594</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.04002130229917569</v>
+        <v>0.07665107832241122</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.001200637436376612</v>
+        <v>0.002076037952137568</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.04307976133580369</v>
+        <v>0.07234927026522282</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BR06_T_29</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>36.74999999999999</v>
+        <v>10.13333333333333</v>
       </c>
       <c r="D42" t="n">
-        <v>36.74999999999999</v>
+        <v>10.13333333333333</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>38.53571428571432</v>
+        <v>27.80357142857142</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2.201135977012072</v>
+        <v>2.111411826295212</v>
       </c>
       <c r="I42" t="n">
-        <v>1.367856290787664</v>
+        <v>0.05060060245371522</v>
       </c>
       <c r="J42" t="n">
         <v>29.01</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1.292833793699242</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.00606426814655327</v>
+        <v>0.0006879481871742564</v>
       </c>
       <c r="N42" t="n">
-        <v>0.02658763966420979</v>
+        <v>0.04290404542881167</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4553,97 +4553,97 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>27.74999999999999</v>
+        <v>0.1333333333333329</v>
       </c>
       <c r="Q42" t="n">
-        <v>38.52142857142859</v>
+        <v>25.66428571428573</v>
       </c>
       <c r="R42" t="n">
-        <v>1.271484763312922</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>37.22098955276511</v>
+        <v>28.24180486627298</v>
       </c>
       <c r="T42" t="n">
-        <v>2.424264375004855</v>
+        <v>2.198068889704301</v>
       </c>
       <c r="U42" t="n">
-        <v>0.01729870254736678</v>
+        <v>0.007080005996886602</v>
       </c>
       <c r="V42" t="n">
-        <v>0.4515719991981164</v>
+        <v>0.1093276616638276</v>
       </c>
       <c r="W42" t="n">
-        <v>0.012525</v>
+        <v>0.007053333333333333</v>
       </c>
       <c r="X42" t="n">
-        <v>0.012525</v>
+        <v>0.003526666666666667</v>
       </c>
       <c r="Y42" t="n">
-        <v>35.88074137169464</v>
+        <v>24.01327123307239</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.002755062935632535</v>
+        <v>0.04682466286201208</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.0007877412004656704</v>
+        <v>0.001543705722077936</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.03035616983223068</v>
+        <v>0.04292053230848831</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.0009041858127903936</v>
+        <v>0.001524917290400108</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.03365469069162967</v>
+        <v>0.04306641655268557</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BR06_T_29</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>39.24999999999999</v>
+        <v>11.56666666666667</v>
       </c>
       <c r="D43" t="n">
-        <v>39.24999999999999</v>
+        <v>11.56666666666667</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>38.4107142857143</v>
+        <v>28.21071428571433</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>2.218083921309183</v>
+        <v>2.092706775844421</v>
       </c>
       <c r="I43" t="n">
-        <v>1.418921479557499</v>
+        <v>0.1044036282464569</v>
       </c>
       <c r="J43" t="n">
         <v>28.995</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>0.4995599667938492</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.009481488583403936</v>
+        <v>-0.01656280347506739</v>
       </c>
       <c r="N43" t="n">
-        <v>0.01602933015956215</v>
+        <v>0.03752923222291429</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4651,97 +4651,97 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>30.24999999999999</v>
+        <v>1.566666666666666</v>
       </c>
       <c r="Q43" t="n">
-        <v>38.53571428571432</v>
+        <v>27.80357142857142</v>
       </c>
       <c r="R43" t="n">
-        <v>1.367856290787664</v>
+        <v>0.05060060245371522</v>
       </c>
       <c r="S43" t="n">
-        <v>38.36845407620109</v>
+        <v>28.4719136932899</v>
       </c>
       <c r="T43" t="n">
-        <v>2.456514375004855</v>
+        <v>2.203329228297969</v>
       </c>
       <c r="U43" t="n">
-        <v>0.01755270915052975</v>
+        <v>0.007575520339906265</v>
       </c>
       <c r="V43" t="n">
-        <v>0.4661272466448358</v>
+        <v>0.1171360667459857</v>
       </c>
       <c r="W43" t="n">
-        <v>0.013275</v>
+        <v>0.007626666666666667</v>
       </c>
       <c r="X43" t="n">
-        <v>0.013275</v>
+        <v>0.003813333333333334</v>
       </c>
       <c r="Y43" t="n">
-        <v>37.22098955276511</v>
+        <v>28.24180486627298</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.00427463023031503</v>
+        <v>0.009793628241382288</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.0005752221800972709</v>
+        <v>0.001301027884616268</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.02209469481052197</v>
+        <v>0.03670292593065684</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.0006176214361136928</v>
+        <v>0.001330806855107732</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.02369717970800559</v>
+        <v>0.03789061792106591</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BR06</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BR06_T_29</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>46.53333333333333</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="D44" t="n">
-        <v>46.53333333333333</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>38.53571428571432</v>
+        <v>28.84999999999995</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2.343484672856569</v>
+        <v>2.059106202419109</v>
       </c>
       <c r="I44" t="n">
-        <v>1.418921479557499</v>
+        <v>0.1491197853115378</v>
       </c>
       <c r="J44" t="n">
-        <v>28.98</v>
+        <v>28.995</v>
       </c>
       <c r="K44" t="n">
-        <v>0.06716247139589093</v>
+        <v>0.5552285401125786</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.02498843900561543</v>
+        <v>-0.01268043122870065</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>0.03318261877259444</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -4749,1371 +4749,1371 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>37.53333333333333</v>
+        <v>2.666666666666668</v>
       </c>
       <c r="Q44" t="n">
-        <v>38.4107142857143</v>
+        <v>28.21071428571433</v>
       </c>
       <c r="R44" t="n">
-        <v>1.418921479557499</v>
+        <v>0.1044036282464569</v>
       </c>
       <c r="S44" t="n">
-        <v>41.89268704809879</v>
+        <v>28.65987999487189</v>
       </c>
       <c r="T44" t="n">
-        <v>2.561157666671522</v>
+        <v>2.207644899280302</v>
       </c>
       <c r="U44" t="n">
-        <v>0.01795719004239548</v>
+        <v>0.007944459054335712</v>
       </c>
       <c r="V44" t="n">
-        <v>0.4993967422800068</v>
+        <v>0.1229649217459871</v>
       </c>
       <c r="W44" t="n">
-        <v>0.01546</v>
+        <v>0.008066666666666666</v>
       </c>
       <c r="X44" t="n">
-        <v>0.01546</v>
+        <v>0.004033333333333333</v>
       </c>
       <c r="Y44" t="n">
-        <v>38.36845407620109</v>
+        <v>28.4719136932899</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.01240580410774891</v>
+        <v>0.01308713559294417</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.0003926195848303751</v>
+        <v>0.00111834683420231</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.01512987614399911</v>
+        <v>0.03226430616673658</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.0002044529213800594</v>
+        <v>0.001176819229347382</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.008565082251444374</v>
+        <v>0.03372749788875357</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BR07_T_32</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>12.81666666666666</v>
+        <v>14.13333333333333</v>
       </c>
       <c r="D45" t="n">
-        <v>12.81666666666666</v>
+        <v>14.13333333333333</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>25.23928571428564</v>
+        <v>29.8214285714287</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>2.278816680963244</v>
+        <v>2.054382414798483</v>
       </c>
       <c r="I45" t="n">
-        <v>0.06375494686076261</v>
+        <v>0.1918414613393818</v>
       </c>
       <c r="J45" t="n">
-        <v>31.995</v>
+        <v>28.995</v>
       </c>
       <c r="K45" t="n">
-        <v>0.4353959074716391</v>
+        <v>0.4551298135529764</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.0004893160721017838</v>
+        <v>-0.00225385966014273</v>
       </c>
       <c r="N45" t="n">
-        <v>0.07400598633331852</v>
+        <v>0.02512562920803933</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.8166666666666629</v>
+        <v>4.133333333333333</v>
       </c>
       <c r="Q45" t="n">
-        <v>24.49345238095237</v>
+        <v>28.84999999999995</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>0.1491197853115378</v>
       </c>
       <c r="S45" t="n">
-        <v>23.93967898481781</v>
+        <v>28.92563754904663</v>
       </c>
       <c r="T45" t="n">
-        <v>2.098491694429187</v>
+        <v>2.213775572077636</v>
       </c>
       <c r="U45" t="n">
-        <v>0.01007990389195562</v>
+        <v>0.008420554940361971</v>
       </c>
       <c r="V45" t="n">
-        <v>0.194954990695357</v>
+        <v>0.1305037237789266</v>
       </c>
       <c r="W45" t="n">
-        <v>0.004063333333333333</v>
+        <v>0.008653333333333332</v>
       </c>
       <c r="X45" t="n">
-        <v>0.004063333333333333</v>
+        <v>0.004326666666666666</v>
       </c>
       <c r="Y45" t="n">
-        <v>23.76781114532759</v>
+        <v>28.65987999487189</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.01703599848924725</v>
+        <v>0.01416473965932023</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.002931631959375182</v>
+        <v>0.0008354784274698437</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.07399229663180125</v>
+        <v>0.02491516024776152</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.003096509180803947</v>
+        <v>0.0008945528030801951</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.07412943576198766</v>
+        <v>0.02587551015038141</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BR07_T_32</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>14.25</v>
+        <v>16.85</v>
       </c>
       <c r="D46" t="n">
-        <v>14.25</v>
+        <v>16.85</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>24.77321428571426</v>
+        <v>30.18571428571434</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>2.248670452497834</v>
+        <v>2.052763135178324</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1716212668026328</v>
+        <v>0.2448076315621145</v>
       </c>
       <c r="J46" t="n">
-        <v>32.01</v>
+        <v>28.995</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1810170901112961</v>
+        <v>0.2858643792140457</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.007667444579284276</v>
+        <v>0.004342262917761283</v>
       </c>
       <c r="N46" t="n">
-        <v>0.06544157794863636</v>
+        <v>0.01531393640884581</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.249999999999996</v>
+        <v>6.850000000000001</v>
       </c>
       <c r="Q46" t="n">
-        <v>25.23928571428564</v>
+        <v>29.8214285714287</v>
       </c>
       <c r="R46" t="n">
-        <v>0.06375494686076261</v>
+        <v>0.1918414613393818</v>
       </c>
       <c r="S46" t="n">
-        <v>24.22814583540682</v>
+        <v>29.46262799242987</v>
       </c>
       <c r="T46" t="n">
-        <v>2.104521249984743</v>
+        <v>2.226267723458663</v>
       </c>
       <c r="U46" t="n">
-        <v>0.01063211162014986</v>
+        <v>0.009253028608468754</v>
       </c>
       <c r="V46" t="n">
-        <v>0.2075172963667405</v>
+        <v>0.1437185005742433</v>
       </c>
       <c r="W46" t="n">
-        <v>0.00435</v>
+        <v>0.009740000000000002</v>
       </c>
       <c r="X46" t="n">
-        <v>0.00435</v>
+        <v>0.004870000000000001</v>
       </c>
       <c r="Y46" t="n">
-        <v>23.93967898481781</v>
+        <v>28.92563754904663</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.003897200232591663</v>
+        <v>0.01158551351625574</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.002618004611547352</v>
+        <v>0.0005244793669481728</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.06485638924285067</v>
+        <v>0.01583178431944987</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.00271569751353864</v>
+        <v>0.0005561275272637884</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.06579631540286586</v>
+        <v>0.0163849784521229</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BR07_T_32</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>15.75</v>
+        <v>22.4</v>
       </c>
       <c r="D47" t="n">
-        <v>15.75</v>
+        <v>22.4</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>25.0285714285714</v>
+        <v>32.48928571428564</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>2.244283907325788</v>
+        <v>2.136378998440389</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2547670720457892</v>
+        <v>0.2862295508009267</v>
       </c>
       <c r="J47" t="n">
-        <v>32.01</v>
+        <v>28.995</v>
       </c>
       <c r="K47" t="n">
-        <v>0.3823145532014923</v>
+        <v>0.2861652497401637</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.002599879469374555</v>
+        <v>0.002939955113684175</v>
       </c>
       <c r="N47" t="n">
-        <v>0.04901672183657229</v>
+        <v>0.003419686402695349</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.75</v>
+        <v>12.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>24.77321428571426</v>
+        <v>30.18571428571434</v>
       </c>
       <c r="R47" t="n">
-        <v>0.1716212668026328</v>
+        <v>0.2448076315621145</v>
       </c>
       <c r="S47" t="n">
-        <v>24.54912556934151</v>
+        <v>30.7324548714269</v>
       </c>
       <c r="T47" t="n">
-        <v>2.111271249984743</v>
+        <v>2.256376503567413</v>
       </c>
       <c r="U47" t="n">
-        <v>0.01118090177937685</v>
+        <v>0.0107472221904619</v>
       </c>
       <c r="V47" t="n">
-        <v>0.2204127839316294</v>
+        <v>0.1673901041055427</v>
       </c>
       <c r="W47" t="n">
-        <v>0.00465</v>
+        <v>0.01196</v>
       </c>
       <c r="X47" t="n">
-        <v>0.00465</v>
+        <v>0.005979999999999999</v>
       </c>
       <c r="Y47" t="n">
-        <v>24.22814583540682</v>
+        <v>29.46262799242987</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.01411667984325947</v>
+        <v>0.01018412764647287</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.00194663879778472</v>
+        <v>0.0001173795623522832</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.04872158819598323</v>
+        <v>0.003813578138281135</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.002019535772512294</v>
+        <v>0.0001606398135696006</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.0495778372711814</v>
+        <v>0.004936855821082179</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BR07_T_32</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>17.75</v>
+        <v>24.05</v>
       </c>
       <c r="D48" t="n">
-        <v>17.75</v>
+        <v>24.05</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>26.25714285714279</v>
+        <v>32.9321428571429</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>2.251576086548178</v>
+        <v>2.119328558258994</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3345630000595383</v>
+        <v>0.2889524121591054</v>
       </c>
       <c r="J48" t="n">
-        <v>31.98</v>
+        <v>28.98962893733009</v>
       </c>
       <c r="K48" t="n">
-        <v>0.428809017662136</v>
+        <v>0.2278965996953445</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.002166785495083</v>
+        <v>0.003428148603602897</v>
       </c>
       <c r="N48" t="n">
-        <v>0.0325183459304893</v>
+        <v>0.002167744356653061</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>5.75</v>
+        <v>14.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>25.0285714285714</v>
+        <v>32.48928571428564</v>
       </c>
       <c r="R48" t="n">
-        <v>0.2547670720457892</v>
+        <v>0.2862295508009267</v>
       </c>
       <c r="S48" t="n">
-        <v>25.00680786687655</v>
+        <v>31.15248097068912</v>
       </c>
       <c r="T48" t="n">
-        <v>2.120971249984743</v>
+        <v>2.266515763706663</v>
       </c>
       <c r="U48" t="n">
-        <v>0.01186590939888761</v>
+        <v>0.01113734553511684</v>
       </c>
       <c r="V48" t="n">
-        <v>0.2371876907011177</v>
+        <v>0.1734983778862526</v>
       </c>
       <c r="W48" t="n">
-        <v>0.005050000000000001</v>
+        <v>0.01262</v>
       </c>
       <c r="X48" t="n">
-        <v>0.005050000000000001</v>
+        <v>0.00631</v>
       </c>
       <c r="Y48" t="n">
-        <v>24.54912556934151</v>
+        <v>30.7324548714269</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.01729347944990734</v>
+        <v>0.0085377509283628</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.001250719091027115</v>
+        <v>8.001736341849413e-05</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.03284030984725474</v>
+        <v>0.002635143243149769</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.001332234624952042</v>
+        <v>0.0001212306820646025</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.03331493529977605</v>
+        <v>0.003776636516081191</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BR07_T_32</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>22.08333333333333</v>
+        <v>25.55</v>
       </c>
       <c r="D49" t="n">
-        <v>22.08333333333333</v>
+        <v>25.55</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>27.40000000000004</v>
+        <v>33.08366238246173</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2.300076229570327</v>
+        <v>2.122927932215827</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4114676331552647</v>
+        <v>0.2916972101212668</v>
       </c>
       <c r="J49" t="n">
-        <v>31.995</v>
+        <v>29.01</v>
       </c>
       <c r="K49" t="n">
-        <v>0.398400608225738</v>
+        <v>0.2049207718657497</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.00133238024820435</v>
+        <v>0.01007802025635504</v>
       </c>
       <c r="N49" t="n">
-        <v>0.003015511680013446</v>
+        <v>0.002083661045468459</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>10.08333333333333</v>
+        <v>15.55</v>
       </c>
       <c r="Q49" t="n">
-        <v>26.25714285714279</v>
+        <v>32.9321428571429</v>
       </c>
       <c r="R49" t="n">
-        <v>0.3345630000595383</v>
+        <v>0.2889524121591054</v>
       </c>
       <c r="S49" t="n">
-        <v>26.11045456330866</v>
+        <v>31.55039960381982</v>
       </c>
       <c r="T49" t="n">
-        <v>2.144732361095854</v>
+        <v>2.276205773396663</v>
       </c>
       <c r="U49" t="n">
-        <v>0.01316720038405787</v>
+        <v>0.01147067535725597</v>
       </c>
       <c r="V49" t="n">
-        <v>0.2717707554568806</v>
+        <v>0.1786624859513175</v>
       </c>
       <c r="W49" t="n">
-        <v>0.005916666666666667</v>
+        <v>0.01322</v>
       </c>
       <c r="X49" t="n">
-        <v>0.005916666666666667</v>
+        <v>0.00661</v>
       </c>
       <c r="Y49" t="n">
-        <v>25.00680786687655</v>
+        <v>31.15248097068912</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.01396089162246411</v>
+        <v>0.01094124388489767</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.0001013561359319036</v>
+        <v>0.0001048376628482425</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.002777158124534164</v>
+        <v>0.003468413842637606</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.0001589641491270462</v>
+        <v>0.0001197389718612452</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.004150626192976761</v>
+        <v>0.003777812410372822</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BR07_T_32</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>23.75</v>
+        <v>27.01666666666667</v>
       </c>
       <c r="D50" t="n">
-        <v>23.75</v>
+        <v>27.01666666666667</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>28.4607142857143</v>
+        <v>33.286006759061</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2.268649013339584</v>
+        <v>2.149102129882635</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4067877264015557</v>
+        <v>0.2947411967231239</v>
       </c>
       <c r="J50" t="n">
-        <v>31.98</v>
+        <v>29.01</v>
       </c>
       <c r="K50" t="n">
-        <v>0.3265950774100435</v>
+        <v>0.2878082500112895</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-5.158002532211318e-05</v>
+        <v>0.01358415797906408</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>0.002564129205513765</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>11.75</v>
+        <v>17.01666666666667</v>
       </c>
       <c r="Q50" t="n">
-        <v>27.40000000000004</v>
+        <v>33.08366238246173</v>
       </c>
       <c r="R50" t="n">
-        <v>0.4114676331552647</v>
+        <v>0.2916972101212668</v>
       </c>
       <c r="S50" t="n">
-        <v>26.57397314534754</v>
+        <v>31.95385449141603</v>
       </c>
       <c r="T50" t="n">
-        <v>2.154871249984743</v>
+        <v>2.286115561084218</v>
       </c>
       <c r="U50" t="n">
-        <v>0.01360207800305404</v>
+        <v>0.01177717880123003</v>
       </c>
       <c r="V50" t="n">
-        <v>0.2843859629506359</v>
+        <v>0.1833455418032794</v>
       </c>
       <c r="W50" t="n">
-        <v>0.00625</v>
+        <v>0.01380666666666667</v>
       </c>
       <c r="X50" t="n">
-        <v>0.00625</v>
+        <v>0.006903333333333334</v>
       </c>
       <c r="Y50" t="n">
-        <v>26.11045456330866</v>
+        <v>31.55039960381982</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.01145255846603085</v>
+        <v>0.01496737650102324</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>0.0001330031843039391</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>0.004427144891717553</v>
       </c>
       <c r="AC50" t="n">
-        <v>4.43986780696222e-05</v>
+        <v>0.0001359515592164647</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.001179849278711071</v>
+        <v>0.004344176341084042</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BR07_T_32</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>26.25</v>
+        <v>30.05</v>
       </c>
       <c r="D51" t="n">
-        <v>26.25</v>
+        <v>30.05</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>28.6821428571429</v>
+        <v>34.92500000000002</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>2.284143082979641</v>
+        <v>2.204791765804646</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4021708299263646</v>
+        <v>0.3061500936386944</v>
       </c>
       <c r="J51" t="n">
-        <v>31.98</v>
+        <v>28.995</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1367895124707587</v>
+        <v>0.3273118051359381</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.01001273194867519</v>
+        <v>0.01005866658037854</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>0.005592359312335324</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>14.25</v>
+        <v>20.05</v>
       </c>
       <c r="Q51" t="n">
-        <v>28.4607142857143</v>
+        <v>33.286006759061</v>
       </c>
       <c r="R51" t="n">
-        <v>0.4067877264015557</v>
+        <v>0.2947411967231239</v>
       </c>
       <c r="S51" t="n">
-        <v>27.30784322790872</v>
+        <v>32.83159453257377</v>
       </c>
       <c r="T51" t="n">
-        <v>2.171121249984743</v>
+        <v>2.307975805166663</v>
       </c>
       <c r="U51" t="n">
-        <v>0.01418845246147928</v>
+        <v>0.01235152301479269</v>
       </c>
       <c r="V51" t="n">
-        <v>0.3025561516882164</v>
+        <v>0.1918565388801183</v>
       </c>
       <c r="W51" t="n">
-        <v>0.006750000000000001</v>
+        <v>0.01502</v>
       </c>
       <c r="X51" t="n">
-        <v>0.006750000000000001</v>
+        <v>0.007509999999999999</v>
       </c>
       <c r="Y51" t="n">
-        <v>26.57397314534754</v>
+        <v>31.95385449141603</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.009152735978746178</v>
+        <v>0.01393403278476044</v>
       </c>
       <c r="AA51" t="n">
-        <v>6.146505253398153e-05</v>
+        <v>0.0002001166067567213</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.001762949417501451</v>
+        <v>0.006989072490978496</v>
       </c>
       <c r="AC51" t="n">
-        <v>4.578707085297215e-05</v>
+        <v>0.0002310196494435036</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.001250346152718112</v>
+        <v>0.00758474345958644</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BR07_T_32</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>27.91666666666666</v>
+        <v>33.05</v>
       </c>
       <c r="D52" t="n">
-        <v>27.91666666666666</v>
+        <v>33.05</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>28.78571428571429</v>
+        <v>35.32500000000002</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>2.31298452078502</v>
+        <v>2.222071473920533</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3873938421634567</v>
+        <v>0.3308651428571041</v>
       </c>
       <c r="J52" t="n">
-        <v>32.01</v>
+        <v>29.01</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1117051303339633</v>
+        <v>0.3206543266788474</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.009834545481641204</v>
+        <v>0.005559533698940396</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>0.01134058524405515</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>15.91666666666666</v>
+        <v>23.05</v>
       </c>
       <c r="Q52" t="n">
-        <v>28.6821428571429</v>
+        <v>34.92500000000002</v>
       </c>
       <c r="R52" t="n">
-        <v>0.4021708299263646</v>
+        <v>0.3061500936386944</v>
       </c>
       <c r="S52" t="n">
-        <v>27.82182632859923</v>
+        <v>33.75408934834246</v>
       </c>
       <c r="T52" t="n">
-        <v>2.182649027762521</v>
+        <v>2.331405828596663</v>
       </c>
       <c r="U52" t="n">
-        <v>0.01453689738861425</v>
+        <v>0.01284341417557715</v>
       </c>
       <c r="V52" t="n">
-        <v>0.3141530853075174</v>
+        <v>0.1986846191052666</v>
       </c>
       <c r="W52" t="n">
-        <v>0.007083333333333334</v>
+        <v>0.01622</v>
       </c>
       <c r="X52" t="n">
-        <v>0.007083333333333334</v>
+        <v>0.008110000000000001</v>
       </c>
       <c r="Y52" t="n">
-        <v>27.30784322790872</v>
+        <v>32.83159453257377</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.00813246080612828</v>
+        <v>0.01157922320647989</v>
       </c>
       <c r="AA52" t="n">
-        <v>5.722124060260651e-05</v>
+        <v>0.0003444698247772432</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.001647154283060745</v>
+        <v>0.01216839656025612</v>
       </c>
       <c r="AC52" t="n">
-        <v>4.518776391829954e-05</v>
+        <v>0.0004041724259929835</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.001257206119912673</v>
+        <v>0.0136424721791035</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BR07_T_32</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>30.7</v>
+        <v>35.71666666666666</v>
       </c>
       <c r="D53" t="n">
-        <v>30.7</v>
+        <v>35.71666666666666</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>28.80357142857139</v>
+        <v>36.71428571428564</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2.339434992829764</v>
+        <v>2.225119195750334</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3689307159607038</v>
+        <v>0.3724108962071924</v>
       </c>
       <c r="J53" t="n">
-        <v>31.995</v>
+        <v>28.98</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1591840739798124</v>
+        <v>0.2482560989697474</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.003489528740332326</v>
+        <v>0.005575616292307751</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>0.01868335460030837</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>18.7</v>
+        <v>25.71666666666666</v>
       </c>
       <c r="Q53" t="n">
-        <v>28.78571428571429</v>
+        <v>35.32500000000002</v>
       </c>
       <c r="R53" t="n">
-        <v>0.3873938421634567</v>
+        <v>0.3308651428571041</v>
       </c>
       <c r="S53" t="n">
-        <v>28.72212538793305</v>
+        <v>34.61647934279947</v>
       </c>
       <c r="T53" t="n">
-        <v>2.203138999984743</v>
+        <v>2.353743628712218</v>
       </c>
       <c r="U53" t="n">
-        <v>0.01504659661323521</v>
+        <v>0.01322035169194992</v>
       </c>
       <c r="V53" t="n">
-        <v>0.3325682403572446</v>
+        <v>0.2034072317266347</v>
       </c>
       <c r="W53" t="n">
-        <v>0.007640000000000001</v>
+        <v>0.01728666666666667</v>
       </c>
       <c r="X53" t="n">
-        <v>0.007640000000000001</v>
+        <v>0.008643333333333333</v>
       </c>
       <c r="Y53" t="n">
-        <v>27.82182632859923</v>
+        <v>33.75408934834246</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.007018151213335786</v>
+        <v>0.009267599997966548</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.910531806293016e-05</v>
+        <v>0.0005343022972248991</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.0005503013934911842</v>
+        <v>0.01961652719811411</v>
       </c>
       <c r="AC53" t="n">
-        <v>4.454302433905062e-05</v>
+        <v>0.000618736018383067</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.001279370330223965</v>
+        <v>0.02141846259900344</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BR07_T_32</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>33.75</v>
+        <v>38.41666666666666</v>
       </c>
       <c r="D54" t="n">
-        <v>33.75</v>
+        <v>38.41666666666666</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>29.79999999999999</v>
+        <v>36.54999999999995</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>2.329200727712629</v>
+        <v>2.238126974352284</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3542503465167628</v>
+        <v>0.4370511859323505</v>
       </c>
       <c r="J54" t="n">
-        <v>31.98</v>
+        <v>28.98</v>
       </c>
       <c r="K54" t="n">
-        <v>0.2652253372484213</v>
+        <v>0.09314611508350956</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.002792843482472269</v>
+        <v>0.008164208448361089</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>0.02804497875626173</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>21.75</v>
+        <v>28.41666666666666</v>
       </c>
       <c r="Q54" t="n">
-        <v>28.80357142857139</v>
+        <v>36.71428571428564</v>
       </c>
       <c r="R54" t="n">
-        <v>0.3689307159607038</v>
+        <v>0.3724108962071924</v>
       </c>
       <c r="S54" t="n">
-        <v>29.76547646571371</v>
+        <v>35.52745852239852</v>
       </c>
       <c r="T54" t="n">
-        <v>2.227371249984743</v>
+        <v>2.377809652778218</v>
       </c>
       <c r="U54" t="n">
-        <v>0.0155078415118352</v>
+        <v>0.01354761888358153</v>
       </c>
       <c r="V54" t="n">
-        <v>0.3513494137153382</v>
+        <v>0.2068914320190001</v>
       </c>
       <c r="W54" t="n">
-        <v>0.00825</v>
+        <v>0.01836666666666667</v>
       </c>
       <c r="X54" t="n">
-        <v>0.00825</v>
+        <v>0.009183333333333333</v>
       </c>
       <c r="Y54" t="n">
-        <v>28.72212538793305</v>
+        <v>34.61647934279947</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.01009923569250023</v>
+        <v>0.006196243412663805</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.425389975077348e-05</v>
+        <v>0.0008109233377192746</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.0004247662125730495</v>
+        <v>0.02963924799363945</v>
       </c>
       <c r="AC54" t="n">
-        <v>4.408174559026023e-05</v>
+        <v>0.0008844102245227135</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.00131211416093447</v>
+        <v>0.03142084756851587</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BR07_T_32</t>
+          <t>BR08_T_29</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>36.75</v>
+        <v>46.41666666666666</v>
       </c>
       <c r="D55" t="n">
-        <v>36.75</v>
+        <v>46.41666666666666</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>31.12500000000002</v>
+        <v>37.45357142857144</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>2.349291749610435</v>
+        <v>2.350696964539372</v>
       </c>
       <c r="I55" t="n">
-        <v>0.363160750555521</v>
+        <v>0.792026695150037</v>
       </c>
       <c r="J55" t="n">
-        <v>32.01</v>
+        <v>28.98</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1493127970909461</v>
+        <v>0.2428851122484339</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.007052842307412845</v>
+        <v>0.02098979306862803</v>
       </c>
       <c r="N55" t="n">
-        <v>0.007864429537239377</v>
+        <v>0.05964752041359847</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>24.75</v>
+        <v>36.41666666666666</v>
       </c>
       <c r="Q55" t="n">
-        <v>29.79999999999999</v>
+        <v>36.54999999999995</v>
       </c>
       <c r="R55" t="n">
-        <v>0.3542503465167628</v>
+        <v>0.4370511859323505</v>
       </c>
       <c r="S55" t="n">
-        <v>30.84541916498249</v>
+        <v>38.42283179752014</v>
       </c>
       <c r="T55" t="n">
-        <v>2.253021249984743</v>
+        <v>2.457676399311551</v>
       </c>
       <c r="U55" t="n">
-        <v>0.01587051773015364</v>
+        <v>0.01423124238248902</v>
       </c>
       <c r="V55" t="n">
-        <v>0.3683701508436424</v>
+        <v>0.2096355868065772</v>
       </c>
       <c r="W55" t="n">
-        <v>0.00885</v>
+        <v>0.02156666666666666</v>
       </c>
       <c r="X55" t="n">
-        <v>0.00885</v>
+        <v>0.01078333333333333</v>
       </c>
       <c r="Y55" t="n">
-        <v>29.76547646571371</v>
+        <v>35.52745852239852</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.007799312579268405</v>
+        <v>0.01541414394739185</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.0002877005497867221</v>
+        <v>0.001781396691915808</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.008954679612111731</v>
+        <v>0.06671966824328958</v>
       </c>
       <c r="AC55" t="n">
-        <v>0.0003012099228746798</v>
+        <v>0.001733285414237923</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.009290946327721546</v>
+        <v>0.06659773392835873</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BR07_T_32</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>39.33333333333334</v>
+        <v>10.08333333333333</v>
       </c>
       <c r="D56" t="n">
-        <v>39.33333333333334</v>
+        <v>10.08333333333333</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>30.88214285714287</v>
+        <v>22.74159954433088</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>2.372062773813742</v>
+        <v>2.151754877317993</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3954213588988506</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>32.01</v>
+        <v>28.995</v>
       </c>
       <c r="K56" t="n">
-        <v>0.05927397226391524</v>
+        <v>0.8532992157616837</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.0106978221806986</v>
+        <v>0.0143222143423807</v>
       </c>
       <c r="N56" t="n">
-        <v>0.02013887067289918</v>
+        <v>0</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>27.33333333333334</v>
+        <v>0.08333333333333215</v>
       </c>
       <c r="Q56" t="n">
-        <v>31.12500000000002</v>
+        <v>21.79285714285717</v>
       </c>
       <c r="R56" t="n">
-        <v>0.363160750555521</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>31.81469618008588</v>
+        <v>28.31815807004039</v>
       </c>
       <c r="T56" t="n">
-        <v>2.276551111095854</v>
+        <v>2.196892806206484</v>
       </c>
       <c r="U56" t="n">
-        <v>0.01611696629211079</v>
+        <v>0.01041196717294989</v>
       </c>
       <c r="V56" t="n">
-        <v>0.3818576537329387</v>
+        <v>0.2041873938903916</v>
       </c>
       <c r="W56" t="n">
-        <v>0.009366666666666667</v>
+        <v>0.007033333333333333</v>
       </c>
       <c r="X56" t="n">
-        <v>0.009366666666666667</v>
+        <v>0.003516666666666667</v>
       </c>
       <c r="Y56" t="n">
-        <v>30.84541916498249</v>
+        <v>25.42114791934122</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.006429284455135683</v>
+        <v>0.04417757490269928</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.0007098662467225611</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.02192219084074996</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>0.0006841428405296224</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.02176579661523088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BR07</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BR07_T_32</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>46.93333333333334</v>
+        <v>11.2</v>
       </c>
       <c r="D57" t="n">
-        <v>46.93333333333334</v>
+        <v>11.2</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>31.93571428571439</v>
+        <v>22.97108767528296</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>2.515307377137465</v>
+        <v>2.163697271557409</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7360300997802449</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>32.01</v>
+        <v>28.995</v>
       </c>
       <c r="K57" t="n">
-        <v>0.3122489136229731</v>
+        <v>0.4955894525174036</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.02633606438824609</v>
+        <v>0.00991189089150895</v>
       </c>
       <c r="N57" t="n">
-        <v>0.06894461020814052</v>
+        <v>0</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>34.93333333333334</v>
+        <v>1.200000000000001</v>
       </c>
       <c r="Q57" t="n">
-        <v>30.88214285714287</v>
+        <v>22.74159954433088</v>
       </c>
       <c r="R57" t="n">
-        <v>0.3954213588988506</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>34.84968576356192</v>
+        <v>28.49544506515976</v>
       </c>
       <c r="T57" t="n">
-        <v>2.353513777762521</v>
+        <v>2.200944449147011</v>
       </c>
       <c r="U57" t="n">
-        <v>0.01654179887468306</v>
+        <v>0.01098357032200971</v>
       </c>
       <c r="V57" t="n">
-        <v>0.4152720349990343</v>
+        <v>0.2161387857045839</v>
       </c>
       <c r="W57" t="n">
-        <v>0.01088666666666667</v>
+        <v>0.007480000000000001</v>
       </c>
       <c r="X57" t="n">
-        <v>0.01088666666666667</v>
+        <v>0.00374</v>
       </c>
       <c r="Y57" t="n">
-        <v>31.81469618008588</v>
+        <v>28.31815807004039</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.02024773721229721</v>
+        <v>0.02615548495855645</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.002400167963573594</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.07665107832241122</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>0.002076037952137568</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.07234927026522282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>10.13333333333333</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="D58" t="n">
-        <v>10.13333333333333</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>27.80357142857142</v>
+        <v>24.12500000000008</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>2.111411826295212</v>
+        <v>2.18231465451585</v>
       </c>
       <c r="I58" t="n">
-        <v>0.05060060245371522</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>29.01</v>
+        <v>28.98790163201834</v>
       </c>
       <c r="K58" t="n">
-        <v>1.292833793699242</v>
+        <v>0.527194572758186</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.0006879481871742564</v>
+        <v>0.01009690660006621</v>
       </c>
       <c r="N58" t="n">
-        <v>0.04290404542881167</v>
+        <v>0</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -6121,97 +6121,97 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0.1333333333333329</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="Q58" t="n">
-        <v>25.66428571428573</v>
+        <v>22.97108767528296</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>28.24180486627348</v>
+        <v>28.74377626618266</v>
       </c>
       <c r="T58" t="n">
-        <v>2.198068889704301</v>
+        <v>2.2066448992919</v>
       </c>
       <c r="U58" t="n">
-        <v>0.007080000683784983</v>
+        <v>0.01171780391374263</v>
       </c>
       <c r="V58" t="n">
-        <v>0.1093275116122504</v>
+        <v>0.2317374616169707</v>
       </c>
       <c r="W58" t="n">
-        <v>0.007053333333333333</v>
+        <v>0.008066666666666666</v>
       </c>
       <c r="X58" t="n">
-        <v>0.003526666666666667</v>
+        <v>0.004033333333333333</v>
       </c>
       <c r="Y58" t="n">
-        <v>24.01327123307239</v>
+        <v>28.49544506515976</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.04682466286201208</v>
+        <v>0.02647932083128075</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.001543705722077936</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.04292053230848831</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>0.00152491729040008</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.04306641655268557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>11.56666666666667</v>
+        <v>13.85</v>
       </c>
       <c r="D59" t="n">
-        <v>11.56666666666667</v>
+        <v>13.85</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>28.21071428571433</v>
+        <v>24.57500000000017</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>2.092706775844421</v>
+        <v>2.193791961026335</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1044036282464569</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>28.995</v>
+        <v>28.98710002854261</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4995599667938492</v>
+        <v>0.4106539365163594</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.01656280347506739</v>
+        <v>0.01080044764312056</v>
       </c>
       <c r="N59" t="n">
-        <v>0.03752923222291429</v>
+        <v>0</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -6219,97 +6219,97 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.566666666666666</v>
+        <v>3.849999999999998</v>
       </c>
       <c r="Q59" t="n">
-        <v>27.80357142857142</v>
+        <v>24.12500000000008</v>
       </c>
       <c r="R59" t="n">
-        <v>0.05060060245371522</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>28.47191369328903</v>
+        <v>28.95676810363952</v>
       </c>
       <c r="T59" t="n">
-        <v>2.203329228297967</v>
+        <v>2.211557709760262</v>
       </c>
       <c r="U59" t="n">
-        <v>0.00757552039323006</v>
+        <v>0.01228108243496568</v>
       </c>
       <c r="V59" t="n">
-        <v>0.1171360682642126</v>
+        <v>0.2438029808221922</v>
       </c>
       <c r="W59" t="n">
-        <v>0.007626666666666667</v>
+        <v>0.008539999999999999</v>
       </c>
       <c r="X59" t="n">
-        <v>0.003813333333333334</v>
+        <v>0.004269999999999999</v>
       </c>
       <c r="Y59" t="n">
-        <v>28.24180486627348</v>
+        <v>28.74377626618266</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.009793628241382288</v>
+        <v>0.02163341820285943</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.001301027884616268</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.03670292593065684</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.001330806855107773</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.03789061792106591</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>12.66666666666667</v>
+        <v>15.31666666666667</v>
       </c>
       <c r="D60" t="n">
-        <v>12.66666666666667</v>
+        <v>15.31666666666667</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>28.84999999999995</v>
+        <v>25.06785714285721</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>2.059106202419109</v>
+        <v>2.214828125862959</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1491197853115378</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>28.995</v>
+        <v>28.98</v>
       </c>
       <c r="K60" t="n">
-        <v>0.5552285401125786</v>
+        <v>0.3756303196153055</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.01268043122870065</v>
+        <v>0.009872310665280869</v>
       </c>
       <c r="N60" t="n">
-        <v>0.03318261877259444</v>
+        <v>0</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -6317,97 +6317,97 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.666666666666668</v>
+        <v>5.31666666666667</v>
       </c>
       <c r="Q60" t="n">
-        <v>28.21071428571433</v>
+        <v>24.57500000000017</v>
       </c>
       <c r="R60" t="n">
-        <v>0.1044036282464569</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>28.65987999487103</v>
+        <v>29.2361661686984</v>
       </c>
       <c r="T60" t="n">
-        <v>2.2076448992803</v>
+        <v>2.218035494015818</v>
       </c>
       <c r="U60" t="n">
-        <v>0.007944459054335953</v>
+        <v>0.01296737669517052</v>
       </c>
       <c r="V60" t="n">
-        <v>0.1229649217459902</v>
+        <v>0.2588167976329628</v>
       </c>
       <c r="W60" t="n">
-        <v>0.008066666666666666</v>
+        <v>0.009126666666666668</v>
       </c>
       <c r="X60" t="n">
-        <v>0.004033333333333333</v>
+        <v>0.004563333333333334</v>
       </c>
       <c r="Y60" t="n">
-        <v>28.47191369328903</v>
+        <v>28.95676810363952</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.01308713559294417</v>
+        <v>0.01944191146369945</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.00111834683420231</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.03226430616673658</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>0.001176819229347417</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.03372749788875357</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>14.13333333333333</v>
+        <v>17.98333333333333</v>
       </c>
       <c r="D61" t="n">
-        <v>14.13333333333333</v>
+        <v>17.98333333333333</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>29.8214285714287</v>
+        <v>25.90000000000013</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>2.054382414798483</v>
+        <v>2.214024096070052</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1918414613393818</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>28.995</v>
+        <v>28.98</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4551298135529764</v>
+        <v>0.3298559424945083</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.00225385966014273</v>
+        <v>0.008518133778895404</v>
       </c>
       <c r="N61" t="n">
-        <v>0.02512562920803933</v>
+        <v>0</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -6415,97 +6415,97 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>4.133333333333333</v>
+        <v>7.983333333333334</v>
       </c>
       <c r="Q61" t="n">
-        <v>28.84999999999995</v>
+        <v>25.06785714285721</v>
       </c>
       <c r="R61" t="n">
-        <v>0.1491197853115378</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>28.92563754904579</v>
+        <v>29.78688303253967</v>
       </c>
       <c r="T61" t="n">
-        <v>2.213775572077634</v>
+        <v>2.230915506895817</v>
       </c>
       <c r="U61" t="n">
-        <v>0.008420554940362222</v>
+        <v>0.01413309295165512</v>
       </c>
       <c r="V61" t="n">
-        <v>0.13050372377893</v>
+        <v>0.2848807744362734</v>
       </c>
       <c r="W61" t="n">
-        <v>0.008653333333333332</v>
+        <v>0.01019333333333333</v>
       </c>
       <c r="X61" t="n">
-        <v>0.004326666666666666</v>
+        <v>0.005096666666666667</v>
       </c>
       <c r="Y61" t="n">
-        <v>28.65987999487103</v>
+        <v>29.2361661686984</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.01416473965932023</v>
+        <v>0.01658310436687791</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.0008354784274698437</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.02491516024776152</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>0.0008945528030802212</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.02587551015038141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>16.85</v>
+        <v>23.56666666666667</v>
       </c>
       <c r="D62" t="n">
-        <v>16.85</v>
+        <v>23.56666666666667</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>30.18571428571434</v>
+        <v>27.37499999999996</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>2.052763135178324</v>
+        <v>2.307573593937551</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2448076315621145</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>28.995</v>
+        <v>28.99338819905182</v>
       </c>
       <c r="K62" t="n">
-        <v>0.2858643792140457</v>
+        <v>0.3454451519070621</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.004342262917761283</v>
+        <v>0.0129230258223817</v>
       </c>
       <c r="N62" t="n">
-        <v>0.01531393640884581</v>
+        <v>0</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -6513,97 +6513,97 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>6.850000000000001</v>
+        <v>13.56666666666667</v>
       </c>
       <c r="Q62" t="n">
-        <v>29.8214285714287</v>
+        <v>25.90000000000013</v>
       </c>
       <c r="R62" t="n">
-        <v>0.1918414613393818</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>29.46262799242903</v>
+        <v>31.11037299665006</v>
       </c>
       <c r="T62" t="n">
-        <v>2.226267723458661</v>
+        <v>2.262489288469567</v>
       </c>
       <c r="U62" t="n">
-        <v>0.009253028608469023</v>
+        <v>0.01625124162510059</v>
       </c>
       <c r="V62" t="n">
-        <v>0.143718500574247</v>
+        <v>0.3347092315256564</v>
       </c>
       <c r="W62" t="n">
-        <v>0.009740000000000002</v>
+        <v>0.01242666666666667</v>
       </c>
       <c r="X62" t="n">
-        <v>0.004870000000000001</v>
+        <v>0.006213333333333333</v>
       </c>
       <c r="Y62" t="n">
-        <v>28.92563754904579</v>
+        <v>29.78688303253967</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.01158551351625574</v>
+        <v>0.01821926693166444</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.0005244793669481728</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.01583178431944987</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>0.0005561275272638044</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.0163849784521229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>22.4</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="D63" t="n">
-        <v>22.4</v>
+        <v>25.13333333333333</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>32.48928571428564</v>
+        <v>28.11428571428576</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>2.136378998440389</v>
+        <v>2.324643491537374</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2862295508009267</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>28.995</v>
+        <v>28.98907356082457</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2861652497401637</v>
+        <v>0.2438328224960159</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.002939955113684175</v>
+        <v>0.01425711185829255</v>
       </c>
       <c r="N63" t="n">
-        <v>0.003419686402695349</v>
+        <v>0</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -6611,97 +6611,97 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>12.4</v>
+        <v>15.13333333333333</v>
       </c>
       <c r="Q63" t="n">
-        <v>30.18571428571434</v>
+        <v>27.37499999999996</v>
       </c>
       <c r="R63" t="n">
-        <v>0.2448076315621145</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>30.73245487142606</v>
+        <v>31.52104556228423</v>
       </c>
       <c r="T63" t="n">
-        <v>2.256376503567412</v>
+        <v>2.272468965115901</v>
       </c>
       <c r="U63" t="n">
-        <v>0.01074722221765609</v>
+        <v>0.01679004299276455</v>
       </c>
       <c r="V63" t="n">
-        <v>0.1673901049412822</v>
+        <v>0.3481790571704745</v>
       </c>
       <c r="W63" t="n">
-        <v>0.01196</v>
+        <v>0.01305333333333333</v>
       </c>
       <c r="X63" t="n">
-        <v>0.005979999999999999</v>
+        <v>0.006526666666666667</v>
       </c>
       <c r="Y63" t="n">
-        <v>29.46262799242903</v>
+        <v>31.11037299665006</v>
       </c>
       <c r="Z63" t="n">
-        <v>0.01018412764647287</v>
+        <v>0.01480594697664882</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.0001173795623522832</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.003813578138281135</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>0.000160639813569605</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.00493685582108218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>24.05</v>
+        <v>26.68333333333333</v>
       </c>
       <c r="D64" t="n">
-        <v>24.05</v>
+        <v>26.68333333333333</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>32.9321428571429</v>
+        <v>28.14285714285706</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>2.119328558258994</v>
+        <v>2.352668497327067</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2889524121591054</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>28.98962893733009</v>
+        <v>28.995</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2278965996953445</v>
+        <v>0.3483746225501007</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0.003428148603602897</v>
+        <v>0.01556696786466986</v>
       </c>
       <c r="N64" t="n">
-        <v>0.002167744356653061</v>
+        <v>0</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -6709,97 +6709,97 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>14.05</v>
+        <v>16.68333333333333</v>
       </c>
       <c r="Q64" t="n">
-        <v>32.48928571428564</v>
+        <v>28.11428571428576</v>
       </c>
       <c r="R64" t="n">
-        <v>0.2862295508009267</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>31.15248097068831</v>
+        <v>31.94343200509588</v>
       </c>
       <c r="T64" t="n">
-        <v>2.266515763706662</v>
+        <v>2.282825558805818</v>
       </c>
       <c r="U64" t="n">
-        <v>0.01113734544500751</v>
+        <v>0.01726816390210312</v>
       </c>
       <c r="V64" t="n">
-        <v>0.1734983750791186</v>
+        <v>0.360274340850948</v>
       </c>
       <c r="W64" t="n">
-        <v>0.01262</v>
+        <v>0.01367333333333333</v>
       </c>
       <c r="X64" t="n">
-        <v>0.00631</v>
+        <v>0.006836666666666666</v>
       </c>
       <c r="Y64" t="n">
-        <v>30.73245487142606</v>
+        <v>31.52104556228423</v>
       </c>
       <c r="Z64" t="n">
-        <v>0.0085377509283628</v>
+        <v>0.01899552184075797</v>
       </c>
       <c r="AA64" t="n">
-        <v>8.001736341849413e-05</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.002635143243149769</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>0.0001212306820646056</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.003776636516081192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>25.55</v>
+        <v>28.15</v>
       </c>
       <c r="D65" t="n">
-        <v>25.55</v>
+        <v>28.15</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>33.08366238246173</v>
+        <v>29.46071428571427</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>2.122927932215827</v>
+        <v>2.375720882565579</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2916972101212668</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>29.01</v>
+        <v>28.995</v>
       </c>
       <c r="K65" t="n">
-        <v>0.2049207718657497</v>
+        <v>0.4669603785258343</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0.01007802025635504</v>
+        <v>0.01540779486614794</v>
       </c>
       <c r="N65" t="n">
-        <v>0.002083661045468459</v>
+        <v>0</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -6807,97 +6807,97 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>15.55</v>
+        <v>18.15</v>
       </c>
       <c r="Q65" t="n">
-        <v>32.9321428571429</v>
+        <v>28.14285714285706</v>
       </c>
       <c r="R65" t="n">
-        <v>0.2889524121591054</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>31.55039960381902</v>
+        <v>32.3574018720367</v>
       </c>
       <c r="T65" t="n">
-        <v>2.276205773396662</v>
+        <v>2.293067791270262</v>
       </c>
       <c r="U65" t="n">
-        <v>0.0114706754208951</v>
+        <v>0.01769926440963473</v>
       </c>
       <c r="V65" t="n">
-        <v>0.1786624879591527</v>
+        <v>0.3714798347284995</v>
       </c>
       <c r="W65" t="n">
-        <v>0.01322</v>
+        <v>0.01426</v>
       </c>
       <c r="X65" t="n">
-        <v>0.00661</v>
+        <v>0.007129999999999999</v>
       </c>
       <c r="Y65" t="n">
-        <v>31.15248097068831</v>
+        <v>31.94343200509588</v>
       </c>
       <c r="Z65" t="n">
-        <v>0.01094124388489767</v>
+        <v>0.02233579751349438</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.0001048376628482425</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.003468413842637606</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>0.0001197389718612482</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.003777812410372823</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>27.01666666666667</v>
+        <v>31.18333333333333</v>
       </c>
       <c r="D66" t="n">
-        <v>27.01666666666667</v>
+        <v>31.18333333333333</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>33.286006759061</v>
+        <v>30.54107142857147</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>2.149102129882635</v>
+        <v>2.429480867954015</v>
       </c>
       <c r="I66" t="n">
-        <v>0.2947411967231239</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>29.01</v>
+        <v>28.98</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2878082500112895</v>
+        <v>0.1393496146836234</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>0.01358415797906408</v>
+        <v>0.01356607661731992</v>
       </c>
       <c r="N66" t="n">
-        <v>0.002564129205513765</v>
+        <v>0</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -6905,97 +6905,97 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>17.01666666666667</v>
+        <v>21.18333333333333</v>
       </c>
       <c r="Q66" t="n">
-        <v>33.08366238246173</v>
+        <v>29.46071428571427</v>
       </c>
       <c r="R66" t="n">
-        <v>0.2916972101212668</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>31.95385449141525</v>
+        <v>33.25583249482232</v>
       </c>
       <c r="T66" t="n">
-        <v>2.286115561084217</v>
+        <v>2.315615591595817</v>
       </c>
       <c r="U66" t="n">
-        <v>0.01177717876146381</v>
+        <v>0.01851308273432502</v>
       </c>
       <c r="V66" t="n">
-        <v>0.1833455405325909</v>
+        <v>0.3934469053539372</v>
       </c>
       <c r="W66" t="n">
-        <v>0.01380666666666667</v>
+        <v>0.01547333333333333</v>
       </c>
       <c r="X66" t="n">
-        <v>0.006903333333333334</v>
+        <v>0.007736666666666666</v>
       </c>
       <c r="Y66" t="n">
-        <v>31.55039960381902</v>
+        <v>32.3574018720367</v>
       </c>
       <c r="Z66" t="n">
-        <v>0.01496737650102324</v>
+        <v>0.01014663618242141</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.0001330031843039391</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.004427144891717553</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>0.000135951559216468</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>0.004344176341084043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>30.05</v>
+        <v>34.18333333333334</v>
       </c>
       <c r="D67" t="n">
-        <v>30.05</v>
+        <v>34.18333333333334</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>34.92500000000002</v>
+        <v>30.00357142857132</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>2.204791765804646</v>
+        <v>2.451704147576396</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3061500936386944</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>28.995</v>
       </c>
       <c r="K67" t="n">
-        <v>0.3273118051359381</v>
+        <v>0.08855763882758942</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0.01005866658037854</v>
+        <v>0.01490221644458623</v>
       </c>
       <c r="N67" t="n">
-        <v>0.005592359312335324</v>
+        <v>0</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -7003,97 +7003,97 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>20.05</v>
+        <v>24.18333333333334</v>
       </c>
       <c r="Q67" t="n">
-        <v>33.286006759061</v>
+        <v>30.54107142857147</v>
       </c>
       <c r="R67" t="n">
-        <v>0.2947411967231239</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>32.83159453257299</v>
+        <v>34.19735342816631</v>
       </c>
       <c r="T67" t="n">
-        <v>2.307975805166662</v>
+        <v>2.339725615705817</v>
       </c>
       <c r="U67" t="n">
-        <v>0.01235152298094111</v>
+        <v>0.01919070522193477</v>
       </c>
       <c r="V67" t="n">
-        <v>0.1918565377687123</v>
+        <v>0.4125744318193387</v>
       </c>
       <c r="W67" t="n">
-        <v>0.01502</v>
+        <v>0.01667333333333334</v>
       </c>
       <c r="X67" t="n">
-        <v>0.007509999999999999</v>
+        <v>0.008336666666666668</v>
       </c>
       <c r="Y67" t="n">
-        <v>31.95385449141525</v>
+        <v>33.25583249482232</v>
       </c>
       <c r="Z67" t="n">
-        <v>0.01393403278476044</v>
+        <v>0.00902987934884078</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.0002001166067567213</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.006989072490978496</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>0.0002310196494435091</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.007584743459586441</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>33.05</v>
+        <v>35.7</v>
       </c>
       <c r="D68" t="n">
-        <v>33.05</v>
+        <v>35.7</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>35.32500000000002</v>
+        <v>30.12857142857151</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>2.222071473920533</v>
+        <v>2.481063784627632</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3308651428571041</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
         <v>29.01</v>
       </c>
       <c r="K68" t="n">
-        <v>0.3206543266788474</v>
+        <v>0.2239877292055531</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0.005559533698940396</v>
+        <v>0.01559421357166551</v>
       </c>
       <c r="N68" t="n">
-        <v>0.01134058524405515</v>
+        <v>0</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -7101,97 +7101,97 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>23.05</v>
+        <v>25.7</v>
       </c>
       <c r="Q68" t="n">
-        <v>34.92500000000002</v>
+        <v>30.00357142857132</v>
       </c>
       <c r="R68" t="n">
-        <v>0.3061500936386944</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>33.75408934834168</v>
+        <v>34.69219227608998</v>
       </c>
       <c r="T68" t="n">
-        <v>2.331405828596663</v>
+        <v>2.352599600802012</v>
       </c>
       <c r="U68" t="n">
-        <v>0.01284341423264229</v>
+        <v>0.01948896483444288</v>
       </c>
       <c r="V68" t="n">
-        <v>0.1986846210314439</v>
+        <v>0.4212984636054069</v>
       </c>
       <c r="W68" t="n">
-        <v>0.01622</v>
+        <v>0.01728</v>
       </c>
       <c r="X68" t="n">
-        <v>0.008110000000000001</v>
+        <v>0.00864</v>
       </c>
       <c r="Y68" t="n">
-        <v>32.83159453257299</v>
+        <v>34.19735342816631</v>
       </c>
       <c r="Z68" t="n">
-        <v>0.01157922320647989</v>
+        <v>0.01371968923896166</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.0003444698247772432</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.01216839656025612</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>0.0004041724259929929</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.0136424721791035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BR08</t>
+          <t>BR09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BR08_T_29</t>
+          <t>BR09_T_29</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>35.71666666666666</v>
+        <v>36.75</v>
       </c>
       <c r="D69" t="n">
-        <v>35.71666666666666</v>
+        <v>36.75</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>36.71428571428564</v>
+        <v>30.54107142857147</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>2.225119195750334</v>
+        <v>2.497032422101453</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3724108962071924</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>28.98</v>
       </c>
       <c r="K69" t="n">
-        <v>0.2482560989697474</v>
+        <v>0.5198551448550432</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>0.005575616292307751</v>
+        <v>0.01351059041225433</v>
       </c>
       <c r="N69" t="n">
-        <v>0.01868335460030837</v>
+        <v>0</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -7199,1616 +7199,48 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>25.71666666666666</v>
+        <v>26.75</v>
       </c>
       <c r="Q69" t="n">
-        <v>35.32500000000002</v>
+        <v>30.12857142857151</v>
       </c>
       <c r="R69" t="n">
-        <v>0.3308651428571041</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>34.61647934279866</v>
+        <v>35.04183579224857</v>
       </c>
       <c r="T69" t="n">
-        <v>2.353743628712218</v>
+        <v>2.361781859984262</v>
       </c>
       <c r="U69" t="n">
-        <v>0.01322035179421022</v>
+        <v>0.01970497485318354</v>
       </c>
       <c r="V69" t="n">
-        <v>0.2034072352665216</v>
+        <v>0.4278830060214355</v>
       </c>
       <c r="W69" t="n">
-        <v>0.01728666666666667</v>
+        <v>0.0177</v>
       </c>
       <c r="X69" t="n">
-        <v>0.008643333333333333</v>
+        <v>0.00885</v>
       </c>
       <c r="Y69" t="n">
-        <v>33.75408934834168</v>
+        <v>34.69219227608998</v>
       </c>
       <c r="Z69" t="n">
-        <v>0.009267599997966548</v>
+        <v>0.0224321685275548</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.0005343022972248991</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.01961652719811411</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>0.0006187360183830816</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.02141846259900344</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>BR08</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>BR08_T_29</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>38.41666666666666</v>
-      </c>
-      <c r="D70" t="n">
-        <v>38.41666666666666</v>
-      </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" t="n">
-        <v>36.54999999999995</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>2.238126974352284</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0.4370511859323505</v>
-      </c>
-      <c r="J70" t="n">
-        <v>28.98</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0.09314611508350956</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0.008164208448361089</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0.02804497875626173</v>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P70" t="n">
-        <v>28.41666666666666</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>36.71428571428564</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.3724108962071924</v>
-      </c>
-      <c r="S70" t="n">
-        <v>35.52745852239767</v>
-      </c>
-      <c r="T70" t="n">
-        <v>2.377809652778218</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0.01354761888358185</v>
-      </c>
-      <c r="V70" t="n">
-        <v>0.2068914320190066</v>
-      </c>
-      <c r="W70" t="n">
-        <v>0.01836666666666667</v>
-      </c>
-      <c r="X70" t="n">
-        <v>0.009183333333333333</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>34.61647934279866</v>
-      </c>
-      <c r="Z70" t="n">
-        <v>0.006196243412663805</v>
-      </c>
-      <c r="AA70" t="n">
-        <v>0.0008109233377192746</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>0.02963924799363945</v>
-      </c>
-      <c r="AC70" t="n">
-        <v>0.0008844102245227347</v>
-      </c>
-      <c r="AD70" t="n">
-        <v>0.03142084756851587</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>BR08</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>BR08_T_29</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>46.41666666666666</v>
-      </c>
-      <c r="D71" t="n">
-        <v>46.41666666666666</v>
-      </c>
-      <c r="E71" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" t="n">
-        <v>37.45357142857144</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>2.350696964539372</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0.792026695150037</v>
-      </c>
-      <c r="J71" t="n">
-        <v>28.98</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0.2428851122484339</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0.02098979306862803</v>
-      </c>
-      <c r="N71" t="n">
-        <v>0.05964752041359847</v>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P71" t="n">
-        <v>36.41666666666666</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>36.54999999999995</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0.4370511859323505</v>
-      </c>
-      <c r="S71" t="n">
-        <v>38.4228317975193</v>
-      </c>
-      <c r="T71" t="n">
-        <v>2.457676399311552</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0.01423124238248932</v>
-      </c>
-      <c r="V71" t="n">
-        <v>0.2096355868065841</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0.02156666666666666</v>
-      </c>
-      <c r="X71" t="n">
-        <v>0.01078333333333333</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>35.52745852239767</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>0.01541414394739185</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>0.001781396691915808</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>0.06671966824328958</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>0.001733285414237961</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>0.06659773392835873</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>10.08333333333333</v>
-      </c>
-      <c r="D72" t="n">
-        <v>10.08333333333333</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>22.74159954433088</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>2.151754877317993</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>28.995</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0.8532992157616837</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0.0143222143423807</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P72" t="n">
-        <v>0.08333333333333215</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>21.79285714285717</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>28.31815807004039</v>
-      </c>
-      <c r="T72" t="n">
-        <v>2.196892806206484</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0.01041196717294989</v>
-      </c>
-      <c r="V72" t="n">
-        <v>0.2041873938903916</v>
-      </c>
-      <c r="W72" t="n">
-        <v>0.007033333333333333</v>
-      </c>
-      <c r="X72" t="n">
-        <v>0.003516666666666667</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>25.42114791934122</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>0.04417757490269928</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="D73" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>22.97108767528296</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>2.163697271557409</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>28.995</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0.4955894525174036</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0.00991189089150895</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P73" t="n">
-        <v>1.200000000000001</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>22.74159954433088</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>28.49544506515976</v>
-      </c>
-      <c r="T73" t="n">
-        <v>2.200944449147011</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0.01098357032200971</v>
-      </c>
-      <c r="V73" t="n">
-        <v>0.2161387857045839</v>
-      </c>
-      <c r="W73" t="n">
-        <v>0.007480000000000001</v>
-      </c>
-      <c r="X73" t="n">
-        <v>0.00374</v>
-      </c>
-      <c r="Y73" t="n">
-        <v>28.31815807004039</v>
-      </c>
-      <c r="Z73" t="n">
-        <v>0.02615548495855645</v>
-      </c>
-      <c r="AA73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC73" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD73" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>12.66666666666667</v>
-      </c>
-      <c r="D74" t="n">
-        <v>12.66666666666667</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" t="n">
-        <v>24.12500000000008</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>2.18231465451585</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>28.98790163201834</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0.527194572758186</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0.01009690660006621</v>
-      </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P74" t="n">
-        <v>2.666666666666666</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>22.97108767528296</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="n">
-        <v>28.74377626618266</v>
-      </c>
-      <c r="T74" t="n">
-        <v>2.2066448992919</v>
-      </c>
-      <c r="U74" t="n">
-        <v>0.01171780391374263</v>
-      </c>
-      <c r="V74" t="n">
-        <v>0.2317374616169707</v>
-      </c>
-      <c r="W74" t="n">
-        <v>0.008066666666666666</v>
-      </c>
-      <c r="X74" t="n">
-        <v>0.004033333333333333</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>28.49544506515976</v>
-      </c>
-      <c r="Z74" t="n">
-        <v>0.02647932083128075</v>
-      </c>
-      <c r="AA74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD74" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>13.85</v>
-      </c>
-      <c r="D75" t="n">
-        <v>13.85</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="n">
-        <v>24.57500000000017</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="n">
-        <v>2.193791961026335</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" t="n">
-        <v>28.98710002854261</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0.4106539365163594</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0.01080044764312056</v>
-      </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P75" t="n">
-        <v>3.849999999999998</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>24.12500000000008</v>
-      </c>
-      <c r="R75" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" t="n">
-        <v>28.95676810363952</v>
-      </c>
-      <c r="T75" t="n">
-        <v>2.211557709760262</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0.01228108243496568</v>
-      </c>
-      <c r="V75" t="n">
-        <v>0.2438029808221922</v>
-      </c>
-      <c r="W75" t="n">
-        <v>0.008539999999999999</v>
-      </c>
-      <c r="X75" t="n">
-        <v>0.004269999999999999</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>28.74377626618266</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>0.02163341820285943</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>15.31666666666667</v>
-      </c>
-      <c r="D76" t="n">
-        <v>15.31666666666667</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" t="n">
-        <v>25.06785714285721</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" t="n">
-        <v>2.214828125862959</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" t="n">
-        <v>28.98</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0.3756303196153055</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0.009872310665280869</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P76" t="n">
-        <v>5.31666666666667</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>24.57500000000017</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="n">
-        <v>29.2361661686984</v>
-      </c>
-      <c r="T76" t="n">
-        <v>2.218035494015818</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0.01296737669517052</v>
-      </c>
-      <c r="V76" t="n">
-        <v>0.2588167976329628</v>
-      </c>
-      <c r="W76" t="n">
-        <v>0.009126666666666668</v>
-      </c>
-      <c r="X76" t="n">
-        <v>0.004563333333333334</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>28.95676810363952</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>0.01944191146369945</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>17.98333333333333</v>
-      </c>
-      <c r="D77" t="n">
-        <v>17.98333333333333</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="n">
-        <v>25.90000000000013</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>2.214024096070052</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" t="n">
-        <v>28.98</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0.3298559424945083</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0.008518133778895404</v>
-      </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P77" t="n">
-        <v>7.983333333333334</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>25.06785714285721</v>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>29.78688303253967</v>
-      </c>
-      <c r="T77" t="n">
-        <v>2.230915506895817</v>
-      </c>
-      <c r="U77" t="n">
-        <v>0.01413309295165512</v>
-      </c>
-      <c r="V77" t="n">
-        <v>0.2848807744362734</v>
-      </c>
-      <c r="W77" t="n">
-        <v>0.01019333333333333</v>
-      </c>
-      <c r="X77" t="n">
-        <v>0.005096666666666667</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>29.2361661686984</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>0.01658310436687791</v>
-      </c>
-      <c r="AA77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>23.56666666666667</v>
-      </c>
-      <c r="D78" t="n">
-        <v>23.56666666666667</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" t="n">
-        <v>27.37499999999996</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="n">
-        <v>2.307573593937551</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="n">
-        <v>28.99338819905182</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0.3454451519070621</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0.0129230258223817</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P78" t="n">
-        <v>13.56666666666667</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>25.90000000000013</v>
-      </c>
-      <c r="R78" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" t="n">
-        <v>31.11037299665006</v>
-      </c>
-      <c r="T78" t="n">
-        <v>2.262489288469567</v>
-      </c>
-      <c r="U78" t="n">
-        <v>0.01625124162510059</v>
-      </c>
-      <c r="V78" t="n">
-        <v>0.3347092315256564</v>
-      </c>
-      <c r="W78" t="n">
-        <v>0.01242666666666667</v>
-      </c>
-      <c r="X78" t="n">
-        <v>0.006213333333333333</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>29.78688303253967</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>0.01821926693166444</v>
-      </c>
-      <c r="AA78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC78" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD78" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>25.13333333333333</v>
-      </c>
-      <c r="D79" t="n">
-        <v>25.13333333333333</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="n">
-        <v>28.11428571428576</v>
-      </c>
-      <c r="G79" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" t="n">
-        <v>2.324643491537374</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="n">
-        <v>28.98907356082457</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0.2438328224960159</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0.01425711185829255</v>
-      </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P79" t="n">
-        <v>15.13333333333333</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>27.37499999999996</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>31.52104556228423</v>
-      </c>
-      <c r="T79" t="n">
-        <v>2.272468965115901</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0.01679004299276455</v>
-      </c>
-      <c r="V79" t="n">
-        <v>0.3481790571704745</v>
-      </c>
-      <c r="W79" t="n">
-        <v>0.01305333333333333</v>
-      </c>
-      <c r="X79" t="n">
-        <v>0.006526666666666667</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>31.11037299665006</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>0.01480594697664882</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>26.68333333333333</v>
-      </c>
-      <c r="D80" t="n">
-        <v>26.68333333333333</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" t="n">
-        <v>28.14285714285706</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="n">
-        <v>2.352668497327067</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" t="n">
-        <v>28.995</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0.3483746225501007</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0.01556696786466986</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P80" t="n">
-        <v>16.68333333333333</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>28.11428571428576</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="n">
-        <v>31.94343200509588</v>
-      </c>
-      <c r="T80" t="n">
-        <v>2.282825558805818</v>
-      </c>
-      <c r="U80" t="n">
-        <v>0.01726816390210312</v>
-      </c>
-      <c r="V80" t="n">
-        <v>0.360274340850948</v>
-      </c>
-      <c r="W80" t="n">
-        <v>0.01367333333333333</v>
-      </c>
-      <c r="X80" t="n">
-        <v>0.006836666666666666</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>31.52104556228423</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>0.01899552184075797</v>
-      </c>
-      <c r="AA80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD80" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>28.15</v>
-      </c>
-      <c r="D81" t="n">
-        <v>28.15</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" t="n">
-        <v>29.46071428571427</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>2.375720882565579</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="n">
-        <v>28.995</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0.4669603785258343</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0.01540779486614794</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P81" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>28.14285714285706</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="n">
-        <v>32.3574018720367</v>
-      </c>
-      <c r="T81" t="n">
-        <v>2.293067791270262</v>
-      </c>
-      <c r="U81" t="n">
-        <v>0.01769926440963473</v>
-      </c>
-      <c r="V81" t="n">
-        <v>0.3714798347284995</v>
-      </c>
-      <c r="W81" t="n">
-        <v>0.01426</v>
-      </c>
-      <c r="X81" t="n">
-        <v>0.007129999999999999</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>31.94343200509588</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>0.02233579751349438</v>
-      </c>
-      <c r="AA81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC81" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>31.18333333333333</v>
-      </c>
-      <c r="D82" t="n">
-        <v>31.18333333333333</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" t="n">
-        <v>30.54107142857147</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" t="n">
-        <v>2.429480867954015</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" t="n">
-        <v>28.98</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0.1393496146836234</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0.01356607661731992</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P82" t="n">
-        <v>21.18333333333333</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>29.46071428571427</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="n">
-        <v>33.25583249482232</v>
-      </c>
-      <c r="T82" t="n">
-        <v>2.315615591595817</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0.01851308273432502</v>
-      </c>
-      <c r="V82" t="n">
-        <v>0.3934469053539372</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0.01547333333333333</v>
-      </c>
-      <c r="X82" t="n">
-        <v>0.007736666666666666</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>32.3574018720367</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>0.01014663618242141</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>34.18333333333334</v>
-      </c>
-      <c r="D83" t="n">
-        <v>34.18333333333334</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" t="n">
-        <v>30.00357142857132</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>2.451704147576396</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" t="n">
-        <v>28.995</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0.08855763882758942</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0.01490221644458623</v>
-      </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P83" t="n">
-        <v>24.18333333333334</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>30.54107142857147</v>
-      </c>
-      <c r="R83" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" t="n">
-        <v>34.19735342816631</v>
-      </c>
-      <c r="T83" t="n">
-        <v>2.339725615705817</v>
-      </c>
-      <c r="U83" t="n">
-        <v>0.01919070522193477</v>
-      </c>
-      <c r="V83" t="n">
-        <v>0.4125744318193387</v>
-      </c>
-      <c r="W83" t="n">
-        <v>0.01667333333333334</v>
-      </c>
-      <c r="X83" t="n">
-        <v>0.008336666666666668</v>
-      </c>
-      <c r="Y83" t="n">
-        <v>33.25583249482232</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>0.00902987934884078</v>
-      </c>
-      <c r="AA83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD83" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="D84" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" t="n">
-        <v>30.12857142857151</v>
-      </c>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" t="n">
-        <v>2.481063784627632</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0.2239877292055531</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0.01559421357166551</v>
-      </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P84" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>30.00357142857132</v>
-      </c>
-      <c r="R84" t="n">
-        <v>0</v>
-      </c>
-      <c r="S84" t="n">
-        <v>34.69219227608998</v>
-      </c>
-      <c r="T84" t="n">
-        <v>2.352599600802012</v>
-      </c>
-      <c r="U84" t="n">
-        <v>0.01948896483444288</v>
-      </c>
-      <c r="V84" t="n">
-        <v>0.4212984636054069</v>
-      </c>
-      <c r="W84" t="n">
-        <v>0.01728</v>
-      </c>
-      <c r="X84" t="n">
-        <v>0.00864</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>34.19735342816631</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>0.01371968923896166</v>
-      </c>
-      <c r="AA84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>BR09</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>BR09_T_29</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>36.75</v>
-      </c>
-      <c r="D85" t="n">
-        <v>36.75</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>30.54107142857147</v>
-      </c>
-      <c r="G85" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" t="n">
-        <v>2.497032422101453</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" t="n">
-        <v>28.98</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0.5198551448550432</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0.01351059041225433</v>
-      </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="P85" t="n">
-        <v>26.75</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>30.12857142857151</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="n">
-        <v>35.04183579224857</v>
-      </c>
-      <c r="T85" t="n">
-        <v>2.361781859984262</v>
-      </c>
-      <c r="U85" t="n">
-        <v>0.01970497485318354</v>
-      </c>
-      <c r="V85" t="n">
-        <v>0.4278830060214355</v>
-      </c>
-      <c r="W85" t="n">
-        <v>0.0177</v>
-      </c>
-      <c r="X85" t="n">
-        <v>0.00885</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>34.69219227608998</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>0.0224321685275548</v>
-      </c>
-      <c r="AA85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD85" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/processed/BR_processed_ind.xlsx
+++ b/data/processed/BR_processed_ind.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD69"/>
+  <dimension ref="A1:AE69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,70 +511,75 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>t_ind_ad</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Xlag1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Plag1</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>X_calc</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>V_calc</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>mu_calc</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dXdt_calc</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dVdt_calc</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>FS_calc</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Xlag1_calc</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mu</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>qP</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>rP</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>qP_calc</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>rP_calc</t>
         </is>
@@ -636,45 +641,48 @@
         <v>1.77635683940025e-15</v>
       </c>
       <c r="Q2" t="n">
+        <v>8.822964434107203e-17</v>
+      </c>
+      <c r="R2" t="n">
         <v>19.55000000000009</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
         <v>26.65401311151907</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>1.848679151198421</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>0.225235414492541</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>5.970266593250297</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.0023</v>
       </c>
       <c r="X2" t="n">
         <v>0.0023</v>
       </c>
       <c r="Y2" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="Z2" t="n">
         <v>23.31328393927748</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>0.1678276210381796</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>0.001409663588305178</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>0.03252295278732637</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>0.001220189719696316</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>0.03252295278732637</v>
       </c>
     </row>
@@ -734,45 +742,48 @@
         <v>1.283333333333333</v>
       </c>
       <c r="Q3" t="n">
+        <v>0.06374172185430461</v>
+      </c>
+      <c r="R3" t="n">
         <v>23.07142857142841</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>26.81456003794531</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>1.851713165092423</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0.006094652876519476</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>0.1282608693858629</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.002428333333333334</v>
       </c>
       <c r="X3" t="n">
         <v>0.002428333333333334</v>
       </c>
       <c r="Y3" t="n">
+        <v>0.002428333333333334</v>
+      </c>
+      <c r="Z3" t="n">
         <v>26.65401311151907</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>0.02650201917316335</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>0.004441501609194717</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>0.1065167260919373</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>0.004012411300956096</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>0.1075910437264175</v>
       </c>
     </row>
@@ -832,45 +843,48 @@
         <v>3.033333333333333</v>
       </c>
       <c r="Q4" t="n">
+        <v>0.1506622516556291</v>
+      </c>
+      <c r="R4" t="n">
         <v>23.9821428571428</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>0.1310102834270957</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>27.04656525722954</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1.856115873425756</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>0.006462734701134105</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>0.1368600617928715</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.002603333333333333</v>
       </c>
       <c r="X4" t="n">
         <v>0.002603333333333333</v>
       </c>
       <c r="Y4" t="n">
+        <v>0.002603333333333333</v>
+      </c>
+      <c r="Z4" t="n">
         <v>26.81456003794531</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>5.19473822208176e-05</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>0.003429009357781865</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>0.08474551698518029</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>0.003294261940258456</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>0.08909847054160794</v>
       </c>
     </row>
@@ -930,45 +944,48 @@
         <v>5.15</v>
       </c>
       <c r="Q5" t="n">
+        <v>0.255794701986755</v>
+      </c>
+      <c r="R5" t="n">
         <v>24.71428571428569</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>0.3150449672599142</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>27.34710021724216</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>1.861850276203534</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>0.006890089696224523</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>0.1470768854829419</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.002815</v>
       </c>
       <c r="X5" t="n">
         <v>0.002815</v>
       </c>
       <c r="Y5" t="n">
+        <v>0.002815</v>
+      </c>
+      <c r="Z5" t="n">
         <v>27.04656525722954</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>0.009247963860255975</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>0.00255434852123139</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>0.06448817748780201</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>0.002529907594138958</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>0.06918563651728009</v>
       </c>
     </row>
@@ -1028,45 +1045,48 @@
         <v>7.150000000000002</v>
       </c>
       <c r="Q6" t="n">
+        <v>0.3551324503311259</v>
+      </c>
+      <c r="R6" t="n">
         <v>25.24642857142839</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>0.462353720667521</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>27.65075345784806</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>1.867680276203534</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>0.007275813546525556</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>0.1565450600492553</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.003015</v>
       </c>
       <c r="X6" t="n">
         <v>0.003015</v>
       </c>
       <c r="Y6" t="n">
+        <v>0.003015</v>
+      </c>
+      <c r="Z6" t="n">
         <v>27.34710021724216</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>0.00709381743588283</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>0.004181638843259673</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>0.112121445976553</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>0.004332845827374902</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>0.1198064517436091</v>
       </c>
     </row>
@@ -1126,45 +1146,48 @@
         <v>9.100000000000005</v>
       </c>
       <c r="Q7" t="n">
+        <v>0.4519867549668876</v>
+      </c>
+      <c r="R7" t="n">
         <v>26.8128</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>0.6209461221159972</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>27.96486690504819</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>1.873749651203535</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>0.007634557396181491</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>0.1655915818766285</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.003210000000000001</v>
       </c>
       <c r="X7" t="n">
         <v>0.003210000000000001</v>
       </c>
       <c r="Y7" t="n">
+        <v>0.003210000000000001</v>
+      </c>
+      <c r="Z7" t="n">
         <v>27.65075345784806</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
       <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
         <v>0.0081223021414259</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>0.2218548813486614</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>0.008700430054214312</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>0.2433063684827845</v>
       </c>
     </row>
@@ -1224,45 +1247,48 @@
         <v>10.15</v>
       </c>
       <c r="Q8" t="n">
+        <v>0.5041390728476821</v>
+      </c>
+      <c r="R8" t="n">
         <v>27.31428571428567</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>0.9523209449429346</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>28.14125939399925</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>1.877175276203535</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>0.007820572933980099</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>0.1703846797234053</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.003315</v>
       </c>
       <c r="X8" t="n">
         <v>0.003315</v>
       </c>
       <c r="Y8" t="n">
+        <v>0.003315</v>
+      </c>
+      <c r="Z8" t="n">
         <v>27.96486690504819</v>
       </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
       <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
         <v>0.01172475127120083</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>0.3242312467603854</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>0.01278089828636535</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>0.3596705739649278</v>
       </c>
     </row>
@@ -1322,45 +1348,48 @@
         <v>11.16666666666667</v>
       </c>
       <c r="Q9" t="n">
+        <v>0.554635761589404</v>
+      </c>
+      <c r="R9" t="n">
         <v>27.65357142857139</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>1.25504016023201</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>28.31682006871788</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>1.88059720675909</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>0.007995870233005813</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>0.1749716551927243</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.003416666666666667</v>
       </c>
       <c r="X9" t="n">
         <v>0.003416666666666667</v>
       </c>
       <c r="Y9" t="n">
+        <v>0.003416666666666667</v>
+      </c>
+      <c r="Z9" t="n">
         <v>28.14125939399925</v>
       </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
       <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
         <v>0.01728682448100467</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>0.4847102107155994</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>0.01902416488705136</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>0.5387038540642539</v>
       </c>
     </row>
@@ -1420,45 +1449,48 @@
         <v>12.13333333333334</v>
       </c>
       <c r="Q10" t="n">
+        <v>0.6026490066225166</v>
+      </c>
+      <c r="R10" t="n">
         <v>28.03928571428575</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>1.69587337268752</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>28.48804706810438</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>1.88394670675909</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>0.008158145763995973</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>0.1792828694602286</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.003513333333333334</v>
       </c>
       <c r="X10" t="n">
         <v>0.003513333333333334</v>
       </c>
       <c r="Y10" t="n">
+        <v>0.003513333333333334</v>
+      </c>
+      <c r="Z10" t="n">
         <v>28.31682006871788</v>
       </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
       <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
         <v>0.02361088313494781</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>0.6709707039456413</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>0.0263790020874605</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
         <v>0.7514862530771985</v>
       </c>
     </row>
@@ -1518,45 +1550,48 @@
         <v>1.199999999999998</v>
       </c>
       <c r="Q11" t="n">
+        <v>0.06196213425129075</v>
+      </c>
+      <c r="R11" t="n">
         <v>26.35714285714281</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
       <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>27.23145296113909</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>1.908002336876444</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>0.01870882202496487</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>0.3981449934364881</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.007799999999999998</v>
       </c>
       <c r="X11" t="n">
         <v>0.007799999999999998</v>
       </c>
       <c r="Y11" t="n">
+        <v>0.007799999999999998</v>
+      </c>
+      <c r="Z11" t="n">
         <v>26.3278144559028</v>
       </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
       <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
         <v>0.006015752972438381</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>0.1619956336149481</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>0.006010640046182784</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
         <v>0.1636784616839654</v>
       </c>
     </row>
@@ -1616,45 +1651,48 @@
         <v>2.949999999999998</v>
       </c>
       <c r="Q12" t="n">
+        <v>0.1523235800344233</v>
+      </c>
+      <c r="R12" t="n">
         <v>26.92857142857148</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>0.1961577414134905</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>27.96947227900407</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>1.922571086876444</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>0.02051067912378411</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>0.4449234941784995</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0.008849999999999998</v>
       </c>
       <c r="X12" t="n">
         <v>0.008849999999999998</v>
       </c>
       <c r="Y12" t="n">
+        <v>0.008849999999999998</v>
+      </c>
+      <c r="Z12" t="n">
         <v>27.23145296113909</v>
       </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
       <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
         <v>0.00362725892161148</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>0.0921971490896749</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>0.003588200271870521</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>0.1003600680355974</v>
       </c>
     </row>
@@ -1714,45 +1752,48 @@
         <v>5.066666666666665</v>
       </c>
       <c r="Q13" t="n">
+        <v>0.2616179001721169</v>
+      </c>
+      <c r="R13" t="n">
         <v>25.41785714285721</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>0.4648676866334254</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>28.96836793893106</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>1.942647670209777</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>0.022411221550434</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>0.4983091249527896</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.01012</v>
       </c>
       <c r="X13" t="n">
         <v>0.01012</v>
       </c>
       <c r="Y13" t="n">
+        <v>0.01012</v>
+      </c>
+      <c r="Z13" t="n">
         <v>27.96947227900407</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>0.006274829559544594</v>
       </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
         <v>0.000176502193613248</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
         <v>0.005112980486617014</v>
       </c>
     </row>
@@ -1812,45 +1853,48 @@
         <v>7.066666666666666</v>
       </c>
       <c r="Q14" t="n">
+        <v>0.3648881239242685</v>
+      </c>
+      <c r="R14" t="n">
         <v>27.31785714285721</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>0.5273275582417261</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>30.0125510328083</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>1.964087670209778</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>0.02393237056755607</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>0.545294449839189</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0.01132</v>
       </c>
       <c r="X14" t="n">
         <v>0.01132</v>
       </c>
       <c r="Y14" t="n">
+        <v>0.01132</v>
+      </c>
+      <c r="Z14" t="n">
         <v>28.96836793893106</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>0.02643890324335607</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AB14" t="n">
         <v>0.005986466179688899</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>0.166038915540943</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
         <v>0.00583462453234216</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
         <v>0.1751119665341944</v>
       </c>
     </row>
@@ -1910,45 +1954,48 @@
         <v>8.999999999999996</v>
       </c>
       <c r="Q15" t="n">
+        <v>0.4647160068846814</v>
+      </c>
+      <c r="R15" t="n">
         <v>27.73571428571431</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>0.5669120469218694</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>31.10797224550694</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>1.987094336876444</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>0.02516104333188622</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>0.5873345723081156</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.01248</v>
       </c>
       <c r="X15" t="n">
         <v>0.01248</v>
       </c>
       <c r="Y15" t="n">
+        <v>0.01248</v>
+      </c>
+      <c r="Z15" t="n">
         <v>30.0125510328083</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>0.00455350837092449</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AB15" t="n">
         <v>0.02262404581012045</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>0.6940734053890505</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>0.02327612397420674</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AE15" t="n">
         <v>0.7240730185726018</v>
       </c>
     </row>
@@ -2008,45 +2055,48 @@
         <v>10.06666666666667</v>
       </c>
       <c r="Q16" t="n">
+        <v>0.5197934595524957</v>
+      </c>
+      <c r="R16" t="n">
         <v>30.67857142857135</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>1.314363106233276</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>31.74613976555108</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>2.000747670209778</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>0.02574269343420017</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>0.6090542906575316</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.01312</v>
       </c>
       <c r="X16" t="n">
         <v>0.01312</v>
       </c>
       <c r="Y16" t="n">
+        <v>0.01312</v>
+      </c>
+      <c r="Z16" t="n">
         <v>31.10797224550694</v>
       </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
       <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
         <v>0.03368831785424067</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>1.033509465599738</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
         <v>0.0356935510289857</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AE16" t="n">
         <v>1.133132459695009</v>
       </c>
     </row>
@@ -2106,45 +2156,48 @@
         <v>0.8333333333333321</v>
       </c>
       <c r="Q17" t="n">
+        <v>0.05580357142857136</v>
+      </c>
+      <c r="R17" t="n">
         <v>29.52857142857138</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
       <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
         <v>19.99434722445</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>1.878764027775987</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>0.006623944767816831</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>0.1111923506601871</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.001996666666666667</v>
       </c>
       <c r="X17" t="n">
         <v>0.001996666666666667</v>
       </c>
       <c r="Y17" t="n">
+        <v>0.001996666666666667</v>
+      </c>
+      <c r="Z17" t="n">
         <v>16.88071110537751</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>0.04062202704143002</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB17" t="n">
         <v>0.002657762910916</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>0.0816312894067058</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
         <v>0.004090749458152188</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AE17" t="n">
         <v>0.08179186507452553</v>
       </c>
     </row>
@@ -2204,45 +2257,48 @@
         <v>1.933333333333334</v>
       </c>
       <c r="Q18" t="n">
+        <v>0.1294642857142858</v>
+      </c>
+      <c r="R18" t="n">
         <v>30.71428571428574</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>0.09290978010103844</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>20.11820097013989</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>1.88099061110932</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>0.006756699312366905</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>0.1139889619600565</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.002051666666666667</v>
       </c>
       <c r="X18" t="n">
         <v>0.002051666666666667</v>
       </c>
       <c r="Y18" t="n">
+        <v>0.002051666666666667</v>
+      </c>
+      <c r="Z18" t="n">
         <v>19.99434722445</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>0.01789804707363351</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AB18" t="n">
         <v>0.001291368036371657</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>0.04078878183453907</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
         <v>0.002159985784695504</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AE18" t="n">
         <v>0.04345502810914946</v>
       </c>
     </row>
@@ -2302,45 +2358,48 @@
         <v>2.866666666666664</v>
       </c>
       <c r="Q19" t="n">
+        <v>0.1919642857142855</v>
+      </c>
+      <c r="R19" t="n">
         <v>31.58571428571431</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>0.1714635834683609</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>20.22568990499862</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>1.882927277775987</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>0.006866587915181886</v>
       </c>
-      <c r="V19" t="n">
+      <c r="W19" t="n">
         <v>0.1163419779098033</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0.002098333333333333</v>
       </c>
       <c r="X19" t="n">
         <v>0.002098333333333333</v>
       </c>
       <c r="Y19" t="n">
+        <v>0.002098333333333333</v>
+      </c>
+      <c r="Z19" t="n">
         <v>20.11820097013989</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
         <v>0.001401645203937436</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AB19" t="n">
         <v>0.000732260389109694</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
         <v>0.02413582546819065</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
         <v>0.001421388845611391</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AE19" t="n">
         <v>0.02874857002575995</v>
       </c>
     </row>
@@ -2400,45 +2459,48 @@
         <v>3.866666666666667</v>
       </c>
       <c r="Q20" t="n">
+        <v>0.2589285714285715</v>
+      </c>
+      <c r="R20" t="n">
         <v>32.96071428571437</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>0.1940649581558863</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>20.34328539706401</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>1.88505061110932</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>0.006981716693788993</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>0.1188464479797303</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.002148333333333333</v>
       </c>
       <c r="X20" t="n">
         <v>0.002148333333333333</v>
       </c>
       <c r="Y20" t="n">
+        <v>0.002148333333333333</v>
+      </c>
+      <c r="Z20" t="n">
         <v>20.22568990499862</v>
       </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
       <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
         <v>0.001184262765768505</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
         <v>0.03974752399441857</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AD20" t="n">
         <v>0.00225397286104733</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AE20" t="n">
         <v>0.04585321318952273</v>
       </c>
     </row>
@@ -2498,45 +2560,48 @@
         <v>4.949999999999999</v>
       </c>
       <c r="Q21" t="n">
+        <v>0.3314732142857142</v>
+      </c>
+      <c r="R21" t="n">
         <v>33.56309523809537</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>0.2229784488956445</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>20.47349558554726</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>1.887407312498209</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>0.007103330146140919</v>
       </c>
-      <c r="V21" t="n">
+      <c r="W21" t="n">
         <v>0.1215385607924384</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0.0022025</v>
       </c>
       <c r="X21" t="n">
         <v>0.0022025</v>
       </c>
       <c r="Y21" t="n">
+        <v>0.0022025</v>
+      </c>
+      <c r="Z21" t="n">
         <v>20.34328539706401</v>
       </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
       <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
         <v>0.002253668672706707</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
         <v>0.07526448485171559</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AD21" t="n">
         <v>0.004133579428073363</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AE21" t="n">
         <v>0.08462882017316897</v>
       </c>
     </row>
@@ -2596,45 +2661,48 @@
         <v>5.833333333333332</v>
       </c>
       <c r="Q22" t="n">
+        <v>0.3906249999999999</v>
+      </c>
+      <c r="R22" t="n">
         <v>33.39642857142849</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>0.2989185664601128</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>20.58181820790413</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>1.88937236110932</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>0.007200136731366074</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
         <v>0.1237179128238205</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.002246666666666667</v>
       </c>
       <c r="X22" t="n">
         <v>0.002246666666666667</v>
       </c>
       <c r="Y22" t="n">
+        <v>0.002246666666666667</v>
+      </c>
+      <c r="Z22" t="n">
         <v>20.47349558554726</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AA22" t="n">
         <v>0.00396735495458923</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AB22" t="n">
         <v>0.003016123760172439</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
         <v>0.102602067198723</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AD22" t="n">
         <v>0.005534928976968097</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AE22" t="n">
         <v>0.1139189019976181</v>
       </c>
     </row>
@@ -2694,45 +2762,48 @@
         <v>0.8333333333333321</v>
       </c>
       <c r="Q23" t="n">
+        <v>0.05586592178770942</v>
+      </c>
+      <c r="R23" t="n">
         <v>28.42857142857147</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
       <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
         <v>15.01969250829701</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>1.792146527775721</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>0.009244457741737573</v>
       </c>
-      <c r="V23" t="n">
+      <c r="W23" t="n">
         <v>0.1221151697087406</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0.001996666666666667</v>
       </c>
       <c r="X23" t="n">
         <v>0.001996666666666667</v>
       </c>
       <c r="Y23" t="n">
+        <v>0.001996666666666667</v>
+      </c>
+      <c r="Z23" t="n">
         <v>14.80438644820013</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AA23" t="n">
         <v>0.02124826378470669</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AB23" t="n">
         <v>0.002156026816633438</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AC23" t="n">
         <v>0.06320238611045444</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AD23" t="n">
         <v>0.00423544589820138</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AE23" t="n">
         <v>0.06361509502651258</v>
       </c>
     </row>
@@ -2792,45 +2863,48 @@
         <v>1.933333333333334</v>
       </c>
       <c r="Q24" t="n">
+        <v>0.1296089385474861</v>
+      </c>
+      <c r="R24" t="n">
         <v>29.31428571428569</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>0.05810793948216079</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>15.15569778710702</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>1.794373111109054</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>0.009402010873351092</v>
       </c>
-      <c r="V24" t="n">
+      <c r="W24" t="n">
         <v>0.1251651756496959</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.002051666666666667</v>
       </c>
       <c r="X24" t="n">
         <v>0.002051666666666667</v>
       </c>
       <c r="Y24" t="n">
+        <v>0.002051666666666667</v>
+      </c>
+      <c r="Z24" t="n">
         <v>15.01969250829701</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AA24" t="n">
         <v>0.00139773628339818</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AB24" t="n">
         <v>0.001694052966529097</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
         <v>0.05093049240086417</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AD24" t="n">
         <v>0.003538733655060628</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AE24" t="n">
         <v>0.0536319778251635</v>
       </c>
     </row>
@@ -2890,45 +2964,48 @@
         <v>2.899999999999999</v>
       </c>
       <c r="Q25" t="n">
+        <v>0.194413407821229</v>
+      </c>
+      <c r="R25" t="n">
         <v>30.06428571428577</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>0.1219400842896329</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>15.27797946896859</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>1.796379749997943</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>0.00953587058164054</v>
       </c>
-      <c r="V25" t="n">
+      <c r="W25" t="n">
         <v>0.1278286041954265</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0.0021</v>
       </c>
       <c r="X25" t="n">
         <v>0.0021</v>
       </c>
       <c r="Y25" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="Z25" t="n">
         <v>15.15569778710702</v>
       </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
       <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
         <v>0.001179849082637842</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AC25" t="n">
         <v>0.03650228328522884</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AD25" t="n">
         <v>0.002739726214617911</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AE25" t="n">
         <v>0.04185748085752747</v>
       </c>
     </row>
@@ -2988,45 +3065,48 @@
         <v>3.899999999999999</v>
       </c>
       <c r="Q26" t="n">
+        <v>0.2614525139664803</v>
+      </c>
+      <c r="R26" t="n">
         <v>30.93809523809523</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>0.1703755277559266</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15.40717642247015</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>1.798504749997943</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>0.009669531246993858</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>0.1305618575696002</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.00215</v>
       </c>
       <c r="X26" t="n">
         <v>0.00215</v>
       </c>
       <c r="Y26" t="n">
+        <v>0.00215</v>
+      </c>
+      <c r="Z26" t="n">
         <v>15.27797946896859</v>
       </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
       <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
         <v>0.0005275241763407782</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
         <v>0.01662203559450923</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AD26" t="n">
         <v>0.001732058081469855</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AE26" t="n">
         <v>0.02668612443517123</v>
       </c>
     </row>
@@ -3086,35 +3166,35 @@
         <v>4.949999999999999</v>
       </c>
       <c r="Q27" t="n">
+        <v>0.3318435754189944</v>
+      </c>
+      <c r="R27" t="n">
         <v>31.5095238095239</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>0.2036432131066642</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>15.54576471838671</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>1.800789812497944</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>0.009804928460010224</v>
       </c>
-      <c r="V27" t="n">
+      <c r="W27" t="n">
         <v>0.1334114833690572</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0.0022025</v>
       </c>
       <c r="X27" t="n">
         <v>0.0022025</v>
       </c>
       <c r="Y27" t="n">
+        <v>0.0022025</v>
+      </c>
+      <c r="Z27" t="n">
         <v>15.40717642247015</v>
       </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
       <c r="AA27" t="n">
         <v>0</v>
       </c>
@@ -3122,9 +3202,12 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
         <v>0.0006703122036587197</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AE27" t="n">
         <v>0.01042051580594177</v>
       </c>
     </row>
@@ -3184,45 +3267,48 @@
         <v>5.816666666666666</v>
       </c>
       <c r="Q28" t="n">
+        <v>0.3899441340782123</v>
+      </c>
+      <c r="R28" t="n">
         <v>31.73214285714281</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>0.2220723133576301</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>15.66240050600434</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>1.802717423609055</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>0.009912768032329062</v>
       </c>
-      <c r="V28" t="n">
+      <c r="W28" t="n">
         <v>0.1357454552760376</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0.002245833333333333</v>
       </c>
       <c r="X28" t="n">
         <v>0.002245833333333333</v>
       </c>
       <c r="Y28" t="n">
+        <v>0.002245833333333333</v>
+      </c>
+      <c r="Z28" t="n">
         <v>15.54576471838671</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AA28" t="n">
         <v>0.07036365759109456</v>
       </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.795387993961591e-05</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AE28" t="n">
         <v>0.0002812008582509814</v>
       </c>
     </row>
@@ -3282,45 +3368,48 @@
         <v>0.8166666666666629</v>
       </c>
       <c r="Q29" t="n">
+        <v>0.0174005681818181</v>
+      </c>
+      <c r="R29" t="n">
         <v>24.49345238095237</v>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
       <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
         <v>23.93967898481781</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>2.098491694429187</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>0.01007990389195562</v>
       </c>
-      <c r="V29" t="n">
+      <c r="W29" t="n">
         <v>0.194954990695357</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0.004063333333333333</v>
       </c>
       <c r="X29" t="n">
         <v>0.004063333333333333</v>
       </c>
       <c r="Y29" t="n">
+        <v>0.004063333333333333</v>
+      </c>
+      <c r="Z29" t="n">
         <v>23.76781114532759</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AA29" t="n">
         <v>0.01703599848924725</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AB29" t="n">
         <v>0.002931631959375182</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AC29" t="n">
         <v>0.07399229663180125</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AD29" t="n">
         <v>0.003096509180803947</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AE29" t="n">
         <v>0.07412943576198766</v>
       </c>
     </row>
@@ -3380,45 +3469,48 @@
         <v>2.249999999999996</v>
       </c>
       <c r="Q30" t="n">
+        <v>0.04794034090909083</v>
+      </c>
+      <c r="R30" t="n">
         <v>25.23928571428564</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>0.06375494686076261</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>24.22814583540682</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>2.104521249984743</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>0.01063211162014986</v>
       </c>
-      <c r="V30" t="n">
+      <c r="W30" t="n">
         <v>0.2075172963667405</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0.00435</v>
       </c>
       <c r="X30" t="n">
         <v>0.00435</v>
       </c>
       <c r="Y30" t="n">
+        <v>0.00435</v>
+      </c>
+      <c r="Z30" t="n">
         <v>23.93967898481781</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AA30" t="n">
         <v>0.003897200232591663</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AB30" t="n">
         <v>0.002618004611547352</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AC30" t="n">
         <v>0.06485638924285067</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AD30" t="n">
         <v>0.00271569751353864</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AE30" t="n">
         <v>0.06579631540286586</v>
       </c>
     </row>
@@ -3478,45 +3570,48 @@
         <v>3.75</v>
       </c>
       <c r="Q31" t="n">
+        <v>0.07990056818181818</v>
+      </c>
+      <c r="R31" t="n">
         <v>24.77321428571426</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>0.1716212668026328</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>24.54912556934151</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>2.111271249984743</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>0.01118090177937685</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>0.2204127839316294</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0.00465</v>
       </c>
       <c r="X31" t="n">
         <v>0.00465</v>
       </c>
       <c r="Y31" t="n">
+        <v>0.00465</v>
+      </c>
+      <c r="Z31" t="n">
         <v>24.22814583540682</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
         <v>0.01411667984325947</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AB31" t="n">
         <v>0.00194663879778472</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AC31" t="n">
         <v>0.04872158819598323</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AD31" t="n">
         <v>0.002019535772512294</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AE31" t="n">
         <v>0.0495778372711814</v>
       </c>
     </row>
@@ -3576,45 +3671,48 @@
         <v>5.75</v>
       </c>
       <c r="Q32" t="n">
+        <v>0.1225142045454545</v>
+      </c>
+      <c r="R32" t="n">
         <v>25.0285714285714</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>0.2547670720457892</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>25.00680786687655</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>2.120971249984743</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>0.01186590939888761</v>
       </c>
-      <c r="V32" t="n">
+      <c r="W32" t="n">
         <v>0.2371876907011177</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0.005050000000000001</v>
       </c>
       <c r="X32" t="n">
         <v>0.005050000000000001</v>
       </c>
       <c r="Y32" t="n">
+        <v>0.005050000000000001</v>
+      </c>
+      <c r="Z32" t="n">
         <v>24.54912556934151</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AA32" t="n">
         <v>0.01729347944990734</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AB32" t="n">
         <v>0.001250719091027115</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AC32" t="n">
         <v>0.03284030984725474</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AD32" t="n">
         <v>0.001332234624952042</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AE32" t="n">
         <v>0.03331493529977605</v>
       </c>
     </row>
@@ -3674,45 +3772,48 @@
         <v>10.08333333333333</v>
       </c>
       <c r="Q33" t="n">
+        <v>0.2148437499999999</v>
+      </c>
+      <c r="R33" t="n">
         <v>26.25714285714279</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>0.3345630000595383</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>26.11045456330866</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>2.144732361095854</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>0.01316720038405787</v>
       </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
         <v>0.2717707554568806</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0.005916666666666667</v>
       </c>
       <c r="X33" t="n">
         <v>0.005916666666666667</v>
       </c>
       <c r="Y33" t="n">
+        <v>0.005916666666666667</v>
+      </c>
+      <c r="Z33" t="n">
         <v>25.00680786687655</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AA33" t="n">
         <v>0.01396089162246411</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AB33" t="n">
         <v>0.0001013561359319036</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AC33" t="n">
         <v>0.002777158124534164</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AD33" t="n">
         <v>0.0001589641491270462</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AE33" t="n">
         <v>0.004150626192976761</v>
       </c>
     </row>
@@ -3772,45 +3873,48 @@
         <v>11.75</v>
       </c>
       <c r="Q34" t="n">
+        <v>0.2503551136363636</v>
+      </c>
+      <c r="R34" t="n">
         <v>27.40000000000004</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S34" t="n">
         <v>0.4114676331552647</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>26.57397314534754</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U34" t="n">
         <v>2.154871249984743</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>0.01360207800305404</v>
       </c>
-      <c r="V34" t="n">
+      <c r="W34" t="n">
         <v>0.2843859629506359</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0.00625</v>
       </c>
       <c r="X34" t="n">
         <v>0.00625</v>
       </c>
       <c r="Y34" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="Z34" t="n">
         <v>26.11045456330866</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AA34" t="n">
         <v>0.01145255846603085</v>
       </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
         <v>4.43986780696222e-05</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AE34" t="n">
         <v>0.001179849278711071</v>
       </c>
     </row>
@@ -3870,45 +3974,48 @@
         <v>14.25</v>
       </c>
       <c r="Q35" t="n">
+        <v>0.3036221590909091</v>
+      </c>
+      <c r="R35" t="n">
         <v>28.4607142857143</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>0.4067877264015557</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>27.30784322790872</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>2.171121249984743</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>0.01418845246147928</v>
       </c>
-      <c r="V35" t="n">
+      <c r="W35" t="n">
         <v>0.3025561516882164</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0.006750000000000001</v>
       </c>
       <c r="X35" t="n">
         <v>0.006750000000000001</v>
       </c>
       <c r="Y35" t="n">
+        <v>0.006750000000000001</v>
+      </c>
+      <c r="Z35" t="n">
         <v>26.57397314534754</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AA35" t="n">
         <v>0.009152735978746178</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AB35" t="n">
         <v>6.146505253398153e-05</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AC35" t="n">
         <v>0.001762949417501451</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AD35" t="n">
         <v>4.578707085297215e-05</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AE35" t="n">
         <v>0.001250346152718112</v>
       </c>
     </row>
@@ -3968,45 +4075,48 @@
         <v>15.91666666666666</v>
       </c>
       <c r="Q36" t="n">
+        <v>0.3391335227272727</v>
+      </c>
+      <c r="R36" t="n">
         <v>28.6821428571429</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>0.4021708299263646</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>27.82182632859923</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>2.182649027762521</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>0.01453689738861425</v>
       </c>
-      <c r="V36" t="n">
+      <c r="W36" t="n">
         <v>0.3141530853075174</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0.007083333333333334</v>
       </c>
       <c r="X36" t="n">
         <v>0.007083333333333334</v>
       </c>
       <c r="Y36" t="n">
+        <v>0.007083333333333334</v>
+      </c>
+      <c r="Z36" t="n">
         <v>27.30784322790872</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AA36" t="n">
         <v>0.00813246080612828</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AB36" t="n">
         <v>5.722124060260651e-05</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AC36" t="n">
         <v>0.001647154283060745</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AD36" t="n">
         <v>4.518776391829954e-05</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AE36" t="n">
         <v>0.001257206119912673</v>
       </c>
     </row>
@@ -4066,45 +4176,48 @@
         <v>18.7</v>
       </c>
       <c r="Q37" t="n">
+        <v>0.3984374999999999</v>
+      </c>
+      <c r="R37" t="n">
         <v>28.78571428571429</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>0.3873938421634567</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>28.72212538793305</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
         <v>2.203138999984743</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>0.01504659661323521</v>
       </c>
-      <c r="V37" t="n">
+      <c r="W37" t="n">
         <v>0.3325682403572446</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.007640000000000001</v>
       </c>
       <c r="X37" t="n">
         <v>0.007640000000000001</v>
       </c>
       <c r="Y37" t="n">
+        <v>0.007640000000000001</v>
+      </c>
+      <c r="Z37" t="n">
         <v>27.82182632859923</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AA37" t="n">
         <v>0.007018151213335786</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AB37" t="n">
         <v>1.910531806293016e-05</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AC37" t="n">
         <v>0.0005503013934911842</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AD37" t="n">
         <v>4.454302433905062e-05</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AE37" t="n">
         <v>0.001279370330223965</v>
       </c>
     </row>
@@ -4164,45 +4277,48 @@
         <v>21.75</v>
       </c>
       <c r="Q38" t="n">
+        <v>0.4634232954545454</v>
+      </c>
+      <c r="R38" t="n">
         <v>28.80357142857139</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="n">
         <v>0.3689307159607038</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>29.76547646571371</v>
       </c>
-      <c r="T38" t="n">
+      <c r="U38" t="n">
         <v>2.227371249984743</v>
       </c>
-      <c r="U38" t="n">
+      <c r="V38" t="n">
         <v>0.0155078415118352</v>
       </c>
-      <c r="V38" t="n">
+      <c r="W38" t="n">
         <v>0.3513494137153382</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0.00825</v>
       </c>
       <c r="X38" t="n">
         <v>0.00825</v>
       </c>
       <c r="Y38" t="n">
+        <v>0.00825</v>
+      </c>
+      <c r="Z38" t="n">
         <v>28.72212538793305</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AA38" t="n">
         <v>0.01009923569250023</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AB38" t="n">
         <v>1.425389975077348e-05</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AC38" t="n">
         <v>0.0004247662125730495</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AD38" t="n">
         <v>4.408174559026023e-05</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AE38" t="n">
         <v>0.00131211416093447</v>
       </c>
     </row>
@@ -4262,45 +4378,48 @@
         <v>24.75</v>
       </c>
       <c r="Q39" t="n">
+        <v>0.52734375</v>
+      </c>
+      <c r="R39" t="n">
         <v>29.79999999999999</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>0.3542503465167628</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>30.84541916498249</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
         <v>2.253021249984743</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>0.01587051773015364</v>
       </c>
-      <c r="V39" t="n">
+      <c r="W39" t="n">
         <v>0.3683701508436424</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0.00885</v>
       </c>
       <c r="X39" t="n">
         <v>0.00885</v>
       </c>
       <c r="Y39" t="n">
+        <v>0.00885</v>
+      </c>
+      <c r="Z39" t="n">
         <v>29.76547646571371</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AA39" t="n">
         <v>0.007799312579268405</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AB39" t="n">
         <v>0.0002877005497867221</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AC39" t="n">
         <v>0.008954679612111731</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AD39" t="n">
         <v>0.0003012099228746798</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AE39" t="n">
         <v>0.009290946327721546</v>
       </c>
     </row>
@@ -4360,45 +4479,48 @@
         <v>27.33333333333334</v>
       </c>
       <c r="Q40" t="n">
+        <v>0.5823863636363636</v>
+      </c>
+      <c r="R40" t="n">
         <v>31.12500000000002</v>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="n">
         <v>0.363160750555521</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>31.81469618008588</v>
       </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
         <v>2.276551111095854</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>0.01611696629211079</v>
       </c>
-      <c r="V40" t="n">
+      <c r="W40" t="n">
         <v>0.3818576537329387</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0.009366666666666667</v>
       </c>
       <c r="X40" t="n">
         <v>0.009366666666666667</v>
       </c>
       <c r="Y40" t="n">
+        <v>0.009366666666666667</v>
+      </c>
+      <c r="Z40" t="n">
         <v>30.84541916498249</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AA40" t="n">
         <v>0.006429284455135683</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AB40" t="n">
         <v>0.0007098662467225611</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AC40" t="n">
         <v>0.02192219084074996</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AD40" t="n">
         <v>0.0006841428405296224</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AE40" t="n">
         <v>0.02176579661523088</v>
       </c>
     </row>
@@ -4458,45 +4580,48 @@
         <v>34.93333333333334</v>
       </c>
       <c r="Q41" t="n">
+        <v>0.7443181818181819</v>
+      </c>
+      <c r="R41" t="n">
         <v>30.88214285714287</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>0.3954213588988506</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>34.84968576356192</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
         <v>2.353513777762521</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>0.01654179887468306</v>
       </c>
-      <c r="V41" t="n">
+      <c r="W41" t="n">
         <v>0.4152720349990343</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0.01088666666666667</v>
       </c>
       <c r="X41" t="n">
         <v>0.01088666666666667</v>
       </c>
       <c r="Y41" t="n">
+        <v>0.01088666666666667</v>
+      </c>
+      <c r="Z41" t="n">
         <v>31.81469618008588</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AA41" t="n">
         <v>0.02024773721229721</v>
       </c>
-      <c r="AA41" t="n">
+      <c r="AB41" t="n">
         <v>0.002400167963573594</v>
       </c>
-      <c r="AB41" t="n">
+      <c r="AC41" t="n">
         <v>0.07665107832241122</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AD41" t="n">
         <v>0.002076037952137568</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AE41" t="n">
         <v>0.07234927026522282</v>
       </c>
     </row>
@@ -4556,45 +4681,48 @@
         <v>0.1333333333333329</v>
       </c>
       <c r="Q42" t="n">
+        <v>0.002872531418312378</v>
+      </c>
+      <c r="R42" t="n">
         <v>25.66428571428573</v>
       </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
         <v>28.24180486627298</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
         <v>2.198068889704301</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>0.007080005996886602</v>
       </c>
-      <c r="V42" t="n">
+      <c r="W42" t="n">
         <v>0.1093276616638276</v>
       </c>
-      <c r="W42" t="n">
+      <c r="X42" t="n">
         <v>0.007053333333333333</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Y42" t="n">
         <v>0.003526666666666667</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="Z42" t="n">
         <v>24.01327123307239</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AA42" t="n">
         <v>0.04682466286201208</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AB42" t="n">
         <v>0.001543705722077936</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AC42" t="n">
         <v>0.04292053230848831</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AD42" t="n">
         <v>0.001524917290400108</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AE42" t="n">
         <v>0.04306641655268557</v>
       </c>
     </row>
@@ -4654,45 +4782,48 @@
         <v>1.566666666666666</v>
       </c>
       <c r="Q43" t="n">
+        <v>0.03375224416517055</v>
+      </c>
+      <c r="R43" t="n">
         <v>27.80357142857142</v>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>0.05060060245371522</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>28.4719136932899</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
         <v>2.203329228297969</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>0.007575520339906265</v>
       </c>
-      <c r="V43" t="n">
+      <c r="W43" t="n">
         <v>0.1171360667459857</v>
       </c>
-      <c r="W43" t="n">
+      <c r="X43" t="n">
         <v>0.007626666666666667</v>
       </c>
-      <c r="X43" t="n">
+      <c r="Y43" t="n">
         <v>0.003813333333333334</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="Z43" t="n">
         <v>28.24180486627298</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="AA43" t="n">
         <v>0.009793628241382288</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AB43" t="n">
         <v>0.001301027884616268</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AC43" t="n">
         <v>0.03670292593065684</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AD43" t="n">
         <v>0.001330806855107732</v>
       </c>
-      <c r="AD43" t="n">
+      <c r="AE43" t="n">
         <v>0.03789061792106591</v>
       </c>
     </row>
@@ -4752,45 +4883,48 @@
         <v>2.666666666666668</v>
       </c>
       <c r="Q44" t="n">
+        <v>0.05745062836624779</v>
+      </c>
+      <c r="R44" t="n">
         <v>28.21071428571433</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>0.1044036282464569</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>28.65987999487189</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>2.207644899280302</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>0.007944459054335712</v>
       </c>
-      <c r="V44" t="n">
+      <c r="W44" t="n">
         <v>0.1229649217459871</v>
       </c>
-      <c r="W44" t="n">
+      <c r="X44" t="n">
         <v>0.008066666666666666</v>
       </c>
-      <c r="X44" t="n">
+      <c r="Y44" t="n">
         <v>0.004033333333333333</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="Z44" t="n">
         <v>28.4719136932899</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AA44" t="n">
         <v>0.01308713559294417</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AB44" t="n">
         <v>0.00111834683420231</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AC44" t="n">
         <v>0.03226430616673658</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AD44" t="n">
         <v>0.001176819229347382</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AE44" t="n">
         <v>0.03372749788875357</v>
       </c>
     </row>
@@ -4850,45 +4984,48 @@
         <v>4.133333333333333</v>
       </c>
       <c r="Q45" t="n">
+        <v>0.08904847396768402</v>
+      </c>
+      <c r="R45" t="n">
         <v>28.84999999999995</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>0.1491197853115378</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>28.92563754904663</v>
       </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
         <v>2.213775572077636</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>0.008420554940361971</v>
       </c>
-      <c r="V45" t="n">
+      <c r="W45" t="n">
         <v>0.1305037237789266</v>
       </c>
-      <c r="W45" t="n">
+      <c r="X45" t="n">
         <v>0.008653333333333332</v>
       </c>
-      <c r="X45" t="n">
+      <c r="Y45" t="n">
         <v>0.004326666666666666</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="Z45" t="n">
         <v>28.65987999487189</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AA45" t="n">
         <v>0.01416473965932023</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AB45" t="n">
         <v>0.0008354784274698437</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AC45" t="n">
         <v>0.02491516024776152</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AD45" t="n">
         <v>0.0008945528030801951</v>
       </c>
-      <c r="AD45" t="n">
+      <c r="AE45" t="n">
         <v>0.02587551015038141</v>
       </c>
     </row>
@@ -4948,45 +5085,48 @@
         <v>6.850000000000001</v>
       </c>
       <c r="Q46" t="n">
+        <v>0.147576301615799</v>
+      </c>
+      <c r="R46" t="n">
         <v>29.8214285714287</v>
       </c>
-      <c r="R46" t="n">
+      <c r="S46" t="n">
         <v>0.1918414613393818</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>29.46262799242987</v>
       </c>
-      <c r="T46" t="n">
+      <c r="U46" t="n">
         <v>2.226267723458663</v>
       </c>
-      <c r="U46" t="n">
+      <c r="V46" t="n">
         <v>0.009253028608468754</v>
       </c>
-      <c r="V46" t="n">
+      <c r="W46" t="n">
         <v>0.1437185005742433</v>
       </c>
-      <c r="W46" t="n">
+      <c r="X46" t="n">
         <v>0.009740000000000002</v>
       </c>
-      <c r="X46" t="n">
+      <c r="Y46" t="n">
         <v>0.004870000000000001</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="Z46" t="n">
         <v>28.92563754904663</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AA46" t="n">
         <v>0.01158551351625574</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AB46" t="n">
         <v>0.0005244793669481728</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AC46" t="n">
         <v>0.01583178431944987</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AD46" t="n">
         <v>0.0005561275272637884</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AE46" t="n">
         <v>0.0163849784521229</v>
       </c>
     </row>
@@ -5046,45 +5186,48 @@
         <v>12.4</v>
       </c>
       <c r="Q47" t="n">
+        <v>0.2671454219030521</v>
+      </c>
+      <c r="R47" t="n">
         <v>30.18571428571434</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
         <v>0.2448076315621145</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>30.7324548714269</v>
       </c>
-      <c r="T47" t="n">
+      <c r="U47" t="n">
         <v>2.256376503567413</v>
       </c>
-      <c r="U47" t="n">
+      <c r="V47" t="n">
         <v>0.0107472221904619</v>
       </c>
-      <c r="V47" t="n">
+      <c r="W47" t="n">
         <v>0.1673901041055427</v>
       </c>
-      <c r="W47" t="n">
+      <c r="X47" t="n">
         <v>0.01196</v>
       </c>
-      <c r="X47" t="n">
+      <c r="Y47" t="n">
         <v>0.005979999999999999</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="Z47" t="n">
         <v>29.46262799242987</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AA47" t="n">
         <v>0.01018412764647287</v>
       </c>
-      <c r="AA47" t="n">
+      <c r="AB47" t="n">
         <v>0.0001173795623522832</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AC47" t="n">
         <v>0.003813578138281135</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AD47" t="n">
         <v>0.0001606398135696006</v>
       </c>
-      <c r="AD47" t="n">
+      <c r="AE47" t="n">
         <v>0.004936855821082179</v>
       </c>
     </row>
@@ -5144,45 +5287,48 @@
         <v>14.05</v>
       </c>
       <c r="Q48" t="n">
+        <v>0.3026929982046678</v>
+      </c>
+      <c r="R48" t="n">
         <v>32.48928571428564</v>
       </c>
-      <c r="R48" t="n">
+      <c r="S48" t="n">
         <v>0.2862295508009267</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>31.15248097068912</v>
       </c>
-      <c r="T48" t="n">
+      <c r="U48" t="n">
         <v>2.266515763706663</v>
       </c>
-      <c r="U48" t="n">
+      <c r="V48" t="n">
         <v>0.01113734553511684</v>
       </c>
-      <c r="V48" t="n">
+      <c r="W48" t="n">
         <v>0.1734983778862526</v>
       </c>
-      <c r="W48" t="n">
+      <c r="X48" t="n">
         <v>0.01262</v>
       </c>
-      <c r="X48" t="n">
+      <c r="Y48" t="n">
         <v>0.00631</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="Z48" t="n">
         <v>30.7324548714269</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AA48" t="n">
         <v>0.0085377509283628</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AB48" t="n">
         <v>8.001736341849413e-05</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AC48" t="n">
         <v>0.002635143243149769</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AD48" t="n">
         <v>0.0001212306820646025</v>
       </c>
-      <c r="AD48" t="n">
+      <c r="AE48" t="n">
         <v>0.003776636516081191</v>
       </c>
     </row>
@@ -5242,45 +5388,48 @@
         <v>15.55</v>
       </c>
       <c r="Q49" t="n">
+        <v>0.3350089766606822</v>
+      </c>
+      <c r="R49" t="n">
         <v>32.9321428571429</v>
       </c>
-      <c r="R49" t="n">
+      <c r="S49" t="n">
         <v>0.2889524121591054</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>31.55039960381982</v>
       </c>
-      <c r="T49" t="n">
+      <c r="U49" t="n">
         <v>2.276205773396663</v>
       </c>
-      <c r="U49" t="n">
+      <c r="V49" t="n">
         <v>0.01147067535725597</v>
       </c>
-      <c r="V49" t="n">
+      <c r="W49" t="n">
         <v>0.1786624859513175</v>
       </c>
-      <c r="W49" t="n">
+      <c r="X49" t="n">
         <v>0.01322</v>
       </c>
-      <c r="X49" t="n">
+      <c r="Y49" t="n">
         <v>0.00661</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="Z49" t="n">
         <v>31.15248097068912</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AA49" t="n">
         <v>0.01094124388489767</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AB49" t="n">
         <v>0.0001048376628482425</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AC49" t="n">
         <v>0.003468413842637606</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AD49" t="n">
         <v>0.0001197389718612452</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AE49" t="n">
         <v>0.003777812410372822</v>
       </c>
     </row>
@@ -5340,45 +5489,48 @@
         <v>17.01666666666667</v>
       </c>
       <c r="Q50" t="n">
+        <v>0.3666068222621185</v>
+      </c>
+      <c r="R50" t="n">
         <v>33.08366238246173</v>
       </c>
-      <c r="R50" t="n">
+      <c r="S50" t="n">
         <v>0.2916972101212668</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>31.95385449141603</v>
       </c>
-      <c r="T50" t="n">
+      <c r="U50" t="n">
         <v>2.286115561084218</v>
       </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
         <v>0.01177717880123003</v>
       </c>
-      <c r="V50" t="n">
+      <c r="W50" t="n">
         <v>0.1833455418032794</v>
       </c>
-      <c r="W50" t="n">
+      <c r="X50" t="n">
         <v>0.01380666666666667</v>
       </c>
-      <c r="X50" t="n">
+      <c r="Y50" t="n">
         <v>0.006903333333333334</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="Z50" t="n">
         <v>31.55039960381982</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AA50" t="n">
         <v>0.01496737650102324</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AB50" t="n">
         <v>0.0001330031843039391</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AC50" t="n">
         <v>0.004427144891717553</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AD50" t="n">
         <v>0.0001359515592164647</v>
       </c>
-      <c r="AD50" t="n">
+      <c r="AE50" t="n">
         <v>0.004344176341084042</v>
       </c>
     </row>
@@ -5438,45 +5590,48 @@
         <v>20.05</v>
       </c>
       <c r="Q51" t="n">
+        <v>0.4319569120287253</v>
+      </c>
+      <c r="R51" t="n">
         <v>33.286006759061</v>
       </c>
-      <c r="R51" t="n">
+      <c r="S51" t="n">
         <v>0.2947411967231239</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>32.83159453257377</v>
       </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
         <v>2.307975805166663</v>
       </c>
-      <c r="U51" t="n">
+      <c r="V51" t="n">
         <v>0.01235152301479269</v>
       </c>
-      <c r="V51" t="n">
+      <c r="W51" t="n">
         <v>0.1918565388801183</v>
       </c>
-      <c r="W51" t="n">
+      <c r="X51" t="n">
         <v>0.01502</v>
       </c>
-      <c r="X51" t="n">
+      <c r="Y51" t="n">
         <v>0.007509999999999999</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="Z51" t="n">
         <v>31.95385449141603</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="AA51" t="n">
         <v>0.01393403278476044</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AB51" t="n">
         <v>0.0002001166067567213</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AC51" t="n">
         <v>0.006989072490978496</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AD51" t="n">
         <v>0.0002310196494435036</v>
       </c>
-      <c r="AD51" t="n">
+      <c r="AE51" t="n">
         <v>0.00758474345958644</v>
       </c>
     </row>
@@ -5536,45 +5691,48 @@
         <v>23.05</v>
       </c>
       <c r="Q52" t="n">
+        <v>0.4965888689407542</v>
+      </c>
+      <c r="R52" t="n">
         <v>34.92500000000002</v>
       </c>
-      <c r="R52" t="n">
+      <c r="S52" t="n">
         <v>0.3061500936386944</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>33.75408934834246</v>
       </c>
-      <c r="T52" t="n">
+      <c r="U52" t="n">
         <v>2.331405828596663</v>
       </c>
-      <c r="U52" t="n">
+      <c r="V52" t="n">
         <v>0.01284341417557715</v>
       </c>
-      <c r="V52" t="n">
+      <c r="W52" t="n">
         <v>0.1986846191052666</v>
       </c>
-      <c r="W52" t="n">
+      <c r="X52" t="n">
         <v>0.01622</v>
       </c>
-      <c r="X52" t="n">
+      <c r="Y52" t="n">
         <v>0.008110000000000001</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="Z52" t="n">
         <v>32.83159453257377</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AA52" t="n">
         <v>0.01157922320647989</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AB52" t="n">
         <v>0.0003444698247772432</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AC52" t="n">
         <v>0.01216839656025612</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AD52" t="n">
         <v>0.0004041724259929835</v>
       </c>
-      <c r="AD52" t="n">
+      <c r="AE52" t="n">
         <v>0.0136424721791035</v>
       </c>
     </row>
@@ -5634,45 +5792,48 @@
         <v>25.71666666666666</v>
       </c>
       <c r="Q53" t="n">
+        <v>0.5540394973070017</v>
+      </c>
+      <c r="R53" t="n">
         <v>35.32500000000002</v>
       </c>
-      <c r="R53" t="n">
+      <c r="S53" t="n">
         <v>0.3308651428571041</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>34.61647934279947</v>
       </c>
-      <c r="T53" t="n">
+      <c r="U53" t="n">
         <v>2.353743628712218</v>
       </c>
-      <c r="U53" t="n">
+      <c r="V53" t="n">
         <v>0.01322035169194992</v>
       </c>
-      <c r="V53" t="n">
+      <c r="W53" t="n">
         <v>0.2034072317266347</v>
       </c>
-      <c r="W53" t="n">
+      <c r="X53" t="n">
         <v>0.01728666666666667</v>
       </c>
-      <c r="X53" t="n">
+      <c r="Y53" t="n">
         <v>0.008643333333333333</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="Z53" t="n">
         <v>33.75408934834246</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="AA53" t="n">
         <v>0.009267599997966548</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AB53" t="n">
         <v>0.0005343022972248991</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AC53" t="n">
         <v>0.01961652719811411</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AD53" t="n">
         <v>0.000618736018383067</v>
       </c>
-      <c r="AD53" t="n">
+      <c r="AE53" t="n">
         <v>0.02141846259900344</v>
       </c>
     </row>
@@ -5732,45 +5893,48 @@
         <v>28.41666666666666</v>
       </c>
       <c r="Q54" t="n">
+        <v>0.6122082585278277</v>
+      </c>
+      <c r="R54" t="n">
         <v>36.71428571428564</v>
       </c>
-      <c r="R54" t="n">
+      <c r="S54" t="n">
         <v>0.3724108962071924</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>35.52745852239852</v>
       </c>
-      <c r="T54" t="n">
+      <c r="U54" t="n">
         <v>2.377809652778218</v>
       </c>
-      <c r="U54" t="n">
+      <c r="V54" t="n">
         <v>0.01354761888358153</v>
       </c>
-      <c r="V54" t="n">
+      <c r="W54" t="n">
         <v>0.2068914320190001</v>
       </c>
-      <c r="W54" t="n">
+      <c r="X54" t="n">
         <v>0.01836666666666667</v>
       </c>
-      <c r="X54" t="n">
+      <c r="Y54" t="n">
         <v>0.009183333333333333</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="Z54" t="n">
         <v>34.61647934279947</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AA54" t="n">
         <v>0.006196243412663805</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AB54" t="n">
         <v>0.0008109233377192746</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AC54" t="n">
         <v>0.02963924799363945</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AD54" t="n">
         <v>0.0008844102245227135</v>
       </c>
-      <c r="AD54" t="n">
+      <c r="AE54" t="n">
         <v>0.03142084756851587</v>
       </c>
     </row>
@@ -5830,45 +5994,48 @@
         <v>36.41666666666666</v>
       </c>
       <c r="Q55" t="n">
+        <v>0.7845601436265709</v>
+      </c>
+      <c r="R55" t="n">
         <v>36.54999999999995</v>
       </c>
-      <c r="R55" t="n">
+      <c r="S55" t="n">
         <v>0.4370511859323505</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>38.42283179752014</v>
       </c>
-      <c r="T55" t="n">
+      <c r="U55" t="n">
         <v>2.457676399311551</v>
       </c>
-      <c r="U55" t="n">
+      <c r="V55" t="n">
         <v>0.01423124238248902</v>
       </c>
-      <c r="V55" t="n">
+      <c r="W55" t="n">
         <v>0.2096355868065772</v>
       </c>
-      <c r="W55" t="n">
+      <c r="X55" t="n">
         <v>0.02156666666666666</v>
       </c>
-      <c r="X55" t="n">
+      <c r="Y55" t="n">
         <v>0.01078333333333333</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="Z55" t="n">
         <v>35.52745852239852</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AA55" t="n">
         <v>0.01541414394739185</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AB55" t="n">
         <v>0.001781396691915808</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AC55" t="n">
         <v>0.06671966824328958</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AD55" t="n">
         <v>0.001733285414237923</v>
       </c>
-      <c r="AD55" t="n">
+      <c r="AE55" t="n">
         <v>0.06659773392835873</v>
       </c>
     </row>
@@ -5928,38 +6095,38 @@
         <v>0.08333333333333215</v>
       </c>
       <c r="Q56" t="n">
+        <v>0.002267573696145093</v>
+      </c>
+      <c r="R56" t="n">
         <v>21.79285714285717</v>
       </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
         <v>28.31815807004039</v>
       </c>
-      <c r="T56" t="n">
+      <c r="U56" t="n">
         <v>2.196892806206484</v>
       </c>
-      <c r="U56" t="n">
+      <c r="V56" t="n">
         <v>0.01041196717294989</v>
       </c>
-      <c r="V56" t="n">
+      <c r="W56" t="n">
         <v>0.2041873938903916</v>
       </c>
-      <c r="W56" t="n">
+      <c r="X56" t="n">
         <v>0.007033333333333333</v>
       </c>
-      <c r="X56" t="n">
+      <c r="Y56" t="n">
         <v>0.003516666666666667</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="Z56" t="n">
         <v>25.42114791934122</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AA56" t="n">
         <v>0.04417757490269928</v>
       </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
       <c r="AB56" t="n">
         <v>0</v>
       </c>
@@ -5967,6 +6134,9 @@
         <v>0</v>
       </c>
       <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6026,38 +6196,38 @@
         <v>1.200000000000001</v>
       </c>
       <c r="Q57" t="n">
+        <v>0.03265306122448983</v>
+      </c>
+      <c r="R57" t="n">
         <v>22.74159954433088</v>
       </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
       <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
         <v>28.49544506515976</v>
       </c>
-      <c r="T57" t="n">
+      <c r="U57" t="n">
         <v>2.200944449147011</v>
       </c>
-      <c r="U57" t="n">
+      <c r="V57" t="n">
         <v>0.01098357032200971</v>
       </c>
-      <c r="V57" t="n">
+      <c r="W57" t="n">
         <v>0.2161387857045839</v>
       </c>
-      <c r="W57" t="n">
+      <c r="X57" t="n">
         <v>0.007480000000000001</v>
       </c>
-      <c r="X57" t="n">
+      <c r="Y57" t="n">
         <v>0.00374</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="Z57" t="n">
         <v>28.31815807004039</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AA57" t="n">
         <v>0.02615548495855645</v>
       </c>
-      <c r="AA57" t="n">
-        <v>0</v>
-      </c>
       <c r="AB57" t="n">
         <v>0</v>
       </c>
@@ -6065,6 +6235,9 @@
         <v>0</v>
       </c>
       <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6124,38 +6297,38 @@
         <v>2.666666666666666</v>
       </c>
       <c r="Q58" t="n">
+        <v>0.07256235827664398</v>
+      </c>
+      <c r="R58" t="n">
         <v>22.97108767528296</v>
       </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
         <v>28.74377626618266</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U58" t="n">
         <v>2.2066448992919</v>
       </c>
-      <c r="U58" t="n">
+      <c r="V58" t="n">
         <v>0.01171780391374263</v>
       </c>
-      <c r="V58" t="n">
+      <c r="W58" t="n">
         <v>0.2317374616169707</v>
       </c>
-      <c r="W58" t="n">
+      <c r="X58" t="n">
         <v>0.008066666666666666</v>
       </c>
-      <c r="X58" t="n">
+      <c r="Y58" t="n">
         <v>0.004033333333333333</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="Z58" t="n">
         <v>28.49544506515976</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AA58" t="n">
         <v>0.02647932083128075</v>
       </c>
-      <c r="AA58" t="n">
-        <v>0</v>
-      </c>
       <c r="AB58" t="n">
         <v>0</v>
       </c>
@@ -6163,6 +6336,9 @@
         <v>0</v>
       </c>
       <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6222,38 +6398,38 @@
         <v>3.849999999999998</v>
       </c>
       <c r="Q59" t="n">
+        <v>0.1047619047619047</v>
+      </c>
+      <c r="R59" t="n">
         <v>24.12500000000008</v>
       </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
       <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
         <v>28.95676810363952</v>
       </c>
-      <c r="T59" t="n">
+      <c r="U59" t="n">
         <v>2.211557709760262</v>
       </c>
-      <c r="U59" t="n">
+      <c r="V59" t="n">
         <v>0.01228108243496568</v>
       </c>
-      <c r="V59" t="n">
+      <c r="W59" t="n">
         <v>0.2438029808221922</v>
       </c>
-      <c r="W59" t="n">
+      <c r="X59" t="n">
         <v>0.008539999999999999</v>
       </c>
-      <c r="X59" t="n">
+      <c r="Y59" t="n">
         <v>0.004269999999999999</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="Z59" t="n">
         <v>28.74377626618266</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AA59" t="n">
         <v>0.02163341820285943</v>
       </c>
-      <c r="AA59" t="n">
-        <v>0</v>
-      </c>
       <c r="AB59" t="n">
         <v>0</v>
       </c>
@@ -6261,6 +6437,9 @@
         <v>0</v>
       </c>
       <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6320,38 +6499,38 @@
         <v>5.31666666666667</v>
       </c>
       <c r="Q60" t="n">
+        <v>0.144671201814059</v>
+      </c>
+      <c r="R60" t="n">
         <v>24.57500000000017</v>
       </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
         <v>29.2361661686984</v>
       </c>
-      <c r="T60" t="n">
+      <c r="U60" t="n">
         <v>2.218035494015818</v>
       </c>
-      <c r="U60" t="n">
+      <c r="V60" t="n">
         <v>0.01296737669517052</v>
       </c>
-      <c r="V60" t="n">
+      <c r="W60" t="n">
         <v>0.2588167976329628</v>
       </c>
-      <c r="W60" t="n">
+      <c r="X60" t="n">
         <v>0.009126666666666668</v>
       </c>
-      <c r="X60" t="n">
+      <c r="Y60" t="n">
         <v>0.004563333333333334</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="Z60" t="n">
         <v>28.95676810363952</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="AA60" t="n">
         <v>0.01944191146369945</v>
       </c>
-      <c r="AA60" t="n">
-        <v>0</v>
-      </c>
       <c r="AB60" t="n">
         <v>0</v>
       </c>
@@ -6359,6 +6538,9 @@
         <v>0</v>
       </c>
       <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6418,38 +6600,38 @@
         <v>7.983333333333334</v>
       </c>
       <c r="Q61" t="n">
+        <v>0.217233560090703</v>
+      </c>
+      <c r="R61" t="n">
         <v>25.06785714285721</v>
       </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
       <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
         <v>29.78688303253967</v>
       </c>
-      <c r="T61" t="n">
+      <c r="U61" t="n">
         <v>2.230915506895817</v>
       </c>
-      <c r="U61" t="n">
+      <c r="V61" t="n">
         <v>0.01413309295165512</v>
       </c>
-      <c r="V61" t="n">
+      <c r="W61" t="n">
         <v>0.2848807744362734</v>
       </c>
-      <c r="W61" t="n">
+      <c r="X61" t="n">
         <v>0.01019333333333333</v>
       </c>
-      <c r="X61" t="n">
+      <c r="Y61" t="n">
         <v>0.005096666666666667</v>
       </c>
-      <c r="Y61" t="n">
+      <c r="Z61" t="n">
         <v>29.2361661686984</v>
       </c>
-      <c r="Z61" t="n">
+      <c r="AA61" t="n">
         <v>0.01658310436687791</v>
       </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
       <c r="AB61" t="n">
         <v>0</v>
       </c>
@@ -6457,6 +6639,9 @@
         <v>0</v>
       </c>
       <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6516,38 +6701,38 @@
         <v>13.56666666666667</v>
       </c>
       <c r="Q62" t="n">
+        <v>0.3691609977324263</v>
+      </c>
+      <c r="R62" t="n">
         <v>25.90000000000013</v>
       </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
         <v>31.11037299665006</v>
       </c>
-      <c r="T62" t="n">
+      <c r="U62" t="n">
         <v>2.262489288469567</v>
       </c>
-      <c r="U62" t="n">
+      <c r="V62" t="n">
         <v>0.01625124162510059</v>
       </c>
-      <c r="V62" t="n">
+      <c r="W62" t="n">
         <v>0.3347092315256564</v>
       </c>
-      <c r="W62" t="n">
+      <c r="X62" t="n">
         <v>0.01242666666666667</v>
       </c>
-      <c r="X62" t="n">
+      <c r="Y62" t="n">
         <v>0.006213333333333333</v>
       </c>
-      <c r="Y62" t="n">
+      <c r="Z62" t="n">
         <v>29.78688303253967</v>
       </c>
-      <c r="Z62" t="n">
+      <c r="AA62" t="n">
         <v>0.01821926693166444</v>
       </c>
-      <c r="AA62" t="n">
-        <v>0</v>
-      </c>
       <c r="AB62" t="n">
         <v>0</v>
       </c>
@@ -6555,6 +6740,9 @@
         <v>0</v>
       </c>
       <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6614,38 +6802,38 @@
         <v>15.13333333333333</v>
       </c>
       <c r="Q63" t="n">
+        <v>0.4117913832199546</v>
+      </c>
+      <c r="R63" t="n">
         <v>27.37499999999996</v>
       </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
       <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
         <v>31.52104556228423</v>
       </c>
-      <c r="T63" t="n">
+      <c r="U63" t="n">
         <v>2.272468965115901</v>
       </c>
-      <c r="U63" t="n">
+      <c r="V63" t="n">
         <v>0.01679004299276455</v>
       </c>
-      <c r="V63" t="n">
+      <c r="W63" t="n">
         <v>0.3481790571704745</v>
       </c>
-      <c r="W63" t="n">
+      <c r="X63" t="n">
         <v>0.01305333333333333</v>
       </c>
-      <c r="X63" t="n">
+      <c r="Y63" t="n">
         <v>0.006526666666666667</v>
       </c>
-      <c r="Y63" t="n">
+      <c r="Z63" t="n">
         <v>31.11037299665006</v>
       </c>
-      <c r="Z63" t="n">
+      <c r="AA63" t="n">
         <v>0.01480594697664882</v>
       </c>
-      <c r="AA63" t="n">
-        <v>0</v>
-      </c>
       <c r="AB63" t="n">
         <v>0</v>
       </c>
@@ -6653,6 +6841,9 @@
         <v>0</v>
       </c>
       <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6712,38 +6903,38 @@
         <v>16.68333333333333</v>
       </c>
       <c r="Q64" t="n">
+        <v>0.4539682539682539</v>
+      </c>
+      <c r="R64" t="n">
         <v>28.11428571428576</v>
       </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
         <v>31.94343200509588</v>
       </c>
-      <c r="T64" t="n">
+      <c r="U64" t="n">
         <v>2.282825558805818</v>
       </c>
-      <c r="U64" t="n">
+      <c r="V64" t="n">
         <v>0.01726816390210312</v>
       </c>
-      <c r="V64" t="n">
+      <c r="W64" t="n">
         <v>0.360274340850948</v>
       </c>
-      <c r="W64" t="n">
+      <c r="X64" t="n">
         <v>0.01367333333333333</v>
       </c>
-      <c r="X64" t="n">
+      <c r="Y64" t="n">
         <v>0.006836666666666666</v>
       </c>
-      <c r="Y64" t="n">
+      <c r="Z64" t="n">
         <v>31.52104556228423</v>
       </c>
-      <c r="Z64" t="n">
+      <c r="AA64" t="n">
         <v>0.01899552184075797</v>
       </c>
-      <c r="AA64" t="n">
-        <v>0</v>
-      </c>
       <c r="AB64" t="n">
         <v>0</v>
       </c>
@@ -6751,6 +6942,9 @@
         <v>0</v>
       </c>
       <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6810,38 +7004,38 @@
         <v>18.15</v>
       </c>
       <c r="Q65" t="n">
+        <v>0.4938775510204081</v>
+      </c>
+      <c r="R65" t="n">
         <v>28.14285714285706</v>
       </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
       <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
         <v>32.3574018720367</v>
       </c>
-      <c r="T65" t="n">
+      <c r="U65" t="n">
         <v>2.293067791270262</v>
       </c>
-      <c r="U65" t="n">
+      <c r="V65" t="n">
         <v>0.01769926440963473</v>
       </c>
-      <c r="V65" t="n">
+      <c r="W65" t="n">
         <v>0.3714798347284995</v>
       </c>
-      <c r="W65" t="n">
+      <c r="X65" t="n">
         <v>0.01426</v>
       </c>
-      <c r="X65" t="n">
+      <c r="Y65" t="n">
         <v>0.007129999999999999</v>
       </c>
-      <c r="Y65" t="n">
+      <c r="Z65" t="n">
         <v>31.94343200509588</v>
       </c>
-      <c r="Z65" t="n">
+      <c r="AA65" t="n">
         <v>0.02233579751349438</v>
       </c>
-      <c r="AA65" t="n">
-        <v>0</v>
-      </c>
       <c r="AB65" t="n">
         <v>0</v>
       </c>
@@ -6849,6 +7043,9 @@
         <v>0</v>
       </c>
       <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6908,38 +7105,38 @@
         <v>21.18333333333333</v>
       </c>
       <c r="Q66" t="n">
+        <v>0.5764172335600906</v>
+      </c>
+      <c r="R66" t="n">
         <v>29.46071428571427</v>
       </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
         <v>33.25583249482232</v>
       </c>
-      <c r="T66" t="n">
+      <c r="U66" t="n">
         <v>2.315615591595817</v>
       </c>
-      <c r="U66" t="n">
+      <c r="V66" t="n">
         <v>0.01851308273432502</v>
       </c>
-      <c r="V66" t="n">
+      <c r="W66" t="n">
         <v>0.3934469053539372</v>
       </c>
-      <c r="W66" t="n">
+      <c r="X66" t="n">
         <v>0.01547333333333333</v>
       </c>
-      <c r="X66" t="n">
+      <c r="Y66" t="n">
         <v>0.007736666666666666</v>
       </c>
-      <c r="Y66" t="n">
+      <c r="Z66" t="n">
         <v>32.3574018720367</v>
       </c>
-      <c r="Z66" t="n">
+      <c r="AA66" t="n">
         <v>0.01014663618242141</v>
       </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
       <c r="AB66" t="n">
         <v>0</v>
       </c>
@@ -6947,6 +7144,9 @@
         <v>0</v>
       </c>
       <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7006,38 +7206,38 @@
         <v>24.18333333333334</v>
       </c>
       <c r="Q67" t="n">
+        <v>0.6580498866213152</v>
+      </c>
+      <c r="R67" t="n">
         <v>30.54107142857147</v>
       </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
       <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
         <v>34.19735342816631</v>
       </c>
-      <c r="T67" t="n">
+      <c r="U67" t="n">
         <v>2.339725615705817</v>
       </c>
-      <c r="U67" t="n">
+      <c r="V67" t="n">
         <v>0.01919070522193477</v>
       </c>
-      <c r="V67" t="n">
+      <c r="W67" t="n">
         <v>0.4125744318193387</v>
       </c>
-      <c r="W67" t="n">
+      <c r="X67" t="n">
         <v>0.01667333333333334</v>
       </c>
-      <c r="X67" t="n">
+      <c r="Y67" t="n">
         <v>0.008336666666666668</v>
       </c>
-      <c r="Y67" t="n">
+      <c r="Z67" t="n">
         <v>33.25583249482232</v>
       </c>
-      <c r="Z67" t="n">
+      <c r="AA67" t="n">
         <v>0.00902987934884078</v>
       </c>
-      <c r="AA67" t="n">
-        <v>0</v>
-      </c>
       <c r="AB67" t="n">
         <v>0</v>
       </c>
@@ -7045,6 +7245,9 @@
         <v>0</v>
       </c>
       <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7104,38 +7307,38 @@
         <v>25.7</v>
       </c>
       <c r="Q68" t="n">
+        <v>0.6993197278911566</v>
+      </c>
+      <c r="R68" t="n">
         <v>30.00357142857132</v>
       </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
         <v>34.69219227608998</v>
       </c>
-      <c r="T68" t="n">
+      <c r="U68" t="n">
         <v>2.352599600802012</v>
       </c>
-      <c r="U68" t="n">
+      <c r="V68" t="n">
         <v>0.01948896483444288</v>
       </c>
-      <c r="V68" t="n">
+      <c r="W68" t="n">
         <v>0.4212984636054069</v>
       </c>
-      <c r="W68" t="n">
+      <c r="X68" t="n">
         <v>0.01728</v>
       </c>
-      <c r="X68" t="n">
+      <c r="Y68" t="n">
         <v>0.00864</v>
       </c>
-      <c r="Y68" t="n">
+      <c r="Z68" t="n">
         <v>34.19735342816631</v>
       </c>
-      <c r="Z68" t="n">
+      <c r="AA68" t="n">
         <v>0.01371968923896166</v>
       </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
       <c r="AB68" t="n">
         <v>0</v>
       </c>
@@ -7143,6 +7346,9 @@
         <v>0</v>
       </c>
       <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7202,38 +7408,38 @@
         <v>26.75</v>
       </c>
       <c r="Q69" t="n">
+        <v>0.7278911564625851</v>
+      </c>
+      <c r="R69" t="n">
         <v>30.12857142857151</v>
       </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
       <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
         <v>35.04183579224857</v>
       </c>
-      <c r="T69" t="n">
+      <c r="U69" t="n">
         <v>2.361781859984262</v>
       </c>
-      <c r="U69" t="n">
+      <c r="V69" t="n">
         <v>0.01970497485318354</v>
       </c>
-      <c r="V69" t="n">
+      <c r="W69" t="n">
         <v>0.4278830060214355</v>
       </c>
-      <c r="W69" t="n">
+      <c r="X69" t="n">
         <v>0.0177</v>
       </c>
-      <c r="X69" t="n">
+      <c r="Y69" t="n">
         <v>0.00885</v>
       </c>
-      <c r="Y69" t="n">
+      <c r="Z69" t="n">
         <v>34.69219227608998</v>
       </c>
-      <c r="Z69" t="n">
+      <c r="AA69" t="n">
         <v>0.0224321685275548</v>
       </c>
-      <c r="AA69" t="n">
-        <v>0</v>
-      </c>
       <c r="AB69" t="n">
         <v>0</v>
       </c>
@@ -7241,6 +7447,9 @@
         <v>0</v>
       </c>
       <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/processed/BR_processed_ind.xlsx
+++ b/data/processed/BR_processed_ind.xlsx
@@ -563,20 +563,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR02 T = 27°C </t>
+          <t xml:space="preserve">BR02 T = 28°C </t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>8.000000000000002</v>
       </c>
       <c r="D2" t="n">
-        <v>19.05262902677044</v>
+        <v>21.90414778532685</v>
       </c>
       <c r="E2" t="n">
-        <v>2.049747697602164</v>
+        <v>2.649441600808605</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1887704590557334</v>
+        <v>-1.295412204256244</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -591,13 +591,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.661753679825134</v>
+        <v>1.732544197577736</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02116585337266269</v>
+        <v>0.03515241974005306</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.003688629944443481</v>
+        <v>-0.031181254695054</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -606,36 +606,36 @@
         <v>0.03252295278732637</v>
       </c>
       <c r="P2" t="n">
-        <v>0.06210425234447112</v>
+        <v>0.05443836246253775</v>
       </c>
       <c r="Q2" t="n">
-        <v>34.10634806072469</v>
+        <v>36.93</v>
       </c>
       <c r="R2" t="n">
-        <v>-1.129238752531311</v>
+        <v>-2.423755890127565</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.07261435880592892</v>
+        <v>-2.832949004219552</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U2" t="n">
-        <v>0.1203205153263328</v>
+        <v>0.1412456392075651</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001707006037939912</v>
+        <v>0.001484785124081059</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001707006037939912</v>
+        <v>0.001484785124081059</v>
       </c>
       <c r="X2" t="n">
         <v>0.03252295278732637</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.292422142822466</v>
+        <v>3.093865355235462</v>
       </c>
     </row>
     <row r="3">
@@ -646,20 +646,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR02 T = 27°C </t>
+          <t xml:space="preserve">BR02 T = 28°C </t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>9.283333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>21.52662588935287</v>
+        <v>24.05923551807384</v>
       </c>
       <c r="E3" t="n">
-        <v>1.797410283781123</v>
+        <v>1.141303698996739</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.203338151244387</v>
+        <v>-0.8593776337987036</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -674,51 +674,51 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1.685805576420896</v>
+        <v>1.747560645109918</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0157369463273454</v>
+        <v>-0.001525725957827073</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.004693089628969995</v>
+        <v>-0.02106598609327475</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1812276192202432</v>
+        <v>0.1342631518511158</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1339063422267454</v>
+        <v>0.1030262922903092</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02967253657757675</v>
+        <v>0.02803753103562011</v>
       </c>
       <c r="Q3" t="n">
-        <v>32.60219692482897</v>
+        <v>27.99</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.176680051674746</v>
+        <v>-4.011728271728281</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.006513322326042292</v>
+        <v>0.2567126075990498</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.09283204550952165</v>
+        <v>0.04656417835443825</v>
       </c>
       <c r="V3" t="n">
-        <v>0.006299087349346905</v>
+        <v>0.004277320963704851</v>
       </c>
       <c r="W3" t="n">
-        <v>0.005517556110707368</v>
+        <v>0.004017468428302058</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1355980968137462</v>
+        <v>0.1029090724521696</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.998360714226853</v>
+        <v>1.120298533735026</v>
       </c>
     </row>
     <row r="4">
@@ -729,20 +729,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR02 T = 27°C </t>
+          <t xml:space="preserve">BR02 T = 28°C </t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>11.03333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>24.36096103771159</v>
+        <v>24.77268809228702</v>
       </c>
       <c r="E4" t="n">
-        <v>1.425552212805243</v>
+        <v>0.3909939650415275</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2214956341316789</v>
+        <v>-0.226662046390678</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -757,51 +757,51 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1.706174707848912</v>
+        <v>1.713326541501377</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006419696128146302</v>
+        <v>-0.02045914131039706</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.005945069647257308</v>
+        <v>-0.005871871669710796</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3328214823492746</v>
+        <v>0.310754475196559</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06811991192267786</v>
+        <v>0.08789846497755463</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.02167241116099959</v>
+        <v>-0.007010515913380644</v>
       </c>
       <c r="Q4" t="n">
-        <v>30.53199560014573</v>
+        <v>28.02</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.115404229500459</v>
+        <v>0.002969628796401835</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07587642226584537</v>
+        <v>1.255370959962038</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.06228052246697103</v>
+        <v>0.003842087191651498</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002847678888626873</v>
+        <v>0.003398407529152446</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001996797194064146</v>
+        <v>0.003350211476126097</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06937219445375307</v>
+        <v>0.08418768973017335</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.517213381226203</v>
+        <v>0.09517882762215352</v>
       </c>
     </row>
     <row r="5">
@@ -812,20 +812,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR02 T = 27°C </t>
+          <t xml:space="preserve">BR02 T = 28°C </t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>13.15</v>
       </c>
       <c r="D5" t="n">
-        <v>26.88153533147904</v>
+        <v>25.55755469146949</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9336647696916227</v>
+        <v>0.4285991589614797</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2434697029466248</v>
+        <v>0.01374980761621421</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -840,51 +840,51 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1.706399528797393</v>
+        <v>1.667725417950852</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.007753705476298056</v>
+        <v>-0.02022226065842669</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.007460207799806062</v>
+        <v>-3.482416462333333e-06</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4296325009568908</v>
+        <v>0.4636426472540663</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06300394549100846</v>
+        <v>0.07724272848791154</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01717396136316476</v>
+        <v>0.0089492289119854</v>
       </c>
       <c r="Q5" t="n">
-        <v>28.34404134021948</v>
+        <v>27.99</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.850186782877107</v>
+        <v>0.0008267716535437231</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1755839603946379</v>
+        <v>-0.0008032708150662968</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.03018867054836238</v>
+        <v>0.004644306008744943</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002271140336988443</v>
+        <v>0.002802332196263887</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001788651748880595</v>
+        <v>0.002718079287151608</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06105173921150204</v>
+        <v>0.07162075836968011</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.8115178139561839</v>
+        <v>0.1186971048224192</v>
       </c>
     </row>
     <row r="6">
@@ -895,20 +895,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR02 T = 27°C </t>
+          <t xml:space="preserve">BR02 T = 28°C </t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>15.15</v>
       </c>
       <c r="D6" t="n">
-        <v>28.26289750462441</v>
+        <v>26.52397387472312</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4257831252853226</v>
+        <v>0.4485086783228001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2640612010484938</v>
+        <v>-0.01280234260742574</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -923,51 +923,51 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.67603872553432</v>
+        <v>1.629778365432976</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.02411811330320823</v>
+        <v>-0.02044729390490119</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.008880016059032788</v>
+        <v>-0.001959573974700634</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5882699158161641</v>
+        <v>0.6275997817476178</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1343741423177349</v>
+        <v>0.1215665755293277</v>
       </c>
       <c r="P6" t="n">
-        <v>0.05357618676949637</v>
+        <v>0.04451854124995235</v>
       </c>
       <c r="Q6" t="n">
-        <v>26.99042505643214</v>
+        <v>28.02</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.4039932633865915</v>
+        <v>-0.0003846153846156497</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2690180712737683</v>
+        <v>-0.001597293035547397</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>0.0006751411795002851</v>
+        <v>0.004363500136320473</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00445492071987811</v>
+        <v>0.004286411711977421</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00444086818882521</v>
+        <v>0.004183164297161491</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1259089676971426</v>
+        <v>0.1136926722647963</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01908144595736783</v>
+        <v>0.1157373636181149</v>
       </c>
     </row>
     <row r="7">
@@ -978,20 +978,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR02 T = 27°C </t>
+          <t xml:space="preserve">BR02 T = 28°C </t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>17.1</v>
       </c>
       <c r="D7" t="n">
-        <v>28.58953735003319</v>
+        <v>27.33259068603333</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1083775870389516</v>
+        <v>0.3802771695130964</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2845139494308431</v>
+        <v>-0.02928478232179146</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -1006,51 +1006,51 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.612015580277298</v>
+        <v>1.587104141581531</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.04276085996010182</v>
+        <v>-0.0277801809450372</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.01029025736024805</v>
+        <v>-0.006633669323007008</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9549736389167448</v>
+        <v>0.9399213047770094</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2728631382553512</v>
+        <v>0.2508832504244607</v>
       </c>
       <c r="P7" t="n">
-        <v>0.08973312654678273</v>
+        <v>0.09969346862095835</v>
       </c>
       <c r="Q7" t="n">
-        <v>26.72132748058987</v>
+        <v>27.99</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2078998691408387</v>
+        <v>-0.005384615384617319</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3618226040321808</v>
+        <v>0.002435897435898352</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>-0.03031714458434982</v>
+        <v>-0.003590733905795075</v>
       </c>
       <c r="V7" t="n">
-        <v>0.008658104107478031</v>
+        <v>0.008576982722137571</v>
       </c>
       <c r="W7" t="n">
-        <v>0.009670784849065759</v>
+        <v>0.008700461953821473</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2475311907612189</v>
+        <v>0.2344311580653662</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.8667531374406255</v>
+        <v>-0.09814406010955845</v>
       </c>
     </row>
     <row r="8">
@@ -1061,20 +1061,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR02 T = 27°C </t>
+          <t xml:space="preserve">BR02 T = 28°C </t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>18.15</v>
       </c>
       <c r="D8" t="n">
-        <v>28.31975963591092</v>
+        <v>27.71243354711543</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4131020443805529</v>
+        <v>0.352754082873016</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2966830351023522</v>
+        <v>-0.01812639682461964</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -1089,51 +1089,51 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.56150326872988</v>
+        <v>1.554601464485233</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.05397828997879961</v>
+        <v>-0.03637000496997356</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.01112933027559248</v>
+        <v>-0.01008345654633598</v>
       </c>
       <c r="N8" t="n">
-        <v>1.289430173305989</v>
+        <v>1.254639486655337</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3776630361626201</v>
+        <v>0.3744323620437509</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1112459760447468</v>
+        <v>0.1396218551781902</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.13518810480123</v>
+        <v>27.99</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6149697354540997</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4170399415131241</v>
+        <v>0.002522746071134084</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U8" t="n">
-        <v>-0.04915521729275212</v>
+        <v>-0.01066597591190639</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01176174571798969</v>
+        <v>0.01245217194545731</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01399983746620902</v>
+        <v>0.01293505824701726</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3330898116321727</v>
+        <v>0.3450799875557407</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.392063938581712</v>
+        <v>-0.2955801486738396</v>
       </c>
     </row>
     <row r="9">
@@ -1144,20 +1144,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR02 T = 27°C </t>
+          <t xml:space="preserve">BR02 T = 28°C </t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>19.16666666666667</v>
       </c>
       <c r="D9" t="n">
-        <v>27.74603925731927</v>
+        <v>28.06220633394021</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.721098087621117</v>
+        <v>0.342285434983685</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3057552701479339</v>
+        <v>-0.006786826796083723</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -1172,51 +1172,51 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.500845656383778</v>
+        <v>1.512294739366261</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.06573221031521581</v>
+        <v>-0.04849449309935661</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.01175487166085905</v>
+        <v>-0.01275168581360319</v>
       </c>
       <c r="N9" t="n">
-        <v>1.731597621365545</v>
+        <v>1.708847184073986</v>
       </c>
       <c r="O9" t="n">
-        <v>0.502021154285482</v>
+        <v>0.537994582719196</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1272841265199728</v>
+        <v>0.1704121024990759</v>
       </c>
       <c r="Q9" t="n">
-        <v>27.97777748505647</v>
+        <v>27.99</v>
       </c>
       <c r="R9" t="n">
-        <v>1.067856520773798</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4582052909683145</v>
+        <v>-3.767873678472845e-15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U9" t="n">
-        <v>-0.0697860082905714</v>
+        <v>-0.01986944509974919</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01536012929511546</v>
+        <v>0.0172187913778917</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0197153918549301</v>
+        <v>0.01842874062079043</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4261827504197734</v>
+        <v>0.4831972764674675</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.936285325641802</v>
+        <v>-0.5575804681300589</v>
       </c>
     </row>
     <row r="10">
@@ -1227,20 +1227,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR02 T = 27°C </t>
+          <t xml:space="preserve">BR02 T = 28°C </t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>20.13333333333334</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90487452637114</v>
+        <v>28.39147068543616</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.019242735030183</v>
+        <v>0.3389511543182806</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3110957244915109</v>
+        <v>-0.0001116849254426677</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
@@ -1255,51 +1255,51 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1.431726359709964</v>
+        <v>1.459091930642513</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.07727323107888129</v>
+        <v>-0.0615802835704673</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.01212310233293153</v>
+        <v>-0.0143223634369706</v>
       </c>
       <c r="N10" t="n">
-        <v>2.278560233133178</v>
+        <v>2.31276312763137</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6296256286820312</v>
+        <v>0.7114866798133201</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1367251308521974</v>
+        <v>0.1885370639025594</v>
       </c>
       <c r="Q10" t="n">
-        <v>29.22978343139038</v>
+        <v>27.99</v>
       </c>
       <c r="R10" t="n">
-        <v>1.522500609572212</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4824376513732296</v>
+        <v>-1.093301050966713e-14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U10" t="n">
-        <v>-0.09185526676327188</v>
+        <v>-0.03026604090839843</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01883104946327431</v>
+        <v>0.02162190239001286</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02661022560644812</v>
+        <v>0.02408736760693919</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5066470230092839</v>
+        <v>0.6138776078694121</v>
       </c>
       <c r="Y10" t="n">
-        <v>-2.471354426852179</v>
+        <v>-0.8592974132150057</v>
       </c>
     </row>
     <row r="11">
@@ -1310,20 +1310,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR03 T = 29°C </t>
+          <t xml:space="preserve">BR03 T = 30°C </t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>10.5</v>
       </c>
       <c r="D11" t="n">
-        <v>23.52791200490306</v>
+        <v>26.69145309571078</v>
       </c>
       <c r="E11" t="n">
-        <v>2.316544066344294</v>
+        <v>0.8134625588328568</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2375741956052722</v>
+        <v>-1.43954721797159</v>
       </c>
       <c r="G11" t="n">
         <v>1</v>
@@ -1338,51 +1338,51 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1.674751595520777</v>
+        <v>1.719501008249469</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01266188371502724</v>
+        <v>0.00318450749037974</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.004493110740924771</v>
+        <v>-0.01580984071727767</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3159644021002254</v>
+        <v>0.204463869615075</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2051548433059102</v>
+        <v>0.1538041984211156</v>
       </c>
       <c r="P11" t="n">
-        <v>0.02937649115637974</v>
+        <v>0.03270764869073212</v>
       </c>
       <c r="Q11" t="n">
-        <v>33.29067866596316</v>
+        <v>30</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.9957240944342418</v>
+        <v>-3.138731268731276</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02540418081576101</v>
+        <v>0.1665283087856843</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="U11" t="n">
-        <v>0.106019853386771</v>
+        <v>0.03232851343233704</v>
       </c>
       <c r="V11" t="n">
-        <v>0.008821168569424848</v>
+        <v>0.005776488224851725</v>
       </c>
       <c r="W11" t="n">
-        <v>0.00739739158576715</v>
+        <v>0.00552884292313</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2075436778818445</v>
+        <v>0.1541828645115554</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.494425781256671</v>
+        <v>0.8628949999332802</v>
       </c>
     </row>
     <row r="12">
@@ -1393,20 +1393,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR03 T = 29°C </t>
+          <t xml:space="preserve">BR03 T = 30°C </t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>12.25</v>
       </c>
       <c r="D12" t="n">
-        <v>27.21932846330558</v>
+        <v>26.65311597876561</v>
       </c>
       <c r="E12" t="n">
-        <v>1.813259649026344</v>
+        <v>-0.005810554401408652</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3368053623150932</v>
+        <v>-0.1637940475849494</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -1421,51 +1421,51 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1.690052953639005</v>
+        <v>1.700781977625797</v>
       </c>
       <c r="L12" t="n">
-        <v>0.003178550504756628</v>
+        <v>-0.01866294361773202</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.006330125624464644</v>
+        <v>-0.009212041269210904</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4563022093622141</v>
+        <v>0.4604525526429791</v>
       </c>
       <c r="O12" t="n">
-        <v>0.03573014900032404</v>
+        <v>0.09364511936364667</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.05227963609279587</v>
+        <v>-0.03311824047486412</v>
       </c>
       <c r="Q12" t="n">
-        <v>31.58607851272036</v>
+        <v>30.015</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.8824143255624861</v>
+        <v>0.001484814398200918</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1034613310554022</v>
+        <v>0.9812306983742416</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="U12" t="n">
-        <v>0.06849735974899573</v>
+        <v>-0.01119116119163786</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001344204172829594</v>
+        <v>0.003323907882975883</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0001959210095957637</v>
+        <v>0.003517243579328763</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03658833490199469</v>
+        <v>0.08859250230768947</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.864452133877122</v>
+        <v>-0.2982793171777847</v>
       </c>
     </row>
     <row r="13">
@@ -1476,20 +1476,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR03 T = 29°C </t>
+          <t xml:space="preserve">BR03 T = 30°C </t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>14.36666666666667</v>
       </c>
       <c r="D13" t="n">
-        <v>30.29927748512164</v>
+        <v>26.68202623302077</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9743586309066501</v>
+        <v>0.4267071201364878</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.456809695671073</v>
+        <v>0.224155456203944</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -1504,51 +1504,51 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1.682533390467791</v>
+        <v>1.640883614461325</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.01255271988981854</v>
+        <v>-0.02978437064723932</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.008551703317981583</v>
+        <v>-0.001233050891147341</v>
       </c>
       <c r="N13" t="n">
-        <v>0.418098984820363</v>
+        <v>0.5239163327854991</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0390869107452726</v>
+        <v>0.02676648632536745</v>
       </c>
       <c r="P13" t="n">
-        <v>0.05631346778219003</v>
+        <v>0.03095467918531082</v>
       </c>
       <c r="Q13" t="n">
-        <v>29.95292190655258</v>
+        <v>30</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.5643100271728168</v>
+        <v>-0.003442889476873212</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1978590549637418</v>
+        <v>0.0007682955046346132</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="U13" t="n">
-        <v>0.02469721063787212</v>
+        <v>-0.002159116125110338</v>
       </c>
       <c r="V13" t="n">
-        <v>0.001187079087101865</v>
+        <v>0.0006467522300865029</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0008462828849264338</v>
+        <v>0.0006891476685905666</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03596763865688429</v>
+        <v>0.01725665996943276</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.7483076382253857</v>
+        <v>-0.0576095930903322</v>
       </c>
     </row>
     <row r="14">
@@ -1559,20 +1559,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR03 T = 29°C </t>
+          <t xml:space="preserve">BR03 T = 30°C </t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>16.36666666666667</v>
       </c>
       <c r="D14" t="n">
-        <v>31.33951840964705</v>
+        <v>28.31600500677294</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.05355085052978126</v>
+        <v>0.9124663425295276</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5694136107073439</v>
+        <v>0.06681355908669991</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
@@ -1587,51 +1587,51 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1.640419754732038</v>
+        <v>1.578506813909641</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.03177191941127966</v>
+        <v>-0.02465141743153448</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0106362809232351</v>
+        <v>0.006253891700679903</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6042457415777299</v>
+        <v>0.5713710655667389</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2551360751442919</v>
+        <v>0.206882239222587</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1582098601898775</v>
+        <v>0.182774664945801</v>
       </c>
       <c r="Q14" t="n">
-        <v>29.21597433658841</v>
+        <v>30</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.07868912733376909</v>
+        <v>0.003945061367620184</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2864354670426333</v>
+        <v>-0.000879830493848421</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="U14" t="n">
-        <v>-0.02107689674990086</v>
+        <v>0.01660748072661906</v>
       </c>
       <c r="V14" t="n">
-        <v>0.007767603226448825</v>
+        <v>0.006991070313086991</v>
       </c>
       <c r="W14" t="n">
-        <v>0.008173979129879452</v>
+        <v>0.006655958281680099</v>
       </c>
       <c r="X14" t="n">
-        <v>0.2434329443141267</v>
+        <v>0.1979591819880729</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0.6605397937117481</v>
+        <v>0.4702575074048302</v>
       </c>
     </row>
     <row r="15">
@@ -1642,20 +1642,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR03 T = 29°C </t>
+          <t xml:space="preserve">BR03 T = 30°C </t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>18.3</v>
       </c>
       <c r="D15" t="n">
-        <v>30.1638588229373</v>
+        <v>30.25854242389568</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.258063630476993</v>
+        <v>0.7125913349319077</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.654828821212973</v>
+        <v>-0.2315382207953283</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1670,51 +1670,51 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1.558968709652448</v>
+        <v>1.543064301479925</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.05425414887990376</v>
+        <v>-0.005669191047846911</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.01221752820856005</v>
+        <v>0.01193307947419959</v>
       </c>
       <c r="N15" t="n">
-        <v>1.400385993478641</v>
+        <v>1.313639501511926</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6547991799333863</v>
+        <v>0.7335239672869962</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2355029259279834</v>
+        <v>0.3299149962450657</v>
       </c>
       <c r="Q15" t="n">
-        <v>29.60541735059252</v>
+        <v>30.015</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5566164187276215</v>
+        <v>-0.006303879310344485</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3536247195754161</v>
+        <v>-0.01125986265341659</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="U15" t="n">
-        <v>-0.07650895594378182</v>
+        <v>0.01987610556165762</v>
       </c>
       <c r="V15" t="n">
-        <v>0.02009238673417443</v>
+        <v>0.02408237874456443</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0236443881842632</v>
+        <v>0.02321948068965366</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6060639168654957</v>
+        <v>0.7286976789107263</v>
       </c>
       <c r="Y15" t="n">
-        <v>-2.307805345778565</v>
+        <v>0.601421983359246</v>
       </c>
     </row>
     <row r="16">
@@ -1725,20 +1725,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR03 T = 29°C </t>
+          <t xml:space="preserve">BR03 T = 30°C </t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>19.36666666666667</v>
       </c>
       <c r="D16" t="n">
-        <v>28.43941682599761</v>
+        <v>30.84669647792873</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.975265113784928</v>
+        <v>0.3901975163800557</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6899239599894009</v>
+        <v>-0.3729501889893923</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
@@ -1753,51 +1753,51 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1.493962398474742</v>
+        <v>1.544469496775293</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.06763268457829597</v>
+        <v>0.008303932226661814</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.01286722622592525</v>
+        <v>0.01426652666550419</v>
       </c>
       <c r="N16" t="n">
-        <v>2.241846818663709</v>
+        <v>2.301801978160599</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9229398672886127</v>
+        <v>1.11928067642926</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2672608628630645</v>
+        <v>0.3933788333966759</v>
       </c>
       <c r="Q16" t="n">
-        <v>30.40816722370049</v>
+        <v>30</v>
       </c>
       <c r="R16" t="n">
-        <v>0.948539593349814</v>
+        <v>-0.02182112068965125</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3812312328411926</v>
+        <v>-0.0178349649327835</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="U16" t="n">
-        <v>-0.1147258644270966</v>
+        <v>0.01802613182238104</v>
       </c>
       <c r="V16" t="n">
-        <v>0.02888420518697409</v>
+        <v>0.03668647152063631</v>
       </c>
       <c r="W16" t="n">
-        <v>0.03792791433748015</v>
+        <v>0.03534134900753256</v>
       </c>
       <c r="X16" t="n">
-        <v>0.8214499509999984</v>
+        <v>1.131656451843245</v>
       </c>
       <c r="Y16" t="n">
-        <v>-3.262736679165092</v>
+        <v>0.5560466169961201</v>
       </c>
     </row>
     <row r="17">
@@ -1815,13 +1815,13 @@
         <v>9.933333333333332</v>
       </c>
       <c r="D17" t="n">
-        <v>29.16665187820275</v>
+        <v>30.89887988078042</v>
       </c>
       <c r="E17" t="n">
-        <v>3.596862535827155</v>
+        <v>2.233794122914519</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7747942922915634</v>
+        <v>-1.703333547076863</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -1836,31 +1836,31 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.713270704685991</v>
+        <v>1.734422026025228</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0169528679198977</v>
+        <v>0.008505521406492411</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.01472281457431383</v>
+        <v>-0.02735817092336115</v>
       </c>
       <c r="N17" t="n">
         <v>0.09992942551812453</v>
       </c>
       <c r="O17" t="n">
-        <v>0.08299349804587818</v>
+        <v>0.08185682734345162</v>
       </c>
       <c r="P17" t="n">
-        <v>0.008793914571732968</v>
+        <v>0.008651385330049385</v>
       </c>
       <c r="Q17" t="n">
-        <v>34.84886841496646</v>
+        <v>32.985</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.5858100528225876</v>
+        <v>-2.231858630801907</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.001219740238408706</v>
+        <v>0.6327758308205903</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1868,19 +1868,19 @@
         </is>
       </c>
       <c r="U17" t="n">
-        <v>0.1332160954482464</v>
+        <v>0.07719764402011454</v>
       </c>
       <c r="V17" t="n">
-        <v>0.002879394701491584</v>
+        <v>0.002665044063479796</v>
       </c>
       <c r="W17" t="n">
-        <v>0.002422975913915229</v>
+        <v>0.002415380766685625</v>
       </c>
       <c r="X17" t="n">
-        <v>0.08398230287834656</v>
+        <v>0.08234687639444917</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.885467480512433</v>
+        <v>2.385320729656766</v>
       </c>
     </row>
     <row r="18">
@@ -1898,13 +1898,13 @@
         <v>11.03333333333333</v>
       </c>
       <c r="D18" t="n">
-        <v>32.65374302811206</v>
+        <v>32.44142377184905</v>
       </c>
       <c r="E18" t="n">
-        <v>2.589028428188929</v>
+        <v>0.9335646748834137</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.068801525232791</v>
+        <v>-0.875063755176267</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
@@ -1919,13 +1919,13 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1.72299862511218</v>
+        <v>1.725086923845535</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.002087151124310682</v>
+        <v>-0.02209687942287031</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.02009968437838661</v>
+        <v>-0.02349838121968312</v>
       </c>
       <c r="N18" t="n">
         <v>0.1630367842941541</v>
@@ -1934,16 +1934,16 @@
         <v>0.04467957304505052</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.02203976004903232</v>
+        <v>-0.02156544142506893</v>
       </c>
       <c r="Q18" t="n">
-        <v>34.20380484117022</v>
+        <v>33</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.5727577934578569</v>
+        <v>0.006259314456038112</v>
       </c>
       <c r="S18" t="n">
-        <v>0.02598469440410001</v>
+        <v>0.9303108769638049</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1951,19 +1951,19 @@
         </is>
       </c>
       <c r="U18" t="n">
-        <v>0.07807599196709611</v>
+        <v>0.01596779318247201</v>
       </c>
       <c r="V18" t="n">
-        <v>0.001362235217769524</v>
+        <v>0.001312865070175834</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0009724098109261872</v>
+        <v>0.001232617739754924</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0444820787448903</v>
+        <v>0.04259121209683257</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.549473378358498</v>
+        <v>0.5180179453338167</v>
       </c>
     </row>
     <row r="19">
@@ -1981,13 +1981,13 @@
         <v>11.96666666666666</v>
       </c>
       <c r="D19" t="n">
-        <v>34.61002140217309</v>
+        <v>32.94154030130098</v>
       </c>
       <c r="E19" t="n">
-        <v>1.470642417886822</v>
+        <v>0.3599284067761737</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.334812757025574</v>
+        <v>-0.3857770911210205</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
@@ -2002,13 +2002,13 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1.71239437428896</v>
+        <v>1.693684814616142</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.02305676735888673</v>
+        <v>-0.04060604047458771</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.02496455707373573</v>
+        <v>-0.01509878365217185</v>
       </c>
       <c r="N19" t="n">
         <v>0.1946876681845432</v>
@@ -2020,13 +2020,13 @@
         <v>0.0002592121117928302</v>
       </c>
       <c r="Q19" t="n">
-        <v>33.68005139719192</v>
+        <v>33</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.5373243017182112</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0505986642615168</v>
+        <v>-0.009885808030295692</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2034,19 +2034,19 @@
         </is>
       </c>
       <c r="U19" t="n">
-        <v>0.02902717272487888</v>
+        <v>-0.01304869134972544</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0009135283029927349</v>
+        <v>0.0008976812172023368</v>
       </c>
       <c r="W19" t="n">
-        <v>0.0007502451744985752</v>
+        <v>0.000974800236789819</v>
       </c>
       <c r="X19" t="n">
-        <v>0.03161723411806942</v>
+        <v>0.0295710019941917</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.004631069252633</v>
+        <v>-0.4298439919762179</v>
       </c>
     </row>
     <row r="20">
@@ -2064,13 +2064,13 @@
         <v>12.96666666666667</v>
       </c>
       <c r="D20" t="n">
-        <v>35.41062439961348</v>
+        <v>33.11299292387466</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.01046537310506324</v>
+        <v>0.2193297400873746</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.615373584809901</v>
+        <v>0.08441974228211516</v>
       </c>
       <c r="G20" t="n">
         <v>1</v>
@@ -2085,13 +2085,13 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1.676807174735472</v>
+        <v>1.645620641881095</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.05069680061989235</v>
+        <v>-0.05063433091410474</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.03009551602337785</v>
+        <v>-0.005374723070970349</v>
       </c>
       <c r="N20" t="n">
         <v>0.2292766274796824</v>
@@ -2103,13 +2103,13 @@
         <v>0.02377783591582186</v>
       </c>
       <c r="Q20" t="n">
-        <v>33.1682700624854</v>
+        <v>33</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.4731889851429276</v>
+        <v>-0.0132923076923035</v>
       </c>
       <c r="S20" t="n">
-        <v>0.07655890553296685</v>
+        <v>-0.01896714963961562</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2117,19 +2117,19 @@
         </is>
       </c>
       <c r="U20" t="n">
-        <v>-0.03052967003720434</v>
+        <v>-0.02414546328281751</v>
       </c>
       <c r="V20" t="n">
-        <v>0.001124785780717345</v>
+        <v>0.001199127514792181</v>
       </c>
       <c r="W20" t="n">
-        <v>0.001322459216384696</v>
+        <v>0.001366312353781091</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0398293668110079</v>
+        <v>0.03970670091213688</v>
       </c>
       <c r="Y20" t="n">
-        <v>-1.081074678731576</v>
+        <v>-0.7995285548276116</v>
       </c>
     </row>
     <row r="21">
@@ -2147,13 +2147,13 @@
         <v>14.05</v>
       </c>
       <c r="D21" t="n">
-        <v>34.44740806054007</v>
+        <v>33.40678925938469</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.918029250782769</v>
+        <v>0.5748685658658061</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.837226029438354</v>
+        <v>0.4562261621977117</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -2168,13 +2168,13 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6041528450346</v>
+        <v>1.587750417194559</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.08618205816494695</v>
+        <v>-0.05099546920429221</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.03415280297699776</v>
+        <v>0.002314542136478109</v>
       </c>
       <c r="N21" t="n">
         <v>0.2942203992942216</v>
@@ -2186,13 +2186,13 @@
         <v>0.04237510135172184</v>
       </c>
       <c r="Q21" t="n">
-        <v>32.70094107216561</v>
+        <v>32.97000000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.3756697087749323</v>
+        <v>-0.04050011069838533</v>
       </c>
       <c r="S21" t="n">
-        <v>0.09708687101803565</v>
+        <v>-0.02430530339071363</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2200,19 +2200,19 @@
         </is>
       </c>
       <c r="U21" t="n">
-        <v>-0.1094042727647439</v>
+        <v>-0.01490992801453295</v>
       </c>
       <c r="V21" t="n">
-        <v>0.002029848152848879</v>
+        <v>0.002283368665355401</v>
       </c>
       <c r="W21" t="n">
-        <v>0.002964286202897984</v>
+        <v>0.002414683439122582</v>
       </c>
       <c r="X21" t="n">
-        <v>0.06992300762211884</v>
+        <v>0.07628001580501038</v>
       </c>
       <c r="Y21" t="n">
-        <v>-3.768693627493764</v>
+        <v>-0.4980928230540984</v>
       </c>
     </row>
     <row r="22">
@@ -2230,13 +2230,13 @@
         <v>14.93333333333333</v>
       </c>
       <c r="D22" t="n">
-        <v>32.01207240393939</v>
+        <v>34.13331149340144</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.595938273596119</v>
+        <v>1.070087435681565</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.961813267497533</v>
+        <v>0.6650241090832518</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
@@ -2251,13 +2251,13 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>1.514256562049008</v>
+        <v>1.544449744541431</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1173566957646939</v>
+        <v>-0.04704378963297895</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.03643128215450478</v>
+        <v>0.006632656892910413</v>
       </c>
       <c r="N22" t="n">
         <v>0.3885178347028093</v>
@@ -2269,13 +2269,13 @@
         <v>0.05281889853409094</v>
       </c>
       <c r="Q22" t="n">
-        <v>32.409225627252</v>
+        <v>32.925</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.2848180910294502</v>
+        <v>-0.06138668175445616</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1086149050094711</v>
+        <v>-0.0229850461702015</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2283,19 +2283,19 @@
         </is>
       </c>
       <c r="U22" t="n">
-        <v>-0.1898318896408102</v>
+        <v>0.0008903347551768859</v>
       </c>
       <c r="V22" t="n">
-        <v>0.003050824813611427</v>
+        <v>0.00339667032848518</v>
       </c>
       <c r="W22" t="n">
-        <v>0.005354739217844569</v>
+        <v>0.00338653621268722</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0976632248250639</v>
+        <v>0.1159396063625789</v>
       </c>
       <c r="Y22" t="n">
-        <v>-6.076912195758247</v>
+        <v>0.03039007353185408</v>
       </c>
     </row>
     <row r="23">
@@ -2313,13 +2313,13 @@
         <v>9.933333333333332</v>
       </c>
       <c r="D23" t="n">
-        <v>27.57824531421593</v>
+        <v>29.27979654368249</v>
       </c>
       <c r="E23" t="n">
-        <v>3.413026118106687</v>
+        <v>1.968853614753954</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7240312558645879</v>
+        <v>-1.792138006022656</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -2334,31 +2334,31 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1.672491162543909</v>
+        <v>1.701860127957618</v>
       </c>
       <c r="L23" t="n">
-        <v>0.005483265783222335</v>
+        <v>0.001216888934549631</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.01708029869932122</v>
+        <v>-0.03386259021818812</v>
       </c>
       <c r="N23" t="n">
         <v>0.05828714481764253</v>
       </c>
       <c r="O23" t="n">
-        <v>0.06368568484117805</v>
+        <v>0.0635362589695575</v>
       </c>
       <c r="P23" t="n">
-        <v>0.01715118829495162</v>
+        <v>0.01711461552917037</v>
       </c>
       <c r="Q23" t="n">
-        <v>36.9487012151763</v>
+        <v>36.945</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.00998282862502009</v>
+        <v>-0.003671328671323693</v>
       </c>
       <c r="S23" t="n">
-        <v>0.003880678155614907</v>
+        <v>0.02811750367545162</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2366,19 +2366,19 @@
         </is>
       </c>
       <c r="U23" t="n">
-        <v>0.1270364163229965</v>
+        <v>0.0679577701438254</v>
       </c>
       <c r="V23" t="n">
-        <v>0.002316201724942602</v>
+        <v>0.002171392694003044</v>
       </c>
       <c r="W23" t="n">
-        <v>0.002047707848302962</v>
+        <v>0.002036109500216239</v>
       </c>
       <c r="X23" t="n">
-        <v>0.06387677936767718</v>
+        <v>0.06357793629684773</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.503441453194464</v>
+        <v>1.989789683373548</v>
       </c>
     </row>
     <row r="24">
@@ -2396,13 +2396,13 @@
         <v>11.03333333333333</v>
       </c>
       <c r="D24" t="n">
-        <v>30.8890301515492</v>
+        <v>30.58525753746805</v>
       </c>
       <c r="E24" t="n">
-        <v>2.465559508795357</v>
+        <v>0.8382629088769171</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.000908997567929</v>
+        <v>-0.736254002251828</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -2417,13 +2417,13 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1.668075196748551</v>
+        <v>1.680004578342074</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.01643209659049949</v>
+        <v>-0.03699830871006193</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.02281289014869143</v>
+        <v>-0.02978005869177474</v>
       </c>
       <c r="N24" t="n">
         <v>0.1229859357626406</v>
@@ -2432,16 +2432,16 @@
         <v>0.05279224712465941</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.01104749108741487</v>
+        <v>-0.01098395222704836</v>
       </c>
       <c r="Q24" t="n">
-        <v>36.94010197948825</v>
+        <v>36.96</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.004779476520646142</v>
+        <v>0.02289665284659392</v>
       </c>
       <c r="S24" t="n">
-        <v>0.005594031916006897</v>
+        <v>-0.008859523896477145</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2449,19 +2449,19 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>0.06996897407773037</v>
+        <v>0.005384674261734224</v>
       </c>
       <c r="V24" t="n">
-        <v>0.001669871818208631</v>
+        <v>0.001637513087263281</v>
       </c>
       <c r="W24" t="n">
-        <v>0.001391287488785454</v>
+        <v>0.001615860851638156</v>
       </c>
       <c r="X24" t="n">
-        <v>0.05158072094186868</v>
+        <v>0.05008375949492182</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.161273749959977</v>
+        <v>0.1646916490505168</v>
       </c>
     </row>
     <row r="25">
@@ -2479,13 +2479,13 @@
         <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>32.81007105907737</v>
+        <v>31.09951252865547</v>
       </c>
       <c r="E25" t="n">
-        <v>1.379445278346303</v>
+        <v>0.3742258271403891</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.254250910546301</v>
+        <v>-0.330239523885744</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -2500,13 +2500,13 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1.641642163320824</v>
+        <v>1.629688014760726</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.04093945598423854</v>
+        <v>-0.06157132878487714</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.02805818605139637</v>
+        <v>-0.01983885374538729</v>
       </c>
       <c r="N25" t="n">
         <v>0.1689003739429969</v>
@@ -2518,13 +2518,13 @@
         <v>-0.01312461346510742</v>
       </c>
       <c r="Q25" t="n">
-        <v>36.93806259340112</v>
+        <v>36.98999999999999</v>
       </c>
       <c r="R25" t="n">
-        <v>0.001361806494688977</v>
+        <v>-0.01371127995324173</v>
       </c>
       <c r="S25" t="n">
-        <v>0.007161743053064948</v>
+        <v>-0.02077151640995265</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2532,19 +2532,19 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>0.01710523739817718</v>
+        <v>-0.02574787930166702</v>
       </c>
       <c r="V25" t="n">
-        <v>0.001125532956094402</v>
+        <v>0.001117690791236708</v>
       </c>
       <c r="W25" t="n">
-        <v>0.001037478255215096</v>
+        <v>0.001257526630730451</v>
       </c>
       <c r="X25" t="n">
-        <v>0.03692881626879076</v>
+        <v>0.03475963876522885</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.5612240545165813</v>
+        <v>-0.8007464949285026</v>
       </c>
     </row>
     <row r="26">
@@ -2562,13 +2562,13 @@
         <v>13</v>
       </c>
       <c r="D26" t="n">
-        <v>33.56071797284095</v>
+        <v>31.3105361887845</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.009996458325007396</v>
+        <v>0.198950616907771</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.515939035342874</v>
+        <v>-0.03027597005130039</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -2583,13 +2583,13 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1.586638977703609</v>
+        <v>1.558268708782472</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.07179668889693058</v>
+        <v>-0.07563620475517907</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0334762853806582</v>
+        <v>-0.008662197311747936</v>
       </c>
       <c r="N26" t="n">
         <v>0.2034652239074256</v>
@@ -2601,13 +2601,13 @@
         <v>-0.01527016551214571</v>
       </c>
       <c r="Q26" t="n">
-        <v>36.94301562359236</v>
+        <v>36.93</v>
       </c>
       <c r="R26" t="n">
-        <v>0.009360127124882212</v>
+        <v>-0.01679442508710238</v>
       </c>
       <c r="S26" t="n">
-        <v>0.008781101582624778</v>
+        <v>0.01663001978470402</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2615,19 +2615,19 @@
         </is>
       </c>
       <c r="U26" t="n">
-        <v>-0.04554866555698327</v>
+        <v>-0.04218450406868358</v>
       </c>
       <c r="V26" t="n">
-        <v>0.0005274285157425904</v>
+        <v>0.0005439678299067449</v>
       </c>
       <c r="W26" t="n">
-        <v>0.0008035718760764139</v>
+        <v>0.0008180953476856608</v>
       </c>
       <c r="X26" t="n">
-        <v>0.01770087966767118</v>
+        <v>0.01703192442382971</v>
       </c>
       <c r="Y26" t="n">
-        <v>-1.52864591879717</v>
+        <v>-1.320819441248444</v>
       </c>
     </row>
     <row r="27">
@@ -2645,13 +2645,13 @@
         <v>14.05</v>
       </c>
       <c r="D27" t="n">
-        <v>32.71161237387202</v>
+        <v>31.50612380638622</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.741195717220425</v>
+        <v>0.3270225106538085</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.718595030692035</v>
+        <v>0.2020212066664041</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
@@ -2666,13 +2666,13 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1.492737616995946</v>
+        <v>1.474201562887973</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.1098342938925544</v>
+        <v>-0.07877505871145862</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.03767215905022527</v>
+        <v>-6.79334186669267e-06</v>
       </c>
       <c r="N27" t="n">
         <v>0.2232766122610665</v>
@@ -2684,13 +2684,13 @@
         <v>-0.01693171964649547</v>
       </c>
       <c r="Q27" t="n">
-        <v>36.95770258144282</v>
+        <v>36.96</v>
       </c>
       <c r="R27" t="n">
-        <v>0.01944329978669401</v>
+        <v>0.02240086000955444</v>
       </c>
       <c r="S27" t="n">
-        <v>0.01003516198329393</v>
+        <v>0.01044027483421081</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2698,19 +2698,19 @@
         </is>
       </c>
       <c r="U27" t="n">
-        <v>-0.1268077753086638</v>
+        <v>-0.04305609581154686</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.0002047519337856777</v>
+        <v>-6.983484559359728e-05</v>
       </c>
       <c r="W27" t="n">
-        <v>0.0006607881122285561</v>
+        <v>0.0002352937468371053</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.006697765890797801</v>
+        <v>-0.002200225291271741</v>
       </c>
       <c r="Y27" t="n">
-        <v>-4.148086791890071</v>
+        <v>-1.356530685258223</v>
       </c>
     </row>
     <row r="28">
@@ -2728,13 +2728,13 @@
         <v>14.91666666666667</v>
       </c>
       <c r="D28" t="n">
-        <v>30.53550091788435</v>
+        <v>31.89022696244574</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.280599950443424</v>
+        <v>0.5593693879450825</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.833876276745654</v>
+        <v>0.3341638947749972</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
@@ -2749,13 +2749,13 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>1.382951713242399</v>
+        <v>1.406851844785045</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.1435177916925539</v>
+        <v>-0.07664736767991442</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.04005898971900421</v>
+        <v>0.004916849568507131</v>
       </c>
       <c r="N28" t="n">
         <v>0.2251736239905764</v>
@@ -2767,13 +2767,13 @@
         <v>-0.01787689785680881</v>
       </c>
       <c r="Q28" t="n">
-        <v>36.97845615799434</v>
+        <v>36.975</v>
       </c>
       <c r="R28" t="n">
-        <v>0.02844956917837038</v>
+        <v>0.01221452460583805</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0107485366128823</v>
+        <v>-0.03394720268894091</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2781,19 +2781,19 @@
         </is>
       </c>
       <c r="U28" t="n">
-        <v>-0.2112120329044745</v>
+        <v>-0.03694101358039363</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.0009405682372076936</v>
+        <v>-0.0005525454326814507</v>
       </c>
       <c r="W28" t="n">
-        <v>0.0006169427729248541</v>
+        <v>-0.0002917087220623052</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.02872072227058839</v>
+        <v>-0.01762079925527425</v>
       </c>
       <c r="Y28" t="n">
-        <v>-6.449465224622801</v>
+        <v>-1.178057307301543</v>
       </c>
     </row>
     <row r="29">
@@ -2804,20 +2804,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR06 T = 28°C </t>
+          <t xml:space="preserve">BR06 T = 29°C </t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>10.06666666666667</v>
       </c>
       <c r="D29" t="n">
-        <v>26.4596333543246</v>
+        <v>32.1722099408478</v>
       </c>
       <c r="E29" t="n">
-        <v>2.066742217080492</v>
+        <v>0.707301664466268</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2072675256585713</v>
+        <v>-1.942919424195476</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -2832,51 +2832,51 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1.993104521533983</v>
+        <v>2.117754022569127</v>
       </c>
       <c r="L29" t="n">
-        <v>0.02034981232116895</v>
+        <v>-0.0100179557286697</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.001923588144043394</v>
+        <v>-0.03346831723782027</v>
       </c>
       <c r="N29" t="n">
-        <v>0.0426703825162681</v>
+        <v>0.04237394890341881</v>
       </c>
       <c r="O29" t="n">
-        <v>0.04098009976662615</v>
+        <v>0.0384219293607548</v>
       </c>
       <c r="P29" t="n">
-        <v>0.01268444638976645</v>
+        <v>0.01325311210845598</v>
       </c>
       <c r="Q29" t="n">
-        <v>32.38793807429549</v>
+        <v>29.01</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.4787116967393708</v>
+        <v>-2.748181818181823</v>
       </c>
       <c r="S29" t="n">
-        <v>0.0353669734395852</v>
+        <v>1.005687371927268</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U29" t="n">
-        <v>0.08831936174854695</v>
+        <v>0.01725440175726392</v>
       </c>
       <c r="V29" t="n">
-        <v>0.00156524349463937</v>
+        <v>0.001188027837066629</v>
       </c>
       <c r="W29" t="n">
-        <v>0.00142281442546305</v>
+        <v>0.001165302101415717</v>
       </c>
       <c r="X29" t="n">
-        <v>0.04141576897839946</v>
+        <v>0.03822148098967892</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.336897929954513</v>
+        <v>0.5551122357384279</v>
       </c>
     </row>
     <row r="30">
@@ -2887,20 +2887,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR06 T = 28°C </t>
+          <t xml:space="preserve">BR06 T = 29°C </t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>11.11666666666667</v>
       </c>
       <c r="D30" t="n">
-        <v>28.51501418161911</v>
+        <v>31.73988227303304</v>
       </c>
       <c r="E30" t="n">
-        <v>1.853513704911915</v>
+        <v>0.05385396511644558</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1979583307181985</v>
+        <v>0.02705240706237722</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -2915,51 +2915,51 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>2.013406418365976</v>
+        <v>2.087215716866762</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01838009446666033</v>
+        <v>-0.02582351642175973</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.00181775417484447</v>
+        <v>-0.003182449610328446</v>
       </c>
       <c r="N30" t="n">
-        <v>0.08737277022458138</v>
+        <v>0.08735887304521579</v>
       </c>
       <c r="O30" t="n">
-        <v>0.04401868345144599</v>
+        <v>0.04425864183807763</v>
       </c>
       <c r="P30" t="n">
-        <v>0.00274890516150034</v>
+        <v>0.003937378394383906</v>
       </c>
       <c r="Q30" t="n">
-        <v>31.90483917033799</v>
+        <v>28.995</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.4420972980480968</v>
+        <v>0.002695417789759347</v>
       </c>
       <c r="S30" t="n">
-        <v>0.03426544042714619</v>
+        <v>1.190800664620253</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U30" t="n">
-        <v>0.07413017963626997</v>
+        <v>-0.01067550311139266</v>
       </c>
       <c r="V30" t="n">
-        <v>0.001571673662245584</v>
+        <v>0.001360364769149424</v>
       </c>
       <c r="W30" t="n">
-        <v>0.001344531599091997</v>
+        <v>0.001389747358315305</v>
       </c>
       <c r="X30" t="n">
-        <v>0.04481629676781007</v>
+        <v>0.0431778176211845</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.113823123614211</v>
+        <v>-0.3388392119610011</v>
       </c>
     </row>
     <row r="31">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR06 T = 28°C </t>
+          <t xml:space="preserve">BR06 T = 29°C </t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>30.07500602511069</v>
+        <v>32.13344672385298</v>
       </c>
       <c r="E31" t="n">
-        <v>1.682452652395733</v>
+        <v>0.5603212606629562</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1891578845357127</v>
+        <v>0.3437661981741477</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -2998,51 +2998,51 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2.028932453543353</v>
+        <v>2.066827954913856</v>
       </c>
       <c r="L31" t="n">
-        <v>0.01681763721118634</v>
+        <v>-0.0198134799459786</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.001717704046323529</v>
+        <v>0.006538852478252349</v>
       </c>
       <c r="N31" t="n">
-        <v>0.1273297372388953</v>
+        <v>0.1275061606761601</v>
       </c>
       <c r="O31" t="n">
-        <v>0.04633914220903992</v>
+        <v>0.04653176532971432</v>
       </c>
       <c r="P31" t="n">
-        <v>0.00249952791013654</v>
+        <v>0.002447857918222877</v>
       </c>
       <c r="Q31" t="n">
-        <v>31.52769377436846</v>
+        <v>29.01</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.4122793897060433</v>
+        <v>-0.007412807318470271</v>
       </c>
       <c r="S31" t="n">
-        <v>0.03322410634226028</v>
+        <v>-0.006531296795447801</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U31" t="n">
-        <v>0.06423079848490801</v>
+        <v>0.00785090253290148</v>
       </c>
       <c r="V31" t="n">
-        <v>0.001575878881642239</v>
+        <v>0.001410039768395712</v>
       </c>
       <c r="W31" t="n">
-        <v>0.001303942420951283</v>
+        <v>0.001378887229783353</v>
       </c>
       <c r="X31" t="n">
-        <v>0.04739456686023503</v>
+        <v>0.04530943777625759</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.931741651431279</v>
+        <v>0.2522765582751521</v>
       </c>
     </row>
     <row r="32">
@@ -3053,20 +3053,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR06 T = 28°C </t>
+          <t xml:space="preserve">BR06 T = 29°C </t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>12.91666666666667</v>
       </c>
       <c r="D32" t="n">
-        <v>31.53775210576515</v>
+        <v>32.75625668859781</v>
       </c>
       <c r="E32" t="n">
-        <v>1.513334910744813</v>
+        <v>0.6570381253092883</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1800245908904757</v>
+        <v>0.04067714968584588</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -3081,51 +3081,51 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>2.043626610195375</v>
+        <v>2.051773362756858</v>
       </c>
       <c r="L32" t="n">
-        <v>0.01529169917870121</v>
+        <v>-0.01407157940694259</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.001613869856093017</v>
+        <v>0.005656133668469661</v>
       </c>
       <c r="N32" t="n">
-        <v>0.1708582719318583</v>
+        <v>0.1711895453687214</v>
       </c>
       <c r="O32" t="n">
-        <v>0.04850917966107438</v>
+        <v>0.04865626228048486</v>
       </c>
       <c r="P32" t="n">
-        <v>0.002240718797744094</v>
+        <v>0.002192943138090632</v>
       </c>
       <c r="Q32" t="n">
-        <v>31.16373324215779</v>
+        <v>28.98</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.3823300435888743</v>
+        <v>-0.008727272727270474</v>
       </c>
       <c r="S32" t="n">
-        <v>0.03214338727610669</v>
+        <v>0.003836681689712501</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U32" t="n">
-        <v>0.05546749796050444</v>
+        <v>0.01320014848713912</v>
       </c>
       <c r="V32" t="n">
-        <v>0.001578668273748277</v>
+        <v>0.001449561274254363</v>
       </c>
       <c r="W32" t="n">
-        <v>0.001278168706812331</v>
+        <v>0.001380575143152895</v>
       </c>
       <c r="X32" t="n">
-        <v>0.04978764867470937</v>
+        <v>0.04748220118532685</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.749320200605423</v>
+        <v>0.432387452172335</v>
       </c>
     </row>
     <row r="33">
@@ -3136,20 +3136,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR06 T = 28°C </t>
+          <t xml:space="preserve">BR06 T = 29°C </t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>14.16666666666667</v>
       </c>
       <c r="D33" t="n">
-        <v>33.28898650612893</v>
+        <v>33.53938799215553</v>
       </c>
       <c r="E33" t="n">
-        <v>1.295919213456481</v>
+        <v>0.5973752035511506</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1680522000833458</v>
+        <v>-0.04659673704326886</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -3164,51 +3164,51 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>2.061482785481993</v>
+        <v>2.038192318106796</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0133609354080888</v>
+        <v>-0.008037363165663169</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.001477758661942332</v>
+        <v>0.004520981411469255</v>
       </c>
       <c r="N33" t="n">
-        <v>0.233239358071672</v>
+        <v>0.233717249579028</v>
       </c>
       <c r="O33" t="n">
-        <v>0.05109429159070879</v>
+        <v>0.05118490160233635</v>
       </c>
       <c r="P33" t="n">
-        <v>0.001901458509137947</v>
+        <v>0.001858787740399326</v>
       </c>
       <c r="Q33" t="n">
-        <v>30.710907863351</v>
+        <v>29.01</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.3430518776810629</v>
+        <v>0.005052631578946531</v>
       </c>
       <c r="S33" t="n">
-        <v>0.03072672516983294</v>
+        <v>0.003652687869404902</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U33" t="n">
-        <v>0.0454105940190612</v>
+        <v>0.01386777576349243</v>
       </c>
       <c r="V33" t="n">
-        <v>0.001580281470128024</v>
+        <v>0.001498633967497358</v>
       </c>
       <c r="W33" t="n">
-        <v>0.00126211204202876</v>
+        <v>0.001401997188973545</v>
       </c>
       <c r="X33" t="n">
-        <v>0.05260596853497737</v>
+        <v>0.05026326609411727</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.511672651535827</v>
+        <v>0.4651167119199837</v>
       </c>
     </row>
     <row r="34">
@@ -3219,20 +3219,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR06 T = 28°C </t>
+          <t xml:space="preserve">BR06 T = 29°C </t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>15.75</v>
       </c>
       <c r="D34" t="n">
-        <v>35.13013826761687</v>
+        <v>34.42681055341428</v>
       </c>
       <c r="E34" t="n">
-        <v>1.041629947473309</v>
+        <v>0.5258705350722535</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1518553041124854</v>
+        <v>-0.04347434076316148</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -3247,51 +3247,51 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>2.080784456875605</v>
+        <v>2.031137146384127</v>
       </c>
       <c r="L34" t="n">
-        <v>0.01115522697107835</v>
+        <v>-0.001493627936065167</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.001293620097837387</v>
+        <v>0.003677054428447219</v>
       </c>
       <c r="N34" t="n">
-        <v>0.3165241063517814</v>
+        <v>0.3170919465744321</v>
       </c>
       <c r="O34" t="n">
-        <v>0.05377074643306822</v>
+        <v>0.05379882295871</v>
       </c>
       <c r="P34" t="n">
-        <v>0.001442488893952362</v>
+        <v>0.001406724296956905</v>
       </c>
       <c r="Q34" t="n">
-        <v>30.20626595455898</v>
+        <v>28.98</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.2957967102058623</v>
+        <v>-0.003947368421052921</v>
       </c>
       <c r="S34" t="n">
-        <v>0.02881018826999</v>
+        <v>-3.304773561734311e-05</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U34" t="n">
-        <v>0.03501167568087551</v>
+        <v>0.01453966378119044</v>
       </c>
       <c r="V34" t="n">
-        <v>0.001578919310507321</v>
+        <v>0.001555928175116516</v>
       </c>
       <c r="W34" t="n">
-        <v>0.001263462557324457</v>
+        <v>0.001422008993618066</v>
       </c>
       <c r="X34" t="n">
-        <v>0.0554676536915325</v>
+        <v>0.0535656445194559</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.229965007650116</v>
+        <v>0.5005542505053826</v>
       </c>
     </row>
     <row r="35">
@@ -3302,20 +3302,20 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR06 T = 28°C </t>
+          <t xml:space="preserve">BR06 T = 29°C </t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>17.75</v>
       </c>
       <c r="D35" t="n">
-        <v>36.90720175668704</v>
+        <v>35.39112373630353</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7600206684885604</v>
+        <v>0.4431824914069873</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.1329994186009909</v>
+        <v>-0.03983935126362285</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -3330,51 +3330,51 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>2.100479410194223</v>
+        <v>2.035633519970628</v>
       </c>
       <c r="L35" t="n">
-        <v>0.008819251402800599</v>
+        <v>0.004708907919431515</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.0010792521294772</v>
+        <v>0.00269458281162871</v>
       </c>
       <c r="N35" t="n">
-        <v>0.4270210167736385</v>
+        <v>0.4275724209378097</v>
       </c>
       <c r="O35" t="n">
-        <v>0.05602944134586357</v>
+        <v>0.05599541243227332</v>
       </c>
       <c r="P35" t="n">
-        <v>0.0009081717919122616</v>
+        <v>0.000880447129478692</v>
       </c>
       <c r="Q35" t="n">
-        <v>29.67258704870807</v>
+        <v>29.01</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.2407915269165324</v>
+        <v>0.01026315789473919</v>
       </c>
       <c r="S35" t="n">
-        <v>0.02657902000003289</v>
+        <v>0.004113573407202947</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U35" t="n">
-        <v>0.02479143201132701</v>
+        <v>0.01483565883992953</v>
       </c>
       <c r="V35" t="n">
-        <v>0.001566696073763311</v>
+        <v>0.001610135080234354</v>
       </c>
       <c r="W35" t="n">
-        <v>0.001279856053364494</v>
+        <v>0.001430900348563791</v>
       </c>
       <c r="X35" t="n">
-        <v>0.05782236808579197</v>
+        <v>0.05698448985673704</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.9149823830792355</v>
+        <v>0.5250506377135312</v>
       </c>
     </row>
     <row r="36">
@@ -3385,20 +3385,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR06 T = 28°C </t>
+          <t xml:space="preserve">BR06 T = 29°C </t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>22.08333333333333</v>
       </c>
       <c r="D36" t="n">
-        <v>38.99404843947845</v>
+        <v>36.94565770426932</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2569722062533657</v>
+        <v>0.284672487384773</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.09758305853537805</v>
+        <v>-0.0330118757323387</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
@@ -3413,51 +3413,51 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>2.129042273586917</v>
+        <v>2.079142224861755</v>
       </c>
       <c r="L36" t="n">
-        <v>0.004975621377167339</v>
+        <v>0.01256711206847716</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.0006766121606807227</v>
+        <v>0.000849240225396646</v>
       </c>
       <c r="N36" t="n">
-        <v>0.6771478546503816</v>
+        <v>0.6773094646637046</v>
       </c>
       <c r="O36" t="n">
-        <v>0.05788825870537029</v>
+        <v>0.05776533634700309</v>
       </c>
       <c r="P36" t="n">
-        <v>-9.541761063941098e-05</v>
+        <v>-0.0001080411410060017</v>
       </c>
       <c r="Q36" t="n">
-        <v>28.8737181818202</v>
+        <v>29.01</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.1342870851354352</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.02238829351479158</v>
+        <v>-0.001697894736842141</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U36" t="n">
-        <v>0.008927059885530813</v>
+        <v>0.01374954112533501</v>
       </c>
       <c r="V36" t="n">
-        <v>0.001525124253365378</v>
+        <v>0.001674330666669242</v>
       </c>
       <c r="W36" t="n">
-        <v>0.001370102148922828</v>
+        <v>0.00142226601502559</v>
       </c>
       <c r="X36" t="n">
-        <v>0.05947076901195293</v>
+        <v>0.06185924769452287</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.3481022055985135</v>
+        <v>0.5079858400074013</v>
       </c>
     </row>
     <row r="37">
@@ -3468,20 +3468,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR06 T = 28°C </t>
+          <t xml:space="preserve">BR06 T = 29°C </t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>23.75</v>
       </c>
       <c r="D37" t="n">
-        <v>39.27835609254961</v>
+        <v>37.37263356747</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1061959857035575</v>
+        <v>0.2319394611418337</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.08156260427646851</v>
+        <v>-0.02992349343528483</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
@@ -3496,51 +3496,51 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>2.136299201115189</v>
+        <v>2.101707053763695</v>
       </c>
       <c r="L37" t="n">
-        <v>0.003982793021991893</v>
+        <v>0.01336444096894196</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.0004944795194109459</v>
+        <v>3.949545837342826e-05</v>
       </c>
       <c r="N37" t="n">
-        <v>0.7737351324502386</v>
+        <v>0.7736707373393487</v>
       </c>
       <c r="O37" t="n">
-        <v>0.05739309123710379</v>
+        <v>0.05725418757268011</v>
       </c>
       <c r="P37" t="n">
-        <v>-0.00054938741692445</v>
+        <v>-0.0005551800082818237</v>
       </c>
       <c r="Q37" t="n">
-        <v>28.68200077631356</v>
+        <v>29.01</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.09837688734702521</v>
+        <v>-0.002399999999999736</v>
       </c>
       <c r="S37" t="n">
-        <v>0.02049263450736968</v>
+        <v>-0.001728000000000164</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U37" t="n">
-        <v>0.004568019268584383</v>
+        <v>0.0125649815468165</v>
       </c>
       <c r="V37" t="n">
-        <v>0.001497913972141309</v>
+        <v>0.001663619557944517</v>
       </c>
       <c r="W37" t="n">
-        <v>0.001407929631007343</v>
+        <v>0.001403505201260744</v>
       </c>
       <c r="X37" t="n">
-        <v>0.05883559839377178</v>
+        <v>0.06217384413473686</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.1794242874690855</v>
+        <v>0.4695864511311953</v>
       </c>
     </row>
     <row r="38">
@@ -3551,20 +3551,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR06 T = 28°C </t>
+          <t xml:space="preserve">BR06 T = 29°C </t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>26.25</v>
       </c>
       <c r="D38" t="n">
-        <v>39.30238878378672</v>
+        <v>37.86155950740491</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.06432379478730255</v>
+        <v>0.1635669362179168</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.05621974674767313</v>
+        <v>-0.02503796202126905</v>
       </c>
       <c r="G38" t="n">
         <v>1</v>
@@ -3579,51 +3579,51 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>2.144863570564026</v>
+        <v>2.134463944790217</v>
       </c>
       <c r="L38" t="n">
-        <v>0.003126159824818231</v>
+        <v>0.01181729755773009</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.0002063627466622074</v>
+        <v>-0.0008948971162764828</v>
       </c>
       <c r="N38" t="n">
-        <v>0.9151205776324591</v>
+        <v>0.9146965461484002</v>
       </c>
       <c r="O38" t="n">
-        <v>0.05507354668492559</v>
+        <v>0.05493439726314542</v>
       </c>
       <c r="P38" t="n">
-        <v>-0.001267525113716479</v>
+        <v>-0.001262511799616995</v>
       </c>
       <c r="Q38" t="n">
-        <v>28.49850939278458</v>
+        <v>28.995</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.05109586669988708</v>
+        <v>-0.007800000000001361</v>
       </c>
       <c r="S38" t="n">
-        <v>0.01749387957995968</v>
+        <v>0.001280265389876509</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U38" t="n">
-        <v>-0.0001791284301386807</v>
+        <v>0.009856556106216902</v>
       </c>
       <c r="V38" t="n">
-        <v>0.001435214135959239</v>
+        <v>0.001584682353749132</v>
       </c>
       <c r="W38" t="n">
-        <v>0.00143938497945073</v>
+        <v>0.001346558041265088</v>
       </c>
       <c r="X38" t="n">
-        <v>0.05640734395945655</v>
+        <v>0.05999854523680726</v>
       </c>
       <c r="Y38" t="n">
-        <v>-0.007040175203539813</v>
+        <v>0.3731845855536065</v>
       </c>
     </row>
     <row r="39">
@@ -3634,20 +3634,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR06 T = 28°C </t>
+          <t xml:space="preserve">BR06 T = 29°C </t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>27.91666666666667</v>
       </c>
       <c r="D39" t="n">
-        <v>39.11303037993883</v>
+        <v>38.09861169026139</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.1447031888682346</v>
+        <v>0.1244048305694658</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.03994946292078036</v>
+        <v>-0.02190141821751917</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
@@ -3662,51 +3662,51 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>2.149740961433483</v>
+        <v>2.152731153105458</v>
       </c>
       <c r="L39" t="n">
-        <v>0.002933655838389282</v>
+        <v>0.0100190915286118</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.13898539020796e-05</v>
+        <v>-0.001062381479664619</v>
       </c>
       <c r="N39" t="n">
-        <v>1.00526467612071</v>
+        <v>1.004613956853115</v>
       </c>
       <c r="O39" t="n">
-        <v>0.05258355228112568</v>
+        <v>0.05245843795733585</v>
       </c>
       <c r="P39" t="n">
-        <v>-0.001728574312305092</v>
+        <v>-0.001716623534717529</v>
       </c>
       <c r="Q39" t="n">
-        <v>28.43812815574222</v>
+        <v>28.98</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.02351554370983822</v>
+        <v>-0.001843707250343662</v>
       </c>
       <c r="S39" t="n">
-        <v>0.01556865888451139</v>
+        <v>0.003175124770036624</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U39" t="n">
-        <v>-0.00233496038882342</v>
+        <v>0.007919468046409125</v>
       </c>
       <c r="V39" t="n">
-        <v>0.001379473585445796</v>
+        <v>0.001499635808012634</v>
       </c>
       <c r="W39" t="n">
-        <v>0.001439485637087521</v>
+        <v>0.001290809087633514</v>
       </c>
       <c r="X39" t="n">
-        <v>0.05395539225586456</v>
+        <v>0.05713404232628472</v>
       </c>
       <c r="Y39" t="n">
-        <v>-0.09132737662400423</v>
+        <v>0.3017207378935743</v>
       </c>
     </row>
     <row r="40">
@@ -3717,20 +3717,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR06 T = 28°C </t>
+          <t xml:space="preserve">BR06 T = 29°C </t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>30.78333333333333</v>
       </c>
       <c r="D40" t="n">
-        <v>38.5449292838805</v>
+        <v>38.36734244472576</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.2184080683001701</v>
+        <v>0.06948934560510711</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.01320057451587207</v>
+        <v>-0.01674483575858813</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -3745,51 +3745,51 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>2.158186380742482</v>
+        <v>2.176811640371411</v>
       </c>
       <c r="L40" t="n">
-        <v>0.003336375811014869</v>
+        <v>0.007055161721050418</v>
       </c>
       <c r="M40" t="n">
-        <v>0.0002827117413136527</v>
+        <v>-0.0009308320182838202</v>
       </c>
       <c r="N40" t="n">
-        <v>1.148593860139766</v>
+        <v>1.147638215923621</v>
       </c>
       <c r="O40" t="n">
-        <v>0.04647168162084708</v>
+        <v>0.04639823005960539</v>
       </c>
       <c r="P40" t="n">
-        <v>-0.002486554547526137</v>
+        <v>-0.002463198348949519</v>
       </c>
       <c r="Q40" t="n">
-        <v>28.43340147458816</v>
+        <v>29.01</v>
       </c>
       <c r="R40" t="n">
-        <v>0.01628485163189808</v>
+        <v>0.005292702485967915</v>
       </c>
       <c r="S40" t="n">
-        <v>0.01240353195216592</v>
+        <v>0.0003672343035050341</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U40" t="n">
-        <v>-0.004120407828292103</v>
+        <v>0.005052211606982032</v>
       </c>
       <c r="V40" t="n">
-        <v>0.001251716182928911</v>
+        <v>0.001306261603118239</v>
       </c>
       <c r="W40" t="n">
-        <v>0.001374499522288346</v>
+        <v>0.001155140604225533</v>
       </c>
       <c r="X40" t="n">
-        <v>0.04824731175448371</v>
+        <v>0.05011778624923392</v>
       </c>
       <c r="Y40" t="n">
-        <v>-0.1588208283622667</v>
+        <v>0.1938399328282979</v>
       </c>
     </row>
     <row r="41">
@@ -3800,20 +3800,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR06 T = 28°C </t>
+          <t xml:space="preserve">BR06 T = 29°C </t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>33.71666666666666</v>
       </c>
       <c r="D41" t="n">
-        <v>37.84353444541116</v>
+        <v>38.49837843298384</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.2195790677199358</v>
+        <v>0.02761008611919902</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01280800834741792</v>
+        <v>-0.0117309675131365</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
@@ -3828,51 +3828,51 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>2.169144586160292</v>
+        <v>2.193469671369374</v>
       </c>
       <c r="L41" t="n">
-        <v>0.004592568183906354</v>
+        <v>0.004634171927431985</v>
       </c>
       <c r="M41" t="n">
-        <v>0.0005783969831938693</v>
+        <v>-0.000716498340384688</v>
       </c>
       <c r="N41" t="n">
-        <v>1.274324712045463</v>
+        <v>1.273252413771963</v>
       </c>
       <c r="O41" t="n">
-        <v>0.03811371873040176</v>
+        <v>0.03812478986921802</v>
       </c>
       <c r="P41" t="n">
-        <v>-0.00322355682807187</v>
+        <v>-0.003189110866347219</v>
       </c>
       <c r="Q41" t="n">
-        <v>28.5349992585698</v>
+        <v>29.01</v>
       </c>
       <c r="R41" t="n">
-        <v>0.04822526961388096</v>
+        <v>-8.881784197001252e-16</v>
       </c>
       <c r="S41" t="n">
-        <v>0.009326003464006791</v>
+        <v>-0.001450367332429243</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U41" t="n">
-        <v>-0.003685062044213975</v>
+        <v>0.00282988831759466</v>
       </c>
       <c r="V41" t="n">
-        <v>0.001078433927391885</v>
+        <v>0.001060169505293938</v>
       </c>
       <c r="W41" t="n">
-        <v>0.001202522908433984</v>
+        <v>0.0009665769365223807</v>
       </c>
       <c r="X41" t="n">
-        <v>0.04081175147835485</v>
+        <v>0.04081480681791529</v>
       </c>
       <c r="Y41" t="n">
-        <v>-0.1394557724036888</v>
+        <v>0.1089461113738392</v>
       </c>
     </row>
     <row r="42">
@@ -3883,20 +3883,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR06 T = 28°C </t>
+          <t xml:space="preserve">BR06 T = 29°C </t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>36.74999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>37.23874733074611</v>
+        <v>38.52861220710172</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.139300484699497</v>
+        <v>1.246305529534197e-05</v>
       </c>
       <c r="F42" t="n">
-        <v>0.04458338864639096</v>
+        <v>-0.005293057087266991</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -3911,51 +3911,51 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>2.18576298847196</v>
+        <v>2.204249697598105</v>
       </c>
       <c r="L42" t="n">
-        <v>0.006818019600986769</v>
+        <v>0.002802193816956455</v>
       </c>
       <c r="M42" t="n">
-        <v>0.0009396435401063385</v>
+        <v>-0.0004546411618555052</v>
       </c>
       <c r="N42" t="n">
-        <v>1.375039710875632</v>
+        <v>1.374160465684623</v>
       </c>
       <c r="O42" t="n">
-        <v>0.02716166643054219</v>
+        <v>0.02729488791987278</v>
       </c>
       <c r="P42" t="n">
-        <v>-0.004123972197438444</v>
+        <v>-0.004075977575900037</v>
       </c>
       <c r="Q42" t="n">
-        <v>28.72390984396326</v>
+        <v>29.01</v>
       </c>
       <c r="R42" t="n">
-        <v>0.07161212291172081</v>
+        <v>-0.003289156626505196</v>
       </c>
       <c r="S42" t="n">
-        <v>0.005566104718035283</v>
+        <v>-0.000863537809759762</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U42" t="n">
-        <v>-0.0006214544812395673</v>
+        <v>0.001271592252182027</v>
       </c>
       <c r="V42" t="n">
-        <v>0.000844572135830265</v>
+        <v>0.0007537726782938218</v>
       </c>
       <c r="W42" t="n">
-        <v>0.0008675193252890383</v>
+        <v>0.0007084201026021043</v>
       </c>
       <c r="X42" t="n">
-        <v>0.03145080836877183</v>
+        <v>0.0290418152142911</v>
       </c>
       <c r="Y42" t="n">
-        <v>-0.02314218640444016</v>
+        <v>0.04899268476987639</v>
       </c>
     </row>
     <row r="43">
@@ -3966,20 +3966,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR06 T = 28°C </t>
+          <t xml:space="preserve">BR06 T = 29°C </t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>39.24999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>37.01428708624839</v>
+        <v>38.50813227567679</v>
       </c>
       <c r="E43" t="n">
-        <v>0.009488869574260539</v>
+        <v>-0.005380082671812447</v>
       </c>
       <c r="F43" t="n">
-        <v>0.06460159320588614</v>
+        <v>-0.001030988424734784</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -3994,51 +3994,51 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>2.205567842623406</v>
+        <v>2.209706430113592</v>
       </c>
       <c r="L43" t="n">
-        <v>0.009591534160947948</v>
+        <v>0.001973230333554898</v>
       </c>
       <c r="M43" t="n">
-        <v>0.001167225630537527</v>
+        <v>-0.0002896734882714569</v>
       </c>
       <c r="N43" t="n">
-        <v>1.43049659583273</v>
+        <v>1.430093764837538</v>
       </c>
       <c r="O43" t="n">
-        <v>0.01579389492353184</v>
+        <v>0.01606302042937672</v>
       </c>
       <c r="P43" t="n">
-        <v>-0.004691225803308819</v>
+        <v>-0.004634695647620763</v>
       </c>
       <c r="Q43" t="n">
-        <v>28.92217210442974</v>
+        <v>28.995</v>
       </c>
       <c r="R43" t="n">
-        <v>0.08111011770416776</v>
+        <v>-0.004993057044509142</v>
       </c>
       <c r="S43" t="n">
-        <v>0.003197402234801932</v>
+        <v>-0.0003015479359590531</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U43" t="n">
-        <v>0.004605139139095444</v>
+        <v>0.0007532701297637439</v>
       </c>
       <c r="V43" t="n">
-        <v>0.0005947652860720422</v>
+        <v>0.0004502963104570966</v>
       </c>
       <c r="W43" t="n">
-        <v>0.0004167897965951815</v>
+        <v>0.0004223217800877304</v>
       </c>
       <c r="X43" t="n">
-        <v>0.02201481304760522</v>
+        <v>0.01734006988633109</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.1704559421665975</v>
+        <v>0.02900702579625847</v>
       </c>
     </row>
     <row r="44">
@@ -4049,20 +4049,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR06 T = 28°C </t>
+          <t xml:space="preserve">BR06 T = 29°C </t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>46.53333333333333</v>
       </c>
       <c r="D44" t="n">
-        <v>39.18984872035002</v>
+        <v>38.52861220710172</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5879193594696641</v>
+        <v>0.01100386246812946</v>
       </c>
       <c r="F44" t="n">
-        <v>0.09423515459147858</v>
+        <v>0.005530012261789766</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -4077,51 +4077,51 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>2.310852895340425</v>
+        <v>2.219633582472838</v>
       </c>
       <c r="L44" t="n">
-        <v>0.01931969312976634</v>
+        <v>0.0007527611609747797</v>
       </c>
       <c r="M44" t="n">
-        <v>0.001504122370053333</v>
+        <v>-4.546678795191661e-05</v>
       </c>
       <c r="N44" t="n">
-        <v>1.409965016559471</v>
+        <v>1.41318925985422</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.021431857195365</v>
+        <v>-0.02070498976118035</v>
       </c>
       <c r="P44" t="n">
-        <v>-0.005530948691582755</v>
+        <v>-0.005461783123241583</v>
       </c>
       <c r="Q44" t="n">
-        <v>29.55122855284597</v>
+        <v>28.98</v>
       </c>
       <c r="R44" t="n">
-        <v>0.09162849513323845</v>
+        <v>0.0008740639094950708</v>
       </c>
       <c r="S44" t="n">
-        <v>-0.0003090606066818401</v>
+        <v>0.001912656664747394</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U44" t="n">
-        <v>0.02336224443183588</v>
+        <v>0.000624739936952795</v>
       </c>
       <c r="V44" t="n">
-        <v>-0.0002460831680675573</v>
+        <v>-0.0005249533532954774</v>
       </c>
       <c r="W44" t="n">
-        <v>-0.00108660561030131</v>
+        <v>-0.0005478681617593275</v>
       </c>
       <c r="X44" t="n">
-        <v>-0.009643962129192041</v>
+        <v>-0.02022572417593911</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.9155628250514879</v>
+        <v>0.02407036276114341</v>
       </c>
     </row>
     <row r="45">
@@ -4132,20 +4132,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR07 T = 31°C </t>
+          <t xml:space="preserve">BR07 T = 32°C </t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>12.81666666666666</v>
       </c>
       <c r="D45" t="n">
-        <v>23.07455853459184</v>
+        <v>24.49794379362827</v>
       </c>
       <c r="E45" t="n">
-        <v>1.128666824053944</v>
+        <v>0.4521706072614453</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.1242303519414173</v>
+        <v>-0.06189192941126924</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -4160,51 +4160,51 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>2.158247766163844</v>
+        <v>2.290444306229041</v>
       </c>
       <c r="L45" t="n">
-        <v>0.02559331796481101</v>
+        <v>0.008260008927685192</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.002513210818926023</v>
+        <v>-0.0205553572250682</v>
       </c>
       <c r="N45" t="n">
-        <v>0.07557290267153295</v>
+        <v>0.07228700779647691</v>
       </c>
       <c r="O45" t="n">
-        <v>0.06879106637283763</v>
+        <v>0.07613253933762341</v>
       </c>
       <c r="P45" t="n">
-        <v>0.01418232536626739</v>
+        <v>0.01846914457861556</v>
       </c>
       <c r="Q45" t="n">
-        <v>34.54781185572865</v>
+        <v>31.995</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.2448447318685663</v>
+        <v>-3.384772978959054</v>
       </c>
       <c r="S45" t="n">
-        <v>0.005065559647005696</v>
+        <v>0.9130218985931944</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U45" t="n">
-        <v>0.06077228566223237</v>
+        <v>0.02206378333645542</v>
       </c>
       <c r="V45" t="n">
-        <v>0.003020089780680529</v>
+        <v>0.003118352624790683</v>
       </c>
       <c r="W45" t="n">
-        <v>0.00282105073849936</v>
+        <v>0.003053248186169309</v>
       </c>
       <c r="X45" t="n">
-        <v>0.0696872384240355</v>
+        <v>0.07639322733083535</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.402293662794117</v>
+        <v>0.5405173240512769</v>
       </c>
     </row>
     <row r="46">
@@ -4215,20 +4215,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR07 T = 31°C </t>
+          <t xml:space="preserve">BR07 T = 32°C </t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>14.25</v>
       </c>
       <c r="D46" t="n">
-        <v>24.56563399126617</v>
+        <v>25.1190264320092</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9579451973911466</v>
+        <v>0.415516544927705</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.1143977997260323</v>
+        <v>-0.02474601114727429</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
@@ -4243,51 +4243,51 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>2.19236874300675</v>
+        <v>2.281876722766255</v>
       </c>
       <c r="L46" t="n">
-        <v>0.02213954139329521</v>
+        <v>-0.00826724930615963</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.002314343712931193</v>
+        <v>-0.006194760464289825</v>
       </c>
       <c r="N46" t="n">
-        <v>0.165317460105968</v>
+        <v>0.1718540470967996</v>
       </c>
       <c r="O46" t="n">
-        <v>0.05688644421455734</v>
+        <v>0.06153739555295379</v>
       </c>
       <c r="P46" t="n">
-        <v>-0.007952724882181189</v>
+        <v>-0.01022264989225095</v>
       </c>
       <c r="Q46" t="n">
-        <v>34.20214860349939</v>
+        <v>32.01</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.2369742150707399</v>
+        <v>0.005351479915431057</v>
       </c>
       <c r="S46" t="n">
-        <v>0.005882338397482506</v>
+        <v>1.205641422530969</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U46" t="n">
-        <v>0.04909379482710192</v>
+        <v>0.01291890048475715</v>
       </c>
       <c r="V46" t="n">
-        <v>0.00238365089584549</v>
+        <v>0.002425044925870336</v>
       </c>
       <c r="W46" t="n">
-        <v>0.002053268155849222</v>
+        <v>0.002336659122449342</v>
       </c>
       <c r="X46" t="n">
-        <v>0.05855589547029404</v>
+        <v>0.06091476759174676</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.206020194964902</v>
+        <v>0.3245102027491114</v>
       </c>
     </row>
     <row r="47">
@@ -4298,20 +4298,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR07 T = 31°C </t>
+          <t xml:space="preserve">BR07 T = 32°C </t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>15.75</v>
       </c>
       <c r="D47" t="n">
-        <v>25.8732971284358</v>
+        <v>25.7143642179953</v>
       </c>
       <c r="E47" t="n">
-        <v>0.793742592062431</v>
+        <v>0.3796950830314882</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.1034520947118708</v>
+        <v>-0.02282520085588392</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
@@ -4326,51 +4326,51 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>2.222963150168166</v>
+        <v>2.265881292506861</v>
       </c>
       <c r="L47" t="n">
-        <v>0.01881757419087338</v>
+        <v>-0.009183291746274969</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.002092962668461944</v>
+        <v>0.0007310512656245724</v>
       </c>
       <c r="N47" t="n">
-        <v>0.2416585788496656</v>
+        <v>0.2517150544388291</v>
       </c>
       <c r="O47" t="n">
-        <v>0.04551121081231673</v>
+        <v>0.04614064345751816</v>
       </c>
       <c r="P47" t="n">
-        <v>-0.007132837898447432</v>
+        <v>-0.009379685711600999</v>
       </c>
       <c r="Q47" t="n">
-        <v>33.85325863109416</v>
+        <v>32.01</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.2275364886085915</v>
+        <v>-0.006428571428570784</v>
       </c>
       <c r="S47" t="n">
-        <v>0.006791585464641495</v>
+        <v>-0.00507509626236555</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U47" t="n">
-        <v>0.03914314715079918</v>
+        <v>0.01071301830702301</v>
       </c>
       <c r="V47" t="n">
-        <v>0.001838067688991994</v>
+        <v>0.00175467991656586</v>
       </c>
       <c r="W47" t="n">
-        <v>0.00147246769355232</v>
+        <v>0.001649811370585271</v>
       </c>
       <c r="X47" t="n">
-        <v>0.04755687145946718</v>
+        <v>0.04512047846057613</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.012762276774712</v>
+        <v>0.275478454620841</v>
       </c>
     </row>
     <row r="48">
@@ -4381,20 +4381,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR07 T = 31°C </t>
+          <t xml:space="preserve">BR07 T = 32°C </t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>17.75</v>
       </c>
       <c r="D48" t="n">
-        <v>27.25269475864781</v>
+        <v>26.42789631927808</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6028818928803052</v>
+        <v>0.3368600779639706</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.08993241723019343</v>
+        <v>-0.02045269624248116</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -4409,51 +4409,51 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>2.25638843921639</v>
+        <v>2.25146225148539</v>
       </c>
       <c r="L48" t="n">
-        <v>0.01495613454235645</v>
+        <v>-0.00414319927982193</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.001819522052448082</v>
+        <v>0.002513933584402321</v>
       </c>
       <c r="N48" t="n">
-        <v>0.3183266848739039</v>
+        <v>0.3250629330769729</v>
       </c>
       <c r="O48" t="n">
-        <v>0.03244727111243419</v>
+        <v>0.02974078052859898</v>
       </c>
       <c r="P48" t="n">
-        <v>-0.006120147754032986</v>
+        <v>-0.007391353161914887</v>
       </c>
       <c r="Q48" t="n">
-        <v>33.41167052408558</v>
+        <v>31.98</v>
       </c>
       <c r="R48" t="n">
-        <v>-0.2126206034840838</v>
+        <v>-0.009170040485829034</v>
       </c>
       <c r="S48" t="n">
-        <v>0.007914649450306449</v>
+        <v>-0.0006732215153267947</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U48" t="n">
-        <v>0.02875026950810264</v>
+        <v>0.0109061566477308</v>
       </c>
       <c r="V48" t="n">
-        <v>0.001268030644857107</v>
+        <v>0.001102720811710549</v>
       </c>
       <c r="W48" t="n">
-        <v>0.000932211451093103</v>
+        <v>0.0009685751640328625</v>
       </c>
       <c r="X48" t="n">
-        <v>0.03455725210890207</v>
+        <v>0.02914259128099655</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.7835223191331806</v>
+        <v>0.2882267771280351</v>
       </c>
     </row>
     <row r="49">
@@ -4464,20 +4464,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR07 T = 31°C </t>
+          <t xml:space="preserve">BR07 T = 32°C </t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>22.08333333333333</v>
       </c>
       <c r="D49" t="n">
-        <v>29.05006852467673</v>
+        <v>27.70072835809506</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2647942276042965</v>
+        <v>0.2572901866479924</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.06491682498823848</v>
+        <v>-0.01606282761716979</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -4492,51 +4492,51 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>2.304706678515673</v>
+        <v>2.262297737274182</v>
       </c>
       <c r="L49" t="n">
-        <v>0.008115562505967788</v>
+        <v>0.006693121938627589</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.001313572190710489</v>
+        <v>0.001532681339414351</v>
       </c>
       <c r="N49" t="n">
-        <v>0.4036611851918545</v>
+        <v>0.3888449911681286</v>
       </c>
       <c r="O49" t="n">
-        <v>0.009793182745430146</v>
+        <v>0.005303235334193024</v>
       </c>
       <c r="P49" t="n">
-        <v>-0.004246357217650304</v>
+        <v>-0.003712321885336485</v>
       </c>
       <c r="Q49" t="n">
-        <v>32.56705418973313</v>
+        <v>31.995</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.1740358189727065</v>
+        <v>-0.005538461538462158</v>
       </c>
       <c r="S49" t="n">
-        <v>0.009992665790945085</v>
+        <v>0.0002927935222678262</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U49" t="n">
-        <v>0.01263639772338066</v>
+        <v>0.01224676059052313</v>
       </c>
       <c r="V49" t="n">
-        <v>0.0003860436566944788</v>
+        <v>0.0002329777313350133</v>
       </c>
       <c r="W49" t="n">
-        <v>0.000210456350342944</v>
+        <v>6.10655905385959e-05</v>
       </c>
       <c r="X49" t="n">
-        <v>0.01121459468049139</v>
+        <v>0.006453652849196456</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.3670882197692774</v>
+        <v>0.339244188384705</v>
       </c>
     </row>
     <row r="50">
@@ -4547,20 +4547,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR07 T = 31°C </t>
+          <t xml:space="preserve">BR07 T = 32°C </t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>23.75</v>
       </c>
       <c r="D50" t="n">
-        <v>29.39524843364095</v>
+        <v>28.10618617952874</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1649991381752267</v>
+        <v>0.2319928168977157</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.05357275788364546</v>
+        <v>-0.01407211063616783</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -4575,51 +4575,51 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>2.316287231147895</v>
+        <v>2.276140520773264</v>
       </c>
       <c r="L50" t="n">
-        <v>0.006096161006160838</v>
+        <v>0.008627072778333855</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.001084134121541548</v>
+        <v>0.0006643646156860147</v>
       </c>
       <c r="N50" t="n">
-        <v>0.4136373908887124</v>
+        <v>0.3916480108607699</v>
       </c>
       <c r="O50" t="n">
-        <v>0.003345093362539506</v>
+        <v>0.0003513601541866307</v>
       </c>
       <c r="P50" t="n">
-        <v>-0.003396630959759563</v>
+        <v>-0.002089204690189239</v>
       </c>
       <c r="Q50" t="n">
-        <v>32.29037631375358</v>
+        <v>31.98</v>
       </c>
       <c r="R50" t="n">
-        <v>-0.1566836293532736</v>
+        <v>-0.005399999999998961</v>
       </c>
       <c r="S50" t="n">
-        <v>0.01093500433662594</v>
+        <v>0.002641846153846253</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U50" t="n">
-        <v>0.008244990231579423</v>
+        <v>0.01204437474977316</v>
       </c>
       <c r="V50" t="n">
-        <v>0.0001508315932234864</v>
+        <v>6.531630339965662e-05</v>
       </c>
       <c r="W50" t="n">
-        <v>3.481160941581729e-05</v>
+        <v>-0.0001025170476882296</v>
       </c>
       <c r="X50" t="n">
-        <v>0.004433732154446257</v>
+        <v>0.001835792183909335</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.24236353619022</v>
+        <v>0.3385214391331394</v>
       </c>
     </row>
     <row r="51">
@@ -4630,20 +4630,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR07 T = 31°C </t>
+          <t xml:space="preserve">BR07 T = 32°C </t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>26.25</v>
       </c>
       <c r="D51" t="n">
-        <v>29.64983825206663</v>
+        <v>28.64386118691368</v>
       </c>
       <c r="E51" t="n">
-        <v>0.05470835261784934</v>
+        <v>0.2009612073597893</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.03568248598137824</v>
+        <v>-0.0109326309643531</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -4658,51 +4658,51 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>2.328331994013901</v>
+        <v>2.298913462764915</v>
       </c>
       <c r="L51" t="n">
-        <v>0.003863976121091794</v>
+        <v>0.008427962237032349</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.000722296572070325</v>
+        <v>-0.0004135900704281699</v>
       </c>
       <c r="N51" t="n">
-        <v>0.412097761586654</v>
+        <v>0.3875372175159932</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.003375649024453836</v>
+        <v>-0.001564450004481743</v>
       </c>
       <c r="P51" t="n">
-        <v>-0.002056561859674032</v>
+        <v>-0.00014870938964822</v>
       </c>
       <c r="Q51" t="n">
-        <v>31.93362885124961</v>
+        <v>31.98</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.1273822788930854</v>
+        <v>0.01079999999999792</v>
       </c>
       <c r="S51" t="n">
-        <v>0.01242112855034749</v>
+        <v>0.002030397093453932</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U51" t="n">
-        <v>0.003504695324616781</v>
+        <v>0.01068191935259054</v>
       </c>
       <c r="V51" t="n">
-        <v>-9.078476053328273e-05</v>
+        <v>-5.017271922451634e-06</v>
       </c>
       <c r="W51" t="n">
-        <v>-0.0001394958896139656</v>
+        <v>-0.0001495383361958823</v>
       </c>
       <c r="X51" t="n">
-        <v>-0.002691753465564435</v>
+        <v>-0.0001437140404837041</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.1039136494976617</v>
+        <v>0.3059714151454102</v>
       </c>
     </row>
     <row r="52">
@@ -4713,20 +4713,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR07 T = 31°C </t>
+          <t xml:space="preserve">BR07 T = 32°C </t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>27.91666666666666</v>
       </c>
       <c r="D52" t="n">
-        <v>29.68865486781591</v>
+        <v>28.96312009296423</v>
       </c>
       <c r="E52" t="n">
-        <v>0.004608462917299772</v>
+        <v>0.1843846144756647</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.0241089883061308</v>
+        <v>-0.008901652291602401</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -4741,51 +4741,51 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>2.333712033076487</v>
+        <v>2.312203161427049</v>
       </c>
       <c r="L52" t="n">
-        <v>0.002849678925371579</v>
+        <v>0.007367594504199215</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.0004882181824013199</v>
+        <v>-0.0006469654449942448</v>
       </c>
       <c r="N52" t="n">
-        <v>0.4034052384307527</v>
+        <v>0.3850185423234447</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.006101324240440215</v>
+        <v>-0.001126060460763079</v>
       </c>
       <c r="P52" t="n">
-        <v>-0.00118965012690458</v>
+        <v>0.0003152317813900813</v>
       </c>
       <c r="Q52" t="n">
-        <v>31.73834361543725</v>
+        <v>32.01</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.1059019664577594</v>
+        <v>0.009239991926260238</v>
       </c>
       <c r="S52" t="n">
-        <v>0.01338252562841304</v>
+        <v>-0.002523729481803018</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U52" t="n">
-        <v>0.001376319181468215</v>
+        <v>0.009552581993302903</v>
       </c>
       <c r="V52" t="n">
-        <v>-0.0001889182598341751</v>
+        <v>3.478942026938983e-06</v>
       </c>
       <c r="W52" t="n">
-        <v>-0.0002076194899851877</v>
+        <v>-0.000123507417960572</v>
       </c>
       <c r="X52" t="n">
-        <v>-0.005608729014445193</v>
+        <v>0.0001007610157226942</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.04086106516656473</v>
+        <v>0.2766725794699196</v>
       </c>
     </row>
     <row r="53">
@@ -4796,20 +4796,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR07 T = 31°C </t>
+          <t xml:space="preserve">BR07 T = 32°C </t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>30.7</v>
       </c>
       <c r="D53" t="n">
-        <v>29.61464700032266</v>
+        <v>29.44299319235574</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.03483390129384834</v>
+        <v>0.1644624453651566</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.005601465390944315</v>
+        <v>-0.005653854142682241</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -4824,51 +4824,51 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>2.339885031068742</v>
+        <v>2.32989179938618</v>
       </c>
       <c r="L53" t="n">
-        <v>0.002050258952000283</v>
+        <v>0.005516930369822814</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.0001138964965713318</v>
+        <v>-0.0005999021027103894</v>
       </c>
       <c r="N53" t="n">
-        <v>0.3823058251674145</v>
+        <v>0.3836745572537825</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.007340573548667177</v>
+        <v>-6.040075839673642e-06</v>
       </c>
       <c r="P53" t="n">
-        <v>0.000196654101072157</v>
+        <v>0.0003402937690272116</v>
       </c>
       <c r="Q53" t="n">
-        <v>31.4959641458635</v>
+        <v>31.995</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.06635617060108867</v>
+        <v>-0.005164397200911885</v>
       </c>
       <c r="S53" t="n">
-        <v>0.01491992417050935</v>
+        <v>-0.001490830113050614</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U53" t="n">
-        <v>-0.0003000168601736781</v>
+        <v>0.0079536835586646</v>
       </c>
       <c r="V53" t="n">
-        <v>-0.0002365582388839427</v>
+        <v>3.065108018757976e-05</v>
       </c>
       <c r="W53" t="n">
-        <v>-0.0002326852164132854</v>
+        <v>-7.299415716891363e-05</v>
       </c>
       <c r="X53" t="n">
-        <v>-0.007005588739565965</v>
+        <v>0.0009024595453012609</v>
       </c>
       <c r="Y53" t="n">
-        <v>-0.008884893408188637</v>
+        <v>0.2341802508719136</v>
       </c>
     </row>
     <row r="54">
@@ -4879,20 +4879,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR07 T = 31°C </t>
+          <t xml:space="preserve">BR07 T = 32°C </t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>33.75</v>
       </c>
       <c r="D54" t="n">
-        <v>29.48084954634703</v>
+        <v>29.9180428917296</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.02327744189551861</v>
+        <v>0.1522442521237526</v>
       </c>
       <c r="F54" t="n">
-        <v>0.01347142236421972</v>
+        <v>-0.002306842777105907</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -4907,51 +4907,51 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>2.345578216886011</v>
+        <v>2.343916761655924</v>
       </c>
       <c r="L54" t="n">
-        <v>0.002282148309927012</v>
+        <v>0.003904496922610412</v>
       </c>
       <c r="M54" t="n">
-        <v>0.0002718599080472746</v>
+        <v>-0.0004552165880612599</v>
       </c>
       <c r="N54" t="n">
-        <v>0.3607193879635406</v>
+        <v>0.3852497996998289</v>
       </c>
       <c r="O54" t="n">
-        <v>-0.004595432513972535</v>
+        <v>0.0008242750400914711</v>
       </c>
       <c r="P54" t="n">
-        <v>0.00162530692813485</v>
+        <v>0.0002020591873632122</v>
       </c>
       <c r="Q54" t="n">
-        <v>31.36284949969735</v>
+        <v>31.98</v>
       </c>
       <c r="R54" t="n">
-        <v>-0.01847123301841869</v>
+        <v>0.00260262837013947</v>
       </c>
       <c r="S54" t="n">
-        <v>0.01650428691655278</v>
+        <v>0.001602920970721021</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U54" t="n">
-        <v>0.0001833792711786235</v>
+        <v>0.006754510432644329</v>
       </c>
       <c r="V54" t="n">
-        <v>-0.0001439737282029538</v>
+        <v>4.900134090875597e-05</v>
       </c>
       <c r="W54" t="n">
-        <v>-0.0001462175054170656</v>
+        <v>-3.797539753177769e-05</v>
       </c>
       <c r="X54" t="n">
-        <v>-0.00424446781977794</v>
+        <v>0.001466024219060425</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.00540617670353577</v>
+        <v>0.2020817328364881</v>
       </c>
     </row>
     <row r="55">
@@ -4962,20 +4962,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR07 T = 31°C </t>
+          <t xml:space="preserve">BR07 T = 32°C </t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>36.75</v>
       </c>
       <c r="D55" t="n">
-        <v>29.47177629679577</v>
+        <v>30.36441901562919</v>
       </c>
       <c r="E55" t="n">
-        <v>0.04570789849064916</v>
+        <v>0.1503375270647895</v>
       </c>
       <c r="F55" t="n">
-        <v>0.03588489279407513</v>
+        <v>0.001626391730103559</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
@@ -4990,51 +4990,51 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>2.35365081594125</v>
+        <v>2.353582822173603</v>
       </c>
       <c r="L55" t="n">
-        <v>0.003675588851543399</v>
+        <v>0.002755585205470978</v>
       </c>
       <c r="M55" t="n">
-        <v>0.0007251808670461134</v>
+        <v>-0.0002851896605268836</v>
       </c>
       <c r="N55" t="n">
-        <v>0.3542572841680695</v>
+        <v>0.3886308933324487</v>
       </c>
       <c r="O55" t="n">
-        <v>0.002420601773796688</v>
+        <v>0.00122337801467666</v>
       </c>
       <c r="P55" t="n">
-        <v>0.003304185779882367</v>
+        <v>3.961306235677705e-05</v>
       </c>
       <c r="Q55" t="n">
-        <v>31.38171652831098</v>
+        <v>32.01</v>
       </c>
       <c r="R55" t="n">
-        <v>0.03341499377427581</v>
+        <v>0.004626865671641944</v>
       </c>
       <c r="S55" t="n">
-        <v>0.01836614800515476</v>
+        <v>-0.0006501566143000317</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U55" t="n">
-        <v>0.003112558365148435</v>
+        <v>0.006121912736337415</v>
       </c>
       <c r="V55" t="n">
-        <v>0.0001009043073977552</v>
+        <v>5.527485268731127e-05</v>
       </c>
       <c r="W55" t="n">
-        <v>6.349066588026133e-05</v>
+        <v>-2.307884195777648e-05</v>
       </c>
       <c r="X55" t="n">
-        <v>0.002973829175009757</v>
+        <v>0.001678388788024696</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.09173262384837508</v>
+        <v>0.1858883235032663</v>
       </c>
     </row>
     <row r="56">
@@ -5045,20 +5045,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR07 T = 31°C </t>
+          <t xml:space="preserve">BR07 T = 32°C </t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>39.33333333333334</v>
       </c>
       <c r="D56" t="n">
-        <v>29.69826187419854</v>
+        <v>30.75622895087086</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1670843297319879</v>
+        <v>0.1595708678456065</v>
       </c>
       <c r="F56" t="n">
-        <v>0.05066186087828568</v>
+        <v>0.004219532357862998</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -5073,51 +5073,51 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>2.365336638813073</v>
+        <v>2.359663815428079</v>
       </c>
       <c r="L56" t="n">
-        <v>0.006128911090795705</v>
+        <v>0.002236362509041953</v>
       </c>
       <c r="M56" t="n">
-        <v>0.001024050663403341</v>
+        <v>-0.0001730926744980744</v>
       </c>
       <c r="N56" t="n">
-        <v>0.3706869534581737</v>
+        <v>0.3920056135704909</v>
       </c>
       <c r="O56" t="n">
-        <v>0.01310422264100411</v>
+        <v>0.001117892700609307</v>
       </c>
       <c r="P56" t="n">
-        <v>0.004411053156229573</v>
+        <v>-6.748597936174069e-05</v>
       </c>
       <c r="Q56" t="n">
-        <v>31.52838135216115</v>
+        <v>32.01</v>
       </c>
       <c r="R56" t="n">
-        <v>0.0832427748486122</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="S56" t="n">
-        <v>0.01959365366830485</v>
+        <v>-0.001336688081686393</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U56" t="n">
-        <v>0.008217201179631079</v>
+        <v>0.006135991785462943</v>
       </c>
       <c r="V56" t="n">
-        <v>0.0004735874224254427</v>
+        <v>4.842643580783609e-05</v>
       </c>
       <c r="W56" t="n">
-        <v>0.0003710221853037145</v>
+        <v>-2.978026594894044e-05</v>
       </c>
       <c r="X56" t="n">
-        <v>0.01406472329151749</v>
+        <v>0.001489414546980458</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.244036592505657</v>
+        <v>0.1887199681943611</v>
       </c>
     </row>
     <row r="57">
@@ -5128,20 +5128,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR07 T = 31°C </t>
+          <t xml:space="preserve">BR07 T = 32°C </t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>46.93333333333334</v>
       </c>
       <c r="D57" t="n">
-        <v>32.74366366301908</v>
+        <v>32.14565737977434</v>
       </c>
       <c r="E57" t="n">
-        <v>0.634337193641838</v>
+        <v>0.2060681923921539</v>
       </c>
       <c r="F57" t="n">
-        <v>0.07229941909799065</v>
+        <v>0.008016605680702123</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -5156,51 +5156,51 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>2.447810292266285</v>
+        <v>2.374031448869096</v>
       </c>
       <c r="L57" t="n">
-        <v>0.01557468192320755</v>
+        <v>0.001544593659646765</v>
       </c>
       <c r="M57" t="n">
-        <v>0.001461678503020828</v>
+        <v>-8.95175955329075e-06</v>
       </c>
       <c r="N57" t="n">
-        <v>0.6210740238488811</v>
+        <v>0.3962880854534297</v>
       </c>
       <c r="O57" t="n">
-        <v>0.05278711167233995</v>
+        <v>9.073584374602595e-06</v>
       </c>
       <c r="P57" t="n">
-        <v>0.006031812378332486</v>
+        <v>-0.0002243085249105499</v>
       </c>
       <c r="Q57" t="n">
-        <v>32.75284571542353</v>
+        <v>32.01</v>
       </c>
       <c r="R57" t="n">
-        <v>0.2389846891678031</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="S57" t="n">
-        <v>0.02139106062621907</v>
+        <v>0.00133668808168651</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="U57" t="n">
-        <v>0.02573552253541112</v>
+        <v>0.007061072516470514</v>
       </c>
       <c r="V57" t="n">
-        <v>0.001732818287826253</v>
+        <v>8.303042474814183e-06</v>
       </c>
       <c r="W57" t="n">
-        <v>0.001244673017907255</v>
+        <v>-7.874507341036715e-05</v>
       </c>
       <c r="X57" t="n">
-        <v>0.05673881920571143</v>
+        <v>0.0002669067586050903</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.8426752940915495</v>
+        <v>0.2269828178482022</v>
       </c>
     </row>
     <row r="58">
@@ -5211,20 +5211,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR08 T = 28°C </t>
+          <t xml:space="preserve">BR08 T = 29°C </t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>10.13333333333333</v>
       </c>
       <c r="D58" t="n">
-        <v>23.11175811287947</v>
+        <v>27.6820262224195</v>
       </c>
       <c r="E58" t="n">
-        <v>1.746366839713414</v>
+        <v>1.528888314475401</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1671047275670764</v>
+        <v>-1.289454724126297</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
@@ -5239,51 +5239,51 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1.998950494918027</v>
+        <v>2.127365951524089</v>
       </c>
       <c r="L58" t="n">
-        <v>0.02192985751491006</v>
+        <v>0.00899374684160803</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.001943089096018349</v>
+        <v>-0.03592025573400803</v>
       </c>
       <c r="N58" t="n">
-        <v>0.05620523198655621</v>
+        <v>0.06174320854979103</v>
       </c>
       <c r="O58" t="n">
-        <v>0.03760206479158185</v>
+        <v>0.02991833792610701</v>
       </c>
       <c r="P58" t="n">
-        <v>0.007670067572190874</v>
+        <v>0.004322299855940482</v>
       </c>
       <c r="Q58" t="n">
-        <v>32.8679965679046</v>
+        <v>29.01</v>
       </c>
       <c r="R58" t="n">
-        <v>-0.4692570434409902</v>
+        <v>-4.215569548270928</v>
       </c>
       <c r="S58" t="n">
-        <v>0.02947609057148798</v>
+        <v>0.6769278106501221</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U58" t="n">
-        <v>0.08653252007405218</v>
+        <v>0.05945800591186536</v>
       </c>
       <c r="V58" t="n">
-        <v>0.001653646362041202</v>
+        <v>0.001090215218210349</v>
       </c>
       <c r="W58" t="n">
-        <v>0.001443208872111212</v>
+        <v>0.0009575974672742633</v>
       </c>
       <c r="X58" t="n">
-        <v>0.03821867472373937</v>
+        <v>0.03017936625857966</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.999918672849381</v>
+        <v>1.645918078785031</v>
       </c>
     </row>
     <row r="59">
@@ -5294,20 +5294,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR08 T = 28°C </t>
+          <t xml:space="preserve">BR08 T = 29°C </t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>11.56666666666667</v>
       </c>
       <c r="D59" t="n">
-        <v>25.44367436290397</v>
+        <v>28.6328130121517</v>
       </c>
       <c r="E59" t="n">
-        <v>1.514218382126945</v>
+        <v>0.4818298852329832</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.1563538520637208</v>
+        <v>-0.390496584403931</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
@@ -5322,51 +5322,51 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>2.028393103911445</v>
+        <v>2.101395432153724</v>
       </c>
       <c r="L59" t="n">
-        <v>0.01924094535067988</v>
+        <v>-0.02027197462144348</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.001802752746940446</v>
+        <v>-0.008004647669356267</v>
       </c>
       <c r="N59" t="n">
-        <v>0.1059729094802487</v>
+        <v>0.1022310869594348</v>
       </c>
       <c r="O59" t="n">
-        <v>0.03204952682352688</v>
+        <v>0.02666920580504741</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.003700684174612169</v>
+        <v>-0.002189665929867298</v>
       </c>
       <c r="Q59" t="n">
-        <v>32.22563282073414</v>
+        <v>28.995</v>
       </c>
       <c r="R59" t="n">
-        <v>-0.4276795554969937</v>
+        <v>-0.004544063647491825</v>
       </c>
       <c r="S59" t="n">
-        <v>0.02849621689117698</v>
+        <v>1.278015112506714</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U59" t="n">
-        <v>0.06899837419483427</v>
+        <v>0.007180981049318367</v>
       </c>
       <c r="V59" t="n">
-        <v>0.001299134901296968</v>
+        <v>0.0008969775900507867</v>
       </c>
       <c r="W59" t="n">
-        <v>0.001011756657158846</v>
+        <v>0.0008713384920761881</v>
       </c>
       <c r="X59" t="n">
-        <v>0.03305476538208344</v>
+        <v>0.02568299161201464</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.75557216458316</v>
+        <v>0.2056116876289377</v>
       </c>
     </row>
     <row r="60">
@@ -5377,20 +5377,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR08 T = 28°C </t>
+          <t xml:space="preserve">BR08 T = 29°C </t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>12.66666666666667</v>
       </c>
       <c r="D60" t="n">
-        <v>27.0141748733384</v>
+        <v>29.00959789988407</v>
       </c>
       <c r="E60" t="n">
-        <v>1.346965187380055</v>
+        <v>0.3393147461468509</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.1468688954413995</v>
+        <v>-0.07623267057361967</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
@@ -5405,51 +5405,51 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>2.048460356022203</v>
+        <v>2.077278721080258</v>
       </c>
       <c r="L60" t="n">
-        <v>0.0173197391701202</v>
+        <v>-0.01859795448544499</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.001678941045919297</v>
+        <v>0.003248003278876897</v>
       </c>
       <c r="N60" t="n">
-        <v>0.1389716321598503</v>
+        <v>0.1302349601016103</v>
       </c>
       <c r="O60" t="n">
-        <v>0.02812496996918184</v>
+        <v>0.02432571948549465</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.003407895369628199</v>
+        <v>-0.002059196469469883</v>
       </c>
       <c r="Q60" t="n">
-        <v>31.77247525154433</v>
+        <v>28.995</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.3967653769629802</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.02763172363662375</v>
+        <v>0.002360552544151721</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U60" t="n">
-        <v>0.05831642586851364</v>
+        <v>0.002743599749419692</v>
       </c>
       <c r="V60" t="n">
-        <v>0.001084614863191834</v>
+        <v>0.0007983468461517041</v>
       </c>
       <c r="W60" t="n">
-        <v>0.000784612034207603</v>
+        <v>0.0007860297983548474</v>
       </c>
       <c r="X60" t="n">
-        <v>0.02929997558448622</v>
+        <v>0.02315972099150155</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.575370126400103</v>
+        <v>0.07959072552888796</v>
       </c>
     </row>
     <row r="61">
@@ -5460,20 +5460,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR08 T = 28°C </t>
+          <t xml:space="preserve">BR08 T = 29°C </t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>14.13333333333333</v>
       </c>
       <c r="D61" t="n">
-        <v>28.83178816271116</v>
+        <v>29.5009685640624</v>
       </c>
       <c r="E61" t="n">
-        <v>1.141686202530624</v>
+        <v>0.3317898541146982</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.133109007313962</v>
+        <v>-0.004414699244993117</v>
       </c>
       <c r="G61" t="n">
         <v>1</v>
@@ -5488,51 +5488,51 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>2.072057237429711</v>
+        <v>2.056506540971785</v>
       </c>
       <c r="L61" t="n">
-        <v>0.01498950746730249</v>
+        <v>-0.01045860128395248</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.001499326607735057</v>
+        <v>0.005052995665750842</v>
       </c>
       <c r="N61" t="n">
-        <v>0.1765571335128697</v>
+        <v>0.1636983145325466</v>
       </c>
       <c r="O61" t="n">
-        <v>0.02343938466751207</v>
+        <v>0.0214448894691804</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.0029831447500983</v>
+        <v>-0.001869923576551122</v>
       </c>
       <c r="Q61" t="n">
-        <v>31.22026941783067</v>
+        <v>28.995</v>
       </c>
       <c r="R61" t="n">
-        <v>-0.3571620179114472</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="S61" t="n">
-        <v>0.02637759766186296</v>
+        <v>1.679754956076457e-16</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U61" t="n">
-        <v>0.04683229376126923</v>
+        <v>0.006161129062847553</v>
       </c>
       <c r="V61" t="n">
-        <v>0.0008572697518118425</v>
+        <v>0.0006987019005542094</v>
       </c>
       <c r="W61" t="n">
-        <v>0.0005704829768931681</v>
+        <v>0.0006645143300337535</v>
       </c>
       <c r="X61" t="n">
-        <v>0.02471661988253902</v>
+        <v>0.02061238280390039</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.350258772898774</v>
+        <v>0.1817592748021969</v>
       </c>
     </row>
     <row r="62">
@@ -5543,20 +5543,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR08 T = 28°C </t>
+          <t xml:space="preserve">BR08 T = 29°C </t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>16.85</v>
       </c>
       <c r="D62" t="n">
-        <v>31.44226728642678</v>
+        <v>30.38604944373159</v>
       </c>
       <c r="E62" t="n">
-        <v>0.8145624617401048</v>
+        <v>0.3233990471364363</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.1120069363913003</v>
+        <v>-0.002210540986952472</v>
       </c>
       <c r="G62" t="n">
         <v>1</v>
@@ -5571,51 +5571,51 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>2.107247171025383</v>
+        <v>2.046733815457519</v>
       </c>
       <c r="L62" t="n">
-        <v>0.01136653917040717</v>
+        <v>0.0007699931430980855</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.001223871125961012</v>
+        <v>0.003524164153454311</v>
       </c>
       <c r="N62" t="n">
-        <v>0.2292286573258575</v>
+        <v>0.2150578774167018</v>
       </c>
       <c r="O62" t="n">
-        <v>0.01639980919113452</v>
+        <v>0.01683934158891357</v>
       </c>
       <c r="P62" t="n">
-        <v>-0.00233175008651166</v>
+        <v>-0.001579655954233453</v>
       </c>
       <c r="Q62" t="n">
-        <v>30.34730815651207</v>
+        <v>28.995</v>
       </c>
       <c r="R62" t="n">
-        <v>-0.2886463354951863</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="S62" t="n">
-        <v>0.02445427858978128</v>
+        <v>-0.0004149356467907026</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U62" t="n">
-        <v>0.03130062974404701</v>
+        <v>0.01101921643202252</v>
       </c>
       <c r="V62" t="n">
-        <v>0.0005609097340836551</v>
+        <v>0.0005568426274757067</v>
       </c>
       <c r="W62" t="n">
-        <v>0.0003327136798894638</v>
+        <v>0.0004788539010684022</v>
       </c>
       <c r="X62" t="n">
-        <v>0.01763627378261685</v>
+        <v>0.01692024761085423</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.9841627666458064</v>
+        <v>0.334830455334616</v>
       </c>
     </row>
     <row r="63">
@@ -5626,20 +5626,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR08 T = 28°C </t>
+          <t xml:space="preserve">BR08 T = 29°C </t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>22.4</v>
       </c>
       <c r="D63" t="n">
-        <v>34.30372124528255</v>
+        <v>32.15372939173055</v>
       </c>
       <c r="E63" t="n">
-        <v>0.288242136901026</v>
+        <v>0.3210867398122836</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.07615063496725427</v>
+        <v>0.001534729473765345</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -5654,51 +5654,51 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>2.152339659456331</v>
+        <v>2.100525400041643</v>
       </c>
       <c r="L63" t="n">
-        <v>0.005818288369869418</v>
+        <v>0.01342336372100172</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.0007558215767206585</v>
+        <v>0.0009263980985296924</v>
       </c>
       <c r="N63" t="n">
-        <v>0.2863631651636567</v>
+        <v>0.2850909902199914</v>
       </c>
       <c r="O63" t="n">
-        <v>0.006400949541983003</v>
+        <v>0.009383391512969796</v>
       </c>
       <c r="P63" t="n">
-        <v>-0.001224910691971632</v>
+        <v>-0.001086437852673271</v>
       </c>
       <c r="Q63" t="n">
-        <v>29.11596121959764</v>
+        <v>28.995</v>
       </c>
       <c r="R63" t="n">
-        <v>-0.1616127323049614</v>
+        <v>-0.007007575757578266</v>
       </c>
       <c r="S63" t="n">
-        <v>0.02118620558234225</v>
+        <v>0.005856180856182273</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U63" t="n">
-        <v>0.0111058881653052</v>
+        <v>0.01637646662611292</v>
       </c>
       <c r="V63" t="n">
-        <v>0.0002091626604718275</v>
+        <v>0.000348490198391928</v>
       </c>
       <c r="W63" t="n">
-        <v>0.0001164520981328291</v>
+        <v>0.0002032882832466225</v>
       </c>
       <c r="X63" t="n">
-        <v>0.007175057599747249</v>
+        <v>0.01120525953476454</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.3809732918039119</v>
+        <v>0.5265644762887414</v>
       </c>
     </row>
     <row r="64">
@@ -5709,20 +5709,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR08 T = 28°C </t>
+          <t xml:space="preserve">BR08 T = 29°C </t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>24.05</v>
       </c>
       <c r="D64" t="n">
-        <v>34.66780366234114</v>
+        <v>32.6847909758343</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1717577969430177</v>
+        <v>0.3245762653317463</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.06151571908440612</v>
+        <v>0.00283005915963172</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -5737,51 +5737,51 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>2.160808411201343</v>
+        <v>2.124504248334809</v>
       </c>
       <c r="L64" t="n">
-        <v>0.004690807579834977</v>
+        <v>0.01428797960705364</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.0005647849803598159</v>
+        <v>-9.519851664598154e-05</v>
       </c>
       <c r="N64" t="n">
-        <v>0.2950147846592398</v>
+        <v>0.2989865956549137</v>
       </c>
       <c r="O64" t="n">
-        <v>0.004662734586390355</v>
+        <v>0.007716826484273992</v>
       </c>
       <c r="P64" t="n">
-        <v>-0.0007731490547813191</v>
+        <v>-0.0008851285948424789</v>
       </c>
       <c r="Q64" t="n">
-        <v>28.87885605423619</v>
+        <v>28.98</v>
       </c>
       <c r="R64" t="n">
-        <v>-0.1274907521351452</v>
+        <v>0.0061471861471869</v>
       </c>
       <c r="S64" t="n">
-        <v>0.01985232641289843</v>
+        <v>0.005102658473445725</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U64" t="n">
-        <v>0.007125247042066955</v>
+        <v>0.01665582251877981</v>
       </c>
       <c r="V64" t="n">
-        <v>0.0001529710320050208</v>
+        <v>0.0002976187991140823</v>
       </c>
       <c r="W64" t="n">
-        <v>9.233687005369179e-05</v>
+        <v>0.0001452584038340783</v>
       </c>
       <c r="X64" t="n">
-        <v>0.005303169703575762</v>
+        <v>0.009727608239522602</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.2470166655000542</v>
+        <v>0.544392077556912</v>
       </c>
     </row>
     <row r="65">
@@ -5792,20 +5792,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR08 T = 28°C </t>
+          <t xml:space="preserve">BR08 T = 29°C </t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>25.55</v>
       </c>
       <c r="D65" t="n">
-        <v>34.85876097585268</v>
+        <v>33.17536550085145</v>
       </c>
       <c r="E65" t="n">
-        <v>0.09186719638974594</v>
+        <v>0.3297966202645242</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.04627215251603842</v>
+        <v>0.002356905619938968</v>
       </c>
       <c r="G65" t="n">
         <v>1</v>
@@ -5820,51 +5820,51 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>2.167242209977472</v>
+        <v>2.14560259630611</v>
       </c>
       <c r="L65" t="n">
-        <v>0.004005271078254546</v>
+        <v>0.01330080708950798</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.0003658033738420734</v>
+        <v>-0.0008570637649848618</v>
       </c>
       <c r="N65" t="n">
-        <v>0.3012170622181319</v>
+        <v>0.3096008091533328</v>
       </c>
       <c r="O65" t="n">
-        <v>0.003885258124221247</v>
+        <v>0.006559466523585245</v>
       </c>
       <c r="P65" t="n">
-        <v>-0.0003025991285178714</v>
+        <v>-0.0006754470977203206</v>
       </c>
       <c r="Q65" t="n">
-        <v>28.70972358251154</v>
+        <v>29.01</v>
       </c>
       <c r="R65" t="n">
-        <v>-0.09884089192780898</v>
+        <v>0.009887640449438351</v>
       </c>
       <c r="S65" t="n">
-        <v>0.01846297261842932</v>
+        <v>-0.002731475765183992</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U65" t="n">
-        <v>0.00448350771494239</v>
+        <v>0.01614011034749322</v>
       </c>
       <c r="V65" t="n">
-        <v>0.0001274266774530305</v>
+        <v>0.0002555725631114712</v>
       </c>
       <c r="W65" t="n">
-        <v>8.868436463064414e-05</v>
+        <v>0.0001049490161522152</v>
       </c>
       <c r="X65" t="n">
-        <v>0.004441936091282263</v>
+        <v>0.008478713193212481</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.1562895237685682</v>
+        <v>0.5354540600021621</v>
       </c>
     </row>
     <row r="66">
@@ -5875,20 +5875,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR08 T = 28°C </t>
+          <t xml:space="preserve">BR08 T = 29°C </t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>27.01666666666667</v>
       </c>
       <c r="D66" t="n">
-        <v>34.94267927345022</v>
+        <v>33.6630065215925</v>
       </c>
       <c r="E66" t="n">
-        <v>0.03402303776847404</v>
+        <v>0.331642475307321</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.03371110307008748</v>
+        <v>-0.0006942422289595851</v>
       </c>
       <c r="G66" t="n">
         <v>1</v>
@@ -5903,51 +5903,51 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>2.172709433623438</v>
+        <v>2.164013726761088</v>
       </c>
       <c r="L66" t="n">
-        <v>0.003599577077815719</v>
+        <v>0.01175847298503752</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.0002018379536043606</v>
+        <v>-0.001043516318232963</v>
       </c>
       <c r="N66" t="n">
-        <v>0.3065575051157421</v>
+        <v>0.3184804086726417</v>
       </c>
       <c r="O66" t="n">
-        <v>0.003750802395749847</v>
+        <v>0.005706662885009567</v>
       </c>
       <c r="P66" t="n">
-        <v>8.514483311173335e-05</v>
+        <v>-0.0005026647215329997</v>
       </c>
       <c r="Q66" t="n">
-        <v>28.58471077563499</v>
+        <v>29.01</v>
       </c>
       <c r="R66" t="n">
-        <v>-0.07267527622447512</v>
+        <v>-0.001611721611721961</v>
       </c>
       <c r="S66" t="n">
-        <v>0.01731811313741561</v>
+        <v>-0.005105980162160129</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U66" t="n">
-        <v>0.002630404143356156</v>
+        <v>0.0152854783221557</v>
       </c>
       <c r="V66" t="n">
-        <v>0.0001218762632783113</v>
+        <v>0.0002209300877437384</v>
       </c>
       <c r="W66" t="n">
-        <v>9.879932274599036e-05</v>
+        <v>7.631658212372236e-05</v>
       </c>
       <c r="X66" t="n">
-        <v>0.004258683178780611</v>
+        <v>0.007437170984533468</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.09191336834084876</v>
+        <v>0.5145551564443881</v>
       </c>
     </row>
     <row r="67">
@@ -5958,20 +5958,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR08 T = 28°C </t>
+          <t xml:space="preserve">BR08 T = 29°C </t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>30.05</v>
       </c>
       <c r="D67" t="n">
-        <v>34.90037538507577</v>
+        <v>34.66371872579222</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.03229885147433809</v>
+        <v>0.3172858729876955</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.0112611959716665</v>
+        <v>-0.008628784912759153</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
@@ -5986,51 +5986,51 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>2.182824671627488</v>
+        <v>2.194696368779029</v>
       </c>
       <c r="L67" t="n">
-        <v>0.003456413735662078</v>
+        <v>0.008643799274912711</v>
       </c>
       <c r="M67" t="n">
-        <v>9.121148207606234e-05</v>
+        <v>-0.0009652523434678254</v>
       </c>
       <c r="N67" t="n">
-        <v>0.3186224585927623</v>
+        <v>0.3336098964013117</v>
       </c>
       <c r="O67" t="n">
-        <v>0.005118347587112895</v>
+        <v>0.0046762155598358</v>
       </c>
       <c r="P67" t="n">
-        <v>0.0007781455217893411</v>
+        <v>-0.0001938570609676674</v>
       </c>
       <c r="Q67" t="n">
-        <v>28.44306197745943</v>
+        <v>28.995</v>
       </c>
       <c r="R67" t="n">
-        <v>-0.02341892350203345</v>
+        <v>5.494505494496593e-05</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0152719474010178</v>
+        <v>-0.0003398084690739731</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U67" t="n">
-        <v>0.0006580005973644717</v>
+        <v>0.01309174983064569</v>
       </c>
       <c r="V67" t="n">
-        <v>0.0001611121134904314</v>
+        <v>0.0001728070869525385</v>
       </c>
       <c r="W67" t="n">
-        <v>0.0001551049068121495</v>
+        <v>4.680971952456418e-05</v>
       </c>
       <c r="X67" t="n">
-        <v>0.005622873239898987</v>
+        <v>0.005990136255946315</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.02296446785162417</v>
+        <v>0.4538087337579402</v>
       </c>
     </row>
     <row r="68">
@@ -6041,20 +6041,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR08 T = 28°C </t>
+          <t xml:space="preserve">BR08 T = 29°C </t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>33.05</v>
       </c>
       <c r="D68" t="n">
-        <v>34.74902631466539</v>
+        <v>35.57813461613436</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.03462250485933716</v>
+        <v>0.2798404352259274</v>
       </c>
       <c r="F68" t="n">
-        <v>0.01098795614498289</v>
+        <v>-0.01680362063193006</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -6069,51 +6069,51 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>2.193555059755428</v>
+        <v>2.216262200589915</v>
       </c>
       <c r="L68" t="n">
-        <v>0.004140709839425993</v>
+        <v>0.005930702185700687</v>
       </c>
       <c r="M68" t="n">
-        <v>0.0003816403664170467</v>
+        <v>-0.0008360712476423337</v>
       </c>
       <c r="N68" t="n">
-        <v>0.3373625607734345</v>
+        <v>0.3467142302807875</v>
       </c>
       <c r="O68" t="n">
-        <v>0.008423913173169664</v>
+        <v>0.004527388652495162</v>
       </c>
       <c r="P68" t="n">
-        <v>0.001464949154059869</v>
+        <v>0.000112189132657267</v>
       </c>
       <c r="Q68" t="n">
-        <v>28.4418732319234</v>
+        <v>29.01</v>
       </c>
       <c r="R68" t="n">
-        <v>0.01952954647438432</v>
+        <v>-0.003602941176470864</v>
       </c>
       <c r="S68" t="n">
-        <v>0.01324407919980949</v>
+        <v>-0.0009821604226976539</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U68" t="n">
-        <v>0.0008913118094583624</v>
+        <v>0.01054151037633381</v>
       </c>
       <c r="V68" t="n">
-        <v>0.0002607481011659217</v>
+        <v>0.0001533299475232635</v>
       </c>
       <c r="W68" t="n">
-        <v>0.0002520947584286729</v>
+        <v>5.060135605658079e-05</v>
       </c>
       <c r="X68" t="n">
-        <v>0.009060742628913647</v>
+        <v>0.005455193513667488</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.03097221752144066</v>
+        <v>0.3750472752265814</v>
       </c>
     </row>
     <row r="69">
@@ -6124,20 +6124,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR08 T = 28°C </t>
+          <t xml:space="preserve">BR08 T = 29°C </t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>35.71666666666666</v>
       </c>
       <c r="D69" t="n">
-        <v>34.69421592606853</v>
+        <v>36.26519980860697</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0225602102492175</v>
+        <v>0.2247864944719238</v>
       </c>
       <c r="F69" t="n">
-        <v>0.03550231201248157</v>
+        <v>-0.02540387016099038</v>
       </c>
       <c r="G69" t="n">
         <v>1</v>
@@ -6152,51 +6152,51 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>2.205933637215893</v>
+        <v>2.229095697575954</v>
       </c>
       <c r="L69" t="n">
-        <v>0.00552236809692308</v>
+        <v>0.003863061996459916</v>
       </c>
       <c r="M69" t="n">
-        <v>0.0007016380448727261</v>
+        <v>-0.0006937381224151099</v>
       </c>
       <c r="N69" t="n">
-        <v>0.3649871291078813</v>
+        <v>0.3591648130206834</v>
       </c>
       <c r="O69" t="n">
-        <v>0.01319111141204364</v>
+        <v>0.005210081099334241</v>
       </c>
       <c r="P69" t="n">
-        <v>0.002221676806614828</v>
+        <v>0.0004493941309906995</v>
       </c>
       <c r="Q69" t="n">
-        <v>28.54118353656358</v>
+        <v>28.98</v>
       </c>
       <c r="R69" t="n">
-        <v>0.05230587036366252</v>
+        <v>-0.005659937888199629</v>
       </c>
       <c r="S69" t="n">
-        <v>0.01100975213529117</v>
+        <v>0.0006535440263062372</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U69" t="n">
-        <v>0.003153673877267354</v>
+        <v>0.007931425284625664</v>
       </c>
       <c r="V69" t="n">
-        <v>0.0004065468958410469</v>
+        <v>0.000160829667548178</v>
       </c>
       <c r="W69" t="n">
-        <v>0.0003733698850949572</v>
+        <v>8.22780838157204e-05</v>
       </c>
       <c r="X69" t="n">
-        <v>0.01410482578838217</v>
+        <v>0.005832520028786509</v>
       </c>
       <c r="Y69" t="n">
-        <v>0.1094142424583153</v>
+        <v>0.2876347227139872</v>
       </c>
     </row>
     <row r="70">
@@ -6207,20 +6207,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR08 T = 28°C </t>
+          <t xml:space="preserve">BR08 T = 29°C </t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>38.41666666666666</v>
       </c>
       <c r="D70" t="n">
-        <v>34.87299168094522</v>
+        <v>36.78228424672304</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1568496803615351</v>
+        <v>0.1431871064357388</v>
       </c>
       <c r="F70" t="n">
-        <v>0.05412781326055578</v>
+        <v>-0.0316287160182974</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -6235,51 +6235,51 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>2.223250828812843</v>
+        <v>2.236930271054624</v>
       </c>
       <c r="L70" t="n">
-        <v>0.007918478225213008</v>
+        <v>0.002213116736538179</v>
       </c>
       <c r="M70" t="n">
-        <v>0.0009447656714630786</v>
+        <v>-0.000585596353735072</v>
       </c>
       <c r="N70" t="n">
-        <v>0.4083448318614631</v>
+        <v>0.3747112984822444</v>
       </c>
       <c r="O70" t="n">
-        <v>0.02037602469041631</v>
+        <v>0.006952110029900082</v>
       </c>
       <c r="P70" t="n">
-        <v>0.002796622846938936</v>
+        <v>0.0007055955238098011</v>
       </c>
       <c r="Q70" t="n">
-        <v>28.72359198016084</v>
+        <v>28.98</v>
       </c>
       <c r="R70" t="n">
-        <v>0.07852925774168296</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="S70" t="n">
-        <v>0.009312156581333596</v>
+        <v>0.001567307134150147</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U70" t="n">
-        <v>0.008059407484176984</v>
+        <v>0.004882182380189196</v>
       </c>
       <c r="V70" t="n">
-        <v>0.000625997707336111</v>
+        <v>0.0001990858490734699</v>
       </c>
       <c r="W70" t="n">
-        <v>0.000531626182686349</v>
+        <v>0.0001493497074342836</v>
       </c>
       <c r="X70" t="n">
-        <v>0.02183041284022298</v>
+        <v>0.007322832290120574</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.2810556501490517</v>
+        <v>0.1795778200524618</v>
       </c>
     </row>
     <row r="71">
@@ -6290,20 +6290,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">BR08 T = 28°C </t>
+          <t xml:space="preserve">BR08 T = 29°C </t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>46.41666666666666</v>
       </c>
       <c r="D71" t="n">
-        <v>38.27620839055427</v>
+        <v>36.78228424672304</v>
       </c>
       <c r="E71" t="n">
-        <v>0.6939544970407301</v>
+        <v>-0.1431871064357377</v>
       </c>
       <c r="F71" t="n">
-        <v>0.08014839090924297</v>
+        <v>-0.03996483719957174</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
@@ -6318,51 +6318,51 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>2.322265701955008</v>
+        <v>2.238313376337733</v>
       </c>
       <c r="L71" t="n">
-        <v>0.01683524006032844</v>
+        <v>-0.001867340415760699</v>
       </c>
       <c r="M71" t="n">
-        <v>0.00128442478731578</v>
+        <v>-0.0004345179343396473</v>
       </c>
       <c r="N71" t="n">
-        <v>0.673696525993121</v>
+        <v>0.4586340146098989</v>
       </c>
       <c r="O71" t="n">
-        <v>0.04596189884249817</v>
+        <v>0.01402856900201359</v>
       </c>
       <c r="P71" t="n">
-        <v>0.00359984569108153</v>
+        <v>0.001063519219218576</v>
       </c>
       <c r="Q71" t="n">
-        <v>29.6118692996441</v>
+        <v>28.98</v>
       </c>
       <c r="R71" t="n">
-        <v>0.1435400721291336</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0.006940547015529052</v>
+        <v>-0.001567307134150175</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="U71" t="n">
-        <v>0.02537966784465346</v>
+        <v>-0.004727090289107653</v>
       </c>
       <c r="V71" t="n">
-        <v>0.001328393188634157</v>
+        <v>0.00037099240092809</v>
       </c>
       <c r="W71" t="n">
-        <v>0.0008816876559612341</v>
+        <v>0.0004299339387122765</v>
       </c>
       <c r="X71" t="n">
-        <v>0.05084585451275387</v>
+        <v>0.01364594794431124</v>
       </c>
       <c r="Y71" t="n">
-        <v>0.9714374553050051</v>
+        <v>-0.1738731786738819</v>
       </c>
     </row>
     <row r="72">
@@ -6380,13 +6380,13 @@
         <v>10.08333333333333</v>
       </c>
       <c r="D72" t="n">
-        <v>20.60389268076319</v>
+        <v>22.7550570219956</v>
       </c>
       <c r="E72" t="n">
-        <v>1.408258288148637</v>
+        <v>0.8154315760058175</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.1642399354503841</v>
+        <v>-0.6178923513600627</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -6401,13 +6401,13 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>2.08476996531689</v>
+        <v>2.153098694933099</v>
       </c>
       <c r="L72" t="n">
-        <v>0.03003074656253291</v>
+        <v>0.02172825403628198</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.002392117032199569</v>
+        <v>-0.01841400855852791</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
@@ -6419,13 +6419,13 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>32.12896052043846</v>
+        <v>28.995</v>
       </c>
       <c r="R72" t="n">
-        <v>-0.5121057277200194</v>
+        <v>1.19760442260443</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0362103224138024</v>
+        <v>5.446590793890114</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="U72" t="n">
-        <v>0.0827539622446743</v>
+        <v>0.04592680060041407</v>
       </c>
       <c r="V72" t="n">
         <v>0</v>
@@ -6445,7 +6445,7 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.705053756997198</v>
+        <v>1.045066966500244</v>
       </c>
     </row>
     <row r="73">
@@ -6463,13 +6463,13 @@
         <v>11.2</v>
       </c>
       <c r="D73" t="n">
-        <v>22.07428041729738</v>
+        <v>23.31338769086442</v>
       </c>
       <c r="E73" t="n">
-        <v>1.23140311465384</v>
+        <v>0.4489009626739628</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.1533090762882253</v>
+        <v>-0.2062592192850646</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -6484,13 +6484,13 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>2.116816306437273</v>
+        <v>2.16688838194055</v>
       </c>
       <c r="L73" t="n">
-        <v>0.02745634748933046</v>
+        <v>0.01104096333472226</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.002230480280817661</v>
+        <v>-0.00584351410709575</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>31.57967240409988</v>
+        <v>28.995</v>
       </c>
       <c r="R73" t="n">
-        <v>-0.4720339499396147</v>
+        <v>-0.004420821114372586</v>
       </c>
       <c r="S73" t="n">
-        <v>0.03560403648127268</v>
+        <v>-0.6091158028459269</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         </is>
       </c>
       <c r="U73" t="n">
-        <v>0.06875510475138136</v>
+        <v>0.02435038000474394</v>
       </c>
       <c r="V73" t="n">
         <v>0</v>
@@ -6528,7 +6528,7 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.517719462402647</v>
+        <v>0.5676898494704686</v>
       </c>
     </row>
     <row r="74">
@@ -6546,13 +6546,13 @@
         <v>12.66666666666667</v>
       </c>
       <c r="D74" t="n">
-        <v>23.71589963656153</v>
+        <v>23.87334480746527</v>
       </c>
       <c r="E74" t="n">
-        <v>1.016313967755268</v>
+        <v>0.3813603406285093</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.1394288098614594</v>
+        <v>-0.02127626603525196</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -6567,13 +6567,13 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>2.154693320268766</v>
+        <v>2.1805620858137</v>
       </c>
       <c r="L74" t="n">
-        <v>0.02432936102738326</v>
+        <v>0.009650423791319973</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.00202523006761318</v>
+        <v>-0.0001834897902143395</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
@@ -6585,13 +6585,13 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>30.92562489613501</v>
+        <v>28.98</v>
       </c>
       <c r="R74" t="n">
-        <v>-0.4203562710518955</v>
+        <v>0.002448783610757843</v>
       </c>
       <c r="S74" t="n">
-        <v>0.03483416010198595</v>
+        <v>0.002091517733637483</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         </is>
       </c>
       <c r="U74" t="n">
-        <v>0.05414503017898187</v>
+        <v>0.02039997424611603</v>
       </c>
       <c r="V74" t="n">
         <v>0</v>
@@ -6611,7 +6611,7 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.284098101543329</v>
+        <v>0.4870156192409393</v>
       </c>
     </row>
     <row r="75">
@@ -6629,13 +6629,13 @@
         <v>13.85</v>
       </c>
       <c r="D75" t="n">
-        <v>24.82022700518329</v>
+        <v>24.32421200879139</v>
       </c>
       <c r="E75" t="n">
-        <v>0.8582191458128028</v>
+        <v>0.3798361778873236</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.1266279083703283</v>
+        <v>-0.002007947925256201</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -6650,13 +6650,13 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>2.18205489951438</v>
+        <v>2.192294376047829</v>
       </c>
       <c r="L75" t="n">
-        <v>0.02203481034029531</v>
+        <v>0.010163289582094</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.001835940634724672</v>
+        <v>0.0004199963446128996</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -6668,13 +6668,13 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>30.45263040189307</v>
+        <v>28.995</v>
       </c>
       <c r="R75" t="n">
-        <v>-0.3795183350540121</v>
+        <v>0.002448783610757843</v>
       </c>
       <c r="S75" t="n">
-        <v>0.03412415127444482</v>
+        <v>-0.002754454158137631</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="U75" t="n">
-        <v>0.04467560167184718</v>
+        <v>0.02025147405166017</v>
       </c>
       <c r="V75" t="n">
         <v>0</v>
@@ -6694,7 +6694,7 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.108858575088393</v>
+        <v>0.4926011483231197</v>
       </c>
     </row>
     <row r="76">
@@ -6712,13 +6712,13 @@
         <v>15.31666666666667</v>
       </c>
       <c r="D76" t="n">
-        <v>25.94258266843361</v>
+        <v>24.87916300213528</v>
       </c>
       <c r="E76" t="n">
-        <v>0.6851746500090439</v>
+        <v>0.3755824823665321</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.1091540578123364</v>
+        <v>-0.003811934374442154</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -6733,13 +6733,13 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>2.212395445455325</v>
+        <v>2.207652591222507</v>
       </c>
       <c r="L76" t="n">
-        <v>0.01952954635369458</v>
+        <v>0.01075490449843414</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.001577551390436449</v>
+        <v>0.0003863900841130491</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
@@ -6751,13 +6751,13 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>29.93271538230435</v>
+        <v>28.98</v>
       </c>
       <c r="R76" t="n">
-        <v>-0.3301726851604139</v>
+        <v>-0.00659824046920976</v>
       </c>
       <c r="S76" t="n">
-        <v>0.03315495483496864</v>
+        <v>-0.002870535133593673</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="U76" t="n">
-        <v>0.03523852730843945</v>
+        <v>0.01996791396703792</v>
       </c>
       <c r="V76" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.9141784078130457</v>
+        <v>0.4967849863985501</v>
       </c>
     </row>
     <row r="77">
@@ -6795,13 +6795,13 @@
         <v>17.98333333333333</v>
       </c>
       <c r="D77" t="n">
-        <v>27.38150732221956</v>
+        <v>25.86717352522962</v>
       </c>
       <c r="E77" t="n">
-        <v>0.4369132870681518</v>
+        <v>0.3609970213513023</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.08264584798071235</v>
+        <v>-0.006548620897526818</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -6816,13 +6816,13 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>2.258863619900905</v>
+        <v>2.23770636880409</v>
       </c>
       <c r="L77" t="n">
-        <v>0.01595587305014148</v>
+        <v>0.01170293273494169</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.001185569309377998</v>
+        <v>0.0003354086589236767</v>
       </c>
       <c r="N77" t="n">
         <v>0</v>
@@ -6834,13 +6834,13 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>29.17014496464282</v>
+        <v>28.98</v>
       </c>
       <c r="R77" t="n">
-        <v>-0.2441342914483566</v>
+        <v>0.001736770691995515</v>
       </c>
       <c r="S77" t="n">
-        <v>0.03168466284062981</v>
+        <v>0.001217265424467607</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="U77" t="n">
-        <v>0.02302018229170168</v>
+        <v>0.01918567558594298</v>
       </c>
       <c r="V77" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.6303272899790584</v>
+        <v>0.4962791995803485</v>
       </c>
     </row>
     <row r="78">
@@ -6878,13 +6878,13 @@
         <v>23.56666666666667</v>
       </c>
       <c r="D78" t="n">
-        <v>28.6205595202824</v>
+        <v>27.77160328645161</v>
       </c>
       <c r="E78" t="n">
-        <v>0.09766084484044235</v>
+        <v>0.3118194120367637</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.03682487188822893</v>
+        <v>-0.01127914206599798</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -6899,13 +6899,13 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>2.330769720901581</v>
+        <v>2.308106824518858</v>
       </c>
       <c r="L78" t="n">
-        <v>0.0111432456237468</v>
+        <v>0.01334063742767566</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.0005080055780303065</v>
+        <v>0.0002472843125575644</v>
       </c>
       <c r="N78" t="n">
         <v>0</v>
@@ -6917,13 +6917,13 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>28.29605439603353</v>
+        <v>29.01</v>
       </c>
       <c r="R78" t="n">
-        <v>-0.07400541747215073</v>
+        <v>-0.01377580184185945</v>
       </c>
       <c r="S78" t="n">
-        <v>0.02914317796671868</v>
+        <v>0.003935535610344511</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="U78" t="n">
-        <v>0.00819319136140532</v>
+        <v>0.01700789928688593</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -6943,7 +6943,7 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0.2344937210201646</v>
+        <v>0.4723366317313193</v>
       </c>
     </row>
     <row r="79">
@@ -6961,13 +6961,13 @@
         <v>25.13333333333333</v>
       </c>
       <c r="D79" t="n">
-        <v>28.71893702802755</v>
+        <v>28.24725212243168</v>
       </c>
       <c r="E79" t="n">
-        <v>0.05049119268484148</v>
+        <v>0.2930624064029619</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.01905457134207864</v>
+        <v>-0.01311373377644165</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -6982,13 +6982,13 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>2.347464561134188</v>
+        <v>2.329328769561197</v>
       </c>
       <c r="L79" t="n">
-        <v>0.01050297065851247</v>
+        <v>0.0137078120305042</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.0002452326698121517</v>
+        <v>0.0002131079100906675</v>
       </c>
       <c r="N79" t="n">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>28.21640089192496</v>
+        <v>28.98</v>
       </c>
       <c r="R79" t="n">
-        <v>-0.02893141622576323</v>
+        <v>-0.004658682590775953</v>
       </c>
       <c r="S79" t="n">
-        <v>0.02815753877055851</v>
+        <v>0.005930868482666279</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="U79" t="n">
-        <v>0.006232291405944243</v>
+        <v>0.01625977611303667</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0.17898478442763</v>
+        <v>0.4592939953192389</v>
       </c>
     </row>
     <row r="80">
@@ -7044,13 +7044,13 @@
         <v>26.68333333333333</v>
       </c>
       <c r="D80" t="n">
-        <v>28.77833165481389</v>
+        <v>28.68533069149266</v>
       </c>
       <c r="E80" t="n">
-        <v>0.03790760012764949</v>
+        <v>0.2709861119968053</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0009261421744974768</v>
+        <v>-0.01517652676585166</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -7065,13 +7065,13 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>2.363509062615961</v>
+        <v>2.350824137729002</v>
       </c>
       <c r="L80" t="n">
-        <v>0.01037351766800509</v>
+        <v>0.01400552860674631</v>
       </c>
       <c r="M80" t="n">
-        <v>5.022604712898344e-05</v>
+        <v>0.0001746803716848652</v>
       </c>
       <c r="N80" t="n">
         <v>0</v>
@@ -7083,13 +7083,13 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>28.20515832557021</v>
+        <v>28.995</v>
       </c>
       <c r="R80" t="n">
-        <v>0.01377257300112156</v>
+        <v>0.004705043664232633</v>
       </c>
       <c r="S80" t="n">
-        <v>0.02704929784024798</v>
+        <v>0.0007241859839866335</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         </is>
       </c>
       <c r="U80" t="n">
-        <v>0.005706259483333013</v>
+        <v>0.01540456339472086</v>
       </c>
       <c r="V80" t="n">
         <v>0</v>
@@ -7109,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0.1642166279197844</v>
+        <v>0.4418849951356306</v>
       </c>
     </row>
     <row r="81">
@@ -7127,13 +7127,13 @@
         <v>28.15</v>
       </c>
       <c r="D81" t="n">
-        <v>28.83335836370024</v>
+        <v>29.0666155901646</v>
       </c>
       <c r="E81" t="n">
-        <v>0.05181814576573007</v>
+        <v>0.2474313265274128</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0167954032280916</v>
+        <v>-0.01681485666939997</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -7148,13 +7148,13 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>2.378754401281694</v>
+        <v>2.371556472260544</v>
       </c>
       <c r="L81" t="n">
-        <v>0.01063279442837373</v>
+        <v>0.01423758569102029</v>
       </c>
       <c r="M81" t="n">
-        <v>0.0002848879127230705</v>
+        <v>0.0001441601083268602</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
@@ -7166,13 +7166,13 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>28.25453804867486</v>
+        <v>28.995</v>
       </c>
       <c r="R81" t="n">
-        <v>0.05274866182366544</v>
+        <v>-0.001611721611721961</v>
       </c>
       <c r="S81" t="n">
-        <v>0.02616910081331403</v>
+        <v>-0.002724079619464575</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="U81" t="n">
-        <v>0.006267059619385476</v>
+        <v>0.01451603799878851</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0.1807003758924162</v>
+        <v>0.4219320964030077</v>
       </c>
     </row>
     <row r="82">
@@ -7210,13 +7210,13 @@
         <v>31.18333333333333</v>
       </c>
       <c r="D82" t="n">
-        <v>29.08025049909232</v>
+        <v>29.73851507129508</v>
       </c>
       <c r="E82" t="n">
-        <v>0.1486292753808174</v>
+        <v>0.1916911875825731</v>
       </c>
       <c r="F82" t="n">
-        <v>0.04444181308352663</v>
+        <v>-0.01966905005867627</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -7231,13 +7231,13 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>2.412501839566561</v>
+        <v>2.415383102800367</v>
       </c>
       <c r="L82" t="n">
-        <v>0.01217517023355535</v>
+        <v>0.01458666219771476</v>
       </c>
       <c r="M82" t="n">
-        <v>0.0006937007800484935</v>
+        <v>9.09896609543959e-05</v>
       </c>
       <c r="N82" t="n">
         <v>0</v>
@@ -7249,13 +7249,13 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>28.53424460947507</v>
+        <v>28.98</v>
       </c>
       <c r="R82" t="n">
-        <v>0.1295843368829663</v>
+        <v>5.494505494496593e-05</v>
       </c>
       <c r="S82" t="n">
-        <v>0.02463567794768706</v>
+        <v>0.001646268147460716</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="U82" t="n">
-        <v>0.01015770279662578</v>
+        <v>0.0124849574353011</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.2953885418212082</v>
+        <v>0.3712840948541792</v>
       </c>
     </row>
     <row r="83">
@@ -7293,13 +7293,13 @@
         <v>34.18333333333334</v>
       </c>
       <c r="D83" t="n">
-        <v>29.72563053625166</v>
+        <v>30.22512911004171</v>
       </c>
       <c r="E83" t="n">
-        <v>0.3191199359307628</v>
+        <v>0.1288471294861875</v>
       </c>
       <c r="F83" t="n">
-        <v>0.07125275945293841</v>
+        <v>-0.02243699086140478</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -7314,13 +7314,13 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>2.452141670099498</v>
+        <v>2.45955349669037</v>
       </c>
       <c r="L83" t="n">
-        <v>0.01480584196674761</v>
+        <v>0.01478815385482313</v>
       </c>
       <c r="M83" t="n">
-        <v>0.001090159485475414</v>
+        <v>3.942600330769219e-05</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
@@ -7332,13 +7332,13 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>29.03388567890103</v>
+        <v>28.995</v>
       </c>
       <c r="R83" t="n">
-        <v>0.2014299819075678</v>
+        <v>0.008248043469444966</v>
       </c>
       <c r="S83" t="n">
-        <v>0.02314859450983792</v>
+        <v>-0.008316959792975405</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         </is>
       </c>
       <c r="U83" t="n">
-        <v>0.01677343718855857</v>
+        <v>0.01027545007842259</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0.4986009966901158</v>
+        <v>0.3105768052841109</v>
       </c>
     </row>
     <row r="84">
@@ -7376,13 +7376,13 @@
         <v>35.7</v>
       </c>
       <c r="D84" t="n">
-        <v>30.28936689835811</v>
+        <v>30.39497004602677</v>
       </c>
       <c r="E84" t="n">
-        <v>0.4382452366280667</v>
+        <v>0.09367601066510289</v>
       </c>
       <c r="F84" t="n">
-        <v>0.08398956853488046</v>
+        <v>-0.02375192891203302</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -7397,13 +7397,13 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>2.475818311135999</v>
+        <v>2.482031797765625</v>
       </c>
       <c r="L84" t="n">
-        <v>0.01662277642944399</v>
+        <v>0.01482668168168111</v>
       </c>
       <c r="M84" t="n">
-        <v>0.00127850117137941</v>
+        <v>1.49301703760759e-05</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -7415,13 +7415,13 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>29.36613464975137</v>
+        <v>29.01</v>
       </c>
       <c r="R84" t="n">
-        <v>0.2359253115733893</v>
+        <v>-0.01283716283716529</v>
       </c>
       <c r="S84" t="n">
-        <v>0.02244214060195683</v>
+        <v>-0.02339688154851417</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         </is>
       </c>
       <c r="U84" t="n">
-        <v>0.02118267002954885</v>
+        <v>0.009055564318615449</v>
       </c>
       <c r="V84" t="n">
         <v>0</v>
@@ -7441,7 +7441,7 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0.6416096644118593</v>
+        <v>0.2752436062141854</v>
       </c>
     </row>
     <row r="85">
@@ -7459,13 +7459,13 @@
         <v>36.75</v>
       </c>
       <c r="D85" t="n">
-        <v>30.79790180503732</v>
+        <v>30.48002205897316</v>
       </c>
       <c r="E85" t="n">
-        <v>0.5303926808561314</v>
+        <v>0.06832782351850142</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0915293728519101</v>
+        <v>-0.02453033231958895</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -7480,13 +7480,13 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>2.494007730294611</v>
+        <v>2.497604047007715</v>
       </c>
       <c r="L85" t="n">
-        <v>0.01802373625362641</v>
+        <v>0.01483474544610974</v>
       </c>
       <c r="M85" t="n">
-        <v>0.001389993731825214</v>
+        <v>4.293809165618889e-07</v>
       </c>
       <c r="N85" t="n">
         <v>0</v>
@@ -7498,13 +7498,13 @@
         <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>29.62611219073723</v>
+        <v>28.98</v>
       </c>
       <c r="R85" t="n">
-        <v>0.2592700045901708</v>
+        <v>-0.04430569430570586</v>
       </c>
       <c r="S85" t="n">
-        <v>0.02202394133477009</v>
+        <v>-0.03654317839156326</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="U85" t="n">
-        <v>0.02444853129970188</v>
+        <v>0.008181315441372846</v>
       </c>
       <c r="V85" t="n">
         <v>0</v>
@@ -7524,7 +7524,7 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0.7529634662456</v>
+        <v>0.2493666751244621</v>
       </c>
     </row>
   </sheetData>
